--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -1104,10 +1104,10 @@
     <t xml:space="preserve">Training Day run</t>
   </si>
   <si>
-    <t xml:space="preserve">Level 110 gold orb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">825K + 825K + 1.65M per orb. Copy the row for each orb</t>
+    <t xml:space="preserve">Level 110 gold orb, promo code Oct 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">825K + 825K + 1.65M. Copy the row for each new orb</t>
   </si>
   <si>
     <t xml:space="preserve">Gold orbs</t>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>510273450.9648</v>
+        <v>515399959.520418</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="B6" s="27" t="n">
         <f aca="false">SUMIFS(B13:B51,$I$13:$I$51,"Yes",$J$13:$J$51,"No")</f>
-        <v>13900000</v>
+        <v>17200000</v>
       </c>
       <c r="C6" s="27" t="n">
         <f aca="false">SUMIFS(C13:C51,$I$13:$I$51,"Yes",$J$13:$J$51,"No")</f>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
-        <v>16720000</v>
+        <v>20020000</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5+C6</f>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B7-B8</f>
-        <v>16720000</v>
+        <v>20020000</v>
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">C7-C8</f>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J40" s="11" t="s">
         <v>253</v>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>19258179.4743865</v>
+        <v>19451658.5188738</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="528">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -1108,6 +1108,24 @@
   </si>
   <si>
     <t xml:space="preserve">825K + 825K + 1.65M. Copy the row for each new orb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 110 gold orb, Breaker of Nature level 120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending claim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breaker of Nature level 110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending claim. Also gives the level 110 training orb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 110 training orb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending claim. Enter amounts once opened</t>
   </si>
   <si>
     <t xml:space="preserve">Gold orbs</t>
@@ -4103,7 +4121,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>515399959.520418</v>
+        <v>515448478.906659</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6935,7 +6953,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -7013,31 +7031,31 @@
         <v>315</v>
       </c>
       <c r="B6" s="27" t="n">
-        <f aca="false">SUMIFS(B13:B51,$I$13:$I$51,"Yes",$J$13:$J$51,"No")</f>
-        <v>17200000</v>
+        <f aca="false">SUMIFS(B13:B54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
+        <v>20500000</v>
       </c>
       <c r="C6" s="27" t="n">
-        <f aca="false">SUMIFS(C13:C51,$I$13:$I$51,"Yes",$J$13:$J$51,"No")</f>
-        <v>3750000</v>
+        <f aca="false">SUMIFS(C13:C54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
+        <v>4000000</v>
       </c>
       <c r="D6" s="27" t="n">
-        <f aca="false">SUMIFS(D13:D51,$I$13:$I$51,"Yes",$J$13:$J$51,"No")</f>
+        <f aca="false">SUMIFS(D13:D54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
         <v>3000000</v>
       </c>
       <c r="E6" s="27" t="n">
-        <f aca="false">SUMIFS(E13:E51,$I$13:$I$51,"Yes",$J$13:$J$51,"No")</f>
+        <f aca="false">SUMIFS(E13:E54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
         <v>2600000</v>
       </c>
       <c r="F6" s="27" t="n">
-        <f aca="false">SUMIFS(F13:F51,$I$13:$I$51,"Yes",$J$13:$J$51,"No")</f>
+        <f aca="false">SUMIFS(F13:F54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
         <v>0</v>
       </c>
       <c r="G6" s="27" t="n">
-        <f aca="false">SUMIFS(G13:G51,$I$13:$I$51,"Yes",$J$13:$J$51,"No")</f>
+        <f aca="false">SUMIFS(G13:G54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
         <v>100</v>
       </c>
       <c r="H6" s="27" t="n">
-        <f aca="false">SUMIFS(H13:H51,$I$13:$I$51,"Yes",$J$13:$J$51,"No")</f>
+        <f aca="false">SUMIFS(H13:H54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
         <v>225</v>
       </c>
     </row>
@@ -7047,11 +7065,11 @@
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
-        <v>20020000</v>
+        <v>23320000</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5+C6</f>
-        <v>4455800</v>
+        <v>4705800</v>
       </c>
       <c r="D7" s="27" t="n">
         <f aca="false">D5+D6</f>
@@ -7079,31 +7097,31 @@
         <v>317</v>
       </c>
       <c r="B8" s="27" t="n">
-        <f aca="false">SUMIF($J$55:$J$73,"Planned",B55:B73)</f>
+        <f aca="false">SUMIF($J$58:$J$76,"Planned",B58:B76)</f>
         <v>0</v>
       </c>
       <c r="C8" s="27" t="n">
-        <f aca="false">SUMIF($J$55:$J$73,"Planned",C55:C73)</f>
+        <f aca="false">SUMIF($J$58:$J$76,"Planned",C58:C76)</f>
         <v>1710000</v>
       </c>
       <c r="D8" s="27" t="n">
-        <f aca="false">SUMIF($J$55:$J$73,"Planned",D55:D73)</f>
+        <f aca="false">SUMIF($J$58:$J$76,"Planned",D58:D76)</f>
         <v>2640000</v>
       </c>
       <c r="E8" s="27" t="n">
-        <f aca="false">SUMIF($J$55:$J$73,"Planned",E55:E73)</f>
+        <f aca="false">SUMIF($J$58:$J$76,"Planned",E58:E76)</f>
         <v>1710000</v>
       </c>
       <c r="F8" s="27" t="n">
-        <f aca="false">SUMIF($J$55:$J$73,"Planned",F55:F73)</f>
+        <f aca="false">SUMIF($J$58:$J$76,"Planned",F58:F76)</f>
         <v>0</v>
       </c>
       <c r="G8" s="27" t="n">
-        <f aca="false">SUMIF($J$55:$J$73,"Planned",G55:G73)</f>
+        <f aca="false">SUMIF($J$58:$J$76,"Planned",G58:G76)</f>
         <v>0</v>
       </c>
       <c r="H8" s="27" t="n">
-        <f aca="false">SUMIF($J$55:$J$73,"Planned",H55:H73)</f>
+        <f aca="false">SUMIF($J$58:$J$76,"Planned",H58:H76)</f>
         <v>0</v>
       </c>
     </row>
@@ -7113,11 +7131,11 @@
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B7-B8</f>
-        <v>20020000</v>
+        <v>23320000</v>
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">C7-C8</f>
-        <v>2745800</v>
+        <v>2995800</v>
       </c>
       <c r="D9" s="28" t="n">
         <f aca="false">D7-D8</f>
@@ -8142,7 +8160,7 @@
         <v>359</v>
       </c>
       <c r="B41" s="30" t="n">
-        <v>0</v>
+        <v>3300000</v>
       </c>
       <c r="C41" s="30" t="n">
         <v>0</v>
@@ -8163,7 +8181,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J41" s="11" t="s">
         <v>253</v>
@@ -8173,43 +8191,103 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="12"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="12"/>
+      <c r="A42" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="B42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="30" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="12"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
+      <c r="A43" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="B43" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="F43" s="30"/>
       <c r="G43" s="30"/>
       <c r="H43" s="30"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="12"/>
+      <c r="I43" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>364</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="12"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="12"/>
+      <c r="A44" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="B44" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K44" s="15" t="s">
+        <v>366</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12"/>
@@ -8302,175 +8380,129 @@
       <c r="J51" s="11"/>
       <c r="K51" s="12"/>
     </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="12"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="12"/>
+    </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="29" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B54" s="3" t="s">
+      <c r="A53" s="12"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="12"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="12"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="12"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="29" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D57" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="E57" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="F57" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="G57" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="H54" s="3" t="s">
+      <c r="H57" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="I54" s="3" t="s">
+      <c r="I57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J54" s="3" t="s">
+      <c r="J57" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K54" s="3" t="s">
+      <c r="K57" s="3" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="B55" s="30" t="n">
-        <v>1837500</v>
-      </c>
-      <c r="C55" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G55" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" s="30" t="n">
-        <v>183</v>
-      </c>
-      <c r="I55" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="K55" s="15" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="B56" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" s="30" t="n">
-        <v>359800</v>
-      </c>
-      <c r="D56" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="K56" s="15"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="B57" s="26"/>
-      <c r="C57" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="26"/>
-      <c r="G57" s="26"/>
-      <c r="H57" s="26"/>
-      <c r="I57" s="30" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="J57" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="K57" s="15" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="B58" s="30" t="n">
+        <v>1837500</v>
+      </c>
+      <c r="C58" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="30" t="n">
+        <v>183</v>
+      </c>
+      <c r="I58" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="B58" s="26"/>
-      <c r="C58" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26"/>
-      <c r="H58" s="26"/>
-      <c r="I58" s="30" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="J58" s="11" t="s">
-        <v>368</v>
-      </c>
       <c r="K58" s="15" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="B59" s="26"/>
+        <v>372</v>
+      </c>
+      <c r="B59" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="C59" s="30" t="n">
-        <v>0</v>
+        <v>359800</v>
       </c>
       <c r="D59" s="30" t="n">
         <v>0</v>
@@ -8478,22 +8510,26 @@
       <c r="E59" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F59" s="26"/>
-      <c r="G59" s="26"/>
-      <c r="H59" s="26"/>
+      <c r="F59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="I59" s="30" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="K59" s="15" t="s">
-        <v>369</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="K59" s="15"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B60" s="26"/>
       <c r="C60" s="30" t="n">
@@ -8512,15 +8548,15 @@
         <v>3000000</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B61" s="26"/>
       <c r="C61" s="30" t="n">
@@ -8532,55 +8568,41 @@
       <c r="E61" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F61" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="30" t="n">
-        <v>0</v>
-      </c>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
       <c r="I61" s="30" t="n">
-        <v>17000000</v>
+        <v>3000000</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="B62" s="26"/>
+      <c r="C62" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="26"/>
+      <c r="G62" s="26"/>
+      <c r="H62" s="26"/>
+      <c r="I62" s="30" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="J62" s="11" t="s">
         <v>374</v>
-      </c>
-      <c r="B62" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="30" t="n">
-        <v>1710000</v>
-      </c>
-      <c r="D62" s="30" t="n">
-        <v>2640000</v>
-      </c>
-      <c r="E62" s="30" t="n">
-        <v>1710000</v>
-      </c>
-      <c r="F62" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="30" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="J62" s="11" t="s">
-        <v>368</v>
       </c>
       <c r="K62" s="15" t="s">
         <v>375</v>
@@ -8588,43 +8610,45 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="B63" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" s="26"/>
-      <c r="D63" s="26"/>
-      <c r="E63" s="26"/>
-      <c r="F63" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="30" t="n">
-        <v>0</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="B63" s="26"/>
+      <c r="C63" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
+      <c r="H63" s="26"/>
       <c r="I63" s="30" t="n">
-        <v>17000000</v>
+        <v>3000000</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="B64" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" s="26"/>
-      <c r="D64" s="26"/>
-      <c r="E64" s="26"/>
+        <v>379</v>
+      </c>
+      <c r="B64" s="26"/>
+      <c r="C64" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="F64" s="30" t="n">
         <v>0</v>
       </c>
@@ -8638,22 +8662,28 @@
         <v>17000000</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B65" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C65" s="26"/>
-      <c r="D65" s="26"/>
-      <c r="E65" s="26"/>
+      <c r="C65" s="30" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="D65" s="30" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="E65" s="30" t="n">
+        <v>1710000</v>
+      </c>
       <c r="F65" s="30" t="n">
         <v>0</v>
       </c>
@@ -8667,15 +8697,15 @@
         <v>17000000</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B66" s="30" t="n">
         <v>0</v>
@@ -8696,79 +8726,127 @@
         <v>17000000</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="K66" s="15" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="12" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B67" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="26"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="K67" s="15" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="B68" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="26"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="K68" s="15" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="B69" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J69" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="K69" s="15" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="B70" s="30" t="n">
         <v>13000000</v>
       </c>
-      <c r="C67" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="26"/>
-      <c r="G67" s="26"/>
-      <c r="H67" s="26"/>
-      <c r="I67" s="30" t="n">
+      <c r="C70" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="26"/>
+      <c r="G70" s="26"/>
+      <c r="H70" s="26"/>
+      <c r="I70" s="30" t="n">
         <v>8000000</v>
       </c>
-      <c r="J67" s="11" t="s">
-        <v>378</v>
-      </c>
-      <c r="K67" s="15" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="12"/>
-      <c r="B68" s="30"/>
-      <c r="C68" s="30"/>
-      <c r="D68" s="30"/>
-      <c r="E68" s="30"/>
-      <c r="F68" s="30"/>
-      <c r="G68" s="30"/>
-      <c r="H68" s="30"/>
-      <c r="I68" s="30"/>
-      <c r="J68" s="11"/>
-      <c r="K68" s="12"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="12"/>
-      <c r="B69" s="30"/>
-      <c r="C69" s="30"/>
-      <c r="D69" s="30"/>
-      <c r="E69" s="30"/>
-      <c r="F69" s="30"/>
-      <c r="G69" s="30"/>
-      <c r="H69" s="30"/>
-      <c r="I69" s="30"/>
-      <c r="J69" s="11"/>
-      <c r="K69" s="12"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="12"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
-      <c r="J70" s="11"/>
-      <c r="K70" s="12"/>
+      <c r="J70" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="K70" s="15" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="12"/>
@@ -8809,12 +8887,51 @@
       <c r="J73" s="11"/>
       <c r="K73" s="12"/>
     </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="12"/>
+      <c r="B74" s="30"/>
+      <c r="C74" s="30"/>
+      <c r="D74" s="30"/>
+      <c r="E74" s="30"/>
+      <c r="F74" s="30"/>
+      <c r="G74" s="30"/>
+      <c r="H74" s="30"/>
+      <c r="I74" s="30"/>
+      <c r="J74" s="11"/>
+      <c r="K74" s="12"/>
+    </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="16" t="s">
-        <v>383</v>
-      </c>
-      <c r="I75" s="20" t="n">
-        <f aca="false">SUMIF(J55:J73,"Planned",I55:I73)</f>
+      <c r="A75" s="12"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="30"/>
+      <c r="J75" s="11"/>
+      <c r="K75" s="12"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="12"/>
+      <c r="B76" s="30"/>
+      <c r="C76" s="30"/>
+      <c r="D76" s="30"/>
+      <c r="E76" s="30"/>
+      <c r="F76" s="30"/>
+      <c r="G76" s="30"/>
+      <c r="H76" s="30"/>
+      <c r="I76" s="30"/>
+      <c r="J76" s="11"/>
+      <c r="K76" s="12"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="I78" s="20" t="n">
+        <f aca="false">SUMIF(J58:J76,"Planned",I58:I76)</f>
         <v>63000000</v>
       </c>
     </row>
@@ -8824,22 +8941,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J55:J73">
+  <conditionalFormatting sqref="J58:J76">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J13:J51">
+  <conditionalFormatting sqref="J13:J54">
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13:J51" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13:J54" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J55:J73" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J58:J76" type="list">
       <formula1>"Planned,Done,Skipped"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8870,12 +8987,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8889,53 +9006,53 @@
         <v>307</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -8947,19 +9064,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C7" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -8971,19 +9088,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -8995,19 +9112,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>403</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>397</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -9019,19 +9136,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -9043,19 +9160,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -9067,19 +9184,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -9091,19 +9208,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -9115,19 +9232,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -9139,19 +9256,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -9163,19 +9280,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -9187,16 +9304,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -9209,16 +9326,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="32"/>
@@ -9231,16 +9348,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="32"/>
@@ -9253,19 +9370,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>422</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>416</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -9277,21 +9394,21 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="E22" s="32"/>
       <c r="F22" s="32"/>
@@ -9304,16 +9421,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C23" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -9326,16 +9443,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -9348,19 +9465,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -9372,19 +9489,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C26" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -9396,16 +9513,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -9418,16 +9535,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C28" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -9440,21 +9557,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -9467,16 +9584,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C31" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -9489,16 +9606,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C32" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -9511,16 +9628,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C33" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="E33" s="32"/>
       <c r="F33" s="32"/>
@@ -9533,16 +9650,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C34" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -9555,16 +9672,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C35" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -9577,16 +9694,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C36" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -9599,16 +9716,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -9621,7 +9738,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="E39" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$37)*(E5:E37="Done"))</f>
@@ -9658,7 +9775,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="E40" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$37,"Required",E5:E37,"Done")&amp;" of 11"</f>
@@ -9695,7 +9812,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -9739,12 +9856,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9752,10 +9869,10 @@
         <v>155</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9766,13 +9883,13 @@
         <v>46313.6875</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9783,7 +9900,7 @@
         <v>285372765</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -9833,7 +9950,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -9841,7 +9958,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -9850,11 +9967,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>19451658.5188738</v>
+        <v>19453489.6871156</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9865,19 +9982,19 @@
         <v>168</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>467</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
@@ -9893,7 +10010,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -9919,7 +10036,7 @@
       <c r="B14" s="26"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -9945,7 +10062,7 @@
       <c r="B15" s="26"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -9971,7 +10088,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -9996,10 +10113,10 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="12" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -10024,10 +10141,10 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="12" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -10052,10 +10169,10 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="12" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -10080,10 +10197,10 @@
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="12" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -10108,10 +10225,10 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="12" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -10136,10 +10253,10 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="12" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -10165,7 +10282,7 @@
       <c r="B23" s="26"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -10190,10 +10307,10 @@
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="12" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -10218,10 +10335,10 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="12" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -10246,10 +10363,10 @@
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="12" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -10277,7 +10394,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -10304,10 +10421,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -10334,10 +10451,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -10364,10 +10481,10 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
@@ -10388,10 +10505,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -10418,7 +10535,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -10446,10 +10563,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -10476,7 +10593,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -10504,10 +10621,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -10534,7 +10651,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -10562,10 +10679,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -10592,7 +10709,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -10620,10 +10737,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -10650,7 +10767,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -10678,10 +10795,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -10708,7 +10825,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -10736,10 +10853,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -10766,7 +10883,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -10794,7 +10911,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -10822,7 +10939,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -10850,7 +10967,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -10878,7 +10995,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -10906,7 +11023,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -10934,7 +11051,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -10962,7 +11079,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -10990,7 +11107,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -11018,7 +11135,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -11046,7 +11163,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -11068,7 +11185,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -4121,7 +4121,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>515448478.906659</v>
+        <v>515935161.064989</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7005,7 +7005,7 @@
         <v>314</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>2820000</v>
+        <v>2864000</v>
       </c>
       <c r="C5" s="26" t="n">
         <v>705800</v>
@@ -7017,10 +7017,10 @@
         <v>14390000</v>
       </c>
       <c r="F5" s="26" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>647</v>
+        <v>667</v>
       </c>
       <c r="H5" s="26" t="n">
         <v>244</v>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
-        <v>23320000</v>
+        <v>23364000</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5+C6</f>
@@ -7081,11 +7081,11 @@
       </c>
       <c r="F7" s="27" t="n">
         <f aca="false">F5+F6</f>
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G7" s="27" t="n">
         <f aca="false">G5+G6</f>
-        <v>747</v>
+        <v>767</v>
       </c>
       <c r="H7" s="27" t="n">
         <f aca="false">H5+H6</f>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B7-B8</f>
-        <v>23320000</v>
+        <v>23364000</v>
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">C7-C8</f>
@@ -7147,11 +7147,11 @@
       </c>
       <c r="F9" s="28" t="n">
         <f aca="false">F7-F8</f>
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G9" s="28" t="n">
         <f aca="false">G7-G8</f>
-        <v>747</v>
+        <v>767</v>
       </c>
       <c r="H9" s="28" t="n">
         <f aca="false">H7-H8</f>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>19453489.6871156</v>
+        <v>19471857.5178847</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="528">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -1008,7 +1008,7 @@
     <t xml:space="preserve">Today's remaining optional objectives</t>
   </si>
   <si>
-    <t xml:space="preserve">Raids plus the two energy objectives</t>
+    <t xml:space="preserve">Raid battles objective</t>
   </si>
   <si>
     <t xml:space="preserve">Daily objectives, Oct 12</t>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>515935161.064989</v>
+        <v>515957718.978309</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7005,7 +7005,7 @@
         <v>314</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>2864000</v>
+        <v>2920000</v>
       </c>
       <c r="C5" s="26" t="n">
         <v>705800</v>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="B6" s="27" t="n">
         <f aca="false">SUMIFS(B13:B54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
-        <v>20500000</v>
+        <v>20450000</v>
       </c>
       <c r="C6" s="27" t="n">
         <f aca="false">SUMIFS(C13:C54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
-        <v>23364000</v>
+        <v>23370000</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5+C6</f>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B7-B8</f>
-        <v>23364000</v>
+        <v>23370000</v>
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">C7-C8</f>
@@ -7208,7 +7208,7 @@
         <v>324</v>
       </c>
       <c r="B13" s="30" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="C13" s="30" t="n">
         <v>0</v>
@@ -9337,7 +9337,9 @@
       <c r="D18" s="15" t="s">
         <v>425</v>
       </c>
-      <c r="E18" s="32"/>
+      <c r="E18" s="32" t="s">
+        <v>370</v>
+      </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
@@ -9359,7 +9361,9 @@
       <c r="D19" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="E19" s="32"/>
+      <c r="E19" s="32" t="s">
+        <v>370</v>
+      </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
@@ -9410,7 +9414,9 @@
       <c r="D22" s="15" t="s">
         <v>433</v>
       </c>
-      <c r="E22" s="32"/>
+      <c r="E22" s="32" t="s">
+        <v>370</v>
+      </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
       <c r="H22" s="32"/>
@@ -9639,7 +9645,9 @@
       <c r="D33" s="15" t="s">
         <v>457</v>
       </c>
-      <c r="E33" s="32"/>
+      <c r="E33" s="32" t="s">
+        <v>370</v>
+      </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
       <c r="H33" s="32"/>
@@ -9742,7 +9750,7 @@
       </c>
       <c r="E39" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$37)*(E5:E37="Done"))</f>
-        <v>2350000</v>
+        <v>2400000</v>
       </c>
       <c r="F39" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$37)*(F5:F37="Done"))</f>
@@ -9971,7 +9979,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>19471857.5178847</v>
+        <v>19472708.8645584</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -4121,7 +4121,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>515957718.978309</v>
+        <v>520352529.035002</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7005,7 +7005,7 @@
         <v>314</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>2920000</v>
+        <v>3070000</v>
       </c>
       <c r="C5" s="26" t="n">
         <v>705800</v>
@@ -7023,7 +7023,7 @@
         <v>667</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>244</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="B6" s="27" t="n">
         <f aca="false">SUMIFS(B13:B54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
-        <v>20450000</v>
+        <v>20150000</v>
       </c>
       <c r="C6" s="27" t="n">
         <f aca="false">SUMIFS(C13:C54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="H6" s="27" t="n">
         <f aca="false">SUMIFS(H13:H54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
-        <v>225</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
-        <v>23370000</v>
+        <v>23220000</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5+C6</f>
@@ -7089,7 +7089,7 @@
       </c>
       <c r="H7" s="27" t="n">
         <f aca="false">H5+H6</f>
-        <v>469</v>
+        <v>454</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B7-B8</f>
-        <v>23370000</v>
+        <v>23220000</v>
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">C7-C8</f>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="H9" s="28" t="n">
         <f aca="false">H7-H8</f>
-        <v>469</v>
+        <v>454</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7613,7 +7613,7 @@
         <v>249</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K24" s="15"/>
     </row>
@@ -7646,7 +7646,7 @@
         <v>249</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K25" s="15"/>
     </row>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>19472708.8645584</v>
+        <v>19638572.9888335</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="530">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -1126,6 +1126,12 @@
   </si>
   <si>
     <t xml:space="preserve">Pending claim. Enter amounts once opened</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alliance War, Oct 13 to 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defeat reward counted. A win doubles it to 272K each</t>
   </si>
   <si>
     <t xml:space="preserve">Gold orbs</t>
@@ -4121,7 +4127,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>520352529.035002</v>
+        <v>520600173.007745</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6953,7 +6959,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -7005,7 +7011,7 @@
         <v>314</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>3070000</v>
+        <v>6370000</v>
       </c>
       <c r="C5" s="26" t="n">
         <v>705800</v>
@@ -7031,31 +7037,31 @@
         <v>315</v>
       </c>
       <c r="B6" s="27" t="n">
-        <f aca="false">SUMIFS(B13:B54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
-        <v>20150000</v>
+        <f aca="false">SUMIFS(B13:B55,$I$13:$I$55,"Yes",$J$13:$J$55,"No")</f>
+        <v>16850000</v>
       </c>
       <c r="C6" s="27" t="n">
-        <f aca="false">SUMIFS(C13:C54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
+        <f aca="false">SUMIFS(C13:C55,$I$13:$I$55,"Yes",$J$13:$J$55,"No")</f>
         <v>4000000</v>
       </c>
       <c r="D6" s="27" t="n">
-        <f aca="false">SUMIFS(D13:D54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
-        <v>3000000</v>
+        <f aca="false">SUMIFS(D13:D55,$I$13:$I$55,"Yes",$J$13:$J$55,"No")</f>
+        <v>3136000</v>
       </c>
       <c r="E6" s="27" t="n">
-        <f aca="false">SUMIFS(E13:E54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
-        <v>2600000</v>
+        <f aca="false">SUMIFS(E13:E55,$I$13:$I$55,"Yes",$J$13:$J$55,"No")</f>
+        <v>2736000</v>
       </c>
       <c r="F6" s="27" t="n">
-        <f aca="false">SUMIFS(F13:F54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
+        <f aca="false">SUMIFS(F13:F55,$I$13:$I$55,"Yes",$J$13:$J$55,"No")</f>
         <v>0</v>
       </c>
       <c r="G6" s="27" t="n">
-        <f aca="false">SUMIFS(G13:G54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
+        <f aca="false">SUMIFS(G13:G55,$I$13:$I$55,"Yes",$J$13:$J$55,"No")</f>
         <v>100</v>
       </c>
       <c r="H6" s="27" t="n">
-        <f aca="false">SUMIFS(H13:H54,$I$13:$I$54,"Yes",$J$13:$J$54,"No")</f>
+        <f aca="false">SUMIFS(H13:H55,$I$13:$I$55,"Yes",$J$13:$J$55,"No")</f>
         <v>190</v>
       </c>
     </row>
@@ -7073,11 +7079,11 @@
       </c>
       <c r="D7" s="27" t="n">
         <f aca="false">D5+D6</f>
-        <v>7370000</v>
+        <v>7506000</v>
       </c>
       <c r="E7" s="27" t="n">
         <f aca="false">E5+E6</f>
-        <v>16990000</v>
+        <v>17126000</v>
       </c>
       <c r="F7" s="27" t="n">
         <f aca="false">F5+F6</f>
@@ -7097,31 +7103,31 @@
         <v>317</v>
       </c>
       <c r="B8" s="27" t="n">
-        <f aca="false">SUMIF($J$58:$J$76,"Planned",B58:B76)</f>
+        <f aca="false">SUMIF($J$59:$J$77,"Planned",B59:B77)</f>
         <v>0</v>
       </c>
       <c r="C8" s="27" t="n">
-        <f aca="false">SUMIF($J$58:$J$76,"Planned",C58:C76)</f>
+        <f aca="false">SUMIF($J$59:$J$77,"Planned",C59:C77)</f>
         <v>1710000</v>
       </c>
       <c r="D8" s="27" t="n">
-        <f aca="false">SUMIF($J$58:$J$76,"Planned",D58:D76)</f>
+        <f aca="false">SUMIF($J$59:$J$77,"Planned",D59:D77)</f>
         <v>2640000</v>
       </c>
       <c r="E8" s="27" t="n">
-        <f aca="false">SUMIF($J$58:$J$76,"Planned",E58:E76)</f>
+        <f aca="false">SUMIF($J$59:$J$77,"Planned",E59:E77)</f>
         <v>1710000</v>
       </c>
       <c r="F8" s="27" t="n">
-        <f aca="false">SUMIF($J$58:$J$76,"Planned",F58:F76)</f>
+        <f aca="false">SUMIF($J$59:$J$77,"Planned",F59:F77)</f>
         <v>0</v>
       </c>
       <c r="G8" s="27" t="n">
-        <f aca="false">SUMIF($J$58:$J$76,"Planned",G58:G76)</f>
+        <f aca="false">SUMIF($J$59:$J$77,"Planned",G59:G77)</f>
         <v>0</v>
       </c>
       <c r="H8" s="27" t="n">
-        <f aca="false">SUMIF($J$58:$J$76,"Planned",H58:H76)</f>
+        <f aca="false">SUMIF($J$59:$J$77,"Planned",H59:H77)</f>
         <v>0</v>
       </c>
     </row>
@@ -7139,11 +7145,11 @@
       </c>
       <c r="D9" s="28" t="n">
         <f aca="false">D7-D8</f>
-        <v>4730000</v>
+        <v>4866000</v>
       </c>
       <c r="E9" s="28" t="n">
         <f aca="false">E7-E8</f>
-        <v>15280000</v>
+        <v>15416000</v>
       </c>
       <c r="F9" s="28" t="n">
         <f aca="false">F7-F8</f>
@@ -8149,7 +8155,7 @@
         <v>249</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K40" s="15" t="s">
         <v>358</v>
@@ -8265,10 +8271,10 @@
         <v>0</v>
       </c>
       <c r="D44" s="30" t="n">
-        <v>0</v>
+        <v>136000</v>
       </c>
       <c r="E44" s="30" t="n">
-        <v>0</v>
+        <v>136000</v>
       </c>
       <c r="F44" s="30" t="n">
         <v>0</v>
@@ -8280,7 +8286,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J44" s="11" t="s">
         <v>253</v>
@@ -8290,17 +8296,39 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="12"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="12"/>
+      <c r="A45" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="B45" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K45" s="15" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12"/>
@@ -8419,121 +8447,103 @@
       <c r="J54" s="11"/>
       <c r="K54" s="12"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="29" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B57" s="3" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="12"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="12"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="29" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D58" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E58" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="F58" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="G58" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="H57" s="3" t="s">
+      <c r="H58" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="I57" s="3" t="s">
+      <c r="I58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J57" s="3" t="s">
+      <c r="J58" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K57" s="3" t="s">
+      <c r="K58" s="3" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="B58" s="30" t="n">
-        <v>1837500</v>
-      </c>
-      <c r="C58" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G58" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" s="30" t="n">
-        <v>183</v>
-      </c>
-      <c r="I58" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="11" t="s">
-        <v>370</v>
-      </c>
-      <c r="K58" s="15" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="B59" s="30" t="n">
+        <v>1837500</v>
+      </c>
+      <c r="C59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="30" t="n">
+        <v>183</v>
+      </c>
+      <c r="I59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="B59" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" s="30" t="n">
-        <v>359800</v>
-      </c>
-      <c r="D59" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="11" t="s">
-        <v>370</v>
-      </c>
-      <c r="K59" s="15"/>
+      <c r="K59" s="15" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="B60" s="26"/>
+        <v>374</v>
+      </c>
+      <c r="B60" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="C60" s="30" t="n">
-        <v>0</v>
+        <v>359800</v>
       </c>
       <c r="D60" s="30" t="n">
         <v>0</v>
@@ -8541,22 +8551,26 @@
       <c r="E60" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F60" s="26"/>
-      <c r="G60" s="26"/>
-      <c r="H60" s="26"/>
+      <c r="F60" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="I60" s="30" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>374</v>
-      </c>
-      <c r="K60" s="15" t="s">
-        <v>375</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="K60" s="15"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B61" s="26"/>
       <c r="C61" s="30" t="n">
@@ -8575,15 +8589,15 @@
         <v>3000000</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B62" s="26"/>
       <c r="C62" s="30" t="n">
@@ -8602,15 +8616,15 @@
         <v>3000000</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B63" s="26"/>
       <c r="C63" s="30" t="n">
@@ -8629,15 +8643,15 @@
         <v>3000000</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B64" s="26"/>
       <c r="C64" s="30" t="n">
@@ -8649,40 +8663,32 @@
       <c r="E64" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F64" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="30" t="n">
-        <v>0</v>
-      </c>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
       <c r="I64" s="30" t="n">
-        <v>17000000</v>
+        <v>3000000</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="B65" s="30" t="n">
-        <v>0</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="B65" s="26"/>
       <c r="C65" s="30" t="n">
-        <v>1710000</v>
+        <v>0</v>
       </c>
       <c r="D65" s="30" t="n">
-        <v>2640000</v>
+        <v>0</v>
       </c>
       <c r="E65" s="30" t="n">
-        <v>1710000</v>
+        <v>0</v>
       </c>
       <c r="F65" s="30" t="n">
         <v>0</v>
@@ -8697,10 +8703,10 @@
         <v>17000000</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8710,9 +8716,15 @@
       <c r="B66" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C66" s="26"/>
-      <c r="D66" s="26"/>
-      <c r="E66" s="26"/>
+      <c r="C66" s="30" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="D66" s="30" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="E66" s="30" t="n">
+        <v>1710000</v>
+      </c>
       <c r="F66" s="30" t="n">
         <v>0</v>
       </c>
@@ -8726,15 +8738,15 @@
         <v>17000000</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K66" s="15" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="12" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B67" s="30" t="n">
         <v>0</v>
@@ -8755,10 +8767,10 @@
         <v>17000000</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="K67" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8784,15 +8796,15 @@
         <v>17000000</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K68" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B69" s="30" t="n">
         <v>0</v>
@@ -8813,53 +8825,69 @@
         <v>17000000</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K69" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B70" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="26"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J70" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="K70" s="15" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="B71" s="30" t="n">
         <v>13000000</v>
       </c>
-      <c r="C70" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="26"/>
-      <c r="G70" s="26"/>
-      <c r="H70" s="26"/>
-      <c r="I70" s="30" t="n">
+      <c r="C71" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="26"/>
+      <c r="G71" s="26"/>
+      <c r="H71" s="26"/>
+      <c r="I71" s="30" t="n">
         <v>8000000</v>
       </c>
-      <c r="J70" s="11" t="s">
-        <v>384</v>
-      </c>
-      <c r="K70" s="15" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="12"/>
-      <c r="B71" s="30"/>
-      <c r="C71" s="30"/>
-      <c r="D71" s="30"/>
-      <c r="E71" s="30"/>
-      <c r="F71" s="30"/>
-      <c r="G71" s="30"/>
-      <c r="H71" s="30"/>
-      <c r="I71" s="30"/>
-      <c r="J71" s="11"/>
-      <c r="K71" s="12"/>
+      <c r="J71" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="K71" s="15" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="12"/>
@@ -8926,12 +8954,25 @@
       <c r="J76" s="11"/>
       <c r="K76" s="12"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="16" t="s">
-        <v>389</v>
-      </c>
-      <c r="I78" s="20" t="n">
-        <f aca="false">SUMIF(J58:J76,"Planned",I58:I76)</f>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="12"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="30"/>
+      <c r="D77" s="30"/>
+      <c r="E77" s="30"/>
+      <c r="F77" s="30"/>
+      <c r="G77" s="30"/>
+      <c r="H77" s="30"/>
+      <c r="I77" s="30"/>
+      <c r="J77" s="11"/>
+      <c r="K77" s="12"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="I79" s="20" t="n">
+        <f aca="false">SUMIF(J59:J77,"Planned",I59:I77)</f>
         <v>63000000</v>
       </c>
     </row>
@@ -8941,22 +8982,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J58:J76">
+  <conditionalFormatting sqref="J59:J77">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J13:J54">
+  <conditionalFormatting sqref="J13:J55">
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13:J54" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13:J55" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J58:J76" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J59:J77" type="list">
       <formula1>"Planned,Done,Skipped"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8987,12 +9028,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9006,53 +9047,53 @@
         <v>307</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -9064,19 +9105,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>405</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>403</v>
       </c>
       <c r="C7" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -9088,19 +9129,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -9112,19 +9153,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -9136,19 +9177,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -9160,19 +9201,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -9184,19 +9225,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -9208,19 +9249,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -9232,19 +9273,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -9256,19 +9297,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -9280,19 +9321,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -9304,16 +9345,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -9326,19 +9367,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>424</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>422</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -9350,19 +9391,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -9374,19 +9415,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -9398,24 +9439,24 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -9427,16 +9468,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>434</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>432</v>
-      </c>
       <c r="C23" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -9449,16 +9490,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="C24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="15" t="s">
         <v>435</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>432</v>
-      </c>
-      <c r="C24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>433</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -9471,19 +9512,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -9495,19 +9536,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="B26" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>437</v>
-      </c>
       <c r="C26" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -9519,16 +9560,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -9541,16 +9582,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C28" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -9563,21 +9604,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -9590,16 +9631,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="B31" s="13" t="s">
         <v>451</v>
       </c>
-      <c r="B31" s="13" t="s">
-        <v>449</v>
-      </c>
       <c r="C31" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -9612,16 +9653,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C32" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -9634,19 +9675,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C33" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
@@ -9658,16 +9699,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="B34" s="13" t="s">
         <v>458</v>
       </c>
-      <c r="B34" s="13" t="s">
-        <v>456</v>
-      </c>
       <c r="C34" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -9680,16 +9721,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C35" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -9702,16 +9743,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C36" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -9724,16 +9765,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -9746,7 +9787,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E39" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$37)*(E5:E37="Done"))</f>
@@ -9783,7 +9824,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E40" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$37,"Required",E5:E37,"Done")&amp;" of 11"</f>
@@ -9820,7 +9861,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -9864,12 +9905,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9877,10 +9918,10 @@
         <v>155</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9891,13 +9932,13 @@
         <v>46313.6875</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9908,7 +9949,7 @@
         <v>285372765</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -9958,7 +9999,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -9966,7 +10007,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -9975,11 +10016,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>19638572.9888335</v>
+        <v>19647919.2607567</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9990,19 +10031,19 @@
         <v>168</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
@@ -10018,7 +10059,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -10044,7 +10085,7 @@
       <c r="B14" s="26"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -10070,7 +10111,7 @@
       <c r="B15" s="26"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -10096,7 +10137,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -10121,10 +10162,10 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="12" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -10149,10 +10190,10 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="12" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -10177,10 +10218,10 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="12" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -10205,10 +10246,10 @@
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="12" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -10233,10 +10274,10 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="12" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -10261,10 +10302,10 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="12" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -10290,7 +10331,7 @@
       <c r="B23" s="26"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -10315,10 +10356,10 @@
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="12" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -10343,10 +10384,10 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="12" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -10371,10 +10412,10 @@
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="D26" s="12" t="s">
         <v>499</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>497</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -10402,7 +10443,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -10429,10 +10470,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -10459,10 +10500,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -10489,10 +10530,10 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
@@ -10513,10 +10554,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -10543,7 +10584,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -10571,10 +10612,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -10601,7 +10642,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -10629,10 +10670,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -10659,7 +10700,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -10687,10 +10728,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -10717,7 +10758,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -10745,10 +10786,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -10775,7 +10816,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -10803,10 +10844,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -10833,7 +10874,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -10861,10 +10902,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -10891,7 +10932,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -10919,7 +10960,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -10947,7 +10988,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -10975,7 +11016,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -11003,7 +11044,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -11031,7 +11072,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -11059,7 +11100,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -11087,7 +11128,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -11115,7 +11156,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -11143,7 +11184,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -11171,7 +11212,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -11193,7 +11234,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -4127,7 +4127,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>520600173.007745</v>
+        <v>520681298.996326</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9929,7 +9929,7 @@
         <v>157</v>
       </c>
       <c r="B5" s="18" t="n">
-        <v>46313.6875</v>
+        <v>46313.7083333333</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>474</v>
@@ -9946,7 +9946,7 @@
         <v>158</v>
       </c>
       <c r="B6" s="19" t="n">
-        <v>285372765</v>
+        <v>285572765</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>477</v>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="B8" s="20" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>14627235</v>
+        <v>14427235</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>139627235</v>
+        <v>139427235</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>19647919.2607567</v>
+        <v>19565466.1322062</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="I27" s="23" t="n">
         <f aca="false">IF(B27="","",MAX(0,B27-$B$6))</f>
-        <v>14627235</v>
+        <v>14427235</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="I28" s="23" t="n">
         <f aca="false">IF(B28="","",MAX(0,B28-$B$6))</f>
-        <v>39627235</v>
+        <v>39427235</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="I29" s="23" t="n">
         <f aca="false">IF(B29="","",MAX(0,B29-$B$6))</f>
-        <v>64627235</v>
+        <v>64427235</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="I30" s="23" t="n">
         <f aca="false">IF(B30="","",MAX(0,B30-$B$6))</f>
-        <v>89627235</v>
+        <v>89427235</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="I31" s="23" t="n">
         <f aca="false">IF(B31="","",MAX(0,B31-$B$6))</f>
-        <v>114627235</v>
+        <v>114427235</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="I32" s="23" t="n">
         <f aca="false">IF(B32="","",MAX(0,B32-$B$6))</f>
-        <v>139627235</v>
+        <v>139427235</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="I33" s="23" t="n">
         <f aca="false">IF(B33="","",MAX(0,B33-$B$6))</f>
-        <v>164627235</v>
+        <v>164427235</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="I34" s="23" t="n">
         <f aca="false">IF(B34="","",MAX(0,B34-$B$6))</f>
-        <v>189627235</v>
+        <v>189427235</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="I35" s="23" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
-        <v>214627235</v>
+        <v>214427235</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="I36" s="23" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>239627235</v>
+        <v>239427235</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="I37" s="23" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>264627235</v>
+        <v>264427235</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="I38" s="23" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>314627235</v>
+        <v>314427235</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="I39" s="23" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>364627235</v>
+        <v>364427235</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="I40" s="23" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>464627235</v>
+        <v>464427235</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="I41" s="23" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>614627235</v>
+        <v>614427235</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="I42" s="23" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>814627235</v>
+        <v>814427235</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="I43" s="23" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>1014627235</v>
+        <v>1014427235</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="I44" s="23" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>1214627235</v>
+        <v>1214427235</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="I45" s="23" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1414627235</v>
+        <v>1414427235</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="I46" s="23" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1614627235</v>
+        <v>1614427235</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="I47" s="23" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1814627235</v>
+        <v>1814427235</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="I48" s="23" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>2014627235</v>
+        <v>2014427235</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11089,7 +11089,7 @@
       </c>
       <c r="I49" s="23" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>2214627235</v>
+        <v>2214427235</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="I50" s="23" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2414627235</v>
+        <v>2414427235</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="I51" s="23" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2614627235</v>
+        <v>2614427235</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="I52" s="23" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2814627235</v>
+        <v>2814427235</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="I53" s="23" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>3014627235</v>
+        <v>3014427235</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="I54" s="23" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>3214627235</v>
+        <v>3214427235</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -4053,7 +4053,7 @@
         <v>157</v>
       </c>
       <c r="B5" s="18" t="n">
-        <v>46313.6875</v>
+        <v>46313.7083333333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4061,14 +4061,14 @@
         <v>158</v>
       </c>
       <c r="B6" s="19" t="n">
-        <v>425373500</v>
+        <v>432211000</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>159</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">B6+Scoring!F50</f>
-        <v>5945373500</v>
+        <v>5952211000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="B9" s="20" t="n">
         <f aca="false">IFERROR(INDEX(E13:E76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),0)</f>
-        <v>9626500</v>
+        <v>2789000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,B76-B6)</f>
-        <v>3699626500</v>
+        <v>3692789000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>520681298.996326</v>
+        <v>518211012.409315</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4792,7 +4792,7 @@
       <c r="D50" s="12"/>
       <c r="E50" s="23" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>9626500</v>
+        <v>2789000</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>207</v>
@@ -4811,7 +4811,7 @@
       <c r="D51" s="12"/>
       <c r="E51" s="23" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>24626500</v>
+        <v>17789000</v>
       </c>
       <c r="F51" s="11" t="s">
         <v>207</v>
@@ -4830,7 +4830,7 @@
       <c r="D52" s="12"/>
       <c r="E52" s="23" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>54626500</v>
+        <v>47789000</v>
       </c>
       <c r="F52" s="11" t="s">
         <v>207</v>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="E53" s="23" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>84626500</v>
+        <v>77789000</v>
       </c>
       <c r="F53" s="11" t="s">
         <v>207</v>
@@ -4870,7 +4870,7 @@
       <c r="D54" s="12"/>
       <c r="E54" s="23" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>114626500</v>
+        <v>107789000</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>207</v>
@@ -4889,7 +4889,7 @@
       <c r="D55" s="12"/>
       <c r="E55" s="23" t="n">
         <f aca="false">IF(B55="","",MAX(0,B55-$B$6))</f>
-        <v>144626500</v>
+        <v>137789000</v>
       </c>
       <c r="F55" s="11" t="s">
         <v>207</v>
@@ -4908,7 +4908,7 @@
       <c r="D56" s="12"/>
       <c r="E56" s="23" t="n">
         <f aca="false">IF(B56="","",MAX(0,B56-$B$6))</f>
-        <v>174626500</v>
+        <v>167789000</v>
       </c>
       <c r="F56" s="11" t="s">
         <v>207</v>
@@ -4927,7 +4927,7 @@
       <c r="D57" s="12"/>
       <c r="E57" s="23" t="n">
         <f aca="false">IF(B57="","",MAX(0,B57-$B$6))</f>
-        <v>204626500</v>
+        <v>197789000</v>
       </c>
       <c r="F57" s="11" t="s">
         <v>207</v>
@@ -4946,7 +4946,7 @@
       <c r="D58" s="12"/>
       <c r="E58" s="23" t="n">
         <f aca="false">IF(B58="","",MAX(0,B58-$B$6))</f>
-        <v>234626500</v>
+        <v>227789000</v>
       </c>
       <c r="F58" s="11" t="s">
         <v>207</v>
@@ -4965,7 +4965,7 @@
       <c r="D59" s="12"/>
       <c r="E59" s="23" t="n">
         <f aca="false">IF(B59="","",MAX(0,B59-$B$6))</f>
-        <v>264626500</v>
+        <v>257789000</v>
       </c>
       <c r="F59" s="11" t="s">
         <v>207</v>
@@ -4984,7 +4984,7 @@
       <c r="D60" s="12"/>
       <c r="E60" s="23" t="n">
         <f aca="false">IF(B60="","",MAX(0,B60-$B$6))</f>
-        <v>324626500</v>
+        <v>317789000</v>
       </c>
       <c r="F60" s="11" t="s">
         <v>207</v>
@@ -5003,7 +5003,7 @@
       <c r="D61" s="12"/>
       <c r="E61" s="23" t="n">
         <f aca="false">IF(B61="","",MAX(0,B61-$B$6))</f>
-        <v>399626500</v>
+        <v>392789000</v>
       </c>
       <c r="F61" s="11" t="s">
         <v>207</v>
@@ -5022,7 +5022,7 @@
       <c r="D62" s="12"/>
       <c r="E62" s="23" t="n">
         <f aca="false">IF(B62="","",MAX(0,B62-$B$6))</f>
-        <v>474626500</v>
+        <v>467789000</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>207</v>
@@ -5041,7 +5041,7 @@
       <c r="D63" s="12"/>
       <c r="E63" s="23" t="n">
         <f aca="false">IF(B63="","",MAX(0,B63-$B$6))</f>
-        <v>549626500</v>
+        <v>542789000</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>207</v>
@@ -5060,7 +5060,7 @@
       <c r="D64" s="12"/>
       <c r="E64" s="23" t="n">
         <f aca="false">IF(B64="","",MAX(0,B64-$B$6))</f>
-        <v>624626500</v>
+        <v>617789000</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>207</v>
@@ -5079,7 +5079,7 @@
       <c r="D65" s="12"/>
       <c r="E65" s="23" t="n">
         <f aca="false">IF(B65="","",MAX(0,B65-$B$6))</f>
-        <v>699626500</v>
+        <v>692789000</v>
       </c>
       <c r="F65" s="11" t="s">
         <v>207</v>
@@ -5098,7 +5098,7 @@
       <c r="D66" s="12"/>
       <c r="E66" s="23" t="n">
         <f aca="false">IF(B66="","",MAX(0,B66-$B$6))</f>
-        <v>774626500</v>
+        <v>767789000</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>207</v>
@@ -5117,7 +5117,7 @@
       <c r="D67" s="12"/>
       <c r="E67" s="23" t="n">
         <f aca="false">IF(B67="","",MAX(0,B67-$B$6))</f>
-        <v>924626500</v>
+        <v>917789000</v>
       </c>
       <c r="F67" s="11" t="s">
         <v>207</v>
@@ -5136,7 +5136,7 @@
       <c r="D68" s="12"/>
       <c r="E68" s="23" t="n">
         <f aca="false">IF(B68="","",MAX(0,B68-$B$6))</f>
-        <v>1074626500</v>
+        <v>1067789000</v>
       </c>
       <c r="F68" s="11" t="s">
         <v>207</v>
@@ -5155,7 +5155,7 @@
       <c r="D69" s="12"/>
       <c r="E69" s="23" t="n">
         <f aca="false">IF(B69="","",MAX(0,B69-$B$6))</f>
-        <v>1224626500</v>
+        <v>1217789000</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>207</v>
@@ -5174,7 +5174,7 @@
       <c r="D70" s="12"/>
       <c r="E70" s="23" t="n">
         <f aca="false">IF(B70="","",MAX(0,B70-$B$6))</f>
-        <v>1449626500</v>
+        <v>1442789000</v>
       </c>
       <c r="F70" s="11" t="s">
         <v>207</v>
@@ -5193,7 +5193,7 @@
       <c r="D71" s="12"/>
       <c r="E71" s="23" t="n">
         <f aca="false">IF(B71="","",MAX(0,B71-$B$6))</f>
-        <v>1824626500</v>
+        <v>1817789000</v>
       </c>
       <c r="F71" s="11" t="s">
         <v>207</v>
@@ -5212,7 +5212,7 @@
       <c r="D72" s="12"/>
       <c r="E72" s="23" t="n">
         <f aca="false">IF(B72="","",MAX(0,B72-$B$6))</f>
-        <v>2199626500</v>
+        <v>2192789000</v>
       </c>
       <c r="F72" s="11" t="s">
         <v>207</v>
@@ -5231,7 +5231,7 @@
       <c r="D73" s="12"/>
       <c r="E73" s="23" t="n">
         <f aca="false">IF(B73="","",MAX(0,B73-$B$6))</f>
-        <v>2574626500</v>
+        <v>2567789000</v>
       </c>
       <c r="F73" s="11" t="s">
         <v>207</v>
@@ -5250,7 +5250,7 @@
       <c r="D74" s="12"/>
       <c r="E74" s="23" t="n">
         <f aca="false">IF(B74="","",MAX(0,B74-$B$6))</f>
-        <v>2949626500</v>
+        <v>2942789000</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>207</v>
@@ -5269,7 +5269,7 @@
       <c r="D75" s="12"/>
       <c r="E75" s="23" t="n">
         <f aca="false">IF(B75="","",MAX(0,B75-$B$6))</f>
-        <v>3324626500</v>
+        <v>3317789000</v>
       </c>
       <c r="F75" s="11" t="s">
         <v>207</v>
@@ -5288,7 +5288,7 @@
       <c r="D76" s="12"/>
       <c r="E76" s="23" t="n">
         <f aca="false">IF(B76="","",MAX(0,B76-$B$6))</f>
-        <v>3699626500</v>
+        <v>3692789000</v>
       </c>
       <c r="F76" s="11" t="s">
         <v>207</v>
@@ -10020,7 +10020,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>19565466.1322062</v>
+        <v>19565896.8550835</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -4127,7 +4127,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>518211012.409315</v>
+        <v>518546916.466447</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7026,10 +7026,10 @@
         <v>217</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>667</v>
+        <v>715</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>264</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7091,11 +7091,11 @@
       </c>
       <c r="G7" s="27" t="n">
         <f aca="false">G5+G6</f>
-        <v>767</v>
+        <v>815</v>
       </c>
       <c r="H7" s="27" t="n">
         <f aca="false">H5+H6</f>
-        <v>454</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7157,11 +7157,11 @@
       </c>
       <c r="G9" s="28" t="n">
         <f aca="false">G7-G8</f>
-        <v>767</v>
+        <v>815</v>
       </c>
       <c r="H9" s="28" t="n">
         <f aca="false">H7-H8</f>
-        <v>454</v>
+        <v>469</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>19565896.8550835</v>
+        <v>19578579.4664557</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Build Priority'!$A$4:$L$26</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Scoring!$A$4:$J$46</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Scoring!$A$4:$J$47</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Tower Roster'!$A$4:$I$44</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="531">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -922,6 +922,9 @@
   </si>
   <si>
     <t xml:space="preserve">Upgrade an Amazing Avenger to T4 Level 3 Iso-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web store free claim</t>
   </si>
   <si>
     <t xml:space="preserve">Offers</t>
@@ -4067,8 +4070,8 @@
         <v>159</v>
       </c>
       <c r="E6" s="20" t="n">
-        <f aca="false">B6+Scoring!F50</f>
-        <v>5952211000</v>
+        <f aca="false">B6+Scoring!F51</f>
+        <v>5979211000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4127,7 +4130,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>518546916.466447</v>
+        <v>527985465.944581</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5327,7 +5330,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -6861,59 +6864,85 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="B46" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="B46" s="12" t="s">
-        <v>298</v>
-      </c>
       <c r="C46" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>299</v>
+        <v>4500000</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>31500000</v>
       </c>
       <c r="E46" s="24" t="n">
-        <v>0</v>
+        <v>4500000</v>
       </c>
       <c r="F46" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D46),MAX(0,D46-E46),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G46" s="25" t="str">
+        <v>27000000</v>
+      </c>
+      <c r="G46" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D46),ROUNDUP(D46/C46,0),"No limit")</f>
-        <v>No limit</v>
+        <v>7</v>
       </c>
       <c r="H46" s="25" t="n">
         <f aca="false">IFERROR(INT(E46/C46),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="25" t="n">
         <f aca="false">IFERROR(ROUNDUP(F46/C46,0),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J46" s="11" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="C47" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="E47" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(D47),MAX(0,D47-E47),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G47" s="25" t="str">
+        <f aca="false">IF(ISNUMBER(D47),ROUNDUP(D47/C47,0),"No limit")</f>
+        <v>No limit</v>
+      </c>
+      <c r="H47" s="25" t="n">
+        <f aca="false">IFERROR(INT(E47/C47),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="25" t="n">
+        <f aca="false">IFERROR(ROUNDUP(F47/C47,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="11" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="E48" s="20" t="n">
-        <f aca="false">SUM(E5:E46)</f>
-        <v>388623500</v>
-      </c>
-      <c r="F48" s="20"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20" t="n">
-        <f aca="false">SUM(F5:F46)</f>
-        <v>7481376500</v>
-      </c>
+      <c r="E49" s="20" t="n">
+        <f aca="false">SUM(E5:E47)</f>
+        <v>393123500</v>
+      </c>
+      <c r="F49" s="20"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="16" t="s">
@@ -6921,24 +6950,34 @@
       </c>
       <c r="E50" s="20"/>
       <c r="F50" s="20" t="n">
-        <f aca="false">SUMIF(J5:J46,"Yes",F5:F46)</f>
-        <v>5520000000</v>
+        <f aca="false">SUM(F5:F47)</f>
+        <v>7508376500</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="16" t="s">
         <v>303</v>
       </c>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20" t="n">
+        <f aca="false">SUMIF(J5:J47,"Yes",F5:F47)</f>
+        <v>5547000000</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="2" t="s">
+        <v>304</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J46"/>
-  <conditionalFormatting sqref="F5:F46">
+  <autoFilter ref="A4:J47"/>
+  <conditionalFormatting sqref="F5:F47">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J5:J46" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J5:J47" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6972,43 +7011,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B5" s="26" t="n">
         <v>6370000</v>
@@ -7034,7 +7073,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B6" s="27" t="n">
         <f aca="false">SUMIFS(B13:B55,$I$13:$I$55,"Yes",$J$13:$J$55,"No")</f>
@@ -7067,7 +7106,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
@@ -7100,7 +7139,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B8" s="27" t="n">
         <f aca="false">SUMIF($J$59:$J$77,"Planned",B59:B77)</f>
@@ -7133,7 +7172,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B7-B8</f>
@@ -7166,44 +7205,44 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="29" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>13</v>
@@ -7211,7 +7250,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B13" s="30" t="n">
         <v>100000</v>
@@ -7241,12 +7280,12 @@
         <v>253</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B14" s="30" t="n">
         <v>1600000</v>
@@ -7276,12 +7315,12 @@
         <v>253</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B15" s="30" t="n">
         <v>1600000</v>
@@ -7311,12 +7350,12 @@
         <v>253</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B16" s="30" t="n">
         <v>1600000</v>
@@ -7346,12 +7385,12 @@
         <v>253</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B17" s="30" t="n">
         <v>1600000</v>
@@ -7381,12 +7420,12 @@
         <v>253</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B18" s="30" t="n">
         <v>1600000</v>
@@ -7416,12 +7455,12 @@
         <v>253</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B19" s="30" t="n">
         <v>1600000</v>
@@ -7451,12 +7490,12 @@
         <v>253</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B20" s="30" t="n">
         <v>1600000</v>
@@ -7486,12 +7525,12 @@
         <v>253</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B21" s="30" t="n">
         <v>100000</v>
@@ -7524,7 +7563,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B22" s="30" t="n">
         <v>200000</v>
@@ -7557,7 +7596,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B23" s="30" t="n">
         <v>0</v>
@@ -7587,12 +7626,12 @@
         <v>253</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B24" s="30" t="n">
         <v>150000</v>
@@ -7625,7 +7664,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B25" s="30" t="n">
         <v>150000</v>
@@ -7658,7 +7697,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B26" s="30" t="n">
         <v>200000</v>
@@ -7691,7 +7730,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B27" s="30" t="n">
         <v>250000</v>
@@ -7724,7 +7763,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B28" s="30" t="n">
         <v>300000</v>
@@ -7757,7 +7796,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B29" s="30" t="n">
         <v>350000</v>
@@ -7790,7 +7829,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B30" s="30" t="n">
         <v>0</v>
@@ -7823,7 +7862,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B31" s="30" t="n">
         <v>0</v>
@@ -7856,7 +7895,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B32" s="30" t="n">
         <v>350000</v>
@@ -7889,7 +7928,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B33" s="30" t="n">
         <v>500000</v>
@@ -7922,7 +7961,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B34" s="30" t="n">
         <v>0</v>
@@ -7952,12 +7991,12 @@
         <v>253</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B35" s="30" t="n">
         <v>0</v>
@@ -7987,12 +8026,12 @@
         <v>253</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B36" s="30" t="n">
         <v>0</v>
@@ -8025,7 +8064,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B37" s="30" t="n">
         <v>0</v>
@@ -8058,7 +8097,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B38" s="30" t="n">
         <v>900000</v>
@@ -8088,12 +8127,12 @@
         <v>253</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B39" s="30" t="n">
         <v>0</v>
@@ -8123,12 +8162,12 @@
         <v>253</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B40" s="30" t="n">
         <v>3300000</v>
@@ -8158,12 +8197,12 @@
         <v>249</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B41" s="30" t="n">
         <v>3300000</v>
@@ -8193,12 +8232,12 @@
         <v>253</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B42" s="30" t="n">
         <v>0</v>
@@ -8228,12 +8267,12 @@
         <v>253</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B43" s="30" t="n">
         <v>0</v>
@@ -8257,12 +8296,12 @@
         <v>253</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B44" s="30" t="n">
         <v>0</v>
@@ -8292,12 +8331,12 @@
         <v>253</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B45" s="30" t="n">
         <v>0</v>
@@ -8327,7 +8366,7 @@
         <v>253</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8462,33 +8501,33 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="29" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>10</v>
@@ -8502,7 +8541,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B59" s="30" t="n">
         <v>1837500</v>
@@ -8529,15 +8568,15 @@
         <v>0</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B60" s="30" t="n">
         <v>0</v>
@@ -8564,13 +8603,13 @@
         <v>0</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K60" s="15"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B61" s="26"/>
       <c r="C61" s="30" t="n">
@@ -8589,15 +8628,15 @@
         <v>3000000</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B62" s="26"/>
       <c r="C62" s="30" t="n">
@@ -8616,15 +8655,15 @@
         <v>3000000</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B63" s="26"/>
       <c r="C63" s="30" t="n">
@@ -8643,15 +8682,15 @@
         <v>3000000</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B64" s="26"/>
       <c r="C64" s="30" t="n">
@@ -8670,15 +8709,15 @@
         <v>3000000</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B65" s="26"/>
       <c r="C65" s="30" t="n">
@@ -8703,15 +8742,15 @@
         <v>17000000</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B66" s="30" t="n">
         <v>0</v>
@@ -8738,15 +8777,15 @@
         <v>17000000</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K66" s="15" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B67" s="30" t="n">
         <v>0</v>
@@ -8767,15 +8806,15 @@
         <v>17000000</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K67" s="15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B68" s="30" t="n">
         <v>0</v>
@@ -8796,15 +8835,15 @@
         <v>17000000</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K68" s="15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B69" s="30" t="n">
         <v>0</v>
@@ -8825,15 +8864,15 @@
         <v>17000000</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K69" s="15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B70" s="30" t="n">
         <v>0</v>
@@ -8854,15 +8893,15 @@
         <v>17000000</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K70" s="15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B71" s="30" t="n">
         <v>13000000</v>
@@ -8883,10 +8922,10 @@
         <v>8000000</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K71" s="15" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8969,7 +9008,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I79" s="20" t="n">
         <f aca="false">SUMIF(J59:J77,"Planned",I59:I77)</f>
@@ -9028,12 +9067,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9044,56 +9083,56 @@
         <v>237</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -9105,19 +9144,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C7" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -9129,19 +9168,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -9153,19 +9192,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -9177,19 +9216,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -9201,19 +9240,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -9225,19 +9264,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -9249,19 +9288,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -9273,19 +9312,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -9297,19 +9336,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -9321,19 +9360,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -9345,16 +9384,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -9367,19 +9406,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -9391,19 +9430,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -9415,19 +9454,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -9439,24 +9478,24 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -9468,16 +9507,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="C23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>436</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>434</v>
-      </c>
-      <c r="C23" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>435</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -9490,16 +9529,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -9512,19 +9551,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -9536,19 +9575,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C26" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -9560,16 +9599,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -9582,16 +9621,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C28" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -9604,21 +9643,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -9631,16 +9670,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C31" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -9653,16 +9692,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C32" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -9675,19 +9714,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C33" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
@@ -9699,16 +9738,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C34" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -9721,16 +9760,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="C35" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="15" t="s">
         <v>462</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>458</v>
-      </c>
-      <c r="C35" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>461</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -9743,16 +9782,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C36" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -9765,16 +9804,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -9787,7 +9826,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E39" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$37)*(E5:E37="Done"))</f>
@@ -9824,7 +9863,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E40" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$37,"Required",E5:E37,"Done")&amp;" of 11"</f>
@@ -9861,7 +9900,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -9905,12 +9944,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9918,10 +9957,10 @@
         <v>155</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9932,13 +9971,13 @@
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9949,7 +9988,7 @@
         <v>285572765</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -9999,7 +10038,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -10007,7 +10046,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -10016,11 +10055,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>19578579.4664557</v>
+        <v>19934947.2004886</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10031,19 +10070,19 @@
         <v>168</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
@@ -10059,7 +10098,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -10085,7 +10124,7 @@
       <c r="B14" s="26"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -10111,7 +10150,7 @@
       <c r="B15" s="26"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -10137,7 +10176,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -10162,10 +10201,10 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="12" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -10190,10 +10229,10 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="12" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -10218,10 +10257,10 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="12" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -10246,10 +10285,10 @@
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="12" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -10274,10 +10313,10 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="12" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -10302,10 +10341,10 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="12" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -10331,7 +10370,7 @@
       <c r="B23" s="26"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -10356,10 +10395,10 @@
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="12" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -10384,10 +10423,10 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="D25" s="12" t="s">
         <v>500</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>499</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -10412,10 +10451,10 @@
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="12" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -10443,7 +10482,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -10470,10 +10509,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -10500,10 +10539,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -10530,10 +10569,10 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
@@ -10554,10 +10593,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -10584,7 +10623,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -10612,10 +10651,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -10642,7 +10681,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -10670,10 +10709,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -10700,7 +10739,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -10728,10 +10767,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -10758,7 +10797,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -10786,10 +10825,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -10816,7 +10855,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -10844,10 +10883,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -10874,7 +10913,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -10902,10 +10941,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -10932,7 +10971,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -10960,7 +10999,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -10988,7 +11027,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -11016,7 +11055,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -11044,7 +11083,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -11072,7 +11111,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -11100,7 +11139,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -11128,7 +11167,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -11156,7 +11195,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -11184,7 +11223,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -11212,7 +11251,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -11234,7 +11273,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -4130,7 +4130,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>527985465.944581</v>
+        <v>528657281.043092</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7050,10 +7050,10 @@
         <v>315</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>6370000</v>
+        <v>6570000</v>
       </c>
       <c r="C5" s="26" t="n">
-        <v>705800</v>
+        <v>755800</v>
       </c>
       <c r="D5" s="26" t="n">
         <v>4370000</v>
@@ -7068,7 +7068,7 @@
         <v>715</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>279</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7110,11 +7110,11 @@
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
-        <v>23220000</v>
+        <v>23420000</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5+C6</f>
-        <v>4705800</v>
+        <v>4755800</v>
       </c>
       <c r="D7" s="27" t="n">
         <f aca="false">D5+D6</f>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="H7" s="27" t="n">
         <f aca="false">H5+H6</f>
-        <v>469</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7176,11 +7176,11 @@
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B7-B8</f>
-        <v>23220000</v>
+        <v>23420000</v>
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">C7-C8</f>
-        <v>2995800</v>
+        <v>3045800</v>
       </c>
       <c r="D9" s="28" t="n">
         <f aca="false">D7-D8</f>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="H9" s="28" t="n">
         <f aca="false">H7-H8</f>
-        <v>469</v>
+        <v>619</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>19934947.2004886</v>
+        <v>19960312.6844277</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="545">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -1135,6 +1135,48 @@
   </si>
   <si>
     <t xml:space="preserve">Defeat reward counted. A win doubles it to 272K each</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breaker of Nature dailies, today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log in, play any battle, collect essence. 250K gold each</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breaker of Nature dailies, Oct 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250K gold each, plus 3 levels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breaker of Nature dailies, Oct 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breaker of Nature dailies, Oct 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breaker of Nature dailies, Oct 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breaker of Nature dailies, Oct 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breaker of Nature dailies, Oct 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breaker of Nature dailies, Oct 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breaker of Nature level 130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected Oct 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breaker of Nature level 140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected about Oct 15. Gives 2,000 gold orb fragments, one orb</t>
   </si>
   <si>
     <t xml:space="preserve">Gold orbs</t>
@@ -4130,7 +4172,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>528657281.043092</v>
+        <v>528818361.289085</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6998,7 +7040,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -7076,31 +7118,31 @@
         <v>316</v>
       </c>
       <c r="B6" s="27" t="n">
-        <f aca="false">SUMIFS(B13:B55,$I$13:$I$55,"Yes",$J$13:$J$55,"No")</f>
-        <v>16850000</v>
+        <f aca="false">SUMIFS(B13:B65,$I$13:$I$65,"Yes",$J$13:$J$65,"No")</f>
+        <v>22850000</v>
       </c>
       <c r="C6" s="27" t="n">
-        <f aca="false">SUMIFS(C13:C55,$I$13:$I$55,"Yes",$J$13:$J$55,"No")</f>
-        <v>4000000</v>
+        <f aca="false">SUMIFS(C13:C65,$I$13:$I$65,"Yes",$J$13:$J$65,"No")</f>
+        <v>4250000</v>
       </c>
       <c r="D6" s="27" t="n">
-        <f aca="false">SUMIFS(D13:D55,$I$13:$I$55,"Yes",$J$13:$J$55,"No")</f>
+        <f aca="false">SUMIFS(D13:D65,$I$13:$I$65,"Yes",$J$13:$J$65,"No")</f>
         <v>3136000</v>
       </c>
       <c r="E6" s="27" t="n">
-        <f aca="false">SUMIFS(E13:E55,$I$13:$I$55,"Yes",$J$13:$J$55,"No")</f>
+        <f aca="false">SUMIFS(E13:E65,$I$13:$I$65,"Yes",$J$13:$J$65,"No")</f>
         <v>2736000</v>
       </c>
       <c r="F6" s="27" t="n">
-        <f aca="false">SUMIFS(F13:F55,$I$13:$I$55,"Yes",$J$13:$J$55,"No")</f>
+        <f aca="false">SUMIFS(F13:F65,$I$13:$I$65,"Yes",$J$13:$J$65,"No")</f>
         <v>0</v>
       </c>
       <c r="G6" s="27" t="n">
-        <f aca="false">SUMIFS(G13:G55,$I$13:$I$55,"Yes",$J$13:$J$55,"No")</f>
+        <f aca="false">SUMIFS(G13:G65,$I$13:$I$65,"Yes",$J$13:$J$65,"No")</f>
         <v>100</v>
       </c>
       <c r="H6" s="27" t="n">
-        <f aca="false">SUMIFS(H13:H55,$I$13:$I$55,"Yes",$J$13:$J$55,"No")</f>
+        <f aca="false">SUMIFS(H13:H65,$I$13:$I$65,"Yes",$J$13:$J$65,"No")</f>
         <v>190</v>
       </c>
     </row>
@@ -7110,11 +7152,11 @@
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
-        <v>23420000</v>
+        <v>29420000</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5+C6</f>
-        <v>4755800</v>
+        <v>5005800</v>
       </c>
       <c r="D7" s="27" t="n">
         <f aca="false">D5+D6</f>
@@ -7142,31 +7184,31 @@
         <v>318</v>
       </c>
       <c r="B8" s="27" t="n">
-        <f aca="false">SUMIF($J$59:$J$77,"Planned",B59:B77)</f>
+        <f aca="false">SUMIF($J$69:$J$87,"Planned",B69:B87)</f>
         <v>0</v>
       </c>
       <c r="C8" s="27" t="n">
-        <f aca="false">SUMIF($J$59:$J$77,"Planned",C59:C77)</f>
+        <f aca="false">SUMIF($J$69:$J$87,"Planned",C69:C87)</f>
         <v>1710000</v>
       </c>
       <c r="D8" s="27" t="n">
-        <f aca="false">SUMIF($J$59:$J$77,"Planned",D59:D77)</f>
+        <f aca="false">SUMIF($J$69:$J$87,"Planned",D69:D87)</f>
         <v>2640000</v>
       </c>
       <c r="E8" s="27" t="n">
-        <f aca="false">SUMIF($J$59:$J$77,"Planned",E59:E77)</f>
+        <f aca="false">SUMIF($J$69:$J$87,"Planned",E69:E87)</f>
         <v>1710000</v>
       </c>
       <c r="F8" s="27" t="n">
-        <f aca="false">SUMIF($J$59:$J$77,"Planned",F59:F77)</f>
+        <f aca="false">SUMIF($J$69:$J$87,"Planned",F69:F87)</f>
         <v>0</v>
       </c>
       <c r="G8" s="27" t="n">
-        <f aca="false">SUMIF($J$59:$J$77,"Planned",G59:G77)</f>
+        <f aca="false">SUMIF($J$69:$J$87,"Planned",G69:G87)</f>
         <v>0</v>
       </c>
       <c r="H8" s="27" t="n">
-        <f aca="false">SUMIF($J$59:$J$77,"Planned",H59:H77)</f>
+        <f aca="false">SUMIF($J$69:$J$87,"Planned",H69:H87)</f>
         <v>0</v>
       </c>
     </row>
@@ -7176,11 +7218,11 @@
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B7-B8</f>
-        <v>23420000</v>
+        <v>29420000</v>
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">C7-C8</f>
-        <v>3045800</v>
+        <v>3295800</v>
       </c>
       <c r="D9" s="28" t="n">
         <f aca="false">D7-D8</f>
@@ -8339,7 +8381,7 @@
         <v>368</v>
       </c>
       <c r="B45" s="30" t="n">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="C45" s="30" t="n">
         <v>0</v>
@@ -8360,7 +8402,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J45" s="11" t="s">
         <v>253</v>
@@ -8370,504 +8412,558 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="12"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="12"/>
+      <c r="A46" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="B46" s="30" t="n">
+        <v>750000</v>
+      </c>
+      <c r="C46" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K46" s="15" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="12"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-      <c r="K47" s="12"/>
+      <c r="A47" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="B47" s="30" t="n">
+        <v>750000</v>
+      </c>
+      <c r="C47" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K47" s="15" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="12"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
-      <c r="H48" s="30"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
-      <c r="K48" s="12"/>
+      <c r="A48" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B48" s="30" t="n">
+        <v>750000</v>
+      </c>
+      <c r="C48" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K48" s="15" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="12"/>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="11"/>
-      <c r="J49" s="11"/>
-      <c r="K49" s="12"/>
+      <c r="A49" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B49" s="30" t="n">
+        <v>750000</v>
+      </c>
+      <c r="C49" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K49" s="15" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="12"/>
-      <c r="B50" s="30"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="30"/>
-      <c r="F50" s="30"/>
-      <c r="G50" s="30"/>
-      <c r="H50" s="30"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="11"/>
-      <c r="K50" s="12"/>
+      <c r="A50" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B50" s="30" t="n">
+        <v>750000</v>
+      </c>
+      <c r="C50" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K50" s="15" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="12"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="30"/>
-      <c r="H51" s="30"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="11"/>
-      <c r="K51" s="12"/>
+      <c r="A51" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="B51" s="30" t="n">
+        <v>750000</v>
+      </c>
+      <c r="C51" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K51" s="15" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="12"/>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="30"/>
-      <c r="I52" s="11"/>
-      <c r="J52" s="11"/>
-      <c r="K52" s="12"/>
+      <c r="A52" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="B52" s="30" t="n">
+        <v>750000</v>
+      </c>
+      <c r="C52" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K52" s="15" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="12"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-      <c r="G53" s="30"/>
-      <c r="H53" s="30"/>
-      <c r="I53" s="11"/>
-      <c r="J53" s="11"/>
-      <c r="K53" s="12"/>
+      <c r="A53" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="B53" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="30" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D53" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K53" s="15" t="s">
+        <v>379</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="12"/>
-      <c r="B54" s="30"/>
-      <c r="C54" s="30"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="30"/>
-      <c r="H54" s="30"/>
-      <c r="I54" s="11"/>
-      <c r="J54" s="11"/>
-      <c r="K54" s="12"/>
+      <c r="A54" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="B54" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K54" s="15" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="12"/>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="11"/>
-      <c r="J55" s="11"/>
-      <c r="K55" s="12"/>
+      <c r="A55" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="B55" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K55" s="15" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="12"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="30"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="12"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="29" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="B58" s="3" t="s">
+      <c r="A57" s="12"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="12"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="12"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="12"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="12"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
+      <c r="K59" s="12"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="12"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="11"/>
+      <c r="K60" s="12"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="12"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
+      <c r="K61" s="12"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="12"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="30"/>
+      <c r="H62" s="30"/>
+      <c r="I62" s="11"/>
+      <c r="J62" s="11"/>
+      <c r="K62" s="12"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="12"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="30"/>
+      <c r="H63" s="30"/>
+      <c r="I63" s="11"/>
+      <c r="J63" s="11"/>
+      <c r="K63" s="12"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="12"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="11"/>
+      <c r="J64" s="11"/>
+      <c r="K64" s="12"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="12"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="30"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="30"/>
+      <c r="G65" s="30"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="11"/>
+      <c r="K65" s="12"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="29" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="E68" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="F68" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G68" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="H68" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="I58" s="3" t="s">
+      <c r="I68" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J58" s="3" t="s">
+      <c r="J68" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="K68" s="3" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="B59" s="30" t="n">
-        <v>1837500</v>
-      </c>
-      <c r="C59" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G59" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" s="30" t="n">
-        <v>183</v>
-      </c>
-      <c r="I59" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="K59" s="15" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="B60" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" s="30" t="n">
-        <v>359800</v>
-      </c>
-      <c r="D60" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="K60" s="15"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="B61" s="26"/>
-      <c r="C61" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="30" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="J61" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="K61" s="15" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="B62" s="26"/>
-      <c r="C62" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="26"/>
-      <c r="G62" s="26"/>
-      <c r="H62" s="26"/>
-      <c r="I62" s="30" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="J62" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="K62" s="15" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="B63" s="26"/>
-      <c r="C63" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="26"/>
-      <c r="G63" s="26"/>
-      <c r="H63" s="26"/>
-      <c r="I63" s="30" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="J63" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="K63" s="15" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="B64" s="26"/>
-      <c r="C64" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="26"/>
-      <c r="G64" s="26"/>
-      <c r="H64" s="26"/>
-      <c r="I64" s="30" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="J64" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="K64" s="15" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="12" t="s">
-        <v>382</v>
-      </c>
-      <c r="B65" s="26"/>
-      <c r="C65" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="30" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="J65" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="K65" s="15" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="B66" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" s="30" t="n">
-        <v>1710000</v>
-      </c>
-      <c r="D66" s="30" t="n">
-        <v>2640000</v>
-      </c>
-      <c r="E66" s="30" t="n">
-        <v>1710000</v>
-      </c>
-      <c r="F66" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="30" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="J66" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="K66" s="15" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="B67" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" s="26"/>
-      <c r="D67" s="26"/>
-      <c r="E67" s="26"/>
-      <c r="F67" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="30" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="J67" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="K67" s="15" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="B68" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" s="26"/>
-      <c r="D68" s="26"/>
-      <c r="E68" s="26"/>
-      <c r="F68" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="30" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="J68" s="11" t="s">
-        <v>387</v>
-      </c>
-      <c r="K68" s="15" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B69" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" s="26"/>
-      <c r="D69" s="26"/>
-      <c r="E69" s="26"/>
+        <v>1837500</v>
+      </c>
+      <c r="C69" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="F69" s="30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G69" s="30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" s="30" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="I69" s="30" t="n">
-        <v>17000000</v>
+        <v>0</v>
       </c>
       <c r="J69" s="11" t="s">
         <v>387</v>
       </c>
       <c r="K69" s="15" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8877,9 +8973,15 @@
       <c r="B70" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C70" s="26"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="26"/>
+      <c r="C70" s="30" t="n">
+        <v>359800</v>
+      </c>
+      <c r="D70" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="F70" s="30" t="n">
         <v>0</v>
       </c>
@@ -8890,22 +8992,18 @@
         <v>0</v>
       </c>
       <c r="I70" s="30" t="n">
-        <v>17000000</v>
+        <v>0</v>
       </c>
       <c r="J70" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="K70" s="15" t="s">
-        <v>378</v>
-      </c>
+      <c r="K70" s="15"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="B71" s="30" t="n">
-        <v>13000000</v>
-      </c>
+      <c r="B71" s="26"/>
       <c r="C71" s="30" t="n">
         <v>0</v>
       </c>
@@ -8919,99 +9017,393 @@
       <c r="G71" s="26"/>
       <c r="H71" s="26"/>
       <c r="I71" s="30" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="K71" s="15" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="B72" s="26"/>
+      <c r="C72" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="26"/>
+      <c r="G72" s="26"/>
+      <c r="H72" s="26"/>
+      <c r="I72" s="30" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="K72" s="15" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="B73" s="26"/>
+      <c r="C73" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="26"/>
+      <c r="G73" s="26"/>
+      <c r="H73" s="26"/>
+      <c r="I73" s="30" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="K73" s="15" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="B74" s="26"/>
+      <c r="C74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="26"/>
+      <c r="I74" s="30" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="J74" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="K74" s="15" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="B75" s="26"/>
+      <c r="C75" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J75" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="K75" s="15" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="B76" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="30" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="D76" s="30" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="E76" s="30" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="F76" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J76" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="K76" s="15" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="B77" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="26"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J77" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="K77" s="15" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="B78" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J78" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="K78" s="15" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="B79" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="26"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J79" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="K79" s="15" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="B80" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J80" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="K80" s="15" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="B81" s="30" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="C81" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26"/>
+      <c r="H81" s="26"/>
+      <c r="I81" s="30" t="n">
         <v>8000000</v>
       </c>
-      <c r="J71" s="11" t="s">
-        <v>387</v>
-      </c>
-      <c r="K71" s="15" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="12"/>
-      <c r="B72" s="30"/>
-      <c r="C72" s="30"/>
-      <c r="D72" s="30"/>
-      <c r="E72" s="30"/>
-      <c r="F72" s="30"/>
-      <c r="G72" s="30"/>
-      <c r="H72" s="30"/>
-      <c r="I72" s="30"/>
-      <c r="J72" s="11"/>
-      <c r="K72" s="12"/>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="12"/>
-      <c r="B73" s="30"/>
-      <c r="C73" s="30"/>
-      <c r="D73" s="30"/>
-      <c r="E73" s="30"/>
-      <c r="F73" s="30"/>
-      <c r="G73" s="30"/>
-      <c r="H73" s="30"/>
-      <c r="I73" s="30"/>
-      <c r="J73" s="11"/>
-      <c r="K73" s="12"/>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="12"/>
-      <c r="B74" s="30"/>
-      <c r="C74" s="30"/>
-      <c r="D74" s="30"/>
-      <c r="E74" s="30"/>
-      <c r="F74" s="30"/>
-      <c r="G74" s="30"/>
-      <c r="H74" s="30"/>
-      <c r="I74" s="30"/>
-      <c r="J74" s="11"/>
-      <c r="K74" s="12"/>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="12"/>
-      <c r="B75" s="30"/>
-      <c r="C75" s="30"/>
-      <c r="D75" s="30"/>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="30"/>
-      <c r="J75" s="11"/>
-      <c r="K75" s="12"/>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="12"/>
-      <c r="B76" s="30"/>
-      <c r="C76" s="30"/>
-      <c r="D76" s="30"/>
-      <c r="E76" s="30"/>
-      <c r="F76" s="30"/>
-      <c r="G76" s="30"/>
-      <c r="H76" s="30"/>
-      <c r="I76" s="30"/>
-      <c r="J76" s="11"/>
-      <c r="K76" s="12"/>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="12"/>
-      <c r="B77" s="30"/>
-      <c r="C77" s="30"/>
-      <c r="D77" s="30"/>
-      <c r="E77" s="30"/>
-      <c r="F77" s="30"/>
-      <c r="G77" s="30"/>
-      <c r="H77" s="30"/>
-      <c r="I77" s="30"/>
-      <c r="J77" s="11"/>
-      <c r="K77" s="12"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="16" t="s">
-        <v>392</v>
-      </c>
-      <c r="I79" s="20" t="n">
-        <f aca="false">SUMIF(J59:J77,"Planned",I59:I77)</f>
+      <c r="J81" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="K81" s="15" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="12"/>
+      <c r="B82" s="30"/>
+      <c r="C82" s="30"/>
+      <c r="D82" s="30"/>
+      <c r="E82" s="30"/>
+      <c r="F82" s="30"/>
+      <c r="G82" s="30"/>
+      <c r="H82" s="30"/>
+      <c r="I82" s="30"/>
+      <c r="J82" s="11"/>
+      <c r="K82" s="12"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="12"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="30"/>
+      <c r="D83" s="30"/>
+      <c r="E83" s="30"/>
+      <c r="F83" s="30"/>
+      <c r="G83" s="30"/>
+      <c r="H83" s="30"/>
+      <c r="I83" s="30"/>
+      <c r="J83" s="11"/>
+      <c r="K83" s="12"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="12"/>
+      <c r="B84" s="30"/>
+      <c r="C84" s="30"/>
+      <c r="D84" s="30"/>
+      <c r="E84" s="30"/>
+      <c r="F84" s="30"/>
+      <c r="G84" s="30"/>
+      <c r="H84" s="30"/>
+      <c r="I84" s="30"/>
+      <c r="J84" s="11"/>
+      <c r="K84" s="12"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="12"/>
+      <c r="B85" s="30"/>
+      <c r="C85" s="30"/>
+      <c r="D85" s="30"/>
+      <c r="E85" s="30"/>
+      <c r="F85" s="30"/>
+      <c r="G85" s="30"/>
+      <c r="H85" s="30"/>
+      <c r="I85" s="30"/>
+      <c r="J85" s="11"/>
+      <c r="K85" s="12"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="12"/>
+      <c r="B86" s="30"/>
+      <c r="C86" s="30"/>
+      <c r="D86" s="30"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="30"/>
+      <c r="G86" s="30"/>
+      <c r="H86" s="30"/>
+      <c r="I86" s="30"/>
+      <c r="J86" s="11"/>
+      <c r="K86" s="12"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="12"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
+      <c r="H87" s="30"/>
+      <c r="I87" s="30"/>
+      <c r="J87" s="11"/>
+      <c r="K87" s="12"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="I89" s="20" t="n">
+        <f aca="false">SUMIF(J69:J87,"Planned",I69:I87)</f>
         <v>63000000</v>
       </c>
     </row>
@@ -9021,22 +9413,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J59:J77">
+  <conditionalFormatting sqref="J69:J87">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J13:J55">
+  <conditionalFormatting sqref="J13:J65">
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13:J55" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13:J65" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J59:J77" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J69:J87" type="list">
       <formula1>"Planned,Done,Skipped"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9067,12 +9459,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9086,53 +9478,53 @@
         <v>308</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -9144,19 +9536,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C7" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -9168,19 +9560,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -9192,19 +9584,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -9216,19 +9608,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -9240,19 +9632,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -9264,19 +9656,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -9288,19 +9680,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -9312,19 +9704,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -9336,19 +9728,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -9360,19 +9752,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -9384,16 +9776,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -9406,19 +9798,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -9430,19 +9822,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -9454,19 +9846,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -9478,24 +9870,24 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -9507,16 +9899,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="C23" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -9529,16 +9921,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -9551,19 +9943,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -9575,19 +9967,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="C26" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -9599,16 +9991,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -9621,16 +10013,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="C28" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -9643,21 +10035,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -9670,16 +10062,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="C31" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -9692,16 +10084,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="C32" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -9714,19 +10106,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="C33" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
@@ -9738,16 +10130,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="C34" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -9760,16 +10152,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="C35" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -9782,16 +10174,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="C36" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -9804,16 +10196,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="B37" s="13" t="s">
         <v>466</v>
       </c>
-      <c r="B37" s="13" t="s">
-        <v>452</v>
-      </c>
       <c r="C37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -9826,7 +10218,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="E39" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$37)*(E5:E37="Done"))</f>
@@ -9863,7 +10255,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="E40" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$37,"Required",E5:E37,"Done")&amp;" of 11"</f>
@@ -9900,7 +10292,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -9944,12 +10336,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9957,10 +10349,10 @@
         <v>155</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9971,13 +10363,13 @@
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9988,7 +10380,7 @@
         <v>285572765</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -10038,7 +10430,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -10046,7 +10438,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -10055,11 +10447,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>19960312.6844277</v>
+        <v>19966394.5132271</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10070,19 +10462,19 @@
         <v>168</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
@@ -10098,7 +10490,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -10124,7 +10516,7 @@
       <c r="B14" s="26"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -10150,7 +10542,7 @@
       <c r="B15" s="26"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -10176,7 +10568,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -10201,10 +10593,10 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="12" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -10229,10 +10621,10 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="12" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -10257,10 +10649,10 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="12" t="s">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -10285,10 +10677,10 @@
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="12" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -10313,10 +10705,10 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="12" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -10341,10 +10733,10 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="12" t="s">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -10370,7 +10762,7 @@
       <c r="B23" s="26"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -10395,10 +10787,10 @@
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="12" t="s">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -10423,10 +10815,10 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="12" t="s">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -10451,10 +10843,10 @@
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="12" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -10482,7 +10874,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -10509,10 +10901,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -10539,10 +10931,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -10569,10 +10961,10 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
@@ -10593,10 +10985,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -10623,7 +11015,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -10651,10 +11043,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -10681,7 +11073,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -10709,10 +11101,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -10739,7 +11131,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -10767,10 +11159,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -10797,7 +11189,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -10825,10 +11217,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -10855,7 +11247,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -10883,10 +11275,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -10913,7 +11305,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -10941,10 +11333,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -10971,7 +11363,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -10999,7 +11391,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>521</v>
+        <v>535</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -11027,7 +11419,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -11055,7 +11447,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -11083,7 +11475,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>523</v>
+        <v>537</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -11111,7 +11503,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -11139,7 +11531,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -11167,7 +11559,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -11195,7 +11587,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -11223,7 +11615,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -11251,7 +11643,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>529</v>
+        <v>543</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -11273,7 +11665,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>530</v>
+        <v>544</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -4106,14 +4106,14 @@
         <v>158</v>
       </c>
       <c r="B6" s="19" t="n">
-        <v>432211000</v>
+        <v>440711000</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>159</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">B6+Scoring!F51</f>
-        <v>5979211000</v>
+        <v>5987711000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6))+SUMPRODUCT((B13:B76="")*(F13:F76="Claimed"))</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>161</v>
@@ -4138,14 +4138,14 @@
       </c>
       <c r="B8" s="16" t="n">
         <f aca="false">IFERROR(INDEX(A13:A76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),"All done")</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>163</v>
       </c>
       <c r="E8" s="16" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6)*(F13:F76&lt;&gt;"Claimed"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="B9" s="20" t="n">
         <f aca="false">IFERROR(INDEX(E13:E76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),0)</f>
-        <v>2789000</v>
+        <v>9289000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,B76-B6)</f>
-        <v>3692789000</v>
+        <v>3684289000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>528818361.289085</v>
+        <v>528126531.296779</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4837,7 +4837,7 @@
       <c r="D50" s="12"/>
       <c r="E50" s="23" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2789000</v>
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>207</v>
@@ -4856,7 +4856,7 @@
       <c r="D51" s="12"/>
       <c r="E51" s="23" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>17789000</v>
+        <v>9289000</v>
       </c>
       <c r="F51" s="11" t="s">
         <v>207</v>
@@ -4875,7 +4875,7 @@
       <c r="D52" s="12"/>
       <c r="E52" s="23" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>47789000</v>
+        <v>39289000</v>
       </c>
       <c r="F52" s="11" t="s">
         <v>207</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E53" s="23" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>77789000</v>
+        <v>69289000</v>
       </c>
       <c r="F53" s="11" t="s">
         <v>207</v>
@@ -4915,7 +4915,7 @@
       <c r="D54" s="12"/>
       <c r="E54" s="23" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>107789000</v>
+        <v>99289000</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>207</v>
@@ -4934,7 +4934,7 @@
       <c r="D55" s="12"/>
       <c r="E55" s="23" t="n">
         <f aca="false">IF(B55="","",MAX(0,B55-$B$6))</f>
-        <v>137789000</v>
+        <v>129289000</v>
       </c>
       <c r="F55" s="11" t="s">
         <v>207</v>
@@ -4953,7 +4953,7 @@
       <c r="D56" s="12"/>
       <c r="E56" s="23" t="n">
         <f aca="false">IF(B56="","",MAX(0,B56-$B$6))</f>
-        <v>167789000</v>
+        <v>159289000</v>
       </c>
       <c r="F56" s="11" t="s">
         <v>207</v>
@@ -4972,7 +4972,7 @@
       <c r="D57" s="12"/>
       <c r="E57" s="23" t="n">
         <f aca="false">IF(B57="","",MAX(0,B57-$B$6))</f>
-        <v>197789000</v>
+        <v>189289000</v>
       </c>
       <c r="F57" s="11" t="s">
         <v>207</v>
@@ -4991,7 +4991,7 @@
       <c r="D58" s="12"/>
       <c r="E58" s="23" t="n">
         <f aca="false">IF(B58="","",MAX(0,B58-$B$6))</f>
-        <v>227789000</v>
+        <v>219289000</v>
       </c>
       <c r="F58" s="11" t="s">
         <v>207</v>
@@ -5010,7 +5010,7 @@
       <c r="D59" s="12"/>
       <c r="E59" s="23" t="n">
         <f aca="false">IF(B59="","",MAX(0,B59-$B$6))</f>
-        <v>257789000</v>
+        <v>249289000</v>
       </c>
       <c r="F59" s="11" t="s">
         <v>207</v>
@@ -5029,7 +5029,7 @@
       <c r="D60" s="12"/>
       <c r="E60" s="23" t="n">
         <f aca="false">IF(B60="","",MAX(0,B60-$B$6))</f>
-        <v>317789000</v>
+        <v>309289000</v>
       </c>
       <c r="F60" s="11" t="s">
         <v>207</v>
@@ -5048,7 +5048,7 @@
       <c r="D61" s="12"/>
       <c r="E61" s="23" t="n">
         <f aca="false">IF(B61="","",MAX(0,B61-$B$6))</f>
-        <v>392789000</v>
+        <v>384289000</v>
       </c>
       <c r="F61" s="11" t="s">
         <v>207</v>
@@ -5067,7 +5067,7 @@
       <c r="D62" s="12"/>
       <c r="E62" s="23" t="n">
         <f aca="false">IF(B62="","",MAX(0,B62-$B$6))</f>
-        <v>467789000</v>
+        <v>459289000</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>207</v>
@@ -5086,7 +5086,7 @@
       <c r="D63" s="12"/>
       <c r="E63" s="23" t="n">
         <f aca="false">IF(B63="","",MAX(0,B63-$B$6))</f>
-        <v>542789000</v>
+        <v>534289000</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>207</v>
@@ -5105,7 +5105,7 @@
       <c r="D64" s="12"/>
       <c r="E64" s="23" t="n">
         <f aca="false">IF(B64="","",MAX(0,B64-$B$6))</f>
-        <v>617789000</v>
+        <v>609289000</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>207</v>
@@ -5124,7 +5124,7 @@
       <c r="D65" s="12"/>
       <c r="E65" s="23" t="n">
         <f aca="false">IF(B65="","",MAX(0,B65-$B$6))</f>
-        <v>692789000</v>
+        <v>684289000</v>
       </c>
       <c r="F65" s="11" t="s">
         <v>207</v>
@@ -5143,7 +5143,7 @@
       <c r="D66" s="12"/>
       <c r="E66" s="23" t="n">
         <f aca="false">IF(B66="","",MAX(0,B66-$B$6))</f>
-        <v>767789000</v>
+        <v>759289000</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>207</v>
@@ -5162,7 +5162,7 @@
       <c r="D67" s="12"/>
       <c r="E67" s="23" t="n">
         <f aca="false">IF(B67="","",MAX(0,B67-$B$6))</f>
-        <v>917789000</v>
+        <v>909289000</v>
       </c>
       <c r="F67" s="11" t="s">
         <v>207</v>
@@ -5181,7 +5181,7 @@
       <c r="D68" s="12"/>
       <c r="E68" s="23" t="n">
         <f aca="false">IF(B68="","",MAX(0,B68-$B$6))</f>
-        <v>1067789000</v>
+        <v>1059289000</v>
       </c>
       <c r="F68" s="11" t="s">
         <v>207</v>
@@ -5200,7 +5200,7 @@
       <c r="D69" s="12"/>
       <c r="E69" s="23" t="n">
         <f aca="false">IF(B69="","",MAX(0,B69-$B$6))</f>
-        <v>1217789000</v>
+        <v>1209289000</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>207</v>
@@ -5219,7 +5219,7 @@
       <c r="D70" s="12"/>
       <c r="E70" s="23" t="n">
         <f aca="false">IF(B70="","",MAX(0,B70-$B$6))</f>
-        <v>1442789000</v>
+        <v>1434289000</v>
       </c>
       <c r="F70" s="11" t="s">
         <v>207</v>
@@ -5238,7 +5238,7 @@
       <c r="D71" s="12"/>
       <c r="E71" s="23" t="n">
         <f aca="false">IF(B71="","",MAX(0,B71-$B$6))</f>
-        <v>1817789000</v>
+        <v>1809289000</v>
       </c>
       <c r="F71" s="11" t="s">
         <v>207</v>
@@ -5257,7 +5257,7 @@
       <c r="D72" s="12"/>
       <c r="E72" s="23" t="n">
         <f aca="false">IF(B72="","",MAX(0,B72-$B$6))</f>
-        <v>2192789000</v>
+        <v>2184289000</v>
       </c>
       <c r="F72" s="11" t="s">
         <v>207</v>
@@ -5276,7 +5276,7 @@
       <c r="D73" s="12"/>
       <c r="E73" s="23" t="n">
         <f aca="false">IF(B73="","",MAX(0,B73-$B$6))</f>
-        <v>2567789000</v>
+        <v>2559289000</v>
       </c>
       <c r="F73" s="11" t="s">
         <v>207</v>
@@ -5295,7 +5295,7 @@
       <c r="D74" s="12"/>
       <c r="E74" s="23" t="n">
         <f aca="false">IF(B74="","",MAX(0,B74-$B$6))</f>
-        <v>2942789000</v>
+        <v>2934289000</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>207</v>
@@ -5314,7 +5314,7 @@
       <c r="D75" s="12"/>
       <c r="E75" s="23" t="n">
         <f aca="false">IF(B75="","",MAX(0,B75-$B$6))</f>
-        <v>3317789000</v>
+        <v>3309289000</v>
       </c>
       <c r="F75" s="11" t="s">
         <v>207</v>
@@ -5333,7 +5333,7 @@
       <c r="D76" s="12"/>
       <c r="E76" s="23" t="n">
         <f aca="false">IF(B76="","",MAX(0,B76-$B$6))</f>
-        <v>3692789000</v>
+        <v>3684289000</v>
       </c>
       <c r="F76" s="11" t="s">
         <v>207</v>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>19966394.5132271</v>
+        <v>19986277.4313375</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="549">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -1203,10 +1203,22 @@
     <t xml:space="preserve">Iron Monger Iso-8 to T3 level 3</t>
   </si>
   <si>
+    <t xml:space="preserve">Crossbones to level 85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unlocks T3 Iso-8 and his raid tasks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crossbones Iso-8 to T3 level 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate based on Iron Monger</t>
+  </si>
+  <si>
     <t xml:space="preserve">Doctor Strange to level 101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planned</t>
   </si>
   <si>
     <t xml:space="preserve">Check cost in game</t>
@@ -4172,7 +4184,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>528126531.296779</v>
+        <v>528568817.036196</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7040,7 +7052,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -7092,7 +7104,7 @@
         <v>315</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>6570000</v>
+        <v>9320000</v>
       </c>
       <c r="C5" s="26" t="n">
         <v>755800</v>
@@ -7110,7 +7122,7 @@
         <v>715</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>429</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7152,7 +7164,7 @@
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
-        <v>29420000</v>
+        <v>32170000</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5+C6</f>
@@ -7176,7 +7188,7 @@
       </c>
       <c r="H7" s="27" t="n">
         <f aca="false">H5+H6</f>
-        <v>619</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7184,32 +7196,32 @@
         <v>318</v>
       </c>
       <c r="B8" s="27" t="n">
-        <f aca="false">SUMIF($J$69:$J$87,"Planned",B69:B87)</f>
-        <v>0</v>
+        <f aca="false">SUMIF($J$69:$J$89,"Planned",B69:B89)</f>
+        <v>9791250</v>
       </c>
       <c r="C8" s="27" t="n">
-        <f aca="false">SUMIF($J$69:$J$87,"Planned",C69:C87)</f>
+        <f aca="false">SUMIF($J$69:$J$89,"Planned",C69:C89)</f>
+        <v>2070000</v>
+      </c>
+      <c r="D8" s="27" t="n">
+        <f aca="false">SUMIF($J$69:$J$89,"Planned",D69:D89)</f>
+        <v>2640000</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <f aca="false">SUMIF($J$69:$J$89,"Planned",E69:E89)</f>
         <v>1710000</v>
       </c>
-      <c r="D8" s="27" t="n">
-        <f aca="false">SUMIF($J$69:$J$87,"Planned",D69:D87)</f>
-        <v>2640000</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <f aca="false">SUMIF($J$69:$J$87,"Planned",E69:E87)</f>
-        <v>1710000</v>
-      </c>
       <c r="F8" s="27" t="n">
-        <f aca="false">SUMIF($J$69:$J$87,"Planned",F69:F87)</f>
-        <v>0</v>
+        <f aca="false">SUMIF($J$69:$J$89,"Planned",F69:F89)</f>
+        <v>1</v>
       </c>
       <c r="G8" s="27" t="n">
-        <f aca="false">SUMIF($J$69:$J$87,"Planned",G69:G87)</f>
+        <f aca="false">SUMIF($J$69:$J$89,"Planned",G69:G89)</f>
         <v>0</v>
       </c>
       <c r="H8" s="27" t="n">
-        <f aca="false">SUMIF($J$69:$J$87,"Planned",H69:H87)</f>
-        <v>0</v>
+        <f aca="false">SUMIF($J$69:$J$89,"Planned",H69:H89)</f>
+        <v>979</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7218,11 +7230,11 @@
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B7-B8</f>
-        <v>29420000</v>
+        <v>22378750</v>
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">C7-C8</f>
-        <v>3295800</v>
+        <v>2935800</v>
       </c>
       <c r="D9" s="28" t="n">
         <f aca="false">D7-D8</f>
@@ -7234,7 +7246,7 @@
       </c>
       <c r="F9" s="28" t="n">
         <f aca="false">F7-F8</f>
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G9" s="28" t="n">
         <f aca="false">G7-G8</f>
@@ -7242,7 +7254,7 @@
       </c>
       <c r="H9" s="28" t="n">
         <f aca="false">H7-H8</f>
-        <v>619</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9003,7 +9015,9 @@
       <c r="A71" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="B71" s="26"/>
+      <c r="B71" s="30" t="n">
+        <v>9791250</v>
+      </c>
       <c r="C71" s="30" t="n">
         <v>0</v>
       </c>
@@ -9013,11 +9027,17 @@
       <c r="E71" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F71" s="26"/>
-      <c r="G71" s="26"/>
-      <c r="H71" s="26"/>
+      <c r="F71" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="30" t="n">
+        <v>979</v>
+      </c>
       <c r="I71" s="30" t="n">
-        <v>3000000</v>
+        <v>55000000</v>
       </c>
       <c r="J71" s="11" t="s">
         <v>391</v>
@@ -9030,9 +9050,11 @@
       <c r="A72" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="B72" s="26"/>
+      <c r="B72" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="C72" s="30" t="n">
-        <v>0</v>
+        <v>360000</v>
       </c>
       <c r="D72" s="30" t="n">
         <v>0</v>
@@ -9040,22 +9062,28 @@
       <c r="E72" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F72" s="26"/>
-      <c r="G72" s="26"/>
-      <c r="H72" s="26"/>
+      <c r="F72" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="I72" s="30" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="J72" s="11" t="s">
         <v>391</v>
       </c>
       <c r="K72" s="15" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B73" s="26"/>
       <c r="C73" s="30" t="n">
@@ -9077,12 +9105,12 @@
         <v>391</v>
       </c>
       <c r="K73" s="15" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B74" s="26"/>
       <c r="C74" s="30" t="n">
@@ -9104,12 +9132,12 @@
         <v>391</v>
       </c>
       <c r="K74" s="15" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B75" s="26"/>
       <c r="C75" s="30" t="n">
@@ -9121,70 +9149,60 @@
       <c r="E75" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F75" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="30" t="n">
-        <v>0</v>
-      </c>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26"/>
+      <c r="H75" s="26"/>
       <c r="I75" s="30" t="n">
-        <v>17000000</v>
+        <v>3000000</v>
       </c>
       <c r="J75" s="11" t="s">
         <v>391</v>
       </c>
       <c r="K75" s="15" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>397</v>
-      </c>
-      <c r="B76" s="30" t="n">
-        <v>0</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="B76" s="26"/>
       <c r="C76" s="30" t="n">
-        <v>1710000</v>
+        <v>0</v>
       </c>
       <c r="D76" s="30" t="n">
-        <v>2640000</v>
+        <v>0</v>
       </c>
       <c r="E76" s="30" t="n">
-        <v>1710000</v>
-      </c>
-      <c r="F76" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="30" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F76" s="26"/>
+      <c r="G76" s="26"/>
+      <c r="H76" s="26"/>
       <c r="I76" s="30" t="n">
-        <v>17000000</v>
+        <v>3000000</v>
       </c>
       <c r="J76" s="11" t="s">
         <v>391</v>
       </c>
       <c r="K76" s="15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="B77" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" s="26"/>
-      <c r="D77" s="26"/>
-      <c r="E77" s="26"/>
+        <v>400</v>
+      </c>
+      <c r="B77" s="26"/>
+      <c r="C77" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="F77" s="30" t="n">
         <v>0</v>
       </c>
@@ -9201,19 +9219,25 @@
         <v>391</v>
       </c>
       <c r="K77" s="15" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B78" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C78" s="26"/>
-      <c r="D78" s="26"/>
-      <c r="E78" s="26"/>
+      <c r="C78" s="30" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="D78" s="30" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="E78" s="30" t="n">
+        <v>1710000</v>
+      </c>
       <c r="F78" s="30" t="n">
         <v>0</v>
       </c>
@@ -9227,15 +9251,15 @@
         <v>17000000</v>
       </c>
       <c r="J78" s="11" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="K78" s="15" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B79" s="30" t="n">
         <v>0</v>
@@ -9256,15 +9280,15 @@
         <v>17000000</v>
       </c>
       <c r="J79" s="11" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B80" s="30" t="n">
         <v>0</v>
@@ -9285,66 +9309,98 @@
         <v>17000000</v>
       </c>
       <c r="J80" s="11" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="K80" s="15" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B81" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="26"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J81" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="K81" s="15" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="B82" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="26"/>
+      <c r="D82" s="26"/>
+      <c r="E82" s="26"/>
+      <c r="F82" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J82" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="K82" s="15" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="B83" s="30" t="n">
         <v>13000000</v>
       </c>
-      <c r="C81" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="26"/>
-      <c r="G81" s="26"/>
-      <c r="H81" s="26"/>
-      <c r="I81" s="30" t="n">
+      <c r="C83" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="26"/>
+      <c r="G83" s="26"/>
+      <c r="H83" s="26"/>
+      <c r="I83" s="30" t="n">
         <v>8000000</v>
       </c>
-      <c r="J81" s="11" t="s">
-        <v>401</v>
-      </c>
-      <c r="K81" s="15" t="s">
+      <c r="J83" s="11" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="12"/>
-      <c r="B82" s="30"/>
-      <c r="C82" s="30"/>
-      <c r="D82" s="30"/>
-      <c r="E82" s="30"/>
-      <c r="F82" s="30"/>
-      <c r="G82" s="30"/>
-      <c r="H82" s="30"/>
-      <c r="I82" s="30"/>
-      <c r="J82" s="11"/>
-      <c r="K82" s="12"/>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="12"/>
-      <c r="B83" s="30"/>
-      <c r="C83" s="30"/>
-      <c r="D83" s="30"/>
-      <c r="E83" s="30"/>
-      <c r="F83" s="30"/>
-      <c r="G83" s="30"/>
-      <c r="H83" s="30"/>
-      <c r="I83" s="30"/>
-      <c r="J83" s="11"/>
-      <c r="K83" s="12"/>
+      <c r="K83" s="15" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12"/>
@@ -9398,13 +9454,39 @@
       <c r="J87" s="11"/>
       <c r="K87" s="12"/>
     </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="12"/>
+      <c r="B88" s="30"/>
+      <c r="C88" s="30"/>
+      <c r="D88" s="30"/>
+      <c r="E88" s="30"/>
+      <c r="F88" s="30"/>
+      <c r="G88" s="30"/>
+      <c r="H88" s="30"/>
+      <c r="I88" s="30"/>
+      <c r="J88" s="11"/>
+      <c r="K88" s="12"/>
+    </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="16" t="s">
-        <v>406</v>
-      </c>
-      <c r="I89" s="20" t="n">
-        <f aca="false">SUMIF(J69:J87,"Planned",I69:I87)</f>
-        <v>63000000</v>
+      <c r="A89" s="12"/>
+      <c r="B89" s="30"/>
+      <c r="C89" s="30"/>
+      <c r="D89" s="30"/>
+      <c r="E89" s="30"/>
+      <c r="F89" s="30"/>
+      <c r="G89" s="30"/>
+      <c r="H89" s="30"/>
+      <c r="I89" s="30"/>
+      <c r="J89" s="11"/>
+      <c r="K89" s="12"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="I91" s="20" t="n">
+        <f aca="false">SUMIF(J69:J89,"Planned",I69:I89)</f>
+        <v>118000000</v>
       </c>
     </row>
   </sheetData>
@@ -9413,7 +9495,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J69:J87">
+  <conditionalFormatting sqref="J69:J89">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Done"</formula>
     </cfRule>
@@ -9428,7 +9510,7 @@
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J69:J87" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J69:J89" type="list">
       <formula1>"Planned,Done,Skipped"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9459,12 +9541,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9478,50 +9560,50 @@
         <v>308</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>387</v>
@@ -9536,16 +9618,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C7" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E7" s="32" t="s">
         <v>387</v>
@@ -9560,16 +9642,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>424</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>420</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E8" s="32" t="s">
         <v>387</v>
@@ -9584,16 +9666,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E9" s="32" t="s">
         <v>387</v>
@@ -9608,16 +9690,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E10" s="32" t="s">
         <v>387</v>
@@ -9632,16 +9714,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E11" s="32" t="s">
         <v>387</v>
@@ -9656,16 +9738,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="E12" s="32" t="s">
         <v>387</v>
@@ -9680,16 +9762,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E13" s="32" t="s">
         <v>387</v>
@@ -9704,16 +9786,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E14" s="32" t="s">
         <v>387</v>
@@ -9728,16 +9810,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E15" s="32" t="s">
         <v>387</v>
@@ -9752,16 +9834,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E16" s="32" t="s">
         <v>387</v>
@@ -9776,16 +9858,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -9798,16 +9880,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E18" s="32" t="s">
         <v>387</v>
@@ -9822,16 +9904,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>443</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>439</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E19" s="32" t="s">
         <v>387</v>
@@ -9846,16 +9928,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E20" s="32" t="s">
         <v>387</v>
@@ -9870,21 +9952,21 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E22" s="32" t="s">
         <v>387</v>
@@ -9899,16 +9981,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C23" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -9921,16 +10003,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -9943,16 +10025,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E25" s="32" t="s">
         <v>387</v>
@@ -9967,16 +10049,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C26" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E26" s="32" t="s">
         <v>387</v>
@@ -9991,16 +10073,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -10013,16 +10095,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C28" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -10035,21 +10117,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -10062,16 +10144,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C31" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -10084,16 +10166,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="B32" s="13" t="s">
         <v>470</v>
       </c>
-      <c r="B32" s="13" t="s">
-        <v>466</v>
-      </c>
       <c r="C32" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -10106,16 +10188,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C33" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="E33" s="32" t="s">
         <v>387</v>
@@ -10130,16 +10212,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C34" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -10152,16 +10234,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="B35" s="13" t="s">
         <v>477</v>
       </c>
-      <c r="B35" s="13" t="s">
-        <v>473</v>
-      </c>
       <c r="C35" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -10174,16 +10256,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C36" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -10196,16 +10278,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -10218,7 +10300,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="E39" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$37)*(E5:E37="Done"))</f>
@@ -10255,7 +10337,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E40" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$37,"Required",E5:E37,"Done")&amp;" of 11"</f>
@@ -10292,7 +10374,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -10336,12 +10418,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10349,10 +10431,10 @@
         <v>155</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10363,13 +10445,13 @@
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10380,7 +10462,7 @@
         <v>285572765</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -10430,7 +10512,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -10438,7 +10520,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -10447,11 +10529,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>19986277.4313375</v>
+        <v>20003015.1830075</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10462,19 +10544,19 @@
         <v>168</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
@@ -10490,7 +10572,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -10516,7 +10598,7 @@
       <c r="B14" s="26"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -10542,7 +10624,7 @@
       <c r="B15" s="26"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -10568,7 +10650,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -10593,10 +10675,10 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="12" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -10621,10 +10703,10 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="12" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -10649,10 +10731,10 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="12" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -10677,10 +10759,10 @@
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="12" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -10705,10 +10787,10 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="12" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -10733,10 +10815,10 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="12" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -10762,7 +10844,7 @@
       <c r="B23" s="26"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -10787,10 +10869,10 @@
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="12" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -10815,10 +10897,10 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="12" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -10843,10 +10925,10 @@
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="12" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -10874,7 +10956,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -10901,10 +10983,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -10931,10 +11013,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="D29" s="12" t="s">
         <v>518</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>514</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -10961,10 +11043,10 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
@@ -10985,10 +11067,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -11015,7 +11097,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -11043,10 +11125,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -11073,7 +11155,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -11101,10 +11183,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -11131,7 +11213,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -11159,10 +11241,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -11189,7 +11271,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -11217,10 +11299,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -11247,7 +11329,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -11275,10 +11357,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -11305,7 +11387,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -11333,10 +11415,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -11363,7 +11445,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -11391,7 +11473,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -11419,7 +11501,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -11447,7 +11529,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -11475,7 +11557,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -11503,7 +11585,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -11531,7 +11613,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -11559,7 +11641,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -11587,7 +11669,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -11615,7 +11697,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -11643,7 +11725,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -11665,7 +11747,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="552">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -1075,6 +1075,15 @@
   </si>
   <si>
     <t xml:space="preserve">Battle pass level 88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claimed Oct 11, in current stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battle pass level 95, premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battle pass level 97, premium</t>
   </si>
   <si>
     <t xml:space="preserve">Battle pass level 97</t>
@@ -4184,7 +4193,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>528568817.036196</v>
+        <v>533769203.857946</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7052,7 +7061,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -7104,7 +7113,7 @@
         <v>315</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>9320000</v>
+        <v>18170000</v>
       </c>
       <c r="C5" s="26" t="n">
         <v>755800</v>
@@ -7130,32 +7139,32 @@
         <v>316</v>
       </c>
       <c r="B6" s="27" t="n">
-        <f aca="false">SUMIFS(B13:B65,$I$13:$I$65,"Yes",$J$13:$J$65,"No")</f>
-        <v>22850000</v>
+        <f aca="false">SUMIFS(B13:B67,$I$13:$I$67,"Yes",$J$13:$J$67,"No")</f>
+        <v>32500000</v>
       </c>
       <c r="C6" s="27" t="n">
-        <f aca="false">SUMIFS(C13:C65,$I$13:$I$65,"Yes",$J$13:$J$65,"No")</f>
+        <f aca="false">SUMIFS(C13:C67,$I$13:$I$67,"Yes",$J$13:$J$67,"No")</f>
         <v>4250000</v>
       </c>
       <c r="D6" s="27" t="n">
-        <f aca="false">SUMIFS(D13:D65,$I$13:$I$65,"Yes",$J$13:$J$65,"No")</f>
+        <f aca="false">SUMIFS(D13:D67,$I$13:$I$67,"Yes",$J$13:$J$67,"No")</f>
         <v>3136000</v>
       </c>
       <c r="E6" s="27" t="n">
-        <f aca="false">SUMIFS(E13:E65,$I$13:$I$65,"Yes",$J$13:$J$65,"No")</f>
+        <f aca="false">SUMIFS(E13:E67,$I$13:$I$67,"Yes",$J$13:$J$67,"No")</f>
         <v>2736000</v>
       </c>
       <c r="F6" s="27" t="n">
-        <f aca="false">SUMIFS(F13:F65,$I$13:$I$65,"Yes",$J$13:$J$65,"No")</f>
+        <f aca="false">SUMIFS(F13:F67,$I$13:$I$67,"Yes",$J$13:$J$67,"No")</f>
         <v>0</v>
       </c>
       <c r="G6" s="27" t="n">
-        <f aca="false">SUMIFS(G13:G65,$I$13:$I$65,"Yes",$J$13:$J$65,"No")</f>
+        <f aca="false">SUMIFS(G13:G67,$I$13:$I$67,"Yes",$J$13:$J$67,"No")</f>
         <v>100</v>
       </c>
       <c r="H6" s="27" t="n">
-        <f aca="false">SUMIFS(H13:H65,$I$13:$I$65,"Yes",$J$13:$J$65,"No")</f>
-        <v>190</v>
+        <f aca="false">SUMIFS(H13:H67,$I$13:$I$67,"Yes",$J$13:$J$67,"No")</f>
+        <v>990</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7164,7 +7173,7 @@
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
-        <v>32170000</v>
+        <v>50670000</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5+C6</f>
@@ -7188,7 +7197,7 @@
       </c>
       <c r="H7" s="27" t="n">
         <f aca="false">H5+H6</f>
-        <v>1194</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7196,31 +7205,31 @@
         <v>318</v>
       </c>
       <c r="B8" s="27" t="n">
-        <f aca="false">SUMIF($J$69:$J$89,"Planned",B69:B89)</f>
+        <f aca="false">SUMIF($J$71:$J$91,"Planned",B71:B91)</f>
         <v>9791250</v>
       </c>
       <c r="C8" s="27" t="n">
-        <f aca="false">SUMIF($J$69:$J$89,"Planned",C69:C89)</f>
+        <f aca="false">SUMIF($J$71:$J$91,"Planned",C71:C91)</f>
         <v>2070000</v>
       </c>
       <c r="D8" s="27" t="n">
-        <f aca="false">SUMIF($J$69:$J$89,"Planned",D69:D89)</f>
+        <f aca="false">SUMIF($J$71:$J$91,"Planned",D71:D91)</f>
         <v>2640000</v>
       </c>
       <c r="E8" s="27" t="n">
-        <f aca="false">SUMIF($J$69:$J$89,"Planned",E69:E89)</f>
+        <f aca="false">SUMIF($J$71:$J$91,"Planned",E71:E91)</f>
         <v>1710000</v>
       </c>
       <c r="F8" s="27" t="n">
-        <f aca="false">SUMIF($J$69:$J$89,"Planned",F69:F89)</f>
+        <f aca="false">SUMIF($J$71:$J$91,"Planned",F71:F91)</f>
         <v>1</v>
       </c>
       <c r="G8" s="27" t="n">
-        <f aca="false">SUMIF($J$69:$J$89,"Planned",G69:G89)</f>
+        <f aca="false">SUMIF($J$71:$J$91,"Planned",G71:G91)</f>
         <v>0</v>
       </c>
       <c r="H8" s="27" t="n">
-        <f aca="false">SUMIF($J$69:$J$89,"Planned",H69:H89)</f>
+        <f aca="false">SUMIF($J$71:$J$91,"Planned",H71:H91)</f>
         <v>979</v>
       </c>
     </row>
@@ -7230,7 +7239,7 @@
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B7-B8</f>
-        <v>22378750</v>
+        <v>40878750</v>
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">C7-C8</f>
@@ -7254,7 +7263,7 @@
       </c>
       <c r="H9" s="28" t="n">
         <f aca="false">H7-H8</f>
-        <v>215</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7952,7 +7961,7 @@
         <v>347</v>
       </c>
       <c r="B32" s="30" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="C32" s="30" t="n">
         <v>0</v>
@@ -7978,14 +7987,16 @@
       <c r="J32" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="K32" s="15"/>
+      <c r="K32" s="15" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B33" s="30" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="C33" s="30" t="n">
         <v>0</v>
@@ -8003,7 +8014,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="30" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I33" s="11" t="s">
         <v>249</v>
@@ -8015,19 +8026,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B34" s="30" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="C34" s="30" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="D34" s="30" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="E34" s="30" t="n">
-        <v>2600000</v>
+        <v>0</v>
       </c>
       <c r="F34" s="30" t="n">
         <v>0</v>
@@ -8044,25 +8055,23 @@
       <c r="J34" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="K34" s="15" t="s">
-        <v>350</v>
-      </c>
+      <c r="K34" s="15"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
         <v>351</v>
       </c>
       <c r="B35" s="30" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="C35" s="30" t="n">
-        <v>900000</v>
+        <v>0</v>
       </c>
       <c r="D35" s="30" t="n">
-        <v>1300000</v>
+        <v>0</v>
       </c>
       <c r="E35" s="30" t="n">
-        <v>1900000</v>
+        <v>0</v>
       </c>
       <c r="F35" s="30" t="n">
         <v>0</v>
@@ -8074,30 +8083,28 @@
         <v>0</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="K35" s="15" t="s">
-        <v>352</v>
-      </c>
+      <c r="K35" s="15"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B36" s="30" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="30" t="n">
-        <v>950000</v>
+        <v>3000000</v>
       </c>
       <c r="D36" s="30" t="n">
-        <v>0</v>
+        <v>3000000</v>
       </c>
       <c r="E36" s="30" t="n">
-        <v>1900000</v>
+        <v>2600000</v>
       </c>
       <c r="F36" s="30" t="n">
         <v>0</v>
@@ -8109,12 +8116,14 @@
         <v>0</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="K36" s="15"/>
+      <c r="K36" s="15" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
@@ -8124,10 +8133,10 @@
         <v>0</v>
       </c>
       <c r="C37" s="30" t="n">
-        <v>0</v>
+        <v>900000</v>
       </c>
       <c r="D37" s="30" t="n">
-        <v>1400000</v>
+        <v>1300000</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>1900000</v>
@@ -8147,23 +8156,25 @@
       <c r="J37" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="K37" s="15"/>
+      <c r="K37" s="15" t="s">
+        <v>355</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B38" s="30" t="n">
-        <v>900000</v>
+        <v>0</v>
       </c>
       <c r="C38" s="30" t="n">
-        <v>0</v>
+        <v>950000</v>
       </c>
       <c r="D38" s="30" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="30" t="n">
-        <v>0</v>
+        <v>1900000</v>
       </c>
       <c r="F38" s="30" t="n">
         <v>0</v>
@@ -8180,9 +8191,7 @@
       <c r="J38" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="K38" s="15" t="s">
-        <v>356</v>
-      </c>
+      <c r="K38" s="15"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
@@ -8195,19 +8204,19 @@
         <v>0</v>
       </c>
       <c r="D39" s="30" t="n">
-        <v>0</v>
+        <v>1400000</v>
       </c>
       <c r="E39" s="30" t="n">
-        <v>0</v>
+        <v>1900000</v>
       </c>
       <c r="F39" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="30" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H39" s="30" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I39" s="11" t="s">
         <v>253</v>
@@ -8215,16 +8224,14 @@
       <c r="J39" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="K39" s="15" t="s">
-        <v>356</v>
-      </c>
+      <c r="K39" s="15"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
         <v>358</v>
       </c>
       <c r="B40" s="30" t="n">
-        <v>3300000</v>
+        <v>900000</v>
       </c>
       <c r="C40" s="30" t="n">
         <v>0</v>
@@ -8245,10 +8252,10 @@
         <v>0</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K40" s="15" t="s">
         <v>359</v>
@@ -8259,7 +8266,7 @@
         <v>360</v>
       </c>
       <c r="B41" s="30" t="n">
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="C41" s="30" t="n">
         <v>0</v>
@@ -8274,30 +8281,30 @@
         <v>0</v>
       </c>
       <c r="G41" s="30" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H41" s="30" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="J41" s="11" t="s">
         <v>253</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B42" s="30" t="n">
-        <v>0</v>
+        <v>3300000</v>
       </c>
       <c r="C42" s="30" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="D42" s="30" t="n">
         <v>0</v>
@@ -8318,18 +8325,18 @@
         <v>249</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B43" s="30" t="n">
-        <v>0</v>
+        <v>3300000</v>
       </c>
       <c r="C43" s="30" t="n">
         <v>0</v>
@@ -8340,9 +8347,15 @@
       <c r="E43" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
+      <c r="F43" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="I43" s="11" t="s">
         <v>249</v>
       </c>
@@ -8350,24 +8363,24 @@
         <v>253</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B44" s="30" t="n">
         <v>0</v>
       </c>
       <c r="C44" s="30" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="D44" s="30" t="n">
-        <v>136000</v>
+        <v>0</v>
       </c>
       <c r="E44" s="30" t="n">
-        <v>136000</v>
+        <v>0</v>
       </c>
       <c r="F44" s="30" t="n">
         <v>0</v>
@@ -8385,15 +8398,15 @@
         <v>253</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B45" s="30" t="n">
-        <v>750000</v>
+        <v>0</v>
       </c>
       <c r="C45" s="30" t="n">
         <v>0</v>
@@ -8404,15 +8417,9 @@
       <c r="E45" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="30" t="n">
-        <v>0</v>
-      </c>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
       <c r="I45" s="11" t="s">
         <v>249</v>
       </c>
@@ -8420,24 +8427,24 @@
         <v>253</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B46" s="30" t="n">
-        <v>750000</v>
+        <v>0</v>
       </c>
       <c r="C46" s="30" t="n">
         <v>0</v>
       </c>
       <c r="D46" s="30" t="n">
-        <v>0</v>
+        <v>136000</v>
       </c>
       <c r="E46" s="30" t="n">
-        <v>0</v>
+        <v>136000</v>
       </c>
       <c r="F46" s="30" t="n">
         <v>0</v>
@@ -8455,12 +8462,12 @@
         <v>253</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B47" s="30" t="n">
         <v>750000</v>
@@ -8490,7 +8497,7 @@
         <v>253</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8525,12 +8532,12 @@
         <v>253</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B49" s="30" t="n">
         <v>750000</v>
@@ -8560,12 +8567,12 @@
         <v>253</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B50" s="30" t="n">
         <v>750000</v>
@@ -8595,12 +8602,12 @@
         <v>253</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B51" s="30" t="n">
         <v>750000</v>
@@ -8630,12 +8637,12 @@
         <v>253</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B52" s="30" t="n">
         <v>750000</v>
@@ -8665,18 +8672,18 @@
         <v>253</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B53" s="30" t="n">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="C53" s="30" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="D53" s="30" t="n">
         <v>0</v>
@@ -8700,7 +8707,7 @@
         <v>253</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8708,7 +8715,7 @@
         <v>380</v>
       </c>
       <c r="B54" s="30" t="n">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="C54" s="30" t="n">
         <v>0</v>
@@ -8735,18 +8742,18 @@
         <v>253</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B55" s="30" t="n">
         <v>0</v>
       </c>
       <c r="C55" s="30" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="D55" s="30" t="n">
         <v>0</v>
@@ -8764,40 +8771,84 @@
         <v>0</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J55" s="11" t="s">
         <v>253</v>
       </c>
       <c r="K55" s="15" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="12" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="12"/>
-      <c r="B56" s="30"/>
-      <c r="C56" s="30"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="30"/>
-      <c r="G56" s="30"/>
-      <c r="H56" s="30"/>
-      <c r="I56" s="11"/>
-      <c r="J56" s="11"/>
-      <c r="K56" s="12"/>
+      <c r="B56" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K56" s="15" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="12"/>
-      <c r="B57" s="30"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="30"/>
-      <c r="H57" s="30"/>
-      <c r="I57" s="11"/>
-      <c r="J57" s="11"/>
-      <c r="K57" s="12"/>
+      <c r="A57" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="B57" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K57" s="15" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12"/>
@@ -8903,158 +8954,116 @@
       <c r="J65" s="11"/>
       <c r="K65" s="12"/>
     </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="12"/>
+      <c r="B66" s="30"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="30"/>
+      <c r="E66" s="30"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="30"/>
+      <c r="H66" s="30"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="11"/>
+      <c r="K66" s="12"/>
+    </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="29" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="B68" s="3" t="s">
+      <c r="A67" s="12"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="11"/>
+      <c r="J67" s="11"/>
+      <c r="K67" s="12"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="29" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F70" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="G70" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="H68" s="3" t="s">
+      <c r="H70" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="I68" s="3" t="s">
+      <c r="I70" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J68" s="3" t="s">
+      <c r="J70" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K68" s="3" t="s">
+      <c r="K70" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="B69" s="30" t="n">
-        <v>1837500</v>
-      </c>
-      <c r="C69" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G69" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69" s="30" t="n">
-        <v>183</v>
-      </c>
-      <c r="I69" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="11" t="s">
-        <v>387</v>
-      </c>
-      <c r="K69" s="15" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="B70" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" s="30" t="n">
-        <v>359800</v>
-      </c>
-      <c r="D70" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="11" t="s">
-        <v>387</v>
-      </c>
-      <c r="K70" s="15"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="B71" s="30" t="n">
+        <v>1837500</v>
+      </c>
+      <c r="C71" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="30" t="n">
+        <v>183</v>
+      </c>
+      <c r="I71" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="B71" s="30" t="n">
-        <v>9791250</v>
-      </c>
-      <c r="C71" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="30" t="n">
-        <v>979</v>
-      </c>
-      <c r="I71" s="30" t="n">
-        <v>55000000</v>
-      </c>
-      <c r="J71" s="11" t="s">
+      <c r="K71" s="15" t="s">
         <v>391</v>
-      </c>
-      <c r="K71" s="15" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B72" s="30" t="n">
         <v>0</v>
       </c>
       <c r="C72" s="30" t="n">
-        <v>360000</v>
+        <v>359800</v>
       </c>
       <c r="D72" s="30" t="n">
         <v>0</v>
@@ -9075,64 +9084,78 @@
         <v>0</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>391</v>
-      </c>
-      <c r="K72" s="15" t="s">
-        <v>394</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="K72" s="15"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="B73" s="30" t="n">
+        <v>9791250</v>
+      </c>
+      <c r="C73" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="30" t="n">
+        <v>979</v>
+      </c>
+      <c r="I73" s="30" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="K73" s="15" t="s">
         <v>395</v>
-      </c>
-      <c r="B73" s="26"/>
-      <c r="C73" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="26"/>
-      <c r="G73" s="26"/>
-      <c r="H73" s="26"/>
-      <c r="I73" s="30" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="J73" s="11" t="s">
-        <v>391</v>
-      </c>
-      <c r="K73" s="15" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="B74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="30" t="n">
+        <v>360000</v>
+      </c>
+      <c r="D74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="K74" s="15" t="s">
         <v>397</v>
-      </c>
-      <c r="B74" s="26"/>
-      <c r="C74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="26"/>
-      <c r="G74" s="26"/>
-      <c r="H74" s="26"/>
-      <c r="I74" s="30" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="J74" s="11" t="s">
-        <v>391</v>
-      </c>
-      <c r="K74" s="15" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9156,15 +9179,15 @@
         <v>3000000</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="K75" s="15" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B76" s="26"/>
       <c r="C76" s="30" t="n">
@@ -9183,15 +9206,15 @@
         <v>3000000</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="K76" s="15" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B77" s="26"/>
       <c r="C77" s="30" t="n">
@@ -9203,70 +9226,60 @@
       <c r="E77" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F77" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="30" t="n">
-        <v>0</v>
-      </c>
+      <c r="F77" s="26"/>
+      <c r="G77" s="26"/>
+      <c r="H77" s="26"/>
       <c r="I77" s="30" t="n">
-        <v>17000000</v>
+        <v>3000000</v>
       </c>
       <c r="J77" s="11" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="K77" s="15" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="B78" s="30" t="n">
-        <v>0</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="B78" s="26"/>
       <c r="C78" s="30" t="n">
-        <v>1710000</v>
+        <v>0</v>
       </c>
       <c r="D78" s="30" t="n">
-        <v>2640000</v>
+        <v>0</v>
       </c>
       <c r="E78" s="30" t="n">
-        <v>1710000</v>
-      </c>
-      <c r="F78" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="30" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
       <c r="I78" s="30" t="n">
-        <v>17000000</v>
+        <v>3000000</v>
       </c>
       <c r="J78" s="11" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="K78" s="15" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
         <v>403</v>
       </c>
-      <c r="B79" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" s="26"/>
-      <c r="D79" s="26"/>
-      <c r="E79" s="26"/>
+      <c r="B79" s="26"/>
+      <c r="C79" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="F79" s="30" t="n">
         <v>0</v>
       </c>
@@ -9280,10 +9293,10 @@
         <v>17000000</v>
       </c>
       <c r="J79" s="11" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9293,9 +9306,15 @@
       <c r="B80" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="26"/>
+      <c r="C80" s="30" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="D80" s="30" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="E80" s="30" t="n">
+        <v>1710000</v>
+      </c>
       <c r="F80" s="30" t="n">
         <v>0</v>
       </c>
@@ -9309,10 +9328,10 @@
         <v>17000000</v>
       </c>
       <c r="J80" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="K80" s="15" t="s">
         <v>405</v>
-      </c>
-      <c r="K80" s="15" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9338,10 +9357,10 @@
         <v>17000000</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9367,66 +9386,98 @@
         <v>17000000</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="K82" s="15" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="B83" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="26"/>
+      <c r="D83" s="26"/>
+      <c r="E83" s="26"/>
+      <c r="F83" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J83" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="B83" s="30" t="n">
+      <c r="K83" s="15" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="B84" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="26"/>
+      <c r="D84" s="26"/>
+      <c r="E84" s="26"/>
+      <c r="F84" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J84" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="K84" s="15" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="B85" s="30" t="n">
         <v>13000000</v>
       </c>
-      <c r="C83" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="26"/>
-      <c r="G83" s="26"/>
-      <c r="H83" s="26"/>
-      <c r="I83" s="30" t="n">
+      <c r="C85" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="26"/>
+      <c r="G85" s="26"/>
+      <c r="H85" s="26"/>
+      <c r="I85" s="30" t="n">
         <v>8000000</v>
       </c>
-      <c r="J83" s="11" t="s">
-        <v>405</v>
-      </c>
-      <c r="K83" s="15" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="12"/>
-      <c r="B84" s="30"/>
-      <c r="C84" s="30"/>
-      <c r="D84" s="30"/>
-      <c r="E84" s="30"/>
-      <c r="F84" s="30"/>
-      <c r="G84" s="30"/>
-      <c r="H84" s="30"/>
-      <c r="I84" s="30"/>
-      <c r="J84" s="11"/>
-      <c r="K84" s="12"/>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="12"/>
-      <c r="B85" s="30"/>
-      <c r="C85" s="30"/>
-      <c r="D85" s="30"/>
-      <c r="E85" s="30"/>
-      <c r="F85" s="30"/>
-      <c r="G85" s="30"/>
-      <c r="H85" s="30"/>
-      <c r="I85" s="30"/>
-      <c r="J85" s="11"/>
-      <c r="K85" s="12"/>
+      <c r="J85" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="K85" s="15" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12"/>
@@ -9480,12 +9531,38 @@
       <c r="J89" s="11"/>
       <c r="K89" s="12"/>
     </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="12"/>
+      <c r="B90" s="30"/>
+      <c r="C90" s="30"/>
+      <c r="D90" s="30"/>
+      <c r="E90" s="30"/>
+      <c r="F90" s="30"/>
+      <c r="G90" s="30"/>
+      <c r="H90" s="30"/>
+      <c r="I90" s="30"/>
+      <c r="J90" s="11"/>
+      <c r="K90" s="12"/>
+    </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="16" t="s">
-        <v>410</v>
-      </c>
-      <c r="I91" s="20" t="n">
-        <f aca="false">SUMIF(J69:J89,"Planned",I69:I89)</f>
+      <c r="A91" s="12"/>
+      <c r="B91" s="30"/>
+      <c r="C91" s="30"/>
+      <c r="D91" s="30"/>
+      <c r="E91" s="30"/>
+      <c r="F91" s="30"/>
+      <c r="G91" s="30"/>
+      <c r="H91" s="30"/>
+      <c r="I91" s="30"/>
+      <c r="J91" s="11"/>
+      <c r="K91" s="12"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="I93" s="20" t="n">
+        <f aca="false">SUMIF(J71:J91,"Planned",I71:I91)</f>
         <v>118000000</v>
       </c>
     </row>
@@ -9495,22 +9572,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J69:J89">
+  <conditionalFormatting sqref="J71:J91">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J13:J65">
+  <conditionalFormatting sqref="J13:J67">
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13:J65" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13:J67" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J69:J89" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J71:J91" type="list">
       <formula1>"Planned,Done,Skipped"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9541,12 +9618,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9560,53 +9637,53 @@
         <v>308</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -9618,19 +9695,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C7" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -9642,19 +9719,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -9666,19 +9743,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -9690,19 +9767,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -9714,19 +9791,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -9738,19 +9815,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -9762,19 +9839,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -9786,19 +9863,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -9810,19 +9887,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -9834,19 +9911,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -9858,16 +9935,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -9880,19 +9957,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -9904,19 +9981,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -9928,19 +10005,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -9952,24 +10029,24 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -9981,16 +10058,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C23" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -10003,16 +10080,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>456</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>453</v>
-      </c>
       <c r="C24" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -10025,19 +10102,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -10049,19 +10126,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C26" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -10073,16 +10150,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -10095,16 +10172,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C28" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -10117,21 +10194,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -10144,16 +10221,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C31" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -10166,16 +10243,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C32" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -10188,19 +10265,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C33" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
@@ -10212,16 +10289,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C34" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -10234,16 +10311,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C35" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -10256,16 +10333,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C36" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -10278,16 +10355,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -10300,7 +10377,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E39" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$37)*(E5:E37="Done"))</f>
@@ -10337,7 +10414,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E40" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$37,"Required",E5:E37,"Done")&amp;" of 11"</f>
@@ -10374,7 +10451,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -10418,12 +10495,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10431,10 +10508,10 @@
         <v>155</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10445,13 +10522,13 @@
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10462,7 +10539,7 @@
         <v>285572765</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -10512,7 +10589,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -10520,7 +10597,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -10529,11 +10606,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>20003015.1830075</v>
+        <v>20199817.2122427</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10544,19 +10621,19 @@
         <v>168</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
@@ -10572,7 +10649,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -10598,7 +10675,7 @@
       <c r="B14" s="26"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -10624,7 +10701,7 @@
       <c r="B15" s="26"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -10650,7 +10727,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -10675,10 +10752,10 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="12" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -10703,10 +10780,10 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="12" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -10731,10 +10808,10 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="12" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -10759,10 +10836,10 @@
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="12" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -10787,10 +10864,10 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="12" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -10815,10 +10892,10 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="12" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -10844,7 +10921,7 @@
       <c r="B23" s="26"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -10869,10 +10946,10 @@
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="12" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -10897,10 +10974,10 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="12" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -10925,10 +11002,10 @@
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="12" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -10956,7 +11033,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -10983,10 +11060,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="D28" s="12" t="s">
         <v>521</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>518</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -11013,10 +11090,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -11043,10 +11120,10 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
@@ -11067,10 +11144,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -11097,7 +11174,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -11125,10 +11202,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -11155,7 +11232,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -11183,10 +11260,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -11213,7 +11290,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -11241,10 +11318,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -11271,7 +11348,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -11299,10 +11376,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -11329,7 +11406,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -11357,10 +11434,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -11387,7 +11464,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -11415,10 +11492,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -11445,7 +11522,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -11473,7 +11550,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -11501,7 +11578,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -11529,7 +11606,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -11557,7 +11634,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -11585,7 +11662,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -11613,7 +11690,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -11641,7 +11718,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -11669,7 +11746,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -11697,7 +11774,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -11725,7 +11802,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -11747,7 +11824,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="552">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -1071,13 +1071,13 @@
     <t xml:space="preserve">Battle pass level 86</t>
   </si>
   <si>
+    <t xml:space="preserve">Claimed Oct 11, in current stock</t>
+  </si>
+  <si>
     <t xml:space="preserve">Battle pass level 87</t>
   </si>
   <si>
     <t xml:space="preserve">Battle pass level 88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claimed Oct 11, in current stock</t>
   </si>
   <si>
     <t xml:space="preserve">Battle pass level 95, premium</t>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>533769203.857946</v>
+        <v>533784657.608701</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7116,7 +7116,7 @@
         <v>18170000</v>
       </c>
       <c r="C5" s="26" t="n">
-        <v>755800</v>
+        <v>1505800</v>
       </c>
       <c r="D5" s="26" t="n">
         <v>4370000</v>
@@ -7131,7 +7131,7 @@
         <v>715</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>1004</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="C6" s="27" t="n">
         <f aca="false">SUMIFS(C13:C67,$I$13:$I$67,"Yes",$J$13:$J$67,"No")</f>
-        <v>4250000</v>
+        <v>3500000</v>
       </c>
       <c r="D6" s="27" t="n">
         <f aca="false">SUMIFS(D13:D67,$I$13:$I$67,"Yes",$J$13:$J$67,"No")</f>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="H6" s="27" t="n">
         <f aca="false">SUMIFS(H13:H67,$I$13:$I$67,"Yes",$J$13:$J$67,"No")</f>
-        <v>990</v>
+        <v>940</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7898,7 +7898,7 @@
         <v>0</v>
       </c>
       <c r="C30" s="30" t="n">
-        <v>750000</v>
+        <v>0</v>
       </c>
       <c r="D30" s="30" t="n">
         <v>0</v>
@@ -7921,11 +7921,13 @@
       <c r="J30" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="K30" s="15"/>
+      <c r="K30" s="15" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B31" s="30" t="n">
         <v>0</v>
@@ -7946,7 +7948,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="30" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I31" s="11" t="s">
         <v>249</v>
@@ -7954,11 +7956,13 @@
       <c r="J31" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="K31" s="15"/>
+      <c r="K31" s="15" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B32" s="30" t="n">
         <v>0</v>
@@ -7988,7 +7992,7 @@
         <v>253</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10610,7 +10614,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>20199817.2122427</v>
+        <v>20200402.0255994</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -1137,7 +1137,7 @@
     <t xml:space="preserve">Level 110 training orb</t>
   </si>
   <si>
-    <t xml:space="preserve">Pending claim. Enter amounts once opened</t>
+    <t xml:space="preserve">Claimed Oct 11: 231 orange, in current stock</t>
   </si>
   <si>
     <t xml:space="preserve">Alliance War, Oct 13 to 14</t>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>533784657.608701</v>
+        <v>533860133.837249</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7131,7 +7131,7 @@
         <v>715</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>1054</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="H7" s="27" t="n">
         <f aca="false">H5+H6</f>
-        <v>1994</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="H9" s="28" t="n">
         <f aca="false">H7-H8</f>
-        <v>1015</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8421,9 +8421,15 @@
       <c r="E45" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
+      <c r="F45" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="I45" s="11" t="s">
         <v>249</v>
       </c>
@@ -10614,7 +10620,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>20200402.0255994</v>
+        <v>20203258.3294727</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="554">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -1186,6 +1186,12 @@
   </si>
   <si>
     <t xml:space="preserve">Expected about Oct 15. Gives 2,000 gold orb fragments, one orb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Misc: 14 basic orbs, Oct 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Received, in current stock</t>
   </si>
   <si>
     <t xml:space="preserve">Gold orbs</t>
@@ -4193,7 +4199,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>533860133.837249</v>
+        <v>534005638.900451</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7061,7 +7067,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -7113,7 +7119,7 @@
         <v>315</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>18170000</v>
+        <v>18181000</v>
       </c>
       <c r="C5" s="26" t="n">
         <v>1505800</v>
@@ -7139,31 +7145,31 @@
         <v>316</v>
       </c>
       <c r="B6" s="27" t="n">
-        <f aca="false">SUMIFS(B13:B67,$I$13:$I$67,"Yes",$J$13:$J$67,"No")</f>
+        <f aca="false">SUMIFS(B13:B68,$I$13:$I$68,"Yes",$J$13:$J$68,"No")</f>
         <v>32500000</v>
       </c>
       <c r="C6" s="27" t="n">
-        <f aca="false">SUMIFS(C13:C67,$I$13:$I$67,"Yes",$J$13:$J$67,"No")</f>
+        <f aca="false">SUMIFS(C13:C68,$I$13:$I$68,"Yes",$J$13:$J$68,"No")</f>
         <v>3500000</v>
       </c>
       <c r="D6" s="27" t="n">
-        <f aca="false">SUMIFS(D13:D67,$I$13:$I$67,"Yes",$J$13:$J$67,"No")</f>
+        <f aca="false">SUMIFS(D13:D68,$I$13:$I$68,"Yes",$J$13:$J$68,"No")</f>
         <v>3136000</v>
       </c>
       <c r="E6" s="27" t="n">
-        <f aca="false">SUMIFS(E13:E67,$I$13:$I$67,"Yes",$J$13:$J$67,"No")</f>
+        <f aca="false">SUMIFS(E13:E68,$I$13:$I$68,"Yes",$J$13:$J$68,"No")</f>
         <v>2736000</v>
       </c>
       <c r="F6" s="27" t="n">
-        <f aca="false">SUMIFS(F13:F67,$I$13:$I$67,"Yes",$J$13:$J$67,"No")</f>
+        <f aca="false">SUMIFS(F13:F68,$I$13:$I$68,"Yes",$J$13:$J$68,"No")</f>
         <v>0</v>
       </c>
       <c r="G6" s="27" t="n">
-        <f aca="false">SUMIFS(G13:G67,$I$13:$I$67,"Yes",$J$13:$J$67,"No")</f>
+        <f aca="false">SUMIFS(G13:G68,$I$13:$I$68,"Yes",$J$13:$J$68,"No")</f>
         <v>100</v>
       </c>
       <c r="H6" s="27" t="n">
-        <f aca="false">SUMIFS(H13:H67,$I$13:$I$67,"Yes",$J$13:$J$67,"No")</f>
+        <f aca="false">SUMIFS(H13:H68,$I$13:$I$68,"Yes",$J$13:$J$68,"No")</f>
         <v>940</v>
       </c>
     </row>
@@ -7173,7 +7179,7 @@
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
-        <v>50670000</v>
+        <v>50681000</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5+C6</f>
@@ -7205,31 +7211,31 @@
         <v>318</v>
       </c>
       <c r="B8" s="27" t="n">
-        <f aca="false">SUMIF($J$71:$J$91,"Planned",B71:B91)</f>
+        <f aca="false">SUMIF($J$72:$J$92,"Planned",B72:B92)</f>
         <v>9791250</v>
       </c>
       <c r="C8" s="27" t="n">
-        <f aca="false">SUMIF($J$71:$J$91,"Planned",C71:C91)</f>
+        <f aca="false">SUMIF($J$72:$J$92,"Planned",C72:C92)</f>
         <v>2070000</v>
       </c>
       <c r="D8" s="27" t="n">
-        <f aca="false">SUMIF($J$71:$J$91,"Planned",D71:D91)</f>
+        <f aca="false">SUMIF($J$72:$J$92,"Planned",D72:D92)</f>
         <v>2640000</v>
       </c>
       <c r="E8" s="27" t="n">
-        <f aca="false">SUMIF($J$71:$J$91,"Planned",E71:E91)</f>
+        <f aca="false">SUMIF($J$72:$J$92,"Planned",E72:E92)</f>
         <v>1710000</v>
       </c>
       <c r="F8" s="27" t="n">
-        <f aca="false">SUMIF($J$71:$J$91,"Planned",F71:F91)</f>
+        <f aca="false">SUMIF($J$72:$J$92,"Planned",F72:F92)</f>
         <v>1</v>
       </c>
       <c r="G8" s="27" t="n">
-        <f aca="false">SUMIF($J$71:$J$91,"Planned",G71:G91)</f>
+        <f aca="false">SUMIF($J$72:$J$92,"Planned",G72:G92)</f>
         <v>0</v>
       </c>
       <c r="H8" s="27" t="n">
-        <f aca="false">SUMIF($J$71:$J$91,"Planned",H71:H91)</f>
+        <f aca="false">SUMIF($J$72:$J$92,"Planned",H72:H92)</f>
         <v>979</v>
       </c>
     </row>
@@ -7239,7 +7245,7 @@
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B7-B8</f>
-        <v>40878750</v>
+        <v>40889750</v>
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">C7-C8</f>
@@ -8830,7 +8836,7 @@
         <v>385</v>
       </c>
       <c r="B57" s="30" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="C57" s="30" t="n">
         <v>0</v>
@@ -8851,27 +8857,49 @@
         <v>0</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K57" s="15" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="12"/>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="11"/>
-      <c r="J58" s="11"/>
-      <c r="K58" s="12"/>
+      <c r="A58" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="B58" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K58" s="15" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12"/>
@@ -8990,123 +9018,103 @@
       <c r="J67" s="11"/>
       <c r="K67" s="12"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="29" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="B70" s="3" t="s">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="12"/>
+      <c r="B68" s="30"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
+      <c r="I68" s="11"/>
+      <c r="J68" s="11"/>
+      <c r="K68" s="12"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="29" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D71" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E71" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="F71" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="G71" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="H70" s="3" t="s">
+      <c r="H71" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="I70" s="3" t="s">
+      <c r="I71" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J70" s="3" t="s">
+      <c r="J71" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K70" s="3" t="s">
+      <c r="K71" s="3" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="B71" s="30" t="n">
-        <v>1837500</v>
-      </c>
-      <c r="C71" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G71" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" s="30" t="n">
-        <v>183</v>
-      </c>
-      <c r="I71" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="K71" s="15" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="B72" s="30" t="n">
+        <v>1837500</v>
+      </c>
+      <c r="C72" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G72" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="30" t="n">
+        <v>183</v>
+      </c>
+      <c r="I72" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="B72" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" s="30" t="n">
-        <v>359800</v>
-      </c>
-      <c r="D72" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="K72" s="15"/>
+      <c r="K72" s="15" t="s">
+        <v>393</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B73" s="30" t="n">
-        <v>9791250</v>
+        <v>0</v>
       </c>
       <c r="C73" s="30" t="n">
-        <v>0</v>
+        <v>359800</v>
       </c>
       <c r="D73" s="30" t="n">
         <v>0</v>
@@ -9115,54 +9123,52 @@
         <v>0</v>
       </c>
       <c r="F73" s="30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" s="30" t="n">
         <v>0</v>
       </c>
       <c r="H73" s="30" t="n">
-        <v>979</v>
+        <v>0</v>
       </c>
       <c r="I73" s="30" t="n">
-        <v>55000000</v>
+        <v>0</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>394</v>
-      </c>
-      <c r="K73" s="15" t="s">
-        <v>395</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="K73" s="15"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="B74" s="30" t="n">
+        <v>9791250</v>
+      </c>
+      <c r="C74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="30" t="n">
+        <v>979</v>
+      </c>
+      <c r="I74" s="30" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="J74" s="11" t="s">
         <v>396</v>
-      </c>
-      <c r="B74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C74" s="30" t="n">
-        <v>360000</v>
-      </c>
-      <c r="D74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="11" t="s">
-        <v>394</v>
       </c>
       <c r="K74" s="15" t="s">
         <v>397</v>
@@ -9172,9 +9178,11 @@
       <c r="A75" s="12" t="s">
         <v>398</v>
       </c>
-      <c r="B75" s="26"/>
+      <c r="B75" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="C75" s="30" t="n">
-        <v>0</v>
+        <v>360000</v>
       </c>
       <c r="D75" s="30" t="n">
         <v>0</v>
@@ -9182,14 +9190,20 @@
       <c r="E75" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F75" s="26"/>
-      <c r="G75" s="26"/>
-      <c r="H75" s="26"/>
+      <c r="F75" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="I75" s="30" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K75" s="15" t="s">
         <v>399</v>
@@ -9216,15 +9230,15 @@
         <v>3000000</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K76" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B77" s="26"/>
       <c r="C77" s="30" t="n">
@@ -9243,15 +9257,15 @@
         <v>3000000</v>
       </c>
       <c r="J77" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K77" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B78" s="26"/>
       <c r="C78" s="30" t="n">
@@ -9270,15 +9284,15 @@
         <v>3000000</v>
       </c>
       <c r="J78" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K78" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B79" s="26"/>
       <c r="C79" s="30" t="n">
@@ -9290,40 +9304,32 @@
       <c r="E79" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F79" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="30" t="n">
-        <v>0</v>
-      </c>
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
+      <c r="H79" s="26"/>
       <c r="I79" s="30" t="n">
-        <v>17000000</v>
+        <v>3000000</v>
       </c>
       <c r="J79" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>404</v>
-      </c>
-      <c r="B80" s="30" t="n">
-        <v>0</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="B80" s="26"/>
       <c r="C80" s="30" t="n">
-        <v>1710000</v>
+        <v>0</v>
       </c>
       <c r="D80" s="30" t="n">
-        <v>2640000</v>
+        <v>0</v>
       </c>
       <c r="E80" s="30" t="n">
-        <v>1710000</v>
+        <v>0</v>
       </c>
       <c r="F80" s="30" t="n">
         <v>0</v>
@@ -9338,10 +9344,10 @@
         <v>17000000</v>
       </c>
       <c r="J80" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K80" s="15" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9351,9 +9357,15 @@
       <c r="B81" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C81" s="26"/>
-      <c r="D81" s="26"/>
-      <c r="E81" s="26"/>
+      <c r="C81" s="30" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="D81" s="30" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="E81" s="30" t="n">
+        <v>1710000</v>
+      </c>
       <c r="F81" s="30" t="n">
         <v>0</v>
       </c>
@@ -9367,15 +9379,15 @@
         <v>17000000</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B82" s="30" t="n">
         <v>0</v>
@@ -9396,10 +9408,10 @@
         <v>17000000</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="K82" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9425,15 +9437,15 @@
         <v>17000000</v>
       </c>
       <c r="J83" s="11" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K83" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B84" s="30" t="n">
         <v>0</v>
@@ -9454,53 +9466,69 @@
         <v>17000000</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K84" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B85" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="26"/>
+      <c r="D85" s="26"/>
+      <c r="E85" s="26"/>
+      <c r="F85" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J85" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="K85" s="15" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="B86" s="30" t="n">
         <v>13000000</v>
       </c>
-      <c r="C85" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="26"/>
-      <c r="G85" s="26"/>
-      <c r="H85" s="26"/>
-      <c r="I85" s="30" t="n">
+      <c r="C86" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="26"/>
+      <c r="G86" s="26"/>
+      <c r="H86" s="26"/>
+      <c r="I86" s="30" t="n">
         <v>8000000</v>
       </c>
-      <c r="J85" s="11" t="s">
-        <v>408</v>
-      </c>
-      <c r="K85" s="15" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="12"/>
-      <c r="B86" s="30"/>
-      <c r="C86" s="30"/>
-      <c r="D86" s="30"/>
-      <c r="E86" s="30"/>
-      <c r="F86" s="30"/>
-      <c r="G86" s="30"/>
-      <c r="H86" s="30"/>
-      <c r="I86" s="30"/>
-      <c r="J86" s="11"/>
-      <c r="K86" s="12"/>
+      <c r="J86" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="K86" s="15" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12"/>
@@ -9567,12 +9595,25 @@
       <c r="J91" s="11"/>
       <c r="K91" s="12"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="16" t="s">
-        <v>413</v>
-      </c>
-      <c r="I93" s="20" t="n">
-        <f aca="false">SUMIF(J71:J91,"Planned",I71:I91)</f>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="12"/>
+      <c r="B92" s="30"/>
+      <c r="C92" s="30"/>
+      <c r="D92" s="30"/>
+      <c r="E92" s="30"/>
+      <c r="F92" s="30"/>
+      <c r="G92" s="30"/>
+      <c r="H92" s="30"/>
+      <c r="I92" s="30"/>
+      <c r="J92" s="11"/>
+      <c r="K92" s="12"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="I94" s="20" t="n">
+        <f aca="false">SUMIF(J72:J92,"Planned",I72:I92)</f>
         <v>118000000</v>
       </c>
     </row>
@@ -9582,22 +9623,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J71:J91">
+  <conditionalFormatting sqref="J72:J92">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J13:J67">
+  <conditionalFormatting sqref="J13:J68">
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13:J67" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13:J68" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J71:J91" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J72:J92" type="list">
       <formula1>"Planned,Done,Skipped"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9628,12 +9669,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9647,53 +9688,53 @@
         <v>308</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -9705,19 +9746,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>429</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>427</v>
       </c>
       <c r="C7" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -9729,19 +9770,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -9753,19 +9794,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -9777,19 +9818,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -9801,19 +9842,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -9825,19 +9866,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -9849,19 +9890,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -9873,19 +9914,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -9897,19 +9938,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -9921,19 +9962,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -9945,16 +9986,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -9967,19 +10008,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
+        <v>450</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>448</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>446</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -9991,19 +10032,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -10015,19 +10056,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -10039,24 +10080,24 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -10068,16 +10109,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>458</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>456</v>
-      </c>
       <c r="C23" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -10090,16 +10131,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
+        <v>461</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="C24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="15" t="s">
         <v>459</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>456</v>
-      </c>
-      <c r="C24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>457</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -10112,19 +10153,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -10136,19 +10177,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
+        <v>465</v>
+      </c>
+      <c r="B26" s="13" t="s">
         <v>463</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>461</v>
-      </c>
       <c r="C26" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -10160,16 +10201,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -10182,16 +10223,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C28" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -10204,21 +10245,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -10231,16 +10272,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="B31" s="13" t="s">
         <v>475</v>
       </c>
-      <c r="B31" s="13" t="s">
-        <v>473</v>
-      </c>
       <c r="C31" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -10253,16 +10294,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C32" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -10275,19 +10316,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C33" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
@@ -10299,16 +10340,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
+        <v>484</v>
+      </c>
+      <c r="B34" s="13" t="s">
         <v>482</v>
       </c>
-      <c r="B34" s="13" t="s">
-        <v>480</v>
-      </c>
       <c r="C34" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -10321,16 +10362,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C35" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -10343,16 +10384,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C36" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -10365,16 +10406,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -10387,7 +10428,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E39" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$37)*(E5:E37="Done"))</f>
@@ -10424,7 +10465,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E40" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$37,"Required",E5:E37,"Done")&amp;" of 11"</f>
@@ -10461,7 +10502,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -10505,12 +10546,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10518,10 +10559,10 @@
         <v>155</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10532,13 +10573,13 @@
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10549,7 +10590,7 @@
         <v>285572765</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -10599,7 +10640,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -10607,7 +10648,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -10616,11 +10657,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>20203258.3294727</v>
+        <v>20208764.7798293</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10631,19 +10672,19 @@
         <v>168</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
@@ -10659,7 +10700,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -10685,7 +10726,7 @@
       <c r="B14" s="26"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -10711,7 +10752,7 @@
       <c r="B15" s="26"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -10737,7 +10778,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -10762,10 +10803,10 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="12" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -10790,10 +10831,10 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="12" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -10818,10 +10859,10 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="12" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -10846,10 +10887,10 @@
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="12" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -10874,10 +10915,10 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="12" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -10902,10 +10943,10 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="12" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -10931,7 +10972,7 @@
       <c r="B23" s="26"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -10956,10 +10997,10 @@
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="12" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -10984,10 +11025,10 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="12" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -11012,10 +11053,10 @@
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="D26" s="12" t="s">
         <v>523</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>521</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -11043,7 +11084,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -11070,10 +11111,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -11100,10 +11141,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -11130,10 +11171,10 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
@@ -11154,10 +11195,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -11184,7 +11225,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -11212,10 +11253,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -11242,7 +11283,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -11270,10 +11311,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -11300,7 +11341,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -11328,10 +11369,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -11358,7 +11399,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -11386,10 +11427,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -11416,7 +11457,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -11444,10 +11485,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -11474,7 +11515,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -11502,10 +11543,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -11532,7 +11573,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -11560,7 +11601,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -11588,7 +11629,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -11616,7 +11657,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -11644,7 +11685,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -11672,7 +11713,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -11700,7 +11741,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -11728,7 +11769,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -11756,7 +11797,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -11784,7 +11825,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -11812,7 +11853,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -11834,7 +11875,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -1188,10 +1188,10 @@
     <t xml:space="preserve">Expected about Oct 15. Gives 2,000 gold orb fragments, one orb</t>
   </si>
   <si>
-    <t xml:space="preserve">Misc: 14 basic orbs, Oct 11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Received, in current stock</t>
+    <t xml:space="preserve">Misc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Running total of random drops and other small sources. Already in current stock</t>
   </si>
   <si>
     <t xml:space="preserve">Gold orbs</t>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>534005638.900451</v>
+        <v>534146027.097991</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>20208764.7798293</v>
+        <v>20214077.5935729</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="556">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -1186,6 +1186,12 @@
   </si>
   <si>
     <t xml:space="preserve">Expected about Oct 15. Gives 2,000 gold orb fragments, one orb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign missions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Running total. Fixed rewards per mission. Already in current stock</t>
   </si>
   <si>
     <t xml:space="preserve">Misc</t>
@@ -4199,7 +4205,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>534146027.097991</v>
+        <v>534245313.467777</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7067,7 +7073,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -7119,7 +7125,7 @@
         <v>315</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>18181000</v>
+        <v>18225475</v>
       </c>
       <c r="C5" s="26" t="n">
         <v>1505800</v>
@@ -7131,10 +7137,10 @@
         <v>14390000</v>
       </c>
       <c r="F5" s="26" t="n">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>715</v>
+        <v>735</v>
       </c>
       <c r="H5" s="26" t="n">
         <v>1285</v>
@@ -7145,31 +7151,31 @@
         <v>316</v>
       </c>
       <c r="B6" s="27" t="n">
-        <f aca="false">SUMIFS(B13:B68,$I$13:$I$68,"Yes",$J$13:$J$68,"No")</f>
+        <f aca="false">SUMIFS(B13:B69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
         <v>32500000</v>
       </c>
       <c r="C6" s="27" t="n">
-        <f aca="false">SUMIFS(C13:C68,$I$13:$I$68,"Yes",$J$13:$J$68,"No")</f>
+        <f aca="false">SUMIFS(C13:C69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
         <v>3500000</v>
       </c>
       <c r="D6" s="27" t="n">
-        <f aca="false">SUMIFS(D13:D68,$I$13:$I$68,"Yes",$J$13:$J$68,"No")</f>
+        <f aca="false">SUMIFS(D13:D69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
         <v>3136000</v>
       </c>
       <c r="E6" s="27" t="n">
-        <f aca="false">SUMIFS(E13:E68,$I$13:$I$68,"Yes",$J$13:$J$68,"No")</f>
+        <f aca="false">SUMIFS(E13:E69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
         <v>2736000</v>
       </c>
       <c r="F6" s="27" t="n">
-        <f aca="false">SUMIFS(F13:F68,$I$13:$I$68,"Yes",$J$13:$J$68,"No")</f>
+        <f aca="false">SUMIFS(F13:F69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
         <v>0</v>
       </c>
       <c r="G6" s="27" t="n">
-        <f aca="false">SUMIFS(G13:G68,$I$13:$I$68,"Yes",$J$13:$J$68,"No")</f>
+        <f aca="false">SUMIFS(G13:G69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
         <v>100</v>
       </c>
       <c r="H6" s="27" t="n">
-        <f aca="false">SUMIFS(H13:H68,$I$13:$I$68,"Yes",$J$13:$J$68,"No")</f>
+        <f aca="false">SUMIFS(H13:H69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
         <v>940</v>
       </c>
     </row>
@@ -7179,7 +7185,7 @@
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
-        <v>50681000</v>
+        <v>50725475</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5+C6</f>
@@ -7195,11 +7201,11 @@
       </c>
       <c r="F7" s="27" t="n">
         <f aca="false">F5+F6</f>
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="G7" s="27" t="n">
         <f aca="false">G5+G6</f>
-        <v>815</v>
+        <v>835</v>
       </c>
       <c r="H7" s="27" t="n">
         <f aca="false">H5+H6</f>
@@ -7211,31 +7217,31 @@
         <v>318</v>
       </c>
       <c r="B8" s="27" t="n">
-        <f aca="false">SUMIF($J$72:$J$92,"Planned",B72:B92)</f>
+        <f aca="false">SUMIF($J$73:$J$93,"Planned",B73:B93)</f>
         <v>9791250</v>
       </c>
       <c r="C8" s="27" t="n">
-        <f aca="false">SUMIF($J$72:$J$92,"Planned",C72:C92)</f>
+        <f aca="false">SUMIF($J$73:$J$93,"Planned",C73:C93)</f>
         <v>2070000</v>
       </c>
       <c r="D8" s="27" t="n">
-        <f aca="false">SUMIF($J$72:$J$92,"Planned",D72:D92)</f>
+        <f aca="false">SUMIF($J$73:$J$93,"Planned",D73:D93)</f>
         <v>2640000</v>
       </c>
       <c r="E8" s="27" t="n">
-        <f aca="false">SUMIF($J$72:$J$92,"Planned",E72:E92)</f>
+        <f aca="false">SUMIF($J$73:$J$93,"Planned",E73:E93)</f>
         <v>1710000</v>
       </c>
       <c r="F8" s="27" t="n">
-        <f aca="false">SUMIF($J$72:$J$92,"Planned",F72:F92)</f>
+        <f aca="false">SUMIF($J$73:$J$93,"Planned",F73:F93)</f>
         <v>1</v>
       </c>
       <c r="G8" s="27" t="n">
-        <f aca="false">SUMIF($J$72:$J$92,"Planned",G72:G92)</f>
+        <f aca="false">SUMIF($J$73:$J$93,"Planned",G73:G93)</f>
         <v>0</v>
       </c>
       <c r="H8" s="27" t="n">
-        <f aca="false">SUMIF($J$72:$J$92,"Planned",H72:H92)</f>
+        <f aca="false">SUMIF($J$73:$J$93,"Planned",H73:H93)</f>
         <v>979</v>
       </c>
     </row>
@@ -7245,7 +7251,7 @@
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B7-B8</f>
-        <v>40889750</v>
+        <v>40934225</v>
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">C7-C8</f>
@@ -7261,11 +7267,11 @@
       </c>
       <c r="F9" s="28" t="n">
         <f aca="false">F7-F8</f>
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="G9" s="28" t="n">
         <f aca="false">G7-G8</f>
-        <v>815</v>
+        <v>835</v>
       </c>
       <c r="H9" s="28" t="n">
         <f aca="false">H7-H8</f>
@@ -8836,7 +8842,7 @@
         <v>385</v>
       </c>
       <c r="B57" s="30" t="n">
-        <v>11000</v>
+        <v>44475</v>
       </c>
       <c r="C57" s="30" t="n">
         <v>0</v>
@@ -8848,10 +8854,10 @@
         <v>0</v>
       </c>
       <c r="F57" s="30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G57" s="30" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H57" s="30" t="n">
         <v>0</v>
@@ -8871,7 +8877,7 @@
         <v>387</v>
       </c>
       <c r="B58" s="30" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="C58" s="30" t="n">
         <v>0</v>
@@ -8892,27 +8898,49 @@
         <v>0</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K58" s="15" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="12"/>
-      <c r="B59" s="30"/>
-      <c r="C59" s="30"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="30"/>
-      <c r="H59" s="30"/>
-      <c r="I59" s="11"/>
-      <c r="J59" s="11"/>
-      <c r="K59" s="12"/>
+      <c r="A59" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="B59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K59" s="15" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12"/>
@@ -9031,123 +9059,103 @@
       <c r="J68" s="11"/>
       <c r="K68" s="12"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="29" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="B71" s="3" t="s">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="12"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
+      <c r="K69" s="12"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="29" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D72" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="F72" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="G72" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="H71" s="3" t="s">
+      <c r="H72" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="I71" s="3" t="s">
+      <c r="I72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J71" s="3" t="s">
+      <c r="J72" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K71" s="3" t="s">
+      <c r="K72" s="3" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="B72" s="30" t="n">
-        <v>1837500</v>
-      </c>
-      <c r="C72" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G72" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72" s="30" t="n">
-        <v>183</v>
-      </c>
-      <c r="I72" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="11" t="s">
-        <v>392</v>
-      </c>
-      <c r="K72" s="15" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="B73" s="30" t="n">
+        <v>1837500</v>
+      </c>
+      <c r="C73" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="30" t="n">
+        <v>183</v>
+      </c>
+      <c r="I73" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="B73" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C73" s="30" t="n">
-        <v>359800</v>
-      </c>
-      <c r="D73" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="11" t="s">
-        <v>392</v>
-      </c>
-      <c r="K73" s="15"/>
+      <c r="K73" s="15" t="s">
+        <v>395</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B74" s="30" t="n">
-        <v>9791250</v>
+        <v>0</v>
       </c>
       <c r="C74" s="30" t="n">
-        <v>0</v>
+        <v>359800</v>
       </c>
       <c r="D74" s="30" t="n">
         <v>0</v>
@@ -9156,54 +9164,52 @@
         <v>0</v>
       </c>
       <c r="F74" s="30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" s="30" t="n">
         <v>0</v>
       </c>
       <c r="H74" s="30" t="n">
-        <v>979</v>
+        <v>0</v>
       </c>
       <c r="I74" s="30" t="n">
-        <v>55000000</v>
+        <v>0</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>396</v>
-      </c>
-      <c r="K74" s="15" t="s">
-        <v>397</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="K74" s="15"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="B75" s="30" t="n">
+        <v>9791250</v>
+      </c>
+      <c r="C75" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="30" t="n">
+        <v>979</v>
+      </c>
+      <c r="I75" s="30" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="J75" s="11" t="s">
         <v>398</v>
-      </c>
-      <c r="B75" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C75" s="30" t="n">
-        <v>360000</v>
-      </c>
-      <c r="D75" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="11" t="s">
-        <v>396</v>
       </c>
       <c r="K75" s="15" t="s">
         <v>399</v>
@@ -9213,9 +9219,11 @@
       <c r="A76" s="12" t="s">
         <v>400</v>
       </c>
-      <c r="B76" s="26"/>
+      <c r="B76" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="C76" s="30" t="n">
-        <v>0</v>
+        <v>360000</v>
       </c>
       <c r="D76" s="30" t="n">
         <v>0</v>
@@ -9223,14 +9231,20 @@
       <c r="E76" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F76" s="26"/>
-      <c r="G76" s="26"/>
-      <c r="H76" s="26"/>
+      <c r="F76" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="I76" s="30" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K76" s="15" t="s">
         <v>401</v>
@@ -9257,15 +9271,15 @@
         <v>3000000</v>
       </c>
       <c r="J77" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K77" s="15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B78" s="26"/>
       <c r="C78" s="30" t="n">
@@ -9284,15 +9298,15 @@
         <v>3000000</v>
       </c>
       <c r="J78" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K78" s="15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B79" s="26"/>
       <c r="C79" s="30" t="n">
@@ -9311,15 +9325,15 @@
         <v>3000000</v>
       </c>
       <c r="J79" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B80" s="26"/>
       <c r="C80" s="30" t="n">
@@ -9331,40 +9345,32 @@
       <c r="E80" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F80" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="30" t="n">
-        <v>0</v>
-      </c>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
       <c r="I80" s="30" t="n">
-        <v>17000000</v>
+        <v>3000000</v>
       </c>
       <c r="J80" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K80" s="15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="B81" s="30" t="n">
-        <v>0</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="B81" s="26"/>
       <c r="C81" s="30" t="n">
-        <v>1710000</v>
+        <v>0</v>
       </c>
       <c r="D81" s="30" t="n">
-        <v>2640000</v>
+        <v>0</v>
       </c>
       <c r="E81" s="30" t="n">
-        <v>1710000</v>
+        <v>0</v>
       </c>
       <c r="F81" s="30" t="n">
         <v>0</v>
@@ -9379,10 +9385,10 @@
         <v>17000000</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9392,9 +9398,15 @@
       <c r="B82" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C82" s="26"/>
-      <c r="D82" s="26"/>
-      <c r="E82" s="26"/>
+      <c r="C82" s="30" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="D82" s="30" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="E82" s="30" t="n">
+        <v>1710000</v>
+      </c>
       <c r="F82" s="30" t="n">
         <v>0</v>
       </c>
@@ -9408,15 +9420,15 @@
         <v>17000000</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K82" s="15" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B83" s="30" t="n">
         <v>0</v>
@@ -9437,10 +9449,10 @@
         <v>17000000</v>
       </c>
       <c r="J83" s="11" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="K83" s="15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9466,15 +9478,15 @@
         <v>17000000</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K84" s="15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B85" s="30" t="n">
         <v>0</v>
@@ -9495,53 +9507,69 @@
         <v>17000000</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K85" s="15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B86" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="26"/>
+      <c r="D86" s="26"/>
+      <c r="E86" s="26"/>
+      <c r="F86" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J86" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="K86" s="15" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="B87" s="30" t="n">
         <v>13000000</v>
       </c>
-      <c r="C86" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="26"/>
-      <c r="G86" s="26"/>
-      <c r="H86" s="26"/>
-      <c r="I86" s="30" t="n">
+      <c r="C87" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="26"/>
+      <c r="G87" s="26"/>
+      <c r="H87" s="26"/>
+      <c r="I87" s="30" t="n">
         <v>8000000</v>
       </c>
-      <c r="J86" s="11" t="s">
-        <v>410</v>
-      </c>
-      <c r="K86" s="15" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="12"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="30"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="30"/>
-      <c r="F87" s="30"/>
-      <c r="G87" s="30"/>
-      <c r="H87" s="30"/>
-      <c r="I87" s="30"/>
-      <c r="J87" s="11"/>
-      <c r="K87" s="12"/>
+      <c r="J87" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="K87" s="15" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="12"/>
@@ -9608,12 +9636,25 @@
       <c r="J92" s="11"/>
       <c r="K92" s="12"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="16" t="s">
-        <v>415</v>
-      </c>
-      <c r="I94" s="20" t="n">
-        <f aca="false">SUMIF(J72:J92,"Planned",I72:I92)</f>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="12"/>
+      <c r="B93" s="30"/>
+      <c r="C93" s="30"/>
+      <c r="D93" s="30"/>
+      <c r="E93" s="30"/>
+      <c r="F93" s="30"/>
+      <c r="G93" s="30"/>
+      <c r="H93" s="30"/>
+      <c r="I93" s="30"/>
+      <c r="J93" s="11"/>
+      <c r="K93" s="12"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="I95" s="20" t="n">
+        <f aca="false">SUMIF(J73:J93,"Planned",I73:I93)</f>
         <v>118000000</v>
       </c>
     </row>
@@ -9623,22 +9664,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J72:J92">
+  <conditionalFormatting sqref="J73:J93">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J13:J68">
+  <conditionalFormatting sqref="J13:J69">
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13:J68" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13:J69" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J72:J92" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J73:J93" type="list">
       <formula1>"Planned,Done,Skipped"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9669,12 +9710,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9688,53 +9729,53 @@
         <v>308</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -9746,19 +9787,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>431</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>429</v>
       </c>
       <c r="C7" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -9770,19 +9811,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -9794,19 +9835,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -9818,19 +9859,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -9842,19 +9883,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -9866,19 +9907,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -9890,19 +9931,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -9914,19 +9955,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -9938,19 +9979,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -9962,19 +10003,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -9986,16 +10027,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -10008,19 +10049,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
+        <v>452</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>450</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>448</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -10032,19 +10073,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -10056,19 +10097,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -10080,24 +10121,24 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -10109,16 +10150,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>458</v>
-      </c>
       <c r="C23" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -10131,16 +10172,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="C24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="15" t="s">
         <v>461</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>458</v>
-      </c>
-      <c r="C24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>459</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -10153,19 +10194,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -10177,19 +10218,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="B26" s="13" t="s">
         <v>465</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>463</v>
-      </c>
       <c r="C26" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -10201,16 +10242,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -10223,16 +10264,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C28" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -10245,21 +10286,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -10272,16 +10313,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="B31" s="13" t="s">
         <v>477</v>
       </c>
-      <c r="B31" s="13" t="s">
-        <v>475</v>
-      </c>
       <c r="C31" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -10294,16 +10335,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C32" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -10316,19 +10357,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C33" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
@@ -10340,16 +10381,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="B34" s="13" t="s">
         <v>484</v>
       </c>
-      <c r="B34" s="13" t="s">
-        <v>482</v>
-      </c>
       <c r="C34" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -10362,16 +10403,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C35" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -10384,16 +10425,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C36" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -10406,16 +10447,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -10428,7 +10469,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E39" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$37)*(E5:E37="Done"))</f>
@@ -10465,7 +10506,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E40" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$37,"Required",E5:E37,"Done")&amp;" of 11"</f>
@@ -10502,7 +10543,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
@@ -10546,12 +10587,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10559,10 +10600,10 @@
         <v>155</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10573,13 +10614,13 @@
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10590,7 +10631,7 @@
         <v>285572765</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -10640,7 +10681,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -10648,7 +10689,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -10657,11 +10698,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>20214077.5935729</v>
+        <v>20217834.9610904</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10672,19 +10713,19 @@
         <v>168</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
@@ -10700,7 +10741,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -10726,7 +10767,7 @@
       <c r="B14" s="26"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -10752,7 +10793,7 @@
       <c r="B15" s="26"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -10778,7 +10819,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -10803,10 +10844,10 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="12" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -10831,10 +10872,10 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="12" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -10859,10 +10900,10 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="12" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -10887,10 +10928,10 @@
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="12" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -10915,10 +10956,10 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="12" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -10943,10 +10984,10 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="12" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -10972,7 +11013,7 @@
       <c r="B23" s="26"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -10997,10 +11038,10 @@
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="12" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -11025,10 +11066,10 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="12" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -11053,10 +11094,10 @@
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="12" t="s">
+        <v>527</v>
+      </c>
+      <c r="D26" s="12" t="s">
         <v>525</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>523</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -11084,7 +11125,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -11111,10 +11152,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -11141,10 +11182,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -11171,10 +11212,10 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
@@ -11195,10 +11236,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -11225,7 +11266,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -11253,10 +11294,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -11283,7 +11324,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -11311,10 +11352,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -11341,7 +11382,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -11369,10 +11410,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -11399,7 +11440,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -11427,10 +11468,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -11457,7 +11498,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -11485,10 +11526,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -11515,7 +11556,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -11543,10 +11584,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -11573,7 +11614,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -11601,7 +11642,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -11629,7 +11670,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -11657,7 +11698,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -11685,7 +11726,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -11713,7 +11754,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -11741,7 +11782,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -11769,7 +11810,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -11797,7 +11838,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -11825,7 +11866,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -11853,7 +11894,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -11875,7 +11916,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="553">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -144,19 +144,13 @@
     <t xml:space="preserve">Crossbones</t>
   </si>
   <si>
-    <t xml:space="preserve">T1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fifth Iron Raider, needed for a full team</t>
   </si>
   <si>
     <t xml:space="preserve">Level up, abilities, Iso-8 to T3 L3 for raids</t>
   </si>
   <si>
-    <t xml:space="preserve">Lots of gold and training</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goal: gear tier 20 for Omega. Biggest project of the five</t>
+    <t xml:space="preserve">Gear and abilities</t>
   </si>
   <si>
     <t xml:space="preserve">Hulk</t>
@@ -1227,19 +1221,16 @@
     <t xml:space="preserve">Crossbones to level 85</t>
   </si>
   <si>
+    <t xml:space="preserve">Done Oct 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crossbones Iso-8 to T3 level 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doctor Strange to level 101</t>
+  </si>
+  <si>
     <t xml:space="preserve">Planned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unlocks T3 Iso-8 and his raid tasks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crossbones Iso-8 to T3 level 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate based on Iron Monger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doctor Strange to level 101</t>
   </si>
   <si>
     <t xml:space="preserve">Check cost in game</t>
@@ -2626,31 +2617,31 @@
         <v>15</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>7</v>
       </c>
       <c r="F9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="I9" s="8" t="n">
         <v>15000000</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2658,35 +2649,35 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="I10" s="8" t="n">
         <v>17000000</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2694,33 +2685,33 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>17000000</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2728,35 +2719,35 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>105</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="I12" s="8" t="n">
         <v>17000000</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2764,33 +2755,33 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="I13" s="8" t="n">
         <v>17000000</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2798,33 +2789,33 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="I14" s="8" t="n">
         <v>17000000</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2832,17 +2823,17 @@
         <v>11</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I15" s="8" t="n">
         <v>0</v>
@@ -2852,7 +2843,7 @@
         <v>25</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2860,10 +2851,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>100</v>
@@ -2871,10 +2862,10 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I16" s="8" t="n">
         <v>3000000</v>
@@ -2886,7 +2877,7 @@
         <v>25</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2894,21 +2885,21 @@
         <v>13</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>80</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I17" s="8" t="n">
         <v>0</v>
@@ -2918,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2926,10 +2917,10 @@
         <v>13</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>60</v>
@@ -2938,7 +2929,7 @@
       <c r="F18" s="4"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I18" s="8" t="n">
         <v>0</v>
@@ -2954,21 +2945,21 @@
         <v>13</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>105</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I19" s="8" t="n">
         <v>0</v>
@@ -2984,21 +2975,21 @@
         <v>13</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>105</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>0</v>
@@ -3008,7 +2999,7 @@
         <v>25</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3088,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -3148,12 +3139,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3164,22 +3155,22 @@
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>13</v>
@@ -3187,7 +3178,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>105</v>
@@ -3196,13 +3187,13 @@
         <v>1739574</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
@@ -3210,7 +3201,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>105</v>
@@ -3219,10 +3210,10 @@
         <v>1702227</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="11"/>
@@ -3231,7 +3222,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>105</v>
@@ -3240,10 +3231,10 @@
         <v>1663516</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="11"/>
@@ -3252,7 +3243,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>105</v>
@@ -3261,23 +3252,23 @@
         <v>1649971</v>
       </c>
       <c r="D8" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>94</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>96</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
       <c r="I8" s="15" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>105</v>
@@ -3286,10 +3277,10 @@
         <v>1461088</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="11"/>
@@ -3298,7 +3289,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>100</v>
@@ -3307,10 +3298,10 @@
         <v>1401716</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="11"/>
@@ -3319,7 +3310,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>100</v>
@@ -3328,10 +3319,10 @@
         <v>1341960</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="11"/>
@@ -3340,7 +3331,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>105</v>
@@ -3349,10 +3340,10 @@
         <v>1322529</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="11"/>
@@ -3361,7 +3352,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>105</v>
@@ -3370,10 +3361,10 @@
         <v>1238262</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="11"/>
@@ -3382,7 +3373,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B14" s="12" t="n">
         <v>105</v>
@@ -3391,10 +3382,10 @@
         <v>1095153</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="11"/>
@@ -3403,7 +3394,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>103</v>
@@ -3412,10 +3403,10 @@
         <v>1062491</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F15" s="13"/>
       <c r="G15" s="11"/>
@@ -3424,7 +3415,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B16" s="12" t="n">
         <v>105</v>
@@ -3433,10 +3424,10 @@
         <v>1039168</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F16" s="13"/>
       <c r="G16" s="11"/>
@@ -3445,7 +3436,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B17" s="12" t="n">
         <v>104</v>
@@ -3454,10 +3445,10 @@
         <v>993737</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F17" s="13"/>
       <c r="G17" s="11"/>
@@ -3466,7 +3457,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B18" s="12" t="n">
         <v>100</v>
@@ -3475,10 +3466,10 @@
         <v>946060</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="11"/>
@@ -3487,7 +3478,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B19" s="12" t="n">
         <v>105</v>
@@ -3496,10 +3487,10 @@
         <v>900021</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="11"/>
@@ -3508,7 +3499,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B20" s="12" t="n">
         <v>100</v>
@@ -3517,10 +3508,10 @@
         <v>889970</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F20" s="13"/>
       <c r="G20" s="11"/>
@@ -3529,7 +3520,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B21" s="12" t="n">
         <v>100</v>
@@ -3538,10 +3529,10 @@
         <v>867448</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F21" s="13"/>
       <c r="G21" s="11"/>
@@ -3550,7 +3541,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B22" s="12" t="n">
         <v>100</v>
@@ -3559,10 +3550,10 @@
         <v>847430</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F22" s="13"/>
       <c r="G22" s="11"/>
@@ -3580,10 +3571,10 @@
         <v>827833</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>15</v>
@@ -3591,12 +3582,12 @@
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="15" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B24" s="12" t="n">
         <v>101</v>
@@ -3605,10 +3596,10 @@
         <v>818549</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F24" s="13"/>
       <c r="G24" s="11"/>
@@ -3617,7 +3608,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>103</v>
@@ -3626,10 +3617,10 @@
         <v>787184</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F25" s="13"/>
       <c r="G25" s="11"/>
@@ -3638,7 +3629,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>96</v>
@@ -3647,10 +3638,10 @@
         <v>736328</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F26" s="13"/>
       <c r="G26" s="11"/>
@@ -3668,10 +3659,10 @@
         <v>731016</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>15</v>
@@ -3679,12 +3670,12 @@
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="15" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>95</v>
@@ -3693,10 +3684,10 @@
         <v>573611</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F28" s="13"/>
       <c r="G28" s="11"/>
@@ -3705,7 +3696,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B29" s="12" t="n">
         <v>100</v>
@@ -3714,10 +3705,10 @@
         <v>556594</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F29" s="13"/>
       <c r="G29" s="11"/>
@@ -3726,7 +3717,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>95</v>
@@ -3735,10 +3726,10 @@
         <v>427837</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F30" s="13"/>
       <c r="G30" s="11"/>
@@ -3747,7 +3738,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B31" s="12" t="n">
         <v>90</v>
@@ -3756,10 +3747,10 @@
         <v>334475</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F31" s="13"/>
       <c r="G31" s="11"/>
@@ -3768,7 +3759,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B32" s="12" t="n">
         <v>95</v>
@@ -3777,10 +3768,10 @@
         <v>309062</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F32" s="13"/>
       <c r="G32" s="11"/>
@@ -3789,7 +3780,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B33" s="12" t="n">
         <v>90</v>
@@ -3798,10 +3789,10 @@
         <v>305523</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F33" s="13"/>
       <c r="G33" s="11"/>
@@ -3810,7 +3801,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B34" s="12" t="n">
         <v>95</v>
@@ -3819,10 +3810,10 @@
         <v>302615</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F34" s="13"/>
       <c r="G34" s="11"/>
@@ -3831,7 +3822,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B35" s="12" t="n">
         <v>90</v>
@@ -3840,10 +3831,10 @@
         <v>269160</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F35" s="13"/>
       <c r="G35" s="11"/>
@@ -3852,7 +3843,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B36" s="12" t="n">
         <v>80</v>
@@ -3861,10 +3852,10 @@
         <v>250273</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F36" s="13"/>
       <c r="G36" s="11"/>
@@ -3873,7 +3864,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B37" s="12" t="n">
         <v>90</v>
@@ -3882,10 +3873,10 @@
         <v>245993</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F37" s="13"/>
       <c r="G37" s="11"/>
@@ -3894,7 +3885,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B38" s="12" t="n">
         <v>75</v>
@@ -3903,10 +3894,10 @@
         <v>228686</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F38" s="13"/>
       <c r="G38" s="11"/>
@@ -3915,7 +3906,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B39" s="12" t="n">
         <v>75</v>
@@ -3924,10 +3915,10 @@
         <v>144778</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F39" s="13"/>
       <c r="G39" s="11"/>
@@ -3945,10 +3936,10 @@
         <v>33212</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F40" s="13" t="s">
         <v>15</v>
@@ -3956,7 +3947,7 @@
       <c r="G40" s="11"/>
       <c r="H40" s="11"/>
       <c r="I40" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3970,10 +3961,10 @@
         <v>32994</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F41" s="13" t="s">
         <v>15</v>
@@ -3993,10 +3984,10 @@
         <v>26827</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F42" s="13" t="s">
         <v>15</v>
@@ -4004,36 +3995,36 @@
       <c r="G42" s="11"/>
       <c r="H42" s="11"/>
       <c r="I42" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B43" s="12"/>
       <c r="C43" s="14"/>
       <c r="D43" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E43" s="12"/>
       <c r="F43" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G43" s="11"/>
       <c r="H43" s="11"/>
       <c r="I43" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B44" s="12"/>
       <c r="C44" s="14"/>
       <c r="D44" s="12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E44" s="12"/>
       <c r="F44" s="13"/>
@@ -4043,7 +4034,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B46" s="17" t="n">
         <f aca="false">COUNT(C5:C44)</f>
@@ -4052,7 +4043,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B47" s="17" t="n">
         <f aca="false">COUNTIF(C5:C44,"&gt;=1000000")</f>
@@ -4061,7 +4052,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B48" s="17" t="n">
         <f aca="false">COUNTIF(H5:H44,"Yes")</f>
@@ -4110,25 +4101,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>46313.7083333333</v>
@@ -4136,13 +4127,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B6" s="19" t="n">
         <v>440711000</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">B6+Scoring!F51</f>
@@ -4151,14 +4142,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6))+SUMPRODUCT((B13:B76="")*(F13:F76="Claimed"))</f>
         <v>38</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E7" s="16" t="n">
         <f aca="false">IFERROR(INDEX(A13:A76,MATCH(E6,B13:B76,1)),37)</f>
@@ -4167,14 +4158,14 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B8" s="16" t="n">
         <f aca="false">IFERROR(INDEX(A13:A76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),"All done")</f>
         <v>39</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E8" s="16" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6)*(F13:F76&lt;&gt;"Claimed"))</f>
@@ -4183,7 +4174,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B9" s="20" t="n">
         <f aca="false">IFERROR(INDEX(E13:E76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),0)</f>
@@ -4192,7 +4183,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,B76-B6)</f>
@@ -4201,28 +4192,28 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>534245313.467777</v>
+        <v>534300731.429624</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" s="21" t="s">
         <v>167</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>169</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>12</v>
@@ -4234,7 +4225,7 @@
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="23" t="str">
@@ -4242,7 +4233,7 @@
         <v/>
       </c>
       <c r="F13" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4251,7 +4242,7 @@
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="23" t="str">
@@ -4259,7 +4250,7 @@
         <v/>
       </c>
       <c r="F14" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4268,7 +4259,7 @@
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="23" t="str">
@@ -4276,7 +4267,7 @@
         <v/>
       </c>
       <c r="F15" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4285,7 +4276,7 @@
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="23" t="str">
@@ -4293,7 +4284,7 @@
         <v/>
       </c>
       <c r="F16" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4302,7 +4293,7 @@
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="23" t="str">
@@ -4310,7 +4301,7 @@
         <v/>
       </c>
       <c r="F17" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4319,7 +4310,7 @@
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="23" t="str">
@@ -4327,7 +4318,7 @@
         <v/>
       </c>
       <c r="F18" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4336,7 +4327,7 @@
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="23" t="str">
@@ -4344,7 +4335,7 @@
         <v/>
       </c>
       <c r="F19" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4353,7 +4344,7 @@
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="23" t="str">
@@ -4361,7 +4352,7 @@
         <v/>
       </c>
       <c r="F20" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4370,7 +4361,7 @@
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D21" s="12"/>
       <c r="E21" s="23" t="str">
@@ -4378,7 +4369,7 @@
         <v/>
       </c>
       <c r="F21" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4387,7 +4378,7 @@
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="23" t="str">
@@ -4395,7 +4386,7 @@
         <v/>
       </c>
       <c r="F22" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4404,7 +4395,7 @@
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="23" t="str">
@@ -4412,7 +4403,7 @@
         <v/>
       </c>
       <c r="F23" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4421,7 +4412,7 @@
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="23" t="str">
@@ -4429,7 +4420,7 @@
         <v/>
       </c>
       <c r="F24" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4438,7 +4429,7 @@
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="23" t="str">
@@ -4446,7 +4437,7 @@
         <v/>
       </c>
       <c r="F25" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4455,7 +4446,7 @@
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="23" t="str">
@@ -4463,7 +4454,7 @@
         <v/>
       </c>
       <c r="F26" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4472,7 +4463,7 @@
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="23" t="str">
@@ -4480,7 +4471,7 @@
         <v/>
       </c>
       <c r="F27" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4489,7 +4480,7 @@
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="23" t="str">
@@ -4497,7 +4488,7 @@
         <v/>
       </c>
       <c r="F28" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4506,7 +4497,7 @@
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="23" t="str">
@@ -4514,7 +4505,7 @@
         <v/>
       </c>
       <c r="F29" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4523,7 +4514,7 @@
       </c>
       <c r="B30" s="14"/>
       <c r="C30" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="23" t="str">
@@ -4531,7 +4522,7 @@
         <v/>
       </c>
       <c r="F30" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4540,7 +4531,7 @@
       </c>
       <c r="B31" s="14"/>
       <c r="C31" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="23" t="str">
@@ -4548,7 +4539,7 @@
         <v/>
       </c>
       <c r="F31" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4557,7 +4548,7 @@
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="23" t="str">
@@ -4565,7 +4556,7 @@
         <v/>
       </c>
       <c r="F32" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4574,7 +4565,7 @@
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="23" t="str">
@@ -4582,7 +4573,7 @@
         <v/>
       </c>
       <c r="F33" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4591,7 +4582,7 @@
       </c>
       <c r="B34" s="14"/>
       <c r="C34" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="23" t="str">
@@ -4599,7 +4590,7 @@
         <v/>
       </c>
       <c r="F34" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4608,7 +4599,7 @@
       </c>
       <c r="B35" s="14"/>
       <c r="C35" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="23" t="str">
@@ -4616,7 +4607,7 @@
         <v/>
       </c>
       <c r="F35" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4625,7 +4616,7 @@
       </c>
       <c r="B36" s="14"/>
       <c r="C36" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="23" t="str">
@@ -4633,7 +4624,7 @@
         <v/>
       </c>
       <c r="F36" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4642,7 +4633,7 @@
       </c>
       <c r="B37" s="14"/>
       <c r="C37" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="23" t="str">
@@ -4650,7 +4641,7 @@
         <v/>
       </c>
       <c r="F37" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4659,7 +4650,7 @@
       </c>
       <c r="B38" s="14"/>
       <c r="C38" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="23" t="str">
@@ -4667,7 +4658,7 @@
         <v/>
       </c>
       <c r="F38" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4676,7 +4667,7 @@
       </c>
       <c r="B39" s="14"/>
       <c r="C39" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="23" t="str">
@@ -4684,7 +4675,7 @@
         <v/>
       </c>
       <c r="F39" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4693,7 +4684,7 @@
       </c>
       <c r="B40" s="14"/>
       <c r="C40" s="12" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="23" t="str">
@@ -4701,7 +4692,7 @@
         <v/>
       </c>
       <c r="F40" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4710,7 +4701,7 @@
       </c>
       <c r="B41" s="14"/>
       <c r="C41" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="23" t="str">
@@ -4718,7 +4709,7 @@
         <v/>
       </c>
       <c r="F41" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4728,14 +4719,14 @@
       <c r="B42" s="14"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E42" s="23" t="str">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
         <v/>
       </c>
       <c r="F42" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4745,14 +4736,14 @@
       <c r="B43" s="14"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E43" s="23" t="str">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
         <v/>
       </c>
       <c r="F43" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4762,14 +4753,14 @@
       <c r="B44" s="14"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E44" s="23" t="str">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
         <v/>
       </c>
       <c r="F44" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4779,14 +4770,14 @@
       <c r="B45" s="14"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E45" s="23" t="str">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
         <v/>
       </c>
       <c r="F45" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4795,7 +4786,7 @@
       </c>
       <c r="B46" s="14"/>
       <c r="C46" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="23" t="str">
@@ -4803,7 +4794,7 @@
         <v/>
       </c>
       <c r="F46" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4812,7 +4803,7 @@
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="23" t="str">
@@ -4820,7 +4811,7 @@
         <v/>
       </c>
       <c r="F47" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4829,7 +4820,7 @@
       </c>
       <c r="B48" s="14"/>
       <c r="C48" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="23" t="str">
@@ -4837,7 +4828,7 @@
         <v/>
       </c>
       <c r="F48" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4846,7 +4837,7 @@
       </c>
       <c r="B49" s="14"/>
       <c r="C49" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="23" t="str">
@@ -4854,7 +4845,7 @@
         <v/>
       </c>
       <c r="F49" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4865,7 +4856,7 @@
         <v>435000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="23" t="n">
@@ -4873,7 +4864,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4884,7 +4875,7 @@
         <v>450000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="23" t="n">
@@ -4892,7 +4883,7 @@
         <v>9289000</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4903,7 +4894,7 @@
         <v>480000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="23" t="n">
@@ -4911,7 +4902,7 @@
         <v>39289000</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4922,17 +4913,17 @@
         <v>510000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E53" s="23" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
         <v>69289000</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4943,7 +4934,7 @@
         <v>540000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="23" t="n">
@@ -4951,7 +4942,7 @@
         <v>99289000</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4962,7 +4953,7 @@
         <v>570000000</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D55" s="12"/>
       <c r="E55" s="23" t="n">
@@ -4970,7 +4961,7 @@
         <v>129289000</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4981,7 +4972,7 @@
         <v>600000000</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D56" s="12"/>
       <c r="E56" s="23" t="n">
@@ -4989,7 +4980,7 @@
         <v>159289000</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5000,7 +4991,7 @@
         <v>630000000</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D57" s="12"/>
       <c r="E57" s="23" t="n">
@@ -5008,7 +4999,7 @@
         <v>189289000</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5019,7 +5010,7 @@
         <v>660000000</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D58" s="12"/>
       <c r="E58" s="23" t="n">
@@ -5027,7 +5018,7 @@
         <v>219289000</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5038,7 +5029,7 @@
         <v>690000000</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D59" s="12"/>
       <c r="E59" s="23" t="n">
@@ -5046,7 +5037,7 @@
         <v>249289000</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5057,7 +5048,7 @@
         <v>750000000</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D60" s="12"/>
       <c r="E60" s="23" t="n">
@@ -5065,7 +5056,7 @@
         <v>309289000</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5076,7 +5067,7 @@
         <v>825000000</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D61" s="12"/>
       <c r="E61" s="23" t="n">
@@ -5084,7 +5075,7 @@
         <v>384289000</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5095,7 +5086,7 @@
         <v>900000000</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D62" s="12"/>
       <c r="E62" s="23" t="n">
@@ -5103,7 +5094,7 @@
         <v>459289000</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5114,7 +5105,7 @@
         <v>975000000</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D63" s="12"/>
       <c r="E63" s="23" t="n">
@@ -5122,7 +5113,7 @@
         <v>534289000</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5133,7 +5124,7 @@
         <v>1050000000</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D64" s="12"/>
       <c r="E64" s="23" t="n">
@@ -5141,7 +5132,7 @@
         <v>609289000</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5152,7 +5143,7 @@
         <v>1125000000</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D65" s="12"/>
       <c r="E65" s="23" t="n">
@@ -5160,7 +5151,7 @@
         <v>684289000</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5171,7 +5162,7 @@
         <v>1200000000</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D66" s="12"/>
       <c r="E66" s="23" t="n">
@@ -5179,7 +5170,7 @@
         <v>759289000</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5190,7 +5181,7 @@
         <v>1350000000</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D67" s="12"/>
       <c r="E67" s="23" t="n">
@@ -5198,7 +5189,7 @@
         <v>909289000</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5209,7 +5200,7 @@
         <v>1500000000</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D68" s="12"/>
       <c r="E68" s="23" t="n">
@@ -5217,7 +5208,7 @@
         <v>1059289000</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5228,7 +5219,7 @@
         <v>1650000000</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D69" s="12"/>
       <c r="E69" s="23" t="n">
@@ -5236,7 +5227,7 @@
         <v>1209289000</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5247,7 +5238,7 @@
         <v>1875000000</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D70" s="12"/>
       <c r="E70" s="23" t="n">
@@ -5255,7 +5246,7 @@
         <v>1434289000</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5266,7 +5257,7 @@
         <v>2250000000</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D71" s="12"/>
       <c r="E71" s="23" t="n">
@@ -5274,7 +5265,7 @@
         <v>1809289000</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5285,7 +5276,7 @@
         <v>2625000000</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D72" s="12"/>
       <c r="E72" s="23" t="n">
@@ -5293,7 +5284,7 @@
         <v>2184289000</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5304,7 +5295,7 @@
         <v>3000000000</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D73" s="12"/>
       <c r="E73" s="23" t="n">
@@ -5312,7 +5303,7 @@
         <v>2559289000</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5323,7 +5314,7 @@
         <v>3375000000</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D74" s="12"/>
       <c r="E74" s="23" t="n">
@@ -5331,7 +5322,7 @@
         <v>2934289000</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5342,7 +5333,7 @@
         <v>3750000000</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D75" s="12"/>
       <c r="E75" s="23" t="n">
@@ -5350,7 +5341,7 @@
         <v>3309289000</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5361,7 +5352,7 @@
         <v>4125000000</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D76" s="12"/>
       <c r="E76" s="23" t="n">
@@ -5369,7 +5360,7 @@
         <v>3684289000</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5421,52 +5412,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="C4" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="D4" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="E4" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="F4" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="G4" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="H4" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="I4" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="J4" s="21" t="s">
         <v>244</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="J4" s="21" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>4000000</v>
@@ -5494,15 +5485,15 @@
         <v>7</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C6" s="14" t="n">
         <v>4000000</v>
@@ -5530,15 +5521,15 @@
         <v>8</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C7" s="14" t="n">
         <v>1</v>
@@ -5566,15 +5557,15 @@
         <v>963976500</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C8" s="14" t="n">
         <v>4000</v>
@@ -5602,7 +5593,7 @@
         <v>249350</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5610,7 +5601,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C9" s="14" t="n">
         <v>3000000</v>
@@ -5638,7 +5629,7 @@
         <v>4</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5646,7 +5637,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C10" s="14" t="n">
         <v>8000000</v>
@@ -5674,15 +5665,15 @@
         <v>5</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C11" s="14" t="n">
         <v>7000000</v>
@@ -5710,15 +5701,15 @@
         <v>0</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>257</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>259</v>
       </c>
       <c r="C12" s="14" t="n">
         <v>17000000</v>
@@ -5746,15 +5737,15 @@
         <v>0</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C13" s="14" t="n">
         <v>7000000</v>
@@ -5782,15 +5773,15 @@
         <v>0</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>17000000</v>
@@ -5818,15 +5809,15 @@
         <v>5</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C15" s="14" t="n">
         <v>7000000</v>
@@ -5854,15 +5845,15 @@
         <v>0</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C16" s="14" t="n">
         <v>17000000</v>
@@ -5890,15 +5881,15 @@
         <v>5</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C17" s="14" t="n">
         <v>3000000</v>
@@ -5926,15 +5917,15 @@
         <v>0</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C18" s="14" t="n">
         <v>8000000</v>
@@ -5962,15 +5953,15 @@
         <v>0</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C19" s="14" t="n">
         <v>3000000</v>
@@ -5998,15 +5989,15 @@
         <v>0</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C20" s="14" t="n">
         <v>8000000</v>
@@ -6034,15 +6025,15 @@
         <v>0</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C21" s="14" t="n">
         <v>3000000</v>
@@ -6070,15 +6061,15 @@
         <v>4</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C22" s="14" t="n">
         <v>8000000</v>
@@ -6106,15 +6097,15 @@
         <v>4</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C23" s="14" t="n">
         <v>3000000</v>
@@ -6142,15 +6133,15 @@
         <v>5</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C24" s="14" t="n">
         <v>8000000</v>
@@ -6178,15 +6169,15 @@
         <v>5</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C25" s="14" t="n">
         <v>8000000</v>
@@ -6214,15 +6205,15 @@
         <v>4</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C26" s="14" t="n">
         <v>17000000</v>
@@ -6250,15 +6241,15 @@
         <v>5</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C27" s="14" t="n">
         <v>8000000</v>
@@ -6286,15 +6277,15 @@
         <v>4</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C28" s="14" t="n">
         <v>17000000</v>
@@ -6322,15 +6313,15 @@
         <v>5</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C29" s="14" t="n">
         <v>8000000</v>
@@ -6358,15 +6349,15 @@
         <v>5</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C30" s="14" t="n">
         <v>17000000</v>
@@ -6394,15 +6385,15 @@
         <v>5</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C31" s="14" t="n">
         <v>40000000</v>
@@ -6430,15 +6421,15 @@
         <v>2</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="B32" s="12" t="s">
         <v>278</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>280</v>
       </c>
       <c r="C32" s="14" t="n">
         <v>80000000</v>
@@ -6466,15 +6457,15 @@
         <v>2</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C33" s="14" t="n">
         <v>150000000</v>
@@ -6502,15 +6493,15 @@
         <v>2</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C34" s="14" t="n">
         <v>200000000</v>
@@ -6538,15 +6529,15 @@
         <v>1</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="B35" s="12" t="s">
         <v>282</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>284</v>
       </c>
       <c r="C35" s="14" t="n">
         <v>200000000</v>
@@ -6574,15 +6565,15 @@
         <v>1</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C36" s="14" t="n">
         <v>17000000</v>
@@ -6610,15 +6601,15 @@
         <v>5</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="B37" s="12" t="s">
         <v>285</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>287</v>
       </c>
       <c r="C37" s="14" t="n">
         <v>150000000</v>
@@ -6646,15 +6637,15 @@
         <v>5</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C38" s="14" t="n">
         <v>17000000</v>
@@ -6682,15 +6673,15 @@
         <v>5</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C39" s="14" t="n">
         <v>50000000</v>
@@ -6718,15 +6709,15 @@
         <v>5</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C40" s="14" t="n">
         <v>150000000</v>
@@ -6754,15 +6745,15 @@
         <v>5</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C41" s="14" t="n">
         <v>17000000</v>
@@ -6790,15 +6781,15 @@
         <v>5</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="B42" s="12" t="s">
         <v>291</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>293</v>
       </c>
       <c r="C42" s="14" t="n">
         <v>150000000</v>
@@ -6826,15 +6817,15 @@
         <v>5</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C43" s="14" t="n">
         <v>17000000</v>
@@ -6862,15 +6853,15 @@
         <v>5</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C44" s="14" t="n">
         <v>50000000</v>
@@ -6898,15 +6889,15 @@
         <v>5</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C45" s="14" t="n">
         <v>150000000</v>
@@ -6934,15 +6925,15 @@
         <v>5</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C46" s="14" t="n">
         <v>4500000</v>
@@ -6970,21 +6961,21 @@
         <v>6</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C47" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E47" s="24" t="n">
         <v>0</v>
@@ -7006,12 +6997,12 @@
         <v>0</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="16" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E49" s="20" t="n">
         <f aca="false">SUM(E5:E47)</f>
@@ -7021,7 +7012,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="16" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E50" s="20"/>
       <c r="F50" s="20" t="n">
@@ -7031,7 +7022,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="16" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E51" s="20"/>
       <c r="F51" s="20" t="n">
@@ -7041,7 +7032,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -7086,49 +7077,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>312</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>18225475</v>
+        <v>8434225</v>
       </c>
       <c r="C5" s="26" t="n">
-        <v>1505800</v>
+        <v>1146000</v>
       </c>
       <c r="D5" s="26" t="n">
         <v>4370000</v>
@@ -7137,18 +7128,18 @@
         <v>14390000</v>
       </c>
       <c r="F5" s="26" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G5" s="26" t="n">
         <v>735</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>1285</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B6" s="27" t="n">
         <f aca="false">SUMIFS(B13:B69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
@@ -7181,15 +7172,15 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
-        <v>50725475</v>
+        <v>40934225</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5+C6</f>
-        <v>5005800</v>
+        <v>4646000</v>
       </c>
       <c r="D7" s="27" t="n">
         <f aca="false">D5+D6</f>
@@ -7201,7 +7192,7 @@
       </c>
       <c r="F7" s="27" t="n">
         <f aca="false">F5+F6</f>
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G7" s="27" t="n">
         <f aca="false">G5+G6</f>
@@ -7209,20 +7200,20 @@
       </c>
       <c r="H7" s="27" t="n">
         <f aca="false">H5+H6</f>
-        <v>2225</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B8" s="27" t="n">
         <f aca="false">SUMIF($J$73:$J$93,"Planned",B73:B93)</f>
-        <v>9791250</v>
+        <v>0</v>
       </c>
       <c r="C8" s="27" t="n">
         <f aca="false">SUMIF($J$73:$J$93,"Planned",C73:C93)</f>
-        <v>2070000</v>
+        <v>1710000</v>
       </c>
       <c r="D8" s="27" t="n">
         <f aca="false">SUMIF($J$73:$J$93,"Planned",D73:D93)</f>
@@ -7234,7 +7225,7 @@
       </c>
       <c r="F8" s="27" t="n">
         <f aca="false">SUMIF($J$73:$J$93,"Planned",F73:F93)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="27" t="n">
         <f aca="false">SUMIF($J$73:$J$93,"Planned",G73:G93)</f>
@@ -7242,12 +7233,12 @@
       </c>
       <c r="H8" s="27" t="n">
         <f aca="false">SUMIF($J$73:$J$93,"Planned",H73:H93)</f>
-        <v>979</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B7-B8</f>
@@ -7255,7 +7246,7 @@
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">C7-C8</f>
-        <v>2935800</v>
+        <v>2936000</v>
       </c>
       <c r="D9" s="28" t="n">
         <f aca="false">D7-D8</f>
@@ -7280,44 +7271,44 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="29" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>322</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>324</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>13</v>
@@ -7325,7 +7316,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B13" s="30" t="n">
         <v>100000</v>
@@ -7349,18 +7340,18 @@
         <v>0</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B14" s="30" t="n">
         <v>1600000</v>
@@ -7384,18 +7375,18 @@
         <v>0</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B15" s="30" t="n">
         <v>1600000</v>
@@ -7419,18 +7410,18 @@
         <v>0</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B16" s="30" t="n">
         <v>1600000</v>
@@ -7454,18 +7445,18 @@
         <v>0</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B17" s="30" t="n">
         <v>1600000</v>
@@ -7489,18 +7480,18 @@
         <v>0</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B18" s="30" t="n">
         <v>1600000</v>
@@ -7524,18 +7515,18 @@
         <v>0</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B19" s="30" t="n">
         <v>1600000</v>
@@ -7559,18 +7550,18 @@
         <v>0</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B20" s="30" t="n">
         <v>1600000</v>
@@ -7594,18 +7585,18 @@
         <v>0</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B21" s="30" t="n">
         <v>100000</v>
@@ -7629,16 +7620,16 @@
         <v>0</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B22" s="30" t="n">
         <v>200000</v>
@@ -7662,16 +7653,16 @@
         <v>0</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K22" s="15"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B23" s="30" t="n">
         <v>0</v>
@@ -7695,18 +7686,18 @@
         <v>0</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B24" s="30" t="n">
         <v>150000</v>
@@ -7730,16 +7721,16 @@
         <v>15</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B25" s="30" t="n">
         <v>150000</v>
@@ -7763,16 +7754,16 @@
         <v>20</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B26" s="30" t="n">
         <v>200000</v>
@@ -7796,16 +7787,16 @@
         <v>25</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K26" s="15"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B27" s="30" t="n">
         <v>250000</v>
@@ -7829,16 +7820,16 @@
         <v>30</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K27" s="15"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B28" s="30" t="n">
         <v>300000</v>
@@ -7862,16 +7853,16 @@
         <v>40</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K28" s="15"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B29" s="30" t="n">
         <v>350000</v>
@@ -7895,16 +7886,16 @@
         <v>45</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K29" s="15"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B30" s="30" t="n">
         <v>0</v>
@@ -7928,18 +7919,18 @@
         <v>0</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B31" s="30" t="n">
         <v>0</v>
@@ -7963,18 +7954,18 @@
         <v>0</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B32" s="30" t="n">
         <v>0</v>
@@ -7998,18 +7989,18 @@
         <v>0</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B33" s="30" t="n">
         <v>0</v>
@@ -8033,16 +8024,16 @@
         <v>800</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K33" s="15"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B34" s="30" t="n">
         <v>10000000</v>
@@ -8066,16 +8057,16 @@
         <v>0</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K34" s="15"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B35" s="30" t="n">
         <v>500000</v>
@@ -8099,16 +8090,16 @@
         <v>0</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K35" s="15"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B36" s="30" t="n">
         <v>0</v>
@@ -8132,18 +8123,18 @@
         <v>0</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B37" s="30" t="n">
         <v>0</v>
@@ -8167,18 +8158,18 @@
         <v>0</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B38" s="30" t="n">
         <v>0</v>
@@ -8202,16 +8193,16 @@
         <v>0</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K38" s="15"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B39" s="30" t="n">
         <v>0</v>
@@ -8235,16 +8226,16 @@
         <v>0</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K39" s="15"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B40" s="30" t="n">
         <v>900000</v>
@@ -8268,18 +8259,18 @@
         <v>0</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B41" s="30" t="n">
         <v>0</v>
@@ -8303,18 +8294,18 @@
         <v>90</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B42" s="30" t="n">
         <v>3300000</v>
@@ -8338,18 +8329,18 @@
         <v>0</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B43" s="30" t="n">
         <v>3300000</v>
@@ -8373,18 +8364,18 @@
         <v>0</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B44" s="30" t="n">
         <v>0</v>
@@ -8408,18 +8399,18 @@
         <v>0</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B45" s="30" t="n">
         <v>0</v>
@@ -8443,18 +8434,18 @@
         <v>0</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B46" s="30" t="n">
         <v>0</v>
@@ -8478,18 +8469,18 @@
         <v>0</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B47" s="30" t="n">
         <v>750000</v>
@@ -8513,18 +8504,18 @@
         <v>0</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B48" s="30" t="n">
         <v>750000</v>
@@ -8548,18 +8539,18 @@
         <v>0</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B49" s="30" t="n">
         <v>750000</v>
@@ -8583,18 +8574,18 @@
         <v>0</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B50" s="30" t="n">
         <v>750000</v>
@@ -8618,18 +8609,18 @@
         <v>0</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B51" s="30" t="n">
         <v>750000</v>
@@ -8653,18 +8644,18 @@
         <v>0</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B52" s="30" t="n">
         <v>750000</v>
@@ -8688,18 +8679,18 @@
         <v>0</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B53" s="30" t="n">
         <v>750000</v>
@@ -8723,18 +8714,18 @@
         <v>0</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B54" s="30" t="n">
         <v>750000</v>
@@ -8758,18 +8749,18 @@
         <v>0</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B55" s="30" t="n">
         <v>0</v>
@@ -8793,18 +8784,18 @@
         <v>0</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B56" s="30" t="n">
         <v>0</v>
@@ -8828,18 +8819,18 @@
         <v>0</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B57" s="30" t="n">
         <v>44475</v>
@@ -8863,18 +8854,18 @@
         <v>0</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B58" s="30" t="n">
         <v>11000</v>
@@ -8898,18 +8889,18 @@
         <v>0</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B59" s="30" t="n">
         <v>0</v>
@@ -8933,13 +8924,13 @@
         <v>0</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9074,33 +9065,33 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="29" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="F72" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="G72" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="H72" s="3" t="s">
         <v>312</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>314</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>10</v>
@@ -9114,7 +9105,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B73" s="30" t="n">
         <v>1837500</v>
@@ -9141,15 +9132,15 @@
         <v>0</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="K73" s="15" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B74" s="30" t="n">
         <v>0</v>
@@ -9176,13 +9167,13 @@
         <v>0</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="K74" s="15"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B75" s="30" t="n">
         <v>9791250</v>
@@ -9209,21 +9200,21 @@
         <v>55000000</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="K75" s="15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B76" s="30" t="n">
         <v>0</v>
       </c>
       <c r="C76" s="30" t="n">
-        <v>360000</v>
+        <v>359800</v>
       </c>
       <c r="D76" s="30" t="n">
         <v>0</v>
@@ -9244,15 +9235,15 @@
         <v>0</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="K76" s="15" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B77" s="26"/>
       <c r="C77" s="30" t="n">
@@ -9271,15 +9262,15 @@
         <v>3000000</v>
       </c>
       <c r="J77" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K77" s="15" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B78" s="26"/>
       <c r="C78" s="30" t="n">
@@ -9298,15 +9289,15 @@
         <v>3000000</v>
       </c>
       <c r="J78" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K78" s="15" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B79" s="26"/>
       <c r="C79" s="30" t="n">
@@ -9325,15 +9316,15 @@
         <v>3000000</v>
       </c>
       <c r="J79" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B80" s="26"/>
       <c r="C80" s="30" t="n">
@@ -9352,15 +9343,15 @@
         <v>3000000</v>
       </c>
       <c r="J80" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K80" s="15" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B81" s="26"/>
       <c r="C81" s="30" t="n">
@@ -9385,15 +9376,15 @@
         <v>17000000</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B82" s="30" t="n">
         <v>0</v>
@@ -9420,15 +9411,15 @@
         <v>17000000</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K82" s="15" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B83" s="30" t="n">
         <v>0</v>
@@ -9449,15 +9440,15 @@
         <v>17000000</v>
       </c>
       <c r="J83" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K83" s="15" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B84" s="30" t="n">
         <v>0</v>
@@ -9478,15 +9469,15 @@
         <v>17000000</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="K84" s="15" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B85" s="30" t="n">
         <v>0</v>
@@ -9507,15 +9498,15 @@
         <v>17000000</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="K85" s="15" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B86" s="30" t="n">
         <v>0</v>
@@ -9536,15 +9527,15 @@
         <v>17000000</v>
       </c>
       <c r="J86" s="11" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="K86" s="15" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B87" s="30" t="n">
         <v>13000000</v>
@@ -9565,10 +9556,10 @@
         <v>8000000</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="K87" s="15" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9651,11 +9642,11 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="16" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="I95" s="20" t="n">
         <f aca="false">SUMIF(J73:J93,"Planned",I73:I93)</f>
-        <v>118000000</v>
+        <v>63000000</v>
       </c>
     </row>
   </sheetData>
@@ -9710,72 +9701,72 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>425</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -9787,19 +9778,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C7" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -9811,19 +9802,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -9835,19 +9826,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -9859,19 +9850,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -9883,19 +9874,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -9907,19 +9898,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -9931,19 +9922,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -9955,19 +9946,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -9979,19 +9970,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -10003,19 +9994,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -10027,16 +10018,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -10049,19 +10040,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -10073,19 +10064,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -10097,19 +10088,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -10121,24 +10112,24 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -10150,16 +10141,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C23" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -10172,16 +10163,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -10194,19 +10185,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -10218,19 +10209,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B26" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="C26" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="15" t="s">
         <v>465</v>
       </c>
-      <c r="C26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>468</v>
-      </c>
       <c r="E26" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -10242,16 +10233,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -10264,16 +10255,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C28" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -10286,21 +10277,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -10313,16 +10304,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B31" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="C31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="15" t="s">
         <v>477</v>
-      </c>
-      <c r="C31" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>480</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -10335,16 +10326,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C32" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -10357,19 +10348,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C33" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
@@ -10381,16 +10372,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B34" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="C34" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="15" t="s">
         <v>484</v>
-      </c>
-      <c r="C34" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>487</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -10403,16 +10394,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B35" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="C35" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="15" t="s">
         <v>484</v>
-      </c>
-      <c r="C35" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>487</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -10425,16 +10416,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C36" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -10447,16 +10438,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -10469,7 +10460,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E39" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$37)*(E5:E37="Done"))</f>
@@ -10506,7 +10497,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E40" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$37,"Required",E5:E37,"Done")&amp;" of 11"</f>
@@ -10543,7 +10534,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -10587,51 +10578,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B6" s="19" t="n">
         <v>285572765</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -10648,14 +10639,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">IFERROR(INDEX(A13:A54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),"All done")</f>
         <v>15</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E7" s="20" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -10672,7 +10663,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B8" s="20" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
@@ -10681,7 +10672,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -10689,7 +10680,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -10698,40 +10689,40 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>20217834.9610904</v>
+        <v>20219932.1833902</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10741,7 +10732,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -10753,7 +10744,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I13" s="23" t="str">
         <f aca="false">IF(B13="","",MAX(0,B13-$B$6))</f>
@@ -10767,7 +10758,7 @@
       <c r="B14" s="26"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -10779,7 +10770,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I14" s="23" t="str">
         <f aca="false">IF(B14="","",MAX(0,B14-$B$6))</f>
@@ -10793,7 +10784,7 @@
       <c r="B15" s="26"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -10805,7 +10796,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I15" s="23" t="str">
         <f aca="false">IF(B15="","",MAX(0,B15-$B$6))</f>
@@ -10819,7 +10810,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -10831,7 +10822,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I16" s="23" t="str">
         <f aca="false">IF(B16="","",MAX(0,B16-$B$6))</f>
@@ -10844,10 +10835,10 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="12" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -10859,7 +10850,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I17" s="23" t="str">
         <f aca="false">IF(B17="","",MAX(0,B17-$B$6))</f>
@@ -10872,10 +10863,10 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="12" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -10887,7 +10878,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I18" s="23" t="str">
         <f aca="false">IF(B18="","",MAX(0,B18-$B$6))</f>
@@ -10900,10 +10891,10 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="12" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -10915,7 +10906,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I19" s="23" t="str">
         <f aca="false">IF(B19="","",MAX(0,B19-$B$6))</f>
@@ -10928,10 +10919,10 @@
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -10943,7 +10934,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I20" s="23" t="str">
         <f aca="false">IF(B20="","",MAX(0,B20-$B$6))</f>
@@ -10956,10 +10947,10 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -10971,7 +10962,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I21" s="23" t="str">
         <f aca="false">IF(B21="","",MAX(0,B21-$B$6))</f>
@@ -10984,10 +10975,10 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="12" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -10999,7 +10990,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I22" s="23" t="str">
         <f aca="false">IF(B22="","",MAX(0,B22-$B$6))</f>
@@ -11013,7 +11004,7 @@
       <c r="B23" s="26"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -11025,7 +11016,7 @@
         <v>1900000</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I23" s="23" t="str">
         <f aca="false">IF(B23="","",MAX(0,B23-$B$6))</f>
@@ -11038,10 +11029,10 @@
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="12" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -11053,7 +11044,7 @@
         <v>1900000</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I24" s="23" t="str">
         <f aca="false">IF(B24="","",MAX(0,B24-$B$6))</f>
@@ -11066,10 +11057,10 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -11081,7 +11072,7 @@
         <v>1900000</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I25" s="23" t="str">
         <f aca="false">IF(B25="","",MAX(0,B25-$B$6))</f>
@@ -11094,10 +11085,10 @@
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="12" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -11109,7 +11100,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I26" s="23" t="str">
         <f aca="false">IF(B26="","",MAX(0,B26-$B$6))</f>
@@ -11125,7 +11116,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -11137,7 +11128,7 @@
         <v>1900000</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I27" s="23" t="n">
         <f aca="false">IF(B27="","",MAX(0,B27-$B$6))</f>
@@ -11152,10 +11143,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -11167,7 +11158,7 @@
         <v>1900000</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I28" s="23" t="n">
         <f aca="false">IF(B28="","",MAX(0,B28-$B$6))</f>
@@ -11182,10 +11173,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -11197,7 +11188,7 @@
         <v>1900000</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I29" s="23" t="n">
         <f aca="false">IF(B29="","",MAX(0,B29-$B$6))</f>
@@ -11212,16 +11203,16 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
       <c r="G30" s="26"/>
       <c r="H30" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I30" s="23" t="n">
         <f aca="false">IF(B30="","",MAX(0,B30-$B$6))</f>
@@ -11236,10 +11227,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -11251,7 +11242,7 @@
         <v>1900000</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I31" s="23" t="n">
         <f aca="false">IF(B31="","",MAX(0,B31-$B$6))</f>
@@ -11266,7 +11257,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -11279,7 +11270,7 @@
         <v>1900000</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I32" s="23" t="n">
         <f aca="false">IF(B32="","",MAX(0,B32-$B$6))</f>
@@ -11294,10 +11285,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -11309,7 +11300,7 @@
         <v>1900000</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I33" s="23" t="n">
         <f aca="false">IF(B33="","",MAX(0,B33-$B$6))</f>
@@ -11324,7 +11315,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -11337,7 +11328,7 @@
         <v>1900000</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I34" s="23" t="n">
         <f aca="false">IF(B34="","",MAX(0,B34-$B$6))</f>
@@ -11352,10 +11343,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -11367,7 +11358,7 @@
         <v>1900000</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I35" s="23" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
@@ -11382,7 +11373,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -11395,7 +11386,7 @@
         <v>1900000</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I36" s="23" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
@@ -11410,10 +11401,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -11425,7 +11416,7 @@
         <v>1900000</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I37" s="23" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
@@ -11440,7 +11431,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -11453,7 +11444,7 @@
         <v>2000000</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I38" s="23" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
@@ -11468,10 +11459,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -11483,7 +11474,7 @@
         <v>2000000</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I39" s="23" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
@@ -11498,7 +11489,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -11511,7 +11502,7 @@
         <v>2000000</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I40" s="23" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
@@ -11526,10 +11517,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -11541,7 +11532,7 @@
         <v>2000000</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I41" s="23" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
@@ -11556,7 +11547,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -11569,7 +11560,7 @@
         <v>2000000</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I42" s="23" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
@@ -11584,10 +11575,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -11599,7 +11590,7 @@
         <v>2000000</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I43" s="23" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
@@ -11614,7 +11605,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -11627,7 +11618,7 @@
         <v>2700000</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I44" s="23" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
@@ -11642,7 +11633,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -11655,7 +11646,7 @@
         <v>2700000</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I45" s="23" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
@@ -11670,7 +11661,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -11683,7 +11674,7 @@
         <v>2700000</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I46" s="23" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
@@ -11698,7 +11689,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -11711,7 +11702,7 @@
         <v>2700000</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I47" s="23" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
@@ -11726,7 +11717,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -11739,7 +11730,7 @@
         <v>2700000</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I48" s="23" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
@@ -11754,7 +11745,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -11767,7 +11758,7 @@
         <v>2700000</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I49" s="23" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
@@ -11782,7 +11773,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -11795,7 +11786,7 @@
         <v>2700000</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I50" s="23" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
@@ -11810,7 +11801,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -11823,7 +11814,7 @@
         <v>2700000</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I51" s="23" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
@@ -11838,7 +11829,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -11851,7 +11842,7 @@
         <v>2700000</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I52" s="23" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
@@ -11866,7 +11857,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -11879,7 +11870,7 @@
         <v>2700000</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I53" s="23" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
@@ -11894,7 +11885,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -11907,7 +11898,7 @@
         <v>2700000</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I54" s="23" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
@@ -11916,7 +11907,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="554">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -1092,10 +1092,13 @@
     <t xml:space="preserve">Iso Fest milestone 15</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6 million points away. Set to Yes once scoring is clear</t>
+    <t xml:space="preserve">Reached Oct 11, ready to claim</t>
   </si>
   <si>
     <t xml:space="preserve">Iso Fest milestone 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About 16.7 million points away</t>
   </si>
   <si>
     <t xml:space="preserve">Iso Fest milestone 17</t>
@@ -4196,7 +4199,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>534300731.429624</v>
+        <v>534464107.246895</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7147,15 +7150,15 @@
       </c>
       <c r="C6" s="27" t="n">
         <f aca="false">SUMIFS(C13:C69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
-        <v>3500000</v>
+        <v>5350000</v>
       </c>
       <c r="D6" s="27" t="n">
         <f aca="false">SUMIFS(D13:D69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
-        <v>3136000</v>
+        <v>4436000</v>
       </c>
       <c r="E6" s="27" t="n">
         <f aca="false">SUMIFS(E13:E69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
-        <v>2736000</v>
+        <v>6536000</v>
       </c>
       <c r="F6" s="27" t="n">
         <f aca="false">SUMIFS(F13:F69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
@@ -7180,15 +7183,15 @@
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5+C6</f>
-        <v>4646000</v>
+        <v>6496000</v>
       </c>
       <c r="D7" s="27" t="n">
         <f aca="false">D5+D6</f>
-        <v>7506000</v>
+        <v>8806000</v>
       </c>
       <c r="E7" s="27" t="n">
         <f aca="false">E5+E6</f>
-        <v>17126000</v>
+        <v>20926000</v>
       </c>
       <c r="F7" s="27" t="n">
         <f aca="false">F5+F6</f>
@@ -7246,15 +7249,15 @@
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">C7-C8</f>
-        <v>2936000</v>
+        <v>4786000</v>
       </c>
       <c r="D9" s="28" t="n">
         <f aca="false">D7-D8</f>
-        <v>4866000</v>
+        <v>6166000</v>
       </c>
       <c r="E9" s="28" t="n">
         <f aca="false">E7-E8</f>
-        <v>15416000</v>
+        <v>19216000</v>
       </c>
       <c r="F9" s="28" t="n">
         <f aca="false">F7-F8</f>
@@ -8158,7 +8161,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>251</v>
@@ -8193,16 +8196,18 @@
         <v>0</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="K38" s="15"/>
+      <c r="K38" s="15" t="s">
+        <v>355</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B39" s="30" t="n">
         <v>0</v>
@@ -8235,7 +8240,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B40" s="30" t="n">
         <v>900000</v>
@@ -8265,12 +8270,12 @@
         <v>251</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B41" s="30" t="n">
         <v>0</v>
@@ -8300,12 +8305,12 @@
         <v>251</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B42" s="30" t="n">
         <v>3300000</v>
@@ -8335,12 +8340,12 @@
         <v>247</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B43" s="30" t="n">
         <v>3300000</v>
@@ -8370,12 +8375,12 @@
         <v>251</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B44" s="30" t="n">
         <v>0</v>
@@ -8405,12 +8410,12 @@
         <v>251</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B45" s="30" t="n">
         <v>0</v>
@@ -8440,12 +8445,12 @@
         <v>251</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B46" s="30" t="n">
         <v>0</v>
@@ -8475,12 +8480,12 @@
         <v>251</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B47" s="30" t="n">
         <v>750000</v>
@@ -8510,12 +8515,12 @@
         <v>251</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B48" s="30" t="n">
         <v>750000</v>
@@ -8545,12 +8550,12 @@
         <v>251</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B49" s="30" t="n">
         <v>750000</v>
@@ -8580,12 +8585,12 @@
         <v>251</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B50" s="30" t="n">
         <v>750000</v>
@@ -8615,12 +8620,12 @@
         <v>251</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B51" s="30" t="n">
         <v>750000</v>
@@ -8650,12 +8655,12 @@
         <v>251</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B52" s="30" t="n">
         <v>750000</v>
@@ -8685,12 +8690,12 @@
         <v>251</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B53" s="30" t="n">
         <v>750000</v>
@@ -8720,12 +8725,12 @@
         <v>251</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B54" s="30" t="n">
         <v>750000</v>
@@ -8755,12 +8760,12 @@
         <v>251</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B55" s="30" t="n">
         <v>0</v>
@@ -8790,12 +8795,12 @@
         <v>251</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B56" s="30" t="n">
         <v>0</v>
@@ -8825,12 +8830,12 @@
         <v>251</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B57" s="30" t="n">
         <v>44475</v>
@@ -8860,12 +8865,12 @@
         <v>247</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B58" s="30" t="n">
         <v>11000</v>
@@ -8895,12 +8900,12 @@
         <v>247</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B59" s="30" t="n">
         <v>0</v>
@@ -8930,7 +8935,7 @@
         <v>251</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9065,12 +9070,12 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="29" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>306</v>
@@ -9105,7 +9110,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B73" s="30" t="n">
         <v>1837500</v>
@@ -9132,15 +9137,15 @@
         <v>0</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K73" s="15" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B74" s="30" t="n">
         <v>0</v>
@@ -9167,13 +9172,13 @@
         <v>0</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K74" s="15"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B75" s="30" t="n">
         <v>9791250</v>
@@ -9200,15 +9205,15 @@
         <v>55000000</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K75" s="15" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B76" s="30" t="n">
         <v>0</v>
@@ -9235,15 +9240,15 @@
         <v>0</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K76" s="15" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B77" s="26"/>
       <c r="C77" s="30" t="n">
@@ -9262,15 +9267,15 @@
         <v>3000000</v>
       </c>
       <c r="J77" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K77" s="15" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B78" s="26"/>
       <c r="C78" s="30" t="n">
@@ -9289,15 +9294,15 @@
         <v>3000000</v>
       </c>
       <c r="J78" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K78" s="15" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B79" s="26"/>
       <c r="C79" s="30" t="n">
@@ -9316,15 +9321,15 @@
         <v>3000000</v>
       </c>
       <c r="J79" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B80" s="26"/>
       <c r="C80" s="30" t="n">
@@ -9343,15 +9348,15 @@
         <v>3000000</v>
       </c>
       <c r="J80" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K80" s="15" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B81" s="26"/>
       <c r="C81" s="30" t="n">
@@ -9376,15 +9381,15 @@
         <v>17000000</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B82" s="30" t="n">
         <v>0</v>
@@ -9411,15 +9416,15 @@
         <v>17000000</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K82" s="15" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B83" s="30" t="n">
         <v>0</v>
@@ -9440,15 +9445,15 @@
         <v>17000000</v>
       </c>
       <c r="J83" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K83" s="15" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B84" s="30" t="n">
         <v>0</v>
@@ -9469,15 +9474,15 @@
         <v>17000000</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K84" s="15" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B85" s="30" t="n">
         <v>0</v>
@@ -9498,15 +9503,15 @@
         <v>17000000</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K85" s="15" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B86" s="30" t="n">
         <v>0</v>
@@ -9527,15 +9532,15 @@
         <v>17000000</v>
       </c>
       <c r="J86" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K86" s="15" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B87" s="30" t="n">
         <v>13000000</v>
@@ -9556,10 +9561,10 @@
         <v>8000000</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K87" s="15" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9642,7 +9647,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="16" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="I95" s="20" t="n">
         <f aca="false">SUMIF(J73:J93,"Planned",I73:I93)</f>
@@ -9701,12 +9706,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9720,53 +9725,53 @@
         <v>306</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -9778,19 +9783,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C7" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -9802,19 +9807,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -9826,19 +9831,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -9850,19 +9855,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -9874,19 +9879,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -9898,19 +9903,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -9922,19 +9927,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -9946,19 +9951,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -9970,19 +9975,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -9994,19 +9999,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -10018,16 +10023,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -10040,19 +10045,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -10064,19 +10069,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -10088,19 +10093,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -10112,24 +10117,24 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -10141,16 +10146,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="C23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>459</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>457</v>
-      </c>
-      <c r="C23" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>458</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -10163,16 +10168,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -10185,19 +10190,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -10209,19 +10214,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C26" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -10233,16 +10238,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -10255,16 +10260,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C28" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -10277,21 +10282,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -10304,16 +10309,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C31" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -10326,16 +10331,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C32" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -10348,19 +10353,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C33" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
@@ -10372,16 +10377,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C34" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -10394,16 +10399,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="C35" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="15" t="s">
         <v>485</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>481</v>
-      </c>
-      <c r="C35" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>484</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -10416,16 +10421,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C36" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -10438,16 +10443,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -10460,7 +10465,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E39" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$37)*(E5:E37="Done"))</f>
@@ -10497,7 +10502,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E40" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$37,"Required",E5:E37,"Done")&amp;" of 11"</f>
@@ -10534,7 +10539,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -10578,12 +10583,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10591,10 +10596,10 @@
         <v>153</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10605,13 +10610,13 @@
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10619,10 +10624,10 @@
         <v>156</v>
       </c>
       <c r="B6" s="19" t="n">
-        <v>285572765</v>
+        <v>308343695</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -10643,22 +10648,22 @@
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">IFERROR(INDEX(A13:A54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),"All done")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>161</v>
       </c>
       <c r="E7" s="20" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
-        <v>0</v>
+        <v>900000</v>
       </c>
       <c r="F7" s="20" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*F13:F54)</f>
-        <v>0</v>
+        <v>1300000</v>
       </c>
       <c r="G7" s="20" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*G13:G54)</f>
-        <v>0</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10667,12 +10672,12 @@
       </c>
       <c r="B8" s="20" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>14427235</v>
+        <v>16656305</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -10680,20 +10685,20 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>139427235</v>
+        <v>116656305</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>20219932.1833902</v>
+        <v>16922833.1482074</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10704,19 +10709,19 @@
         <v>166</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
@@ -10732,7 +10737,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -10758,7 +10763,7 @@
       <c r="B14" s="26"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -10784,7 +10789,7 @@
       <c r="B15" s="26"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -10810,7 +10815,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -10835,10 +10840,10 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="12" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -10863,10 +10868,10 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="12" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -10891,10 +10896,10 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="12" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -10919,10 +10924,10 @@
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -10947,10 +10952,10 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="12" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -10975,10 +10980,10 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="12" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -11004,7 +11009,7 @@
       <c r="B23" s="26"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -11029,10 +11034,10 @@
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="12" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -11057,10 +11062,10 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="D25" s="12" t="s">
         <v>523</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>522</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -11085,10 +11090,10 @@
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="12" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -11116,7 +11121,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -11132,7 +11137,7 @@
       </c>
       <c r="I27" s="23" t="n">
         <f aca="false">IF(B27="","",MAX(0,B27-$B$6))</f>
-        <v>14427235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11143,10 +11148,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -11162,7 +11167,7 @@
       </c>
       <c r="I28" s="23" t="n">
         <f aca="false">IF(B28="","",MAX(0,B28-$B$6))</f>
-        <v>39427235</v>
+        <v>16656305</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11173,10 +11178,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -11192,7 +11197,7 @@
       </c>
       <c r="I29" s="23" t="n">
         <f aca="false">IF(B29="","",MAX(0,B29-$B$6))</f>
-        <v>64427235</v>
+        <v>41656305</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11203,10 +11208,10 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
@@ -11216,7 +11221,7 @@
       </c>
       <c r="I30" s="23" t="n">
         <f aca="false">IF(B30="","",MAX(0,B30-$B$6))</f>
-        <v>89427235</v>
+        <v>66656305</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11227,10 +11232,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -11246,7 +11251,7 @@
       </c>
       <c r="I31" s="23" t="n">
         <f aca="false">IF(B31="","",MAX(0,B31-$B$6))</f>
-        <v>114427235</v>
+        <v>91656305</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11257,7 +11262,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -11274,7 +11279,7 @@
       </c>
       <c r="I32" s="23" t="n">
         <f aca="false">IF(B32="","",MAX(0,B32-$B$6))</f>
-        <v>139427235</v>
+        <v>116656305</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11285,10 +11290,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -11304,7 +11309,7 @@
       </c>
       <c r="I33" s="23" t="n">
         <f aca="false">IF(B33="","",MAX(0,B33-$B$6))</f>
-        <v>164427235</v>
+        <v>141656305</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11315,7 +11320,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -11332,7 +11337,7 @@
       </c>
       <c r="I34" s="23" t="n">
         <f aca="false">IF(B34="","",MAX(0,B34-$B$6))</f>
-        <v>189427235</v>
+        <v>166656305</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11343,10 +11348,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -11362,7 +11367,7 @@
       </c>
       <c r="I35" s="23" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
-        <v>214427235</v>
+        <v>191656305</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11373,7 +11378,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -11390,7 +11395,7 @@
       </c>
       <c r="I36" s="23" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>239427235</v>
+        <v>216656305</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11401,10 +11406,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -11420,7 +11425,7 @@
       </c>
       <c r="I37" s="23" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>264427235</v>
+        <v>241656305</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11431,7 +11436,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -11448,7 +11453,7 @@
       </c>
       <c r="I38" s="23" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>314427235</v>
+        <v>291656305</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11459,10 +11464,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -11478,7 +11483,7 @@
       </c>
       <c r="I39" s="23" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>364427235</v>
+        <v>341656305</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11489,7 +11494,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -11506,7 +11511,7 @@
       </c>
       <c r="I40" s="23" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>464427235</v>
+        <v>441656305</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11517,10 +11522,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -11536,7 +11541,7 @@
       </c>
       <c r="I41" s="23" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>614427235</v>
+        <v>591656305</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11547,7 +11552,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -11564,7 +11569,7 @@
       </c>
       <c r="I42" s="23" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>814427235</v>
+        <v>791656305</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11575,10 +11580,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -11594,7 +11599,7 @@
       </c>
       <c r="I43" s="23" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>1014427235</v>
+        <v>991656305</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11605,7 +11610,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -11622,7 +11627,7 @@
       </c>
       <c r="I44" s="23" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>1214427235</v>
+        <v>1191656305</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11633,7 +11638,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -11650,7 +11655,7 @@
       </c>
       <c r="I45" s="23" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1414427235</v>
+        <v>1391656305</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11661,7 +11666,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -11678,7 +11683,7 @@
       </c>
       <c r="I46" s="23" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1614427235</v>
+        <v>1591656305</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11689,7 +11694,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -11706,7 +11711,7 @@
       </c>
       <c r="I47" s="23" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1814427235</v>
+        <v>1791656305</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11717,7 +11722,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -11734,7 +11739,7 @@
       </c>
       <c r="I48" s="23" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>2014427235</v>
+        <v>1991656305</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11745,7 +11750,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -11762,7 +11767,7 @@
       </c>
       <c r="I49" s="23" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>2214427235</v>
+        <v>2191656305</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11773,7 +11778,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -11790,7 +11795,7 @@
       </c>
       <c r="I50" s="23" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2414427235</v>
+        <v>2391656305</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11801,7 +11806,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -11818,7 +11823,7 @@
       </c>
       <c r="I51" s="23" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2614427235</v>
+        <v>2591656305</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11829,7 +11834,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -11846,7 +11851,7 @@
       </c>
       <c r="I52" s="23" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2814427235</v>
+        <v>2791656305</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11857,7 +11862,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -11874,7 +11879,7 @@
       </c>
       <c r="I53" s="23" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>3014427235</v>
+        <v>2991656305</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11885,7 +11890,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -11902,12 +11907,12 @@
       </c>
       <c r="I54" s="23" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>3214427235</v>
+        <v>3191656305</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -648,10 +648,10 @@
     <t xml:space="preserve">Spider-Man Diamond 2</t>
   </si>
   <si>
+    <t xml:space="preserve">Yellowjacket Diamond 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not claimed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yellowjacket Diamond 3</t>
   </si>
   <si>
     <t xml:space="preserve">Crossbones Diamond 3</t>
@@ -4133,14 +4133,14 @@
         <v>156</v>
       </c>
       <c r="B6" s="19" t="n">
-        <v>440711000</v>
+        <v>542501630</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>157</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">B6+Scoring!F51</f>
-        <v>5987711000</v>
+        <v>5997501630</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6))+SUMPRODUCT((B13:B76="")*(F13:F76="Claimed"))</f>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>159</v>
@@ -4165,14 +4165,14 @@
       </c>
       <c r="B8" s="16" t="n">
         <f aca="false">IFERROR(INDEX(A13:A76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),"All done")</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>161</v>
       </c>
       <c r="E8" s="16" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6)*(F13:F76&lt;&gt;"Claimed"))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="B9" s="20" t="n">
         <f aca="false">IFERROR(INDEX(E13:E76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),0)</f>
-        <v>9289000</v>
+        <v>27498370</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,B76-B6)</f>
-        <v>3684289000</v>
+        <v>3582498370</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>534464107.246895</v>
+        <v>519788665.387178</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4878,15 +4878,15 @@
         <v>450000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="23" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>9289000</v>
+        <v>0</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4902,10 +4902,10 @@
       <c r="D52" s="12"/>
       <c r="E52" s="23" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>39289000</v>
+        <v>0</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4923,10 +4923,10 @@
       </c>
       <c r="E53" s="23" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>69289000</v>
+        <v>0</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4942,10 +4942,10 @@
       <c r="D54" s="12"/>
       <c r="E54" s="23" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>99289000</v>
+        <v>0</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4961,10 +4961,10 @@
       <c r="D55" s="12"/>
       <c r="E55" s="23" t="n">
         <f aca="false">IF(B55="","",MAX(0,B55-$B$6))</f>
-        <v>129289000</v>
+        <v>27498370</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4980,10 +4980,10 @@
       <c r="D56" s="12"/>
       <c r="E56" s="23" t="n">
         <f aca="false">IF(B56="","",MAX(0,B56-$B$6))</f>
-        <v>159289000</v>
+        <v>57498370</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4999,10 +4999,10 @@
       <c r="D57" s="12"/>
       <c r="E57" s="23" t="n">
         <f aca="false">IF(B57="","",MAX(0,B57-$B$6))</f>
-        <v>189289000</v>
+        <v>87498370</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5018,10 +5018,10 @@
       <c r="D58" s="12"/>
       <c r="E58" s="23" t="n">
         <f aca="false">IF(B58="","",MAX(0,B58-$B$6))</f>
-        <v>219289000</v>
+        <v>117498370</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5037,10 +5037,10 @@
       <c r="D59" s="12"/>
       <c r="E59" s="23" t="n">
         <f aca="false">IF(B59="","",MAX(0,B59-$B$6))</f>
-        <v>249289000</v>
+        <v>147498370</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5056,10 +5056,10 @@
       <c r="D60" s="12"/>
       <c r="E60" s="23" t="n">
         <f aca="false">IF(B60="","",MAX(0,B60-$B$6))</f>
-        <v>309289000</v>
+        <v>207498370</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5075,10 +5075,10 @@
       <c r="D61" s="12"/>
       <c r="E61" s="23" t="n">
         <f aca="false">IF(B61="","",MAX(0,B61-$B$6))</f>
-        <v>384289000</v>
+        <v>282498370</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5094,10 +5094,10 @@
       <c r="D62" s="12"/>
       <c r="E62" s="23" t="n">
         <f aca="false">IF(B62="","",MAX(0,B62-$B$6))</f>
-        <v>459289000</v>
+        <v>357498370</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5113,10 +5113,10 @@
       <c r="D63" s="12"/>
       <c r="E63" s="23" t="n">
         <f aca="false">IF(B63="","",MAX(0,B63-$B$6))</f>
-        <v>534289000</v>
+        <v>432498370</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5132,10 +5132,10 @@
       <c r="D64" s="12"/>
       <c r="E64" s="23" t="n">
         <f aca="false">IF(B64="","",MAX(0,B64-$B$6))</f>
-        <v>609289000</v>
+        <v>507498370</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5151,10 +5151,10 @@
       <c r="D65" s="12"/>
       <c r="E65" s="23" t="n">
         <f aca="false">IF(B65="","",MAX(0,B65-$B$6))</f>
-        <v>684289000</v>
+        <v>582498370</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5170,10 +5170,10 @@
       <c r="D66" s="12"/>
       <c r="E66" s="23" t="n">
         <f aca="false">IF(B66="","",MAX(0,B66-$B$6))</f>
-        <v>759289000</v>
+        <v>657498370</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5189,10 +5189,10 @@
       <c r="D67" s="12"/>
       <c r="E67" s="23" t="n">
         <f aca="false">IF(B67="","",MAX(0,B67-$B$6))</f>
-        <v>909289000</v>
+        <v>807498370</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5208,10 +5208,10 @@
       <c r="D68" s="12"/>
       <c r="E68" s="23" t="n">
         <f aca="false">IF(B68="","",MAX(0,B68-$B$6))</f>
-        <v>1059289000</v>
+        <v>957498370</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5227,10 +5227,10 @@
       <c r="D69" s="12"/>
       <c r="E69" s="23" t="n">
         <f aca="false">IF(B69="","",MAX(0,B69-$B$6))</f>
-        <v>1209289000</v>
+        <v>1107498370</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5246,10 +5246,10 @@
       <c r="D70" s="12"/>
       <c r="E70" s="23" t="n">
         <f aca="false">IF(B70="","",MAX(0,B70-$B$6))</f>
-        <v>1434289000</v>
+        <v>1332498370</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5265,10 +5265,10 @@
       <c r="D71" s="12"/>
       <c r="E71" s="23" t="n">
         <f aca="false">IF(B71="","",MAX(0,B71-$B$6))</f>
-        <v>1809289000</v>
+        <v>1707498370</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5284,10 +5284,10 @@
       <c r="D72" s="12"/>
       <c r="E72" s="23" t="n">
         <f aca="false">IF(B72="","",MAX(0,B72-$B$6))</f>
-        <v>2184289000</v>
+        <v>2082498370</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5303,10 +5303,10 @@
       <c r="D73" s="12"/>
       <c r="E73" s="23" t="n">
         <f aca="false">IF(B73="","",MAX(0,B73-$B$6))</f>
-        <v>2559289000</v>
+        <v>2457498370</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5322,10 +5322,10 @@
       <c r="D74" s="12"/>
       <c r="E74" s="23" t="n">
         <f aca="false">IF(B74="","",MAX(0,B74-$B$6))</f>
-        <v>2934289000</v>
+        <v>2832498370</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5341,10 +5341,10 @@
       <c r="D75" s="12"/>
       <c r="E75" s="23" t="n">
         <f aca="false">IF(B75="","",MAX(0,B75-$B$6))</f>
-        <v>3309289000</v>
+        <v>3207498370</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5360,10 +5360,10 @@
       <c r="D76" s="12"/>
       <c r="E76" s="23" t="n">
         <f aca="false">IF(B76="","",MAX(0,B76-$B$6))</f>
-        <v>3684289000</v>
+        <v>3582498370</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6045,11 +6045,11 @@
         <v>15000000</v>
       </c>
       <c r="E21" s="24" t="n">
-        <v>3000000</v>
+        <v>9000000</v>
       </c>
       <c r="F21" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D21),MAX(0,D21-E21),0)</f>
-        <v>12000000</v>
+        <v>6000000</v>
       </c>
       <c r="G21" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D21),ROUNDUP(D21/C21,0),"No limit")</f>
@@ -6057,11 +6057,11 @@
       </c>
       <c r="H21" s="25" t="n">
         <f aca="false">IFERROR(INT(E21/C21),0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" s="25" t="n">
         <f aca="false">IFERROR(ROUNDUP(F21/C21,0),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>247</v>
@@ -6081,11 +6081,11 @@
         <v>40000000</v>
       </c>
       <c r="E22" s="24" t="n">
-        <v>8000000</v>
+        <v>24000000</v>
       </c>
       <c r="F22" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D22),MAX(0,D22-E22),0)</f>
-        <v>32000000</v>
+        <v>16000000</v>
       </c>
       <c r="G22" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D22),ROUNDUP(D22/C22,0),"No limit")</f>
@@ -6093,11 +6093,11 @@
       </c>
       <c r="H22" s="25" t="n">
         <f aca="false">IFERROR(INT(E22/C22),0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22" s="25" t="n">
         <f aca="false">IFERROR(ROUNDUP(F22/C22,0),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>247</v>
@@ -6117,11 +6117,11 @@
         <v>15000000</v>
       </c>
       <c r="E23" s="24" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="F23" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D23),MAX(0,D23-E23),0)</f>
-        <v>15000000</v>
+        <v>9000000</v>
       </c>
       <c r="G23" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D23),ROUNDUP(D23/C23,0),"No limit")</f>
@@ -6129,11 +6129,11 @@
       </c>
       <c r="H23" s="25" t="n">
         <f aca="false">IFERROR(INT(E23/C23),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23" s="25" t="n">
         <f aca="false">IFERROR(ROUNDUP(F23/C23,0),0)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>247</v>
@@ -6153,11 +6153,11 @@
         <v>40000000</v>
       </c>
       <c r="E24" s="24" t="n">
-        <v>0</v>
+        <v>16000000</v>
       </c>
       <c r="F24" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D24),MAX(0,D24-E24),0)</f>
-        <v>40000000</v>
+        <v>24000000</v>
       </c>
       <c r="G24" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D24),ROUNDUP(D24/C24,0),"No limit")</f>
@@ -6165,11 +6165,11 @@
       </c>
       <c r="H24" s="25" t="n">
         <f aca="false">IFERROR(INT(E24/C24),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" s="25" t="n">
         <f aca="false">IFERROR(ROUNDUP(F24/C24,0),0)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J24" s="11" t="s">
         <v>247</v>
@@ -6189,11 +6189,11 @@
         <v>40000000</v>
       </c>
       <c r="E25" s="24" t="n">
-        <v>8000000</v>
+        <v>24000000</v>
       </c>
       <c r="F25" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D25),MAX(0,D25-E25),0)</f>
-        <v>32000000</v>
+        <v>16000000</v>
       </c>
       <c r="G25" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D25),ROUNDUP(D25/C25,0),"No limit")</f>
@@ -6201,11 +6201,11 @@
       </c>
       <c r="H25" s="25" t="n">
         <f aca="false">IFERROR(INT(E25/C25),0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25" s="25" t="n">
         <f aca="false">IFERROR(ROUNDUP(F25/C25,0),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>247</v>
@@ -6261,11 +6261,11 @@
         <v>40000000</v>
       </c>
       <c r="E27" s="24" t="n">
-        <v>8000000</v>
+        <v>24000000</v>
       </c>
       <c r="F27" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D27),MAX(0,D27-E27),0)</f>
-        <v>32000000</v>
+        <v>16000000</v>
       </c>
       <c r="G27" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D27),ROUNDUP(D27/C27,0),"No limit")</f>
@@ -6273,11 +6273,11 @@
       </c>
       <c r="H27" s="25" t="n">
         <f aca="false">IFERROR(INT(E27/C27),0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I27" s="25" t="n">
         <f aca="false">IFERROR(ROUNDUP(F27/C27,0),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>247</v>
@@ -6333,11 +6333,11 @@
         <v>40000000</v>
       </c>
       <c r="E29" s="24" t="n">
-        <v>0</v>
+        <v>16000000</v>
       </c>
       <c r="F29" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D29),MAX(0,D29-E29),0)</f>
-        <v>40000000</v>
+        <v>24000000</v>
       </c>
       <c r="G29" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D29),ROUNDUP(D29/C29,0),"No limit")</f>
@@ -6345,11 +6345,11 @@
       </c>
       <c r="H29" s="25" t="n">
         <f aca="false">IFERROR(INT(E29/C29),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29" s="25" t="n">
         <f aca="false">IFERROR(ROUNDUP(F29/C29,0),0)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>247</v>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="E49" s="20" t="n">
         <f aca="false">SUM(E5:E47)</f>
-        <v>393123500</v>
+        <v>485123500</v>
       </c>
       <c r="F49" s="20"/>
     </row>
@@ -7020,7 +7020,7 @@
       <c r="E50" s="20"/>
       <c r="F50" s="20" t="n">
         <f aca="false">SUM(F5:F47)</f>
-        <v>7508376500</v>
+        <v>7416376500</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7030,7 +7030,7 @@
       <c r="E51" s="20"/>
       <c r="F51" s="20" t="n">
         <f aca="false">SUMIF(J5:J47,"Yes",F5:F47)</f>
-        <v>5547000000</v>
+        <v>5455000000</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>16922833.1482074</v>
+        <v>16925792.8096126</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11133,7 +11133,7 @@
         <v>1900000</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I27" s="23" t="n">
         <f aca="false">IF(B27="","",MAX(0,B27-$B$6))</f>
@@ -11163,7 +11163,7 @@
         <v>1900000</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I28" s="23" t="n">
         <f aca="false">IF(B28="","",MAX(0,B28-$B$6))</f>
@@ -11193,7 +11193,7 @@
         <v>1900000</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I29" s="23" t="n">
         <f aca="false">IF(B29="","",MAX(0,B29-$B$6))</f>
@@ -11217,7 +11217,7 @@
       <c r="F30" s="26"/>
       <c r="G30" s="26"/>
       <c r="H30" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I30" s="23" t="n">
         <f aca="false">IF(B30="","",MAX(0,B30-$B$6))</f>
@@ -11247,7 +11247,7 @@
         <v>1900000</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I31" s="23" t="n">
         <f aca="false">IF(B31="","",MAX(0,B31-$B$6))</f>
@@ -11275,7 +11275,7 @@
         <v>1900000</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I32" s="23" t="n">
         <f aca="false">IF(B32="","",MAX(0,B32-$B$6))</f>
@@ -11305,7 +11305,7 @@
         <v>1900000</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I33" s="23" t="n">
         <f aca="false">IF(B33="","",MAX(0,B33-$B$6))</f>
@@ -11333,7 +11333,7 @@
         <v>1900000</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I34" s="23" t="n">
         <f aca="false">IF(B34="","",MAX(0,B34-$B$6))</f>
@@ -11363,7 +11363,7 @@
         <v>1900000</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I35" s="23" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
@@ -11391,7 +11391,7 @@
         <v>1900000</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I36" s="23" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
@@ -11421,7 +11421,7 @@
         <v>1900000</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I37" s="23" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
@@ -11449,7 +11449,7 @@
         <v>2000000</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I38" s="23" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
@@ -11479,7 +11479,7 @@
         <v>2000000</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I39" s="23" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
@@ -11507,7 +11507,7 @@
         <v>2000000</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I40" s="23" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
@@ -11537,7 +11537,7 @@
         <v>2000000</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I41" s="23" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
@@ -11565,7 +11565,7 @@
         <v>2000000</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I42" s="23" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
@@ -11595,7 +11595,7 @@
         <v>2000000</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I43" s="23" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
@@ -11623,7 +11623,7 @@
         <v>2700000</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I44" s="23" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
@@ -11651,7 +11651,7 @@
         <v>2700000</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I45" s="23" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
@@ -11679,7 +11679,7 @@
         <v>2700000</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I46" s="23" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
@@ -11707,7 +11707,7 @@
         <v>2700000</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I47" s="23" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
@@ -11735,7 +11735,7 @@
         <v>2700000</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I48" s="23" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
@@ -11763,7 +11763,7 @@
         <v>2700000</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I49" s="23" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
@@ -11791,7 +11791,7 @@
         <v>2700000</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I50" s="23" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
@@ -11819,7 +11819,7 @@
         <v>2700000</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I51" s="23" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
@@ -11847,7 +11847,7 @@
         <v>2700000</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I52" s="23" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
@@ -11875,7 +11875,7 @@
         <v>2700000</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I53" s="23" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
@@ -11903,7 +11903,7 @@
         <v>2700000</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I54" s="23" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="553">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -651,24 +651,24 @@
     <t xml:space="preserve">Yellowjacket Diamond 3</t>
   </si>
   <si>
+    <t xml:space="preserve">Crossbones Diamond 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whiplash Diamond 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bar and icon cut off, confirm in game</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulysses Klaue Diamond 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iron Monger Diamond 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not claimed</t>
   </si>
   <si>
-    <t xml:space="preserve">Crossbones Diamond 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whiplash Diamond 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bar and icon cut off, confirm in game</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ulysses Klaue Diamond 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iron Monger Diamond 1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hulk Diamond 3</t>
   </si>
   <si>
@@ -1090,9 +1090,6 @@
   </si>
   <si>
     <t xml:space="preserve">Iso Fest milestone 15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reached Oct 11, ready to claim</t>
   </si>
   <si>
     <t xml:space="preserve">Iso Fest milestone 16</t>
@@ -4172,7 +4169,7 @@
       </c>
       <c r="E8" s="16" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6)*(F13:F76&lt;&gt;"Claimed"))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4199,7 +4196,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>519788665.387178</v>
+        <v>520036015.470375</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4886,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4897,7 +4894,7 @@
         <v>480000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="23" t="n">
@@ -4905,7 +4902,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4916,17 +4913,17 @@
         <v>510000000</v>
       </c>
       <c r="C53" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="D53" s="12" t="s">
         <v>208</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>209</v>
       </c>
       <c r="E53" s="23" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
         <v>0</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4937,7 +4934,7 @@
         <v>540000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="23" t="n">
@@ -4945,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4956,7 +4953,7 @@
         <v>570000000</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D55" s="12"/>
       <c r="E55" s="23" t="n">
@@ -4964,7 +4961,7 @@
         <v>27498370</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4983,7 +4980,7 @@
         <v>57498370</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5002,7 +4999,7 @@
         <v>87498370</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5021,7 +5018,7 @@
         <v>117498370</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5040,7 +5037,7 @@
         <v>147498370</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5059,7 +5056,7 @@
         <v>207498370</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5078,7 +5075,7 @@
         <v>282498370</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5097,7 +5094,7 @@
         <v>357498370</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5116,7 +5113,7 @@
         <v>432498370</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5135,7 +5132,7 @@
         <v>507498370</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5154,7 +5151,7 @@
         <v>582498370</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5173,7 +5170,7 @@
         <v>657498370</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5192,7 +5189,7 @@
         <v>807498370</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5211,7 +5208,7 @@
         <v>957498370</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5230,7 +5227,7 @@
         <v>1107498370</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5249,7 +5246,7 @@
         <v>1332498370</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5268,7 +5265,7 @@
         <v>1707498370</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5287,7 +5284,7 @@
         <v>2082498370</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5306,7 +5303,7 @@
         <v>2457498370</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5325,7 +5322,7 @@
         <v>2832498370</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5344,7 +5341,7 @@
         <v>3207498370</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5363,7 +5360,7 @@
         <v>3582498370</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7122,13 +7119,13 @@
         <v>8434225</v>
       </c>
       <c r="C5" s="26" t="n">
-        <v>1146000</v>
+        <v>2046000</v>
       </c>
       <c r="D5" s="26" t="n">
-        <v>4370000</v>
+        <v>5670000</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>14390000</v>
+        <v>16290000</v>
       </c>
       <c r="F5" s="26" t="n">
         <v>226</v>
@@ -7150,15 +7147,15 @@
       </c>
       <c r="C6" s="27" t="n">
         <f aca="false">SUMIFS(C13:C69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
-        <v>5350000</v>
+        <v>4450000</v>
       </c>
       <c r="D6" s="27" t="n">
         <f aca="false">SUMIFS(D13:D69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
-        <v>4436000</v>
+        <v>3136000</v>
       </c>
       <c r="E6" s="27" t="n">
         <f aca="false">SUMIFS(E13:E69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
-        <v>6536000</v>
+        <v>4636000</v>
       </c>
       <c r="F6" s="27" t="n">
         <f aca="false">SUMIFS(F13:F69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
@@ -8143,13 +8140,13 @@
         <v>0</v>
       </c>
       <c r="C37" s="30" t="n">
-        <v>900000</v>
+        <v>0</v>
       </c>
       <c r="D37" s="30" t="n">
-        <v>1300000</v>
+        <v>0</v>
       </c>
       <c r="E37" s="30" t="n">
-        <v>1900000</v>
+        <v>0</v>
       </c>
       <c r="F37" s="30" t="n">
         <v>0</v>
@@ -8167,12 +8164,12 @@
         <v>251</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B38" s="30" t="n">
         <v>0</v>
@@ -8202,12 +8199,12 @@
         <v>251</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B39" s="30" t="n">
         <v>0</v>
@@ -8240,7 +8237,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B40" s="30" t="n">
         <v>900000</v>
@@ -8270,12 +8267,12 @@
         <v>251</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B41" s="30" t="n">
         <v>0</v>
@@ -8305,12 +8302,12 @@
         <v>251</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B42" s="30" t="n">
         <v>3300000</v>
@@ -8340,12 +8337,12 @@
         <v>247</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B43" s="30" t="n">
         <v>3300000</v>
@@ -8375,12 +8372,12 @@
         <v>251</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B44" s="30" t="n">
         <v>0</v>
@@ -8410,12 +8407,12 @@
         <v>251</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B45" s="30" t="n">
         <v>0</v>
@@ -8445,12 +8442,12 @@
         <v>251</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B46" s="30" t="n">
         <v>0</v>
@@ -8480,12 +8477,12 @@
         <v>251</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B47" s="30" t="n">
         <v>750000</v>
@@ -8515,12 +8512,12 @@
         <v>251</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B48" s="30" t="n">
         <v>750000</v>
@@ -8550,12 +8547,12 @@
         <v>251</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B49" s="30" t="n">
         <v>750000</v>
@@ -8585,12 +8582,12 @@
         <v>251</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B50" s="30" t="n">
         <v>750000</v>
@@ -8620,12 +8617,12 @@
         <v>251</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B51" s="30" t="n">
         <v>750000</v>
@@ -8655,12 +8652,12 @@
         <v>251</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B52" s="30" t="n">
         <v>750000</v>
@@ -8690,12 +8687,12 @@
         <v>251</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B53" s="30" t="n">
         <v>750000</v>
@@ -8725,12 +8722,12 @@
         <v>251</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B54" s="30" t="n">
         <v>750000</v>
@@ -8760,12 +8757,12 @@
         <v>251</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B55" s="30" t="n">
         <v>0</v>
@@ -8795,12 +8792,12 @@
         <v>251</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B56" s="30" t="n">
         <v>0</v>
@@ -8830,12 +8827,12 @@
         <v>251</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B57" s="30" t="n">
         <v>44475</v>
@@ -8865,12 +8862,12 @@
         <v>247</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B58" s="30" t="n">
         <v>11000</v>
@@ -8900,12 +8897,12 @@
         <v>247</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B59" s="30" t="n">
         <v>0</v>
@@ -8935,7 +8932,7 @@
         <v>251</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9070,12 +9067,12 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>306</v>
@@ -9110,7 +9107,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B73" s="30" t="n">
         <v>1837500</v>
@@ -9137,15 +9134,15 @@
         <v>0</v>
       </c>
       <c r="J73" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="K73" s="15" t="s">
         <v>393</v>
-      </c>
-      <c r="K73" s="15" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B74" s="30" t="n">
         <v>0</v>
@@ -9172,13 +9169,13 @@
         <v>0</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K74" s="15"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B75" s="30" t="n">
         <v>9791250</v>
@@ -9205,15 +9202,15 @@
         <v>55000000</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K75" s="15" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B76" s="30" t="n">
         <v>0</v>
@@ -9240,15 +9237,15 @@
         <v>0</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K76" s="15" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B77" s="26"/>
       <c r="C77" s="30" t="n">
@@ -9267,15 +9264,15 @@
         <v>3000000</v>
       </c>
       <c r="J77" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K77" s="15" t="s">
         <v>400</v>
-      </c>
-      <c r="K77" s="15" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B78" s="26"/>
       <c r="C78" s="30" t="n">
@@ -9294,15 +9291,15 @@
         <v>3000000</v>
       </c>
       <c r="J78" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K78" s="15" t="s">
         <v>400</v>
-      </c>
-      <c r="K78" s="15" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B79" s="26"/>
       <c r="C79" s="30" t="n">
@@ -9321,15 +9318,15 @@
         <v>3000000</v>
       </c>
       <c r="J79" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K79" s="15" t="s">
         <v>400</v>
-      </c>
-      <c r="K79" s="15" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B80" s="26"/>
       <c r="C80" s="30" t="n">
@@ -9348,15 +9345,15 @@
         <v>3000000</v>
       </c>
       <c r="J80" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K80" s="15" t="s">
         <v>400</v>
-      </c>
-      <c r="K80" s="15" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B81" s="26"/>
       <c r="C81" s="30" t="n">
@@ -9381,15 +9378,15 @@
         <v>17000000</v>
       </c>
       <c r="J81" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K81" s="15" t="s">
         <v>400</v>
-      </c>
-      <c r="K81" s="15" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B82" s="30" t="n">
         <v>0</v>
@@ -9416,15 +9413,15 @@
         <v>17000000</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K82" s="15" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B83" s="30" t="n">
         <v>0</v>
@@ -9445,15 +9442,15 @@
         <v>17000000</v>
       </c>
       <c r="J83" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K83" s="15" t="s">
         <v>400</v>
-      </c>
-      <c r="K83" s="15" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B84" s="30" t="n">
         <v>0</v>
@@ -9474,15 +9471,15 @@
         <v>17000000</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K84" s="15" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B85" s="30" t="n">
         <v>0</v>
@@ -9503,15 +9500,15 @@
         <v>17000000</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K85" s="15" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B86" s="30" t="n">
         <v>0</v>
@@ -9532,15 +9529,15 @@
         <v>17000000</v>
       </c>
       <c r="J86" s="11" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K86" s="15" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B87" s="30" t="n">
         <v>13000000</v>
@@ -9561,10 +9558,10 @@
         <v>8000000</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K87" s="15" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9647,7 +9644,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="16" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I95" s="20" t="n">
         <f aca="false">SUMIF(J73:J93,"Planned",I73:I93)</f>
@@ -9706,12 +9703,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9725,53 +9722,53 @@
         <v>306</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>425</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>428</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>429</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -9783,19 +9780,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C7" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -9807,19 +9804,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -9831,19 +9828,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -9855,19 +9852,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -9879,19 +9876,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -9903,19 +9900,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -9927,19 +9924,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -9951,19 +9948,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -9975,19 +9972,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -9999,19 +9996,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -10023,16 +10020,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>447</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>448</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -10045,19 +10042,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -10069,19 +10066,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -10093,19 +10090,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -10117,24 +10114,24 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="B22" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="C22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="15" t="s">
         <v>458</v>
       </c>
-      <c r="C22" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>459</v>
-      </c>
       <c r="E22" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -10146,16 +10143,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B23" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="C23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>458</v>
-      </c>
-      <c r="C23" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>459</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -10168,16 +10165,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B24" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="C24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="15" t="s">
         <v>458</v>
-      </c>
-      <c r="C24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>459</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -10190,19 +10187,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
+        <v>461</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>462</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>463</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -10214,19 +10211,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
+        <v>464</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="C26" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="15" t="s">
         <v>465</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="C26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>466</v>
-      </c>
       <c r="E26" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -10238,16 +10235,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
+        <v>466</v>
+      </c>
+      <c r="B27" s="13" t="s">
         <v>467</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="C27" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="15" t="s">
         <v>468</v>
-      </c>
-      <c r="C27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>469</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -10260,16 +10257,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
+        <v>469</v>
+      </c>
+      <c r="B28" s="13" t="s">
         <v>470</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="C28" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="15" t="s">
         <v>471</v>
-      </c>
-      <c r="C28" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>472</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -10282,21 +10279,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="B30" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="C30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="15" t="s">
         <v>475</v>
-      </c>
-      <c r="C30" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>476</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -10309,16 +10306,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="C31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="15" t="s">
         <v>477</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>475</v>
-      </c>
-      <c r="C31" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>478</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -10331,16 +10328,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="C32" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="15" t="s">
         <v>479</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>475</v>
-      </c>
-      <c r="C32" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>480</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -10353,19 +10350,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="B33" s="13" t="s">
         <v>481</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="C33" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="15" t="s">
         <v>482</v>
       </c>
-      <c r="C33" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>483</v>
-      </c>
       <c r="E33" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
@@ -10377,16 +10374,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="C34" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="15" t="s">
         <v>484</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>482</v>
-      </c>
-      <c r="C34" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>485</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -10399,16 +10396,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C35" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -10421,16 +10418,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="C36" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="15" t="s">
         <v>487</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>475</v>
-      </c>
-      <c r="C36" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>488</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -10443,16 +10440,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
+        <v>488</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="C37" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="15" t="s">
         <v>489</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>475</v>
-      </c>
-      <c r="C37" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>490</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -10465,7 +10462,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E39" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$37)*(E5:E37="Done"))</f>
@@ -10502,7 +10499,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E40" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$37,"Required",E5:E37,"Done")&amp;" of 11"</f>
@@ -10539,7 +10536,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -10583,12 +10580,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10596,10 +10593,10 @@
         <v>153</v>
       </c>
       <c r="B4" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>496</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10610,13 +10607,13 @@
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="16" t="s">
+        <v>497</v>
+      </c>
+      <c r="F5" s="16" t="s">
         <v>498</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="G5" s="16" t="s">
         <v>499</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10627,19 +10624,19 @@
         <v>308343695</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
-        <v>3150000</v>
+        <v>2250000</v>
       </c>
       <c r="F6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*F13:F54)</f>
-        <v>5500000</v>
+        <v>4200000</v>
       </c>
       <c r="G6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*G13:G54)</f>
-        <v>9500000</v>
+        <v>7600000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10655,15 +10652,15 @@
       </c>
       <c r="E7" s="20" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
-        <v>900000</v>
+        <v>0</v>
       </c>
       <c r="F7" s="20" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*F13:F54)</f>
-        <v>1300000</v>
+        <v>0</v>
       </c>
       <c r="G7" s="20" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*G13:G54)</f>
-        <v>1900000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10677,7 +10674,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -10685,7 +10682,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -10694,11 +10691,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>16925792.8096126</v>
+        <v>16933847.239244</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10709,19 +10706,19 @@
         <v>166</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>499</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>500</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
@@ -10737,7 +10734,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -10763,7 +10760,7 @@
       <c r="B14" s="26"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -10789,7 +10786,7 @@
       <c r="B15" s="26"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -10815,7 +10812,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -10840,10 +10837,10 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>509</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>510</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -10868,10 +10865,10 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>511</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>512</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -10896,10 +10893,10 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="12" t="s">
+        <v>512</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>513</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>514</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -10924,10 +10921,10 @@
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>515</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>516</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -10952,10 +10949,10 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>517</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>518</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -10980,10 +10977,10 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="12" t="s">
+        <v>518</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>519</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>520</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -11009,7 +11006,7 @@
       <c r="B23" s="26"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -11034,10 +11031,10 @@
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>522</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>523</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -11062,10 +11059,10 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="12" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -11090,10 +11087,10 @@
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="12" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -11121,7 +11118,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -11133,7 +11130,7 @@
         <v>1900000</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="I27" s="23" t="n">
         <f aca="false">IF(B27="","",MAX(0,B27-$B$6))</f>
@@ -11148,10 +11145,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -11163,7 +11160,7 @@
         <v>1900000</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I28" s="23" t="n">
         <f aca="false">IF(B28="","",MAX(0,B28-$B$6))</f>
@@ -11178,10 +11175,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -11193,7 +11190,7 @@
         <v>1900000</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I29" s="23" t="n">
         <f aca="false">IF(B29="","",MAX(0,B29-$B$6))</f>
@@ -11208,16 +11205,16 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
+        <v>527</v>
+      </c>
+      <c r="D30" s="12" t="s">
         <v>528</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>529</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
       <c r="G30" s="26"/>
       <c r="H30" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I30" s="23" t="n">
         <f aca="false">IF(B30="","",MAX(0,B30-$B$6))</f>
@@ -11232,10 +11229,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -11247,7 +11244,7 @@
         <v>1900000</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I31" s="23" t="n">
         <f aca="false">IF(B31="","",MAX(0,B31-$B$6))</f>
@@ -11262,7 +11259,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -11275,7 +11272,7 @@
         <v>1900000</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I32" s="23" t="n">
         <f aca="false">IF(B32="","",MAX(0,B32-$B$6))</f>
@@ -11290,10 +11287,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -11305,7 +11302,7 @@
         <v>1900000</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I33" s="23" t="n">
         <f aca="false">IF(B33="","",MAX(0,B33-$B$6))</f>
@@ -11320,7 +11317,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -11333,7 +11330,7 @@
         <v>1900000</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I34" s="23" t="n">
         <f aca="false">IF(B34="","",MAX(0,B34-$B$6))</f>
@@ -11348,10 +11345,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -11363,7 +11360,7 @@
         <v>1900000</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I35" s="23" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
@@ -11378,7 +11375,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -11391,7 +11388,7 @@
         <v>1900000</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I36" s="23" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
@@ -11406,10 +11403,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -11421,7 +11418,7 @@
         <v>1900000</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I37" s="23" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
@@ -11436,7 +11433,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -11449,7 +11446,7 @@
         <v>2000000</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I38" s="23" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
@@ -11464,10 +11461,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -11479,7 +11476,7 @@
         <v>2000000</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I39" s="23" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
@@ -11494,7 +11491,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -11507,7 +11504,7 @@
         <v>2000000</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I40" s="23" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
@@ -11522,10 +11519,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -11537,7 +11534,7 @@
         <v>2000000</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I41" s="23" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
@@ -11552,7 +11549,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -11565,7 +11562,7 @@
         <v>2000000</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I42" s="23" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
@@ -11580,10 +11577,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -11595,7 +11592,7 @@
         <v>2000000</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I43" s="23" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
@@ -11610,7 +11607,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -11623,7 +11620,7 @@
         <v>2700000</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I44" s="23" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
@@ -11638,7 +11635,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -11651,7 +11648,7 @@
         <v>2700000</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I45" s="23" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
@@ -11666,7 +11663,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -11679,7 +11676,7 @@
         <v>2700000</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I46" s="23" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
@@ -11694,7 +11691,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -11707,7 +11704,7 @@
         <v>2700000</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I47" s="23" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
@@ -11722,7 +11719,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -11735,7 +11732,7 @@
         <v>2700000</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I48" s="23" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
@@ -11750,7 +11747,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -11763,7 +11760,7 @@
         <v>2700000</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I49" s="23" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
@@ -11778,7 +11775,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -11791,7 +11788,7 @@
         <v>2700000</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I50" s="23" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
@@ -11806,7 +11803,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -11819,7 +11816,7 @@
         <v>2700000</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I51" s="23" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
@@ -11834,7 +11831,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -11847,7 +11844,7 @@
         <v>2700000</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I52" s="23" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
@@ -11862,7 +11859,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -11875,7 +11872,7 @@
         <v>2700000</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I53" s="23" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
@@ -11890,7 +11887,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -11903,7 +11900,7 @@
         <v>2700000</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I54" s="23" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
@@ -11912,7 +11909,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="556">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -159,27 +159,33 @@
     <t xml:space="preserve">Amazing Avengers</t>
   </si>
   <si>
+    <t xml:space="preserve">T3 L5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main team; next milestones upgrade him</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gear tier 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold and gear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T3 L5 done Oct 11, T4 matrix unlocked. Holding orange ions for now</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider-Man</t>
+  </si>
+  <si>
     <t xml:space="preserve">T3 L4</t>
   </si>
   <si>
-    <t xml:space="preserve">Main team; next milestones upgrade him</t>
+    <t xml:space="preserve">Main team; Diamond 4 at milestone 47</t>
   </si>
   <si>
     <t xml:space="preserve">Iso-8 to T3 L5</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71M, 2.64M, 1.71M purple ions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waits on Founding Force ions. Closest to gear tier 21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider-Man</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main team; Diamond 4 at milestone 47</t>
-  </si>
-  <si>
     <t xml:space="preserve">Purple ions</t>
   </si>
   <si>
@@ -1251,10 +1257,13 @@
     <t xml:space="preserve">Hulk Iso-8 to T3 level 5</t>
   </si>
   <si>
-    <t xml:space="preserve">From Quick Upgrade, Oct 11</t>
+    <t xml:space="preserve">Done Oct 11, plus 500 ion 1 to unlock the T4 matrix</t>
   </si>
   <si>
     <t xml:space="preserve">Spider-Man Iso-8 to T3 level 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumed same as Hulk. Confirm with Quick Upgrade</t>
   </si>
   <si>
     <t xml:space="preserve">Blade (Mighty) Iso-8 to T3 level 5</t>
@@ -2644,7 +2653,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
@@ -2654,7 +2663,9 @@
       <c r="C10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="6" t="n">
+        <v>105</v>
+      </c>
       <c r="E10" s="6" t="n">
         <v>20</v>
       </c>
@@ -2668,13 +2679,13 @@
         <v>44</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>17000000</v>
+        <v>150000000</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>45</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>46</v>
@@ -2693,25 +2704,25 @@
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>17000000</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2719,7 +2730,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>41</v>
@@ -2729,25 +2740,25 @@
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I12" s="8" t="n">
         <v>17000000</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2755,7 +2766,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>41</v>
@@ -2763,25 +2774,25 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I13" s="8" t="n">
         <v>17000000</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2789,7 +2800,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>41</v>
@@ -2797,25 +2808,25 @@
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I14" s="8" t="n">
         <v>17000000</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2823,17 +2834,17 @@
         <v>11</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I15" s="8" t="n">
         <v>0</v>
@@ -2843,7 +2854,7 @@
         <v>25</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2851,10 +2862,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>100</v>
@@ -2862,10 +2873,10 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I16" s="8" t="n">
         <v>3000000</v>
@@ -2877,7 +2888,7 @@
         <v>25</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2885,21 +2896,21 @@
         <v>13</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>80</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I17" s="8" t="n">
         <v>0</v>
@@ -2909,7 +2920,7 @@
         <v>25</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2917,10 +2928,10 @@
         <v>13</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>60</v>
@@ -2929,7 +2940,7 @@
       <c r="F18" s="4"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I18" s="8" t="n">
         <v>0</v>
@@ -2945,21 +2956,21 @@
         <v>13</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>105</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I19" s="8" t="n">
         <v>0</v>
@@ -2975,21 +2986,21 @@
         <v>13</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>105</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>0</v>
@@ -2999,7 +3010,7 @@
         <v>25</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3088,7 +3099,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -3139,12 +3150,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3155,22 +3166,22 @@
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>13</v>
@@ -3178,7 +3189,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>105</v>
@@ -3187,10 +3198,10 @@
         <v>1739574</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>41</v>
@@ -3201,7 +3212,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>105</v>
@@ -3210,10 +3221,10 @@
         <v>1702227</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="11"/>
@@ -3222,7 +3233,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>105</v>
@@ -3231,10 +3242,10 @@
         <v>1663516</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="11"/>
@@ -3243,7 +3254,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>105</v>
@@ -3252,23 +3263,23 @@
         <v>1649971</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
       <c r="I8" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>105</v>
@@ -3277,10 +3288,10 @@
         <v>1461088</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="11"/>
@@ -3289,7 +3300,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>100</v>
@@ -3298,10 +3309,10 @@
         <v>1401716</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="11"/>
@@ -3310,7 +3321,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>100</v>
@@ -3319,10 +3330,10 @@
         <v>1341960</v>
       </c>
       <c r="D11" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>92</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>90</v>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="11"/>
@@ -3331,7 +3342,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>105</v>
@@ -3340,10 +3351,10 @@
         <v>1322529</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="11"/>
@@ -3352,7 +3363,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>105</v>
@@ -3361,10 +3372,10 @@
         <v>1238262</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="11"/>
@@ -3373,7 +3384,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B14" s="12" t="n">
         <v>105</v>
@@ -3382,10 +3393,10 @@
         <v>1095153</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="11"/>
@@ -3394,7 +3405,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>103</v>
@@ -3403,10 +3414,10 @@
         <v>1062491</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F15" s="13"/>
       <c r="G15" s="11"/>
@@ -3415,7 +3426,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B16" s="12" t="n">
         <v>105</v>
@@ -3424,10 +3435,10 @@
         <v>1039168</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F16" s="13"/>
       <c r="G16" s="11"/>
@@ -3436,7 +3447,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B17" s="12" t="n">
         <v>104</v>
@@ -3445,10 +3456,10 @@
         <v>993737</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F17" s="13"/>
       <c r="G17" s="11"/>
@@ -3457,7 +3468,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B18" s="12" t="n">
         <v>100</v>
@@ -3466,10 +3477,10 @@
         <v>946060</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="11"/>
@@ -3478,7 +3489,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B19" s="12" t="n">
         <v>105</v>
@@ -3487,10 +3498,10 @@
         <v>900021</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="11"/>
@@ -3499,7 +3510,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B20" s="12" t="n">
         <v>100</v>
@@ -3508,10 +3519,10 @@
         <v>889970</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F20" s="13"/>
       <c r="G20" s="11"/>
@@ -3520,7 +3531,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B21" s="12" t="n">
         <v>100</v>
@@ -3529,10 +3540,10 @@
         <v>867448</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F21" s="13"/>
       <c r="G21" s="11"/>
@@ -3541,7 +3552,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B22" s="12" t="n">
         <v>100</v>
@@ -3550,10 +3561,10 @@
         <v>847430</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F22" s="13"/>
       <c r="G22" s="11"/>
@@ -3571,10 +3582,10 @@
         <v>827833</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>15</v>
@@ -3582,12 +3593,12 @@
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B24" s="12" t="n">
         <v>101</v>
@@ -3596,10 +3607,10 @@
         <v>818549</v>
       </c>
       <c r="D24" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="12" t="s">
         <v>92</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>90</v>
       </c>
       <c r="F24" s="13"/>
       <c r="G24" s="11"/>
@@ -3608,7 +3619,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>103</v>
@@ -3617,10 +3628,10 @@
         <v>787184</v>
       </c>
       <c r="D25" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>92</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>90</v>
       </c>
       <c r="F25" s="13"/>
       <c r="G25" s="11"/>
@@ -3629,7 +3640,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>96</v>
@@ -3638,10 +3649,10 @@
         <v>736328</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F26" s="13"/>
       <c r="G26" s="11"/>
@@ -3659,10 +3670,10 @@
         <v>731016</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>15</v>
@@ -3670,12 +3681,12 @@
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>95</v>
@@ -3684,10 +3695,10 @@
         <v>573611</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F28" s="13"/>
       <c r="G28" s="11"/>
@@ -3696,7 +3707,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B29" s="12" t="n">
         <v>100</v>
@@ -3705,10 +3716,10 @@
         <v>556594</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F29" s="13"/>
       <c r="G29" s="11"/>
@@ -3717,7 +3728,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>95</v>
@@ -3726,10 +3737,10 @@
         <v>427837</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F30" s="13"/>
       <c r="G30" s="11"/>
@@ -3738,7 +3749,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B31" s="12" t="n">
         <v>90</v>
@@ -3747,10 +3758,10 @@
         <v>334475</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F31" s="13"/>
       <c r="G31" s="11"/>
@@ -3759,7 +3770,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B32" s="12" t="n">
         <v>95</v>
@@ -3768,10 +3779,10 @@
         <v>309062</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F32" s="13"/>
       <c r="G32" s="11"/>
@@ -3780,7 +3791,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B33" s="12" t="n">
         <v>90</v>
@@ -3789,10 +3800,10 @@
         <v>305523</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F33" s="13"/>
       <c r="G33" s="11"/>
@@ -3801,7 +3812,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B34" s="12" t="n">
         <v>95</v>
@@ -3810,10 +3821,10 @@
         <v>302615</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F34" s="13"/>
       <c r="G34" s="11"/>
@@ -3822,7 +3833,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B35" s="12" t="n">
         <v>90</v>
@@ -3831,10 +3842,10 @@
         <v>269160</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F35" s="13"/>
       <c r="G35" s="11"/>
@@ -3843,7 +3854,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B36" s="12" t="n">
         <v>80</v>
@@ -3852,10 +3863,10 @@
         <v>250273</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F36" s="13"/>
       <c r="G36" s="11"/>
@@ -3864,7 +3875,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B37" s="12" t="n">
         <v>90</v>
@@ -3873,10 +3884,10 @@
         <v>245993</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F37" s="13"/>
       <c r="G37" s="11"/>
@@ -3885,7 +3896,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B38" s="12" t="n">
         <v>75</v>
@@ -3894,10 +3905,10 @@
         <v>228686</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F38" s="13"/>
       <c r="G38" s="11"/>
@@ -3906,7 +3917,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B39" s="12" t="n">
         <v>75</v>
@@ -3915,10 +3926,10 @@
         <v>144778</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F39" s="13"/>
       <c r="G39" s="11"/>
@@ -3936,10 +3947,10 @@
         <v>33212</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F40" s="13" t="s">
         <v>15</v>
@@ -3947,7 +3958,7 @@
       <c r="G40" s="11"/>
       <c r="H40" s="11"/>
       <c r="I40" s="15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3961,10 +3972,10 @@
         <v>32994</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F41" s="13" t="s">
         <v>15</v>
@@ -3984,10 +3995,10 @@
         <v>26827</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F42" s="13" t="s">
         <v>15</v>
@@ -3995,36 +4006,36 @@
       <c r="G42" s="11"/>
       <c r="H42" s="11"/>
       <c r="I42" s="15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B43" s="12"/>
       <c r="C43" s="14"/>
       <c r="D43" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E43" s="12"/>
       <c r="F43" s="13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G43" s="11"/>
       <c r="H43" s="11"/>
       <c r="I43" s="15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B44" s="12"/>
       <c r="C44" s="14"/>
       <c r="D44" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E44" s="12"/>
       <c r="F44" s="13"/>
@@ -4034,7 +4045,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B46" s="17" t="n">
         <f aca="false">COUNT(C5:C44)</f>
@@ -4043,7 +4054,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B47" s="17" t="n">
         <f aca="false">COUNTIF(C5:C44,"&gt;=1000000")</f>
@@ -4052,7 +4063,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="16" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B48" s="17" t="n">
         <f aca="false">COUNTIF(H5:H44,"Yes")</f>
@@ -4101,25 +4112,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>46313.7083333333</v>
@@ -4127,13 +4138,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B6" s="19" t="n">
         <v>542501630</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">B6+Scoring!F51</f>
@@ -4142,14 +4153,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6))+SUMPRODUCT((B13:B76="")*(F13:F76="Claimed"))</f>
         <v>42</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E7" s="16" t="n">
         <f aca="false">IFERROR(INDEX(A13:A76,MATCH(E6,B13:B76,1)),37)</f>
@@ -4158,14 +4169,14 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B8" s="16" t="n">
         <f aca="false">IFERROR(INDEX(A13:A76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),"All done")</f>
         <v>43</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E8" s="16" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6)*(F13:F76&lt;&gt;"Claimed"))</f>
@@ -4174,7 +4185,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B9" s="20" t="n">
         <f aca="false">IFERROR(INDEX(E13:E76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),0)</f>
@@ -4183,7 +4194,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,B76-B6)</f>
@@ -4192,28 +4203,28 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>520036015.470375</v>
+        <v>520855874.543334</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>12</v>
@@ -4225,7 +4236,7 @@
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="23" t="str">
@@ -4233,7 +4244,7 @@
         <v/>
       </c>
       <c r="F13" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4242,7 +4253,7 @@
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="23" t="str">
@@ -4250,7 +4261,7 @@
         <v/>
       </c>
       <c r="F14" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4259,7 +4270,7 @@
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="23" t="str">
@@ -4267,7 +4278,7 @@
         <v/>
       </c>
       <c r="F15" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4276,7 +4287,7 @@
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="23" t="str">
@@ -4284,7 +4295,7 @@
         <v/>
       </c>
       <c r="F16" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4293,7 +4304,7 @@
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="23" t="str">
@@ -4301,7 +4312,7 @@
         <v/>
       </c>
       <c r="F17" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4310,7 +4321,7 @@
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="23" t="str">
@@ -4318,7 +4329,7 @@
         <v/>
       </c>
       <c r="F18" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4327,7 +4338,7 @@
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="23" t="str">
@@ -4335,7 +4346,7 @@
         <v/>
       </c>
       <c r="F19" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4344,7 +4355,7 @@
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="23" t="str">
@@ -4352,7 +4363,7 @@
         <v/>
       </c>
       <c r="F20" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4361,7 +4372,7 @@
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D21" s="12"/>
       <c r="E21" s="23" t="str">
@@ -4369,7 +4380,7 @@
         <v/>
       </c>
       <c r="F21" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4378,7 +4389,7 @@
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="23" t="str">
@@ -4386,7 +4397,7 @@
         <v/>
       </c>
       <c r="F22" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4395,7 +4406,7 @@
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="12" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="23" t="str">
@@ -4403,7 +4414,7 @@
         <v/>
       </c>
       <c r="F23" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4412,7 +4423,7 @@
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="12" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="23" t="str">
@@ -4420,7 +4431,7 @@
         <v/>
       </c>
       <c r="F24" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4429,7 +4440,7 @@
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="23" t="str">
@@ -4437,7 +4448,7 @@
         <v/>
       </c>
       <c r="F25" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4446,7 +4457,7 @@
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="23" t="str">
@@ -4454,7 +4465,7 @@
         <v/>
       </c>
       <c r="F26" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4463,7 +4474,7 @@
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="12" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="23" t="str">
@@ -4471,7 +4482,7 @@
         <v/>
       </c>
       <c r="F27" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4480,7 +4491,7 @@
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="23" t="str">
@@ -4488,7 +4499,7 @@
         <v/>
       </c>
       <c r="F28" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4497,7 +4508,7 @@
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="23" t="str">
@@ -4505,7 +4516,7 @@
         <v/>
       </c>
       <c r="F29" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4514,7 +4525,7 @@
       </c>
       <c r="B30" s="14"/>
       <c r="C30" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="23" t="str">
@@ -4522,7 +4533,7 @@
         <v/>
       </c>
       <c r="F30" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4531,7 +4542,7 @@
       </c>
       <c r="B31" s="14"/>
       <c r="C31" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="23" t="str">
@@ -4539,7 +4550,7 @@
         <v/>
       </c>
       <c r="F31" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4548,7 +4559,7 @@
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="23" t="str">
@@ -4556,7 +4567,7 @@
         <v/>
       </c>
       <c r="F32" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4565,7 +4576,7 @@
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="23" t="str">
@@ -4573,7 +4584,7 @@
         <v/>
       </c>
       <c r="F33" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4582,7 +4593,7 @@
       </c>
       <c r="B34" s="14"/>
       <c r="C34" s="12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="23" t="str">
@@ -4590,7 +4601,7 @@
         <v/>
       </c>
       <c r="F34" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4599,7 +4610,7 @@
       </c>
       <c r="B35" s="14"/>
       <c r="C35" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="23" t="str">
@@ -4607,7 +4618,7 @@
         <v/>
       </c>
       <c r="F35" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4616,7 +4627,7 @@
       </c>
       <c r="B36" s="14"/>
       <c r="C36" s="12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="23" t="str">
@@ -4624,7 +4635,7 @@
         <v/>
       </c>
       <c r="F36" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4633,7 +4644,7 @@
       </c>
       <c r="B37" s="14"/>
       <c r="C37" s="12" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="23" t="str">
@@ -4641,7 +4652,7 @@
         <v/>
       </c>
       <c r="F37" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4650,7 +4661,7 @@
       </c>
       <c r="B38" s="14"/>
       <c r="C38" s="12" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="23" t="str">
@@ -4658,7 +4669,7 @@
         <v/>
       </c>
       <c r="F38" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4667,7 +4678,7 @@
       </c>
       <c r="B39" s="14"/>
       <c r="C39" s="12" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="23" t="str">
@@ -4675,7 +4686,7 @@
         <v/>
       </c>
       <c r="F39" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4684,7 +4695,7 @@
       </c>
       <c r="B40" s="14"/>
       <c r="C40" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="23" t="str">
@@ -4692,7 +4703,7 @@
         <v/>
       </c>
       <c r="F40" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4701,7 +4712,7 @@
       </c>
       <c r="B41" s="14"/>
       <c r="C41" s="12" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="23" t="str">
@@ -4709,7 +4720,7 @@
         <v/>
       </c>
       <c r="F41" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4719,14 +4730,14 @@
       <c r="B42" s="14"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E42" s="23" t="str">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
         <v/>
       </c>
       <c r="F42" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4736,14 +4747,14 @@
       <c r="B43" s="14"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E43" s="23" t="str">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
         <v/>
       </c>
       <c r="F43" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4753,14 +4764,14 @@
       <c r="B44" s="14"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E44" s="23" t="str">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
         <v/>
       </c>
       <c r="F44" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4770,14 +4781,14 @@
       <c r="B45" s="14"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E45" s="23" t="str">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
         <v/>
       </c>
       <c r="F45" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4786,7 +4797,7 @@
       </c>
       <c r="B46" s="14"/>
       <c r="C46" s="12" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="23" t="str">
@@ -4794,7 +4805,7 @@
         <v/>
       </c>
       <c r="F46" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4803,7 +4814,7 @@
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="23" t="str">
@@ -4811,7 +4822,7 @@
         <v/>
       </c>
       <c r="F47" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4820,7 +4831,7 @@
       </c>
       <c r="B48" s="14"/>
       <c r="C48" s="12" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="23" t="str">
@@ -4828,7 +4839,7 @@
         <v/>
       </c>
       <c r="F48" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4837,7 +4848,7 @@
       </c>
       <c r="B49" s="14"/>
       <c r="C49" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="23" t="str">
@@ -4845,7 +4856,7 @@
         <v/>
       </c>
       <c r="F49" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4856,7 +4867,7 @@
         <v>435000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="23" t="n">
@@ -4864,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4875,7 +4886,7 @@
         <v>450000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="23" t="n">
@@ -4883,7 +4894,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4894,7 +4905,7 @@
         <v>480000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="23" t="n">
@@ -4902,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4913,17 +4924,17 @@
         <v>510000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E53" s="23" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
         <v>0</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4934,7 +4945,7 @@
         <v>540000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="23" t="n">
@@ -4942,7 +4953,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4953,7 +4964,7 @@
         <v>570000000</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D55" s="12"/>
       <c r="E55" s="23" t="n">
@@ -4961,7 +4972,7 @@
         <v>27498370</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4972,7 +4983,7 @@
         <v>600000000</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D56" s="12"/>
       <c r="E56" s="23" t="n">
@@ -4980,7 +4991,7 @@
         <v>57498370</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4991,7 +5002,7 @@
         <v>630000000</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D57" s="12"/>
       <c r="E57" s="23" t="n">
@@ -4999,7 +5010,7 @@
         <v>87498370</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5010,7 +5021,7 @@
         <v>660000000</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D58" s="12"/>
       <c r="E58" s="23" t="n">
@@ -5018,7 +5029,7 @@
         <v>117498370</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5029,7 +5040,7 @@
         <v>690000000</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D59" s="12"/>
       <c r="E59" s="23" t="n">
@@ -5037,7 +5048,7 @@
         <v>147498370</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5048,7 +5059,7 @@
         <v>750000000</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D60" s="12"/>
       <c r="E60" s="23" t="n">
@@ -5056,7 +5067,7 @@
         <v>207498370</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5067,7 +5078,7 @@
         <v>825000000</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D61" s="12"/>
       <c r="E61" s="23" t="n">
@@ -5075,7 +5086,7 @@
         <v>282498370</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5086,7 +5097,7 @@
         <v>900000000</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D62" s="12"/>
       <c r="E62" s="23" t="n">
@@ -5094,7 +5105,7 @@
         <v>357498370</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5105,7 +5116,7 @@
         <v>975000000</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D63" s="12"/>
       <c r="E63" s="23" t="n">
@@ -5113,7 +5124,7 @@
         <v>432498370</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5124,7 +5135,7 @@
         <v>1050000000</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D64" s="12"/>
       <c r="E64" s="23" t="n">
@@ -5132,7 +5143,7 @@
         <v>507498370</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5143,7 +5154,7 @@
         <v>1125000000</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D65" s="12"/>
       <c r="E65" s="23" t="n">
@@ -5151,7 +5162,7 @@
         <v>582498370</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5162,7 +5173,7 @@
         <v>1200000000</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D66" s="12"/>
       <c r="E66" s="23" t="n">
@@ -5170,7 +5181,7 @@
         <v>657498370</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5181,7 +5192,7 @@
         <v>1350000000</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D67" s="12"/>
       <c r="E67" s="23" t="n">
@@ -5189,7 +5200,7 @@
         <v>807498370</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5200,7 +5211,7 @@
         <v>1500000000</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D68" s="12"/>
       <c r="E68" s="23" t="n">
@@ -5208,7 +5219,7 @@
         <v>957498370</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5219,7 +5230,7 @@
         <v>1650000000</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D69" s="12"/>
       <c r="E69" s="23" t="n">
@@ -5227,7 +5238,7 @@
         <v>1107498370</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5238,7 +5249,7 @@
         <v>1875000000</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D70" s="12"/>
       <c r="E70" s="23" t="n">
@@ -5246,7 +5257,7 @@
         <v>1332498370</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5257,7 +5268,7 @@
         <v>2250000000</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D71" s="12"/>
       <c r="E71" s="23" t="n">
@@ -5265,7 +5276,7 @@
         <v>1707498370</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5276,7 +5287,7 @@
         <v>2625000000</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D72" s="12"/>
       <c r="E72" s="23" t="n">
@@ -5284,7 +5295,7 @@
         <v>2082498370</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5295,7 +5306,7 @@
         <v>3000000000</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D73" s="12"/>
       <c r="E73" s="23" t="n">
@@ -5303,7 +5314,7 @@
         <v>2457498370</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5314,7 +5325,7 @@
         <v>3375000000</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D74" s="12"/>
       <c r="E74" s="23" t="n">
@@ -5322,7 +5333,7 @@
         <v>2832498370</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5333,7 +5344,7 @@
         <v>3750000000</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D75" s="12"/>
       <c r="E75" s="23" t="n">
@@ -5341,7 +5352,7 @@
         <v>3207498370</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5352,7 +5363,7 @@
         <v>4125000000</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D76" s="12"/>
       <c r="E76" s="23" t="n">
@@ -5360,7 +5371,7 @@
         <v>3582498370</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5412,52 +5423,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>4000000</v>
@@ -5485,15 +5496,15 @@
         <v>7</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C6" s="14" t="n">
         <v>4000000</v>
@@ -5521,15 +5532,15 @@
         <v>8</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C7" s="14" t="n">
         <v>1</v>
@@ -5557,15 +5568,15 @@
         <v>963976500</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C8" s="14" t="n">
         <v>4000</v>
@@ -5593,7 +5604,7 @@
         <v>249350</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5601,7 +5612,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C9" s="14" t="n">
         <v>3000000</v>
@@ -5629,7 +5640,7 @@
         <v>4</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5637,7 +5648,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C10" s="14" t="n">
         <v>8000000</v>
@@ -5665,15 +5676,15 @@
         <v>5</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C11" s="14" t="n">
         <v>7000000</v>
@@ -5701,15 +5712,15 @@
         <v>0</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C12" s="14" t="n">
         <v>17000000</v>
@@ -5737,15 +5748,15 @@
         <v>0</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C13" s="14" t="n">
         <v>7000000</v>
@@ -5773,15 +5784,15 @@
         <v>0</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>17000000</v>
@@ -5809,15 +5820,15 @@
         <v>5</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C15" s="14" t="n">
         <v>7000000</v>
@@ -5845,15 +5856,15 @@
         <v>0</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C16" s="14" t="n">
         <v>17000000</v>
@@ -5881,15 +5892,15 @@
         <v>5</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C17" s="14" t="n">
         <v>3000000</v>
@@ -5917,15 +5928,15 @@
         <v>0</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C18" s="14" t="n">
         <v>8000000</v>
@@ -5953,15 +5964,15 @@
         <v>0</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C19" s="14" t="n">
         <v>3000000</v>
@@ -5989,15 +6000,15 @@
         <v>0</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C20" s="14" t="n">
         <v>8000000</v>
@@ -6025,15 +6036,15 @@
         <v>0</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C21" s="14" t="n">
         <v>3000000</v>
@@ -6061,15 +6072,15 @@
         <v>2</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C22" s="14" t="n">
         <v>8000000</v>
@@ -6097,15 +6108,15 @@
         <v>2</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C23" s="14" t="n">
         <v>3000000</v>
@@ -6133,15 +6144,15 @@
         <v>3</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C24" s="14" t="n">
         <v>8000000</v>
@@ -6169,15 +6180,15 @@
         <v>3</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C25" s="14" t="n">
         <v>8000000</v>
@@ -6205,15 +6216,15 @@
         <v>2</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C26" s="14" t="n">
         <v>17000000</v>
@@ -6241,15 +6252,15 @@
         <v>5</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C27" s="14" t="n">
         <v>8000000</v>
@@ -6277,15 +6288,15 @@
         <v>2</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C28" s="14" t="n">
         <v>17000000</v>
@@ -6313,15 +6324,15 @@
         <v>5</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C29" s="14" t="n">
         <v>8000000</v>
@@ -6349,15 +6360,15 @@
         <v>3</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C30" s="14" t="n">
         <v>17000000</v>
@@ -6385,15 +6396,15 @@
         <v>5</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C31" s="14" t="n">
         <v>40000000</v>
@@ -6421,15 +6432,15 @@
         <v>2</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C32" s="14" t="n">
         <v>80000000</v>
@@ -6457,15 +6468,15 @@
         <v>2</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C33" s="14" t="n">
         <v>150000000</v>
@@ -6493,15 +6504,15 @@
         <v>2</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C34" s="14" t="n">
         <v>200000000</v>
@@ -6529,15 +6540,15 @@
         <v>1</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C35" s="14" t="n">
         <v>200000000</v>
@@ -6565,15 +6576,15 @@
         <v>1</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C36" s="14" t="n">
         <v>17000000</v>
@@ -6601,15 +6612,15 @@
         <v>5</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C37" s="14" t="n">
         <v>150000000</v>
@@ -6637,15 +6648,15 @@
         <v>5</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C38" s="14" t="n">
         <v>17000000</v>
@@ -6673,15 +6684,15 @@
         <v>5</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C39" s="14" t="n">
         <v>50000000</v>
@@ -6709,15 +6720,15 @@
         <v>5</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C40" s="14" t="n">
         <v>150000000</v>
@@ -6745,15 +6756,15 @@
         <v>5</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C41" s="14" t="n">
         <v>17000000</v>
@@ -6781,15 +6792,15 @@
         <v>5</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C42" s="14" t="n">
         <v>150000000</v>
@@ -6817,15 +6828,15 @@
         <v>5</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C43" s="14" t="n">
         <v>17000000</v>
@@ -6853,15 +6864,15 @@
         <v>5</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C44" s="14" t="n">
         <v>50000000</v>
@@ -6889,15 +6900,15 @@
         <v>5</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C45" s="14" t="n">
         <v>150000000</v>
@@ -6925,15 +6936,15 @@
         <v>5</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C46" s="14" t="n">
         <v>4500000</v>
@@ -6961,21 +6972,21 @@
         <v>6</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C47" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E47" s="24" t="n">
         <v>0</v>
@@ -6997,12 +7008,12 @@
         <v>0</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="16" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E49" s="20" t="n">
         <f aca="false">SUM(E5:E47)</f>
@@ -7012,7 +7023,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="16" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E50" s="20"/>
       <c r="F50" s="20" t="n">
@@ -7022,7 +7033,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="16" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E51" s="20"/>
       <c r="F51" s="20" t="n">
@@ -7032,7 +7043,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -7077,55 +7088,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B5" s="26" t="n">
         <v>8434225</v>
       </c>
       <c r="C5" s="26" t="n">
-        <v>2046000</v>
+        <v>336000</v>
       </c>
       <c r="D5" s="26" t="n">
-        <v>5670000</v>
+        <v>3960000</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>16290000</v>
+        <v>13650000</v>
       </c>
       <c r="F5" s="26" t="n">
         <v>226</v>
@@ -7139,7 +7150,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B6" s="27" t="n">
         <f aca="false">SUMIFS(B13:B69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
@@ -7172,7 +7183,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
@@ -7180,15 +7191,15 @@
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5+C6</f>
-        <v>6496000</v>
+        <v>4786000</v>
       </c>
       <c r="D7" s="27" t="n">
         <f aca="false">D5+D6</f>
-        <v>8806000</v>
+        <v>7096000</v>
       </c>
       <c r="E7" s="27" t="n">
         <f aca="false">E5+E6</f>
-        <v>20926000</v>
+        <v>18286000</v>
       </c>
       <c r="F7" s="27" t="n">
         <f aca="false">F5+F6</f>
@@ -7205,7 +7216,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B8" s="27" t="n">
         <f aca="false">SUMIF($J$73:$J$93,"Planned",B73:B93)</f>
@@ -7217,11 +7228,11 @@
       </c>
       <c r="D8" s="27" t="n">
         <f aca="false">SUMIF($J$73:$J$93,"Planned",D73:D93)</f>
-        <v>2640000</v>
+        <v>1710000</v>
       </c>
       <c r="E8" s="27" t="n">
         <f aca="false">SUMIF($J$73:$J$93,"Planned",E73:E93)</f>
-        <v>1710000</v>
+        <v>2640000</v>
       </c>
       <c r="F8" s="27" t="n">
         <f aca="false">SUMIF($J$73:$J$93,"Planned",F73:F93)</f>
@@ -7238,7 +7249,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B7-B8</f>
@@ -7246,15 +7257,15 @@
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">C7-C8</f>
-        <v>4786000</v>
+        <v>3076000</v>
       </c>
       <c r="D9" s="28" t="n">
         <f aca="false">D7-D8</f>
-        <v>6166000</v>
+        <v>5386000</v>
       </c>
       <c r="E9" s="28" t="n">
         <f aca="false">E7-E8</f>
-        <v>19216000</v>
+        <v>15646000</v>
       </c>
       <c r="F9" s="28" t="n">
         <f aca="false">F7-F8</f>
@@ -7271,44 +7282,44 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="29" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>13</v>
@@ -7316,7 +7327,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B13" s="30" t="n">
         <v>100000</v>
@@ -7340,18 +7351,18 @@
         <v>0</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B14" s="30" t="n">
         <v>1600000</v>
@@ -7375,18 +7386,18 @@
         <v>0</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B15" s="30" t="n">
         <v>1600000</v>
@@ -7410,18 +7421,18 @@
         <v>0</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B16" s="30" t="n">
         <v>1600000</v>
@@ -7445,18 +7456,18 @@
         <v>0</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B17" s="30" t="n">
         <v>1600000</v>
@@ -7480,18 +7491,18 @@
         <v>0</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B18" s="30" t="n">
         <v>1600000</v>
@@ -7515,18 +7526,18 @@
         <v>0</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B19" s="30" t="n">
         <v>1600000</v>
@@ -7550,18 +7561,18 @@
         <v>0</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B20" s="30" t="n">
         <v>1600000</v>
@@ -7585,18 +7596,18 @@
         <v>0</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B21" s="30" t="n">
         <v>100000</v>
@@ -7620,16 +7631,16 @@
         <v>0</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B22" s="30" t="n">
         <v>200000</v>
@@ -7653,16 +7664,16 @@
         <v>0</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K22" s="15"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B23" s="30" t="n">
         <v>0</v>
@@ -7686,18 +7697,18 @@
         <v>0</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B24" s="30" t="n">
         <v>150000</v>
@@ -7721,16 +7732,16 @@
         <v>15</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B25" s="30" t="n">
         <v>150000</v>
@@ -7754,16 +7765,16 @@
         <v>20</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B26" s="30" t="n">
         <v>200000</v>
@@ -7787,16 +7798,16 @@
         <v>25</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K26" s="15"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B27" s="30" t="n">
         <v>250000</v>
@@ -7820,16 +7831,16 @@
         <v>30</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K27" s="15"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B28" s="30" t="n">
         <v>300000</v>
@@ -7853,16 +7864,16 @@
         <v>40</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K28" s="15"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B29" s="30" t="n">
         <v>350000</v>
@@ -7886,16 +7897,16 @@
         <v>45</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K29" s="15"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B30" s="30" t="n">
         <v>0</v>
@@ -7919,18 +7930,18 @@
         <v>0</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B31" s="30" t="n">
         <v>0</v>
@@ -7954,53 +7965,53 @@
         <v>0</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K32" s="15" t="s">
         <v>346</v>
-      </c>
-      <c r="B32" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="J32" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="K32" s="15" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B33" s="30" t="n">
         <v>0</v>
@@ -8024,16 +8035,16 @@
         <v>800</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K33" s="15"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B34" s="30" t="n">
         <v>10000000</v>
@@ -8057,16 +8068,16 @@
         <v>0</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K34" s="15"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B35" s="30" t="n">
         <v>500000</v>
@@ -8090,16 +8101,16 @@
         <v>0</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K35" s="15"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B36" s="30" t="n">
         <v>0</v>
@@ -8123,18 +8134,18 @@
         <v>0</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B37" s="30" t="n">
         <v>0</v>
@@ -8158,18 +8169,18 @@
         <v>0</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B38" s="30" t="n">
         <v>0</v>
@@ -8193,18 +8204,18 @@
         <v>0</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B39" s="30" t="n">
         <v>0</v>
@@ -8228,16 +8239,16 @@
         <v>0</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K39" s="15"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B40" s="30" t="n">
         <v>900000</v>
@@ -8261,18 +8272,18 @@
         <v>0</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B41" s="30" t="n">
         <v>0</v>
@@ -8296,18 +8307,18 @@
         <v>90</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B42" s="30" t="n">
         <v>3300000</v>
@@ -8331,18 +8342,18 @@
         <v>0</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B43" s="30" t="n">
         <v>3300000</v>
@@ -8366,18 +8377,18 @@
         <v>0</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B44" s="30" t="n">
         <v>0</v>
@@ -8401,18 +8412,18 @@
         <v>0</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B45" s="30" t="n">
         <v>0</v>
@@ -8436,18 +8447,18 @@
         <v>0</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B46" s="30" t="n">
         <v>0</v>
@@ -8471,18 +8482,18 @@
         <v>0</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B47" s="30" t="n">
         <v>750000</v>
@@ -8506,18 +8517,18 @@
         <v>0</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B48" s="30" t="n">
         <v>750000</v>
@@ -8541,18 +8552,18 @@
         <v>0</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B49" s="30" t="n">
         <v>750000</v>
@@ -8576,18 +8587,18 @@
         <v>0</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B50" s="30" t="n">
         <v>750000</v>
@@ -8611,18 +8622,18 @@
         <v>0</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B51" s="30" t="n">
         <v>750000</v>
@@ -8646,18 +8657,18 @@
         <v>0</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B52" s="30" t="n">
         <v>750000</v>
@@ -8681,18 +8692,18 @@
         <v>0</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B53" s="30" t="n">
         <v>750000</v>
@@ -8716,18 +8727,18 @@
         <v>0</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B54" s="30" t="n">
         <v>750000</v>
@@ -8751,18 +8762,18 @@
         <v>0</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B55" s="30" t="n">
         <v>0</v>
@@ -8786,18 +8797,18 @@
         <v>0</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B56" s="30" t="n">
         <v>0</v>
@@ -8821,18 +8832,18 @@
         <v>0</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B57" s="30" t="n">
         <v>44475</v>
@@ -8856,18 +8867,18 @@
         <v>0</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B58" s="30" t="n">
         <v>11000</v>
@@ -8891,18 +8902,18 @@
         <v>0</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B59" s="30" t="n">
         <v>0</v>
@@ -8926,13 +8937,13 @@
         <v>0</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9067,33 +9078,33 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="29" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>10</v>
@@ -9107,7 +9118,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B73" s="30" t="n">
         <v>1837500</v>
@@ -9134,15 +9145,15 @@
         <v>0</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K73" s="15" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B74" s="30" t="n">
         <v>0</v>
@@ -9169,13 +9180,13 @@
         <v>0</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K74" s="15"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B75" s="30" t="n">
         <v>9791250</v>
@@ -9202,15 +9213,15 @@
         <v>55000000</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K75" s="15" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B76" s="30" t="n">
         <v>0</v>
@@ -9237,15 +9248,15 @@
         <v>0</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K76" s="15" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B77" s="26"/>
       <c r="C77" s="30" t="n">
@@ -9264,15 +9275,15 @@
         <v>3000000</v>
       </c>
       <c r="J77" s="11" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K77" s="15" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B78" s="26"/>
       <c r="C78" s="30" t="n">
@@ -9291,15 +9302,15 @@
         <v>3000000</v>
       </c>
       <c r="J78" s="11" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K78" s="15" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B79" s="26"/>
       <c r="C79" s="30" t="n">
@@ -9318,15 +9329,15 @@
         <v>3000000</v>
       </c>
       <c r="J79" s="11" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B80" s="26"/>
       <c r="C80" s="30" t="n">
@@ -9345,15 +9356,15 @@
         <v>3000000</v>
       </c>
       <c r="J80" s="11" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K80" s="15" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B81" s="26"/>
       <c r="C81" s="30" t="n">
@@ -9378,27 +9389,27 @@
         <v>17000000</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B82" s="30" t="n">
         <v>0</v>
       </c>
       <c r="C82" s="30" t="n">
+        <v>1710500</v>
+      </c>
+      <c r="D82" s="30" t="n">
         <v>1710000</v>
       </c>
-      <c r="D82" s="30" t="n">
+      <c r="E82" s="30" t="n">
         <v>2640000</v>
-      </c>
-      <c r="E82" s="30" t="n">
-        <v>1710000</v>
       </c>
       <c r="F82" s="30" t="n">
         <v>0</v>
@@ -9413,22 +9424,28 @@
         <v>17000000</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="K82" s="15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B83" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C83" s="26"/>
-      <c r="D83" s="26"/>
-      <c r="E83" s="26"/>
+      <c r="C83" s="30" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="D83" s="30" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="E83" s="30" t="n">
+        <v>2640000</v>
+      </c>
       <c r="F83" s="30" t="n">
         <v>0</v>
       </c>
@@ -9442,15 +9459,15 @@
         <v>17000000</v>
       </c>
       <c r="J83" s="11" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K83" s="15" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B84" s="30" t="n">
         <v>0</v>
@@ -9471,15 +9488,15 @@
         <v>17000000</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="K84" s="15" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B85" s="30" t="n">
         <v>0</v>
@@ -9500,15 +9517,15 @@
         <v>17000000</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="K85" s="15" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B86" s="30" t="n">
         <v>0</v>
@@ -9529,15 +9546,15 @@
         <v>17000000</v>
       </c>
       <c r="J86" s="11" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="K86" s="15" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B87" s="30" t="n">
         <v>13000000</v>
@@ -9558,10 +9575,10 @@
         <v>8000000</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="K87" s="15" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9644,11 +9661,11 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="16" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="I95" s="20" t="n">
         <f aca="false">SUMIF(J73:J93,"Planned",I73:I93)</f>
-        <v>63000000</v>
+        <v>46000000</v>
       </c>
     </row>
   </sheetData>
@@ -9703,72 +9720,72 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -9780,19 +9797,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C7" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -9804,19 +9821,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -9828,19 +9845,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -9852,19 +9869,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -9876,19 +9893,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -9900,19 +9917,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -9924,19 +9941,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -9948,19 +9965,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -9972,19 +9989,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -9996,19 +10013,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -10020,16 +10037,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -10042,19 +10059,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -10066,19 +10083,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -10090,19 +10107,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -10114,24 +10131,24 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -10143,16 +10160,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C23" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -10165,16 +10182,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>457</v>
-      </c>
       <c r="C24" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -10187,19 +10204,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -10211,19 +10228,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C26" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -10235,16 +10252,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -10257,16 +10274,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C28" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -10279,21 +10296,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -10306,16 +10323,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C31" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -10328,16 +10345,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C32" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -10350,19 +10367,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C33" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
@@ -10374,16 +10391,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C34" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -10396,16 +10413,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C35" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -10418,16 +10435,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C36" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -10440,16 +10457,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -10462,7 +10479,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E39" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$37)*(E5:E37="Done"))</f>
@@ -10499,7 +10516,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E40" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$37,"Required",E5:E37,"Done")&amp;" of 11"</f>
@@ -10536,7 +10553,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
@@ -10580,51 +10597,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B6" s="19" t="n">
         <v>308343695</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -10641,14 +10658,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">IFERROR(INDEX(A13:A54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),"All done")</f>
         <v>16</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E7" s="20" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -10665,7 +10682,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B8" s="20" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
@@ -10674,7 +10691,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -10682,7 +10699,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -10691,40 +10708,40 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>16933847.239244</v>
+        <v>16960544.1746998</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10734,7 +10751,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -10746,7 +10763,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I13" s="23" t="str">
         <f aca="false">IF(B13="","",MAX(0,B13-$B$6))</f>
@@ -10760,7 +10777,7 @@
       <c r="B14" s="26"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -10772,7 +10789,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I14" s="23" t="str">
         <f aca="false">IF(B14="","",MAX(0,B14-$B$6))</f>
@@ -10786,7 +10803,7 @@
       <c r="B15" s="26"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -10798,7 +10815,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I15" s="23" t="str">
         <f aca="false">IF(B15="","",MAX(0,B15-$B$6))</f>
@@ -10812,7 +10829,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -10824,7 +10841,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I16" s="23" t="str">
         <f aca="false">IF(B16="","",MAX(0,B16-$B$6))</f>
@@ -10837,10 +10854,10 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="12" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -10852,7 +10869,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I17" s="23" t="str">
         <f aca="false">IF(B17="","",MAX(0,B17-$B$6))</f>
@@ -10865,10 +10882,10 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="12" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -10880,7 +10897,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I18" s="23" t="str">
         <f aca="false">IF(B18="","",MAX(0,B18-$B$6))</f>
@@ -10893,10 +10910,10 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="12" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -10908,7 +10925,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I19" s="23" t="str">
         <f aca="false">IF(B19="","",MAX(0,B19-$B$6))</f>
@@ -10921,10 +10938,10 @@
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="12" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -10936,7 +10953,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I20" s="23" t="str">
         <f aca="false">IF(B20="","",MAX(0,B20-$B$6))</f>
@@ -10949,10 +10966,10 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="12" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -10964,7 +10981,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I21" s="23" t="str">
         <f aca="false">IF(B21="","",MAX(0,B21-$B$6))</f>
@@ -10977,10 +10994,10 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="12" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -10992,7 +11009,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I22" s="23" t="str">
         <f aca="false">IF(B22="","",MAX(0,B22-$B$6))</f>
@@ -11006,7 +11023,7 @@
       <c r="B23" s="26"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -11018,7 +11035,7 @@
         <v>1900000</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I23" s="23" t="str">
         <f aca="false">IF(B23="","",MAX(0,B23-$B$6))</f>
@@ -11031,10 +11048,10 @@
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="12" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -11046,7 +11063,7 @@
         <v>1900000</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I24" s="23" t="str">
         <f aca="false">IF(B24="","",MAX(0,B24-$B$6))</f>
@@ -11059,10 +11076,10 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="12" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -11074,7 +11091,7 @@
         <v>1900000</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I25" s="23" t="str">
         <f aca="false">IF(B25="","",MAX(0,B25-$B$6))</f>
@@ -11087,10 +11104,10 @@
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="12" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -11102,7 +11119,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I26" s="23" t="str">
         <f aca="false">IF(B26="","",MAX(0,B26-$B$6))</f>
@@ -11118,7 +11135,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -11130,7 +11147,7 @@
         <v>1900000</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I27" s="23" t="n">
         <f aca="false">IF(B27="","",MAX(0,B27-$B$6))</f>
@@ -11145,10 +11162,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
+        <v>528</v>
+      </c>
+      <c r="D28" s="12" t="s">
         <v>525</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>522</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -11160,7 +11177,7 @@
         <v>1900000</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I28" s="23" t="n">
         <f aca="false">IF(B28="","",MAX(0,B28-$B$6))</f>
@@ -11175,10 +11192,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -11190,7 +11207,7 @@
         <v>1900000</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I29" s="23" t="n">
         <f aca="false">IF(B29="","",MAX(0,B29-$B$6))</f>
@@ -11205,16 +11222,16 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
       <c r="G30" s="26"/>
       <c r="H30" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I30" s="23" t="n">
         <f aca="false">IF(B30="","",MAX(0,B30-$B$6))</f>
@@ -11229,10 +11246,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -11244,7 +11261,7 @@
         <v>1900000</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I31" s="23" t="n">
         <f aca="false">IF(B31="","",MAX(0,B31-$B$6))</f>
@@ -11259,7 +11276,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -11272,7 +11289,7 @@
         <v>1900000</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I32" s="23" t="n">
         <f aca="false">IF(B32="","",MAX(0,B32-$B$6))</f>
@@ -11287,10 +11304,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -11302,7 +11319,7 @@
         <v>1900000</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I33" s="23" t="n">
         <f aca="false">IF(B33="","",MAX(0,B33-$B$6))</f>
@@ -11317,7 +11334,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -11330,7 +11347,7 @@
         <v>1900000</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I34" s="23" t="n">
         <f aca="false">IF(B34="","",MAX(0,B34-$B$6))</f>
@@ -11345,10 +11362,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -11360,7 +11377,7 @@
         <v>1900000</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I35" s="23" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
@@ -11375,7 +11392,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -11388,7 +11405,7 @@
         <v>1900000</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I36" s="23" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
@@ -11403,10 +11420,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -11418,7 +11435,7 @@
         <v>1900000</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I37" s="23" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
@@ -11433,7 +11450,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -11446,7 +11463,7 @@
         <v>2000000</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I38" s="23" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
@@ -11461,10 +11478,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -11476,7 +11493,7 @@
         <v>2000000</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I39" s="23" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
@@ -11491,7 +11508,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -11504,7 +11521,7 @@
         <v>2000000</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I40" s="23" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
@@ -11519,10 +11536,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -11534,7 +11551,7 @@
         <v>2000000</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I41" s="23" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
@@ -11549,7 +11566,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -11562,7 +11579,7 @@
         <v>2000000</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I42" s="23" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
@@ -11577,10 +11594,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -11592,7 +11609,7 @@
         <v>2000000</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I43" s="23" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
@@ -11607,7 +11624,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -11620,7 +11637,7 @@
         <v>2700000</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I44" s="23" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
@@ -11635,7 +11652,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -11648,7 +11665,7 @@
         <v>2700000</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I45" s="23" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
@@ -11663,7 +11680,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -11676,7 +11693,7 @@
         <v>2700000</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I46" s="23" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
@@ -11691,7 +11708,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -11704,7 +11721,7 @@
         <v>2700000</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I47" s="23" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
@@ -11719,7 +11736,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -11732,7 +11749,7 @@
         <v>2700000</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I48" s="23" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
@@ -11747,7 +11764,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -11760,7 +11777,7 @@
         <v>2700000</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I49" s="23" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
@@ -11775,7 +11792,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -11788,7 +11805,7 @@
         <v>2700000</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I50" s="23" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
@@ -11803,7 +11820,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -11816,7 +11833,7 @@
         <v>2700000</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I51" s="23" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
@@ -11831,7 +11848,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -11844,7 +11861,7 @@
         <v>2700000</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I52" s="23" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
@@ -11859,7 +11876,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -11872,7 +11889,7 @@
         <v>2700000</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I53" s="23" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
@@ -11887,7 +11904,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -11900,7 +11917,7 @@
         <v>2700000</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I54" s="23" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
@@ -11909,7 +11926,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -924,13 +924,13 @@
     <t xml:space="preserve">Upgrade an Amazing Avenger to T4 Level 3 Iso-8</t>
   </si>
   <si>
-    <t xml:space="preserve">Web store free claim</t>
+    <t xml:space="preserve">Web store free claim, Oct 12 onward</t>
   </si>
   <si>
     <t xml:space="preserve">Offers</t>
   </si>
   <si>
-    <t xml:space="preserve">Milestone points from select offers</t>
+    <t xml:space="preserve">Milestone points from select offers, includes free claims so far</t>
   </si>
   <si>
     <t xml:space="preserve">Unlimited</t>
@@ -4141,14 +4141,14 @@
         <v>158</v>
       </c>
       <c r="B6" s="19" t="n">
-        <v>542501630</v>
+        <v>558501630</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>159</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">B6+Scoring!F51</f>
-        <v>5997501630</v>
+        <v>5988501630</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="B9" s="20" t="n">
         <f aca="false">IFERROR(INDEX(E13:E76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),0)</f>
-        <v>27498370</v>
+        <v>11498370</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,B76-B6)</f>
-        <v>3582498370</v>
+        <v>3566498370</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>520855874.543334</v>
+        <v>518688875.910035</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4969,7 +4969,7 @@
       <c r="D55" s="12"/>
       <c r="E55" s="23" t="n">
         <f aca="false">IF(B55="","",MAX(0,B55-$B$6))</f>
-        <v>27498370</v>
+        <v>11498370</v>
       </c>
       <c r="F55" s="11" t="s">
         <v>213</v>
@@ -4988,7 +4988,7 @@
       <c r="D56" s="12"/>
       <c r="E56" s="23" t="n">
         <f aca="false">IF(B56="","",MAX(0,B56-$B$6))</f>
-        <v>57498370</v>
+        <v>41498370</v>
       </c>
       <c r="F56" s="11" t="s">
         <v>213</v>
@@ -5007,7 +5007,7 @@
       <c r="D57" s="12"/>
       <c r="E57" s="23" t="n">
         <f aca="false">IF(B57="","",MAX(0,B57-$B$6))</f>
-        <v>87498370</v>
+        <v>71498370</v>
       </c>
       <c r="F57" s="11" t="s">
         <v>213</v>
@@ -5026,7 +5026,7 @@
       <c r="D58" s="12"/>
       <c r="E58" s="23" t="n">
         <f aca="false">IF(B58="","",MAX(0,B58-$B$6))</f>
-        <v>117498370</v>
+        <v>101498370</v>
       </c>
       <c r="F58" s="11" t="s">
         <v>213</v>
@@ -5045,7 +5045,7 @@
       <c r="D59" s="12"/>
       <c r="E59" s="23" t="n">
         <f aca="false">IF(B59="","",MAX(0,B59-$B$6))</f>
-        <v>147498370</v>
+        <v>131498370</v>
       </c>
       <c r="F59" s="11" t="s">
         <v>213</v>
@@ -5064,7 +5064,7 @@
       <c r="D60" s="12"/>
       <c r="E60" s="23" t="n">
         <f aca="false">IF(B60="","",MAX(0,B60-$B$6))</f>
-        <v>207498370</v>
+        <v>191498370</v>
       </c>
       <c r="F60" s="11" t="s">
         <v>213</v>
@@ -5083,7 +5083,7 @@
       <c r="D61" s="12"/>
       <c r="E61" s="23" t="n">
         <f aca="false">IF(B61="","",MAX(0,B61-$B$6))</f>
-        <v>282498370</v>
+        <v>266498370</v>
       </c>
       <c r="F61" s="11" t="s">
         <v>213</v>
@@ -5102,7 +5102,7 @@
       <c r="D62" s="12"/>
       <c r="E62" s="23" t="n">
         <f aca="false">IF(B62="","",MAX(0,B62-$B$6))</f>
-        <v>357498370</v>
+        <v>341498370</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>213</v>
@@ -5121,7 +5121,7 @@
       <c r="D63" s="12"/>
       <c r="E63" s="23" t="n">
         <f aca="false">IF(B63="","",MAX(0,B63-$B$6))</f>
-        <v>432498370</v>
+        <v>416498370</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>213</v>
@@ -5140,7 +5140,7 @@
       <c r="D64" s="12"/>
       <c r="E64" s="23" t="n">
         <f aca="false">IF(B64="","",MAX(0,B64-$B$6))</f>
-        <v>507498370</v>
+        <v>491498370</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>213</v>
@@ -5159,7 +5159,7 @@
       <c r="D65" s="12"/>
       <c r="E65" s="23" t="n">
         <f aca="false">IF(B65="","",MAX(0,B65-$B$6))</f>
-        <v>582498370</v>
+        <v>566498370</v>
       </c>
       <c r="F65" s="11" t="s">
         <v>213</v>
@@ -5178,7 +5178,7 @@
       <c r="D66" s="12"/>
       <c r="E66" s="23" t="n">
         <f aca="false">IF(B66="","",MAX(0,B66-$B$6))</f>
-        <v>657498370</v>
+        <v>641498370</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>213</v>
@@ -5197,7 +5197,7 @@
       <c r="D67" s="12"/>
       <c r="E67" s="23" t="n">
         <f aca="false">IF(B67="","",MAX(0,B67-$B$6))</f>
-        <v>807498370</v>
+        <v>791498370</v>
       </c>
       <c r="F67" s="11" t="s">
         <v>213</v>
@@ -5216,7 +5216,7 @@
       <c r="D68" s="12"/>
       <c r="E68" s="23" t="n">
         <f aca="false">IF(B68="","",MAX(0,B68-$B$6))</f>
-        <v>957498370</v>
+        <v>941498370</v>
       </c>
       <c r="F68" s="11" t="s">
         <v>213</v>
@@ -5235,7 +5235,7 @@
       <c r="D69" s="12"/>
       <c r="E69" s="23" t="n">
         <f aca="false">IF(B69="","",MAX(0,B69-$B$6))</f>
-        <v>1107498370</v>
+        <v>1091498370</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>213</v>
@@ -5254,7 +5254,7 @@
       <c r="D70" s="12"/>
       <c r="E70" s="23" t="n">
         <f aca="false">IF(B70="","",MAX(0,B70-$B$6))</f>
-        <v>1332498370</v>
+        <v>1316498370</v>
       </c>
       <c r="F70" s="11" t="s">
         <v>213</v>
@@ -5273,7 +5273,7 @@
       <c r="D71" s="12"/>
       <c r="E71" s="23" t="n">
         <f aca="false">IF(B71="","",MAX(0,B71-$B$6))</f>
-        <v>1707498370</v>
+        <v>1691498370</v>
       </c>
       <c r="F71" s="11" t="s">
         <v>213</v>
@@ -5292,7 +5292,7 @@
       <c r="D72" s="12"/>
       <c r="E72" s="23" t="n">
         <f aca="false">IF(B72="","",MAX(0,B72-$B$6))</f>
-        <v>2082498370</v>
+        <v>2066498370</v>
       </c>
       <c r="F72" s="11" t="s">
         <v>213</v>
@@ -5311,7 +5311,7 @@
       <c r="D73" s="12"/>
       <c r="E73" s="23" t="n">
         <f aca="false">IF(B73="","",MAX(0,B73-$B$6))</f>
-        <v>2457498370</v>
+        <v>2441498370</v>
       </c>
       <c r="F73" s="11" t="s">
         <v>213</v>
@@ -5330,7 +5330,7 @@
       <c r="D74" s="12"/>
       <c r="E74" s="23" t="n">
         <f aca="false">IF(B74="","",MAX(0,B74-$B$6))</f>
-        <v>2832498370</v>
+        <v>2816498370</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>213</v>
@@ -5349,7 +5349,7 @@
       <c r="D75" s="12"/>
       <c r="E75" s="23" t="n">
         <f aca="false">IF(B75="","",MAX(0,B75-$B$6))</f>
-        <v>3207498370</v>
+        <v>3191498370</v>
       </c>
       <c r="F75" s="11" t="s">
         <v>213</v>
@@ -5368,7 +5368,7 @@
       <c r="D76" s="12"/>
       <c r="E76" s="23" t="n">
         <f aca="false">IF(B76="","",MAX(0,B76-$B$6))</f>
-        <v>3582498370</v>
+        <v>3566498370</v>
       </c>
       <c r="F76" s="11" t="s">
         <v>213</v>
@@ -5477,11 +5477,11 @@
         <v>40000000</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="F5" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D5),MAX(0,D5-E5),0)</f>
-        <v>28000000</v>
+        <v>24000000</v>
       </c>
       <c r="G5" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D5),ROUNDUP(D5/C5,0),"No limit")</f>
@@ -5489,11 +5489,11 @@
       </c>
       <c r="H5" s="25" t="n">
         <f aca="false">IFERROR(INT(E5/C5),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" s="25" t="n">
         <f aca="false">IFERROR(ROUNDUP(F5/C5,0),0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5" s="11" t="s">
         <v>249</v>
@@ -5513,11 +5513,11 @@
         <v>40000000</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>8000000</v>
+        <v>12000000</v>
       </c>
       <c r="F6" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D6),MAX(0,D6-E6),0)</f>
-        <v>32000000</v>
+        <v>28000000</v>
       </c>
       <c r="G6" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D6),ROUNDUP(D6/C6,0),"No limit")</f>
@@ -5525,11 +5525,11 @@
       </c>
       <c r="H6" s="25" t="n">
         <f aca="false">IFERROR(INT(E6/C6),0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="25" t="n">
         <f aca="false">IFERROR(ROUNDUP(F6/C6,0),0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J6" s="11" t="s">
         <v>249</v>
@@ -5549,11 +5549,11 @@
         <v>1000000000</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>36023500</v>
+        <v>47651630</v>
       </c>
       <c r="F7" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D7),MAX(0,D7-E7),0)</f>
-        <v>963976500</v>
+        <v>952348370</v>
       </c>
       <c r="G7" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D7),ROUNDUP(D7/C7,0),"No limit")</f>
@@ -5561,11 +5561,11 @@
       </c>
       <c r="H7" s="25" t="n">
         <f aca="false">IFERROR(INT(E7/C7),0)</f>
-        <v>36023500</v>
+        <v>47651630</v>
       </c>
       <c r="I7" s="25" t="n">
         <f aca="false">IFERROR(ROUNDUP(F7/C7,0),0)</f>
-        <v>963976500</v>
+        <v>952348370</v>
       </c>
       <c r="J7" s="11" t="s">
         <v>253</v>
@@ -5585,11 +5585,11 @@
         <v>1000000000</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>2600000</v>
+        <v>3600000</v>
       </c>
       <c r="F8" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D8),MAX(0,D8-E8),0)</f>
-        <v>997400000</v>
+        <v>996400000</v>
       </c>
       <c r="G8" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D8),ROUNDUP(D8/C8,0),"No limit")</f>
@@ -5597,11 +5597,11 @@
       </c>
       <c r="H8" s="25" t="n">
         <f aca="false">IFERROR(INT(E8/C8),0)</f>
-        <v>650</v>
+        <v>900</v>
       </c>
       <c r="I8" s="25" t="n">
         <f aca="false">IFERROR(ROUNDUP(F8/C8,0),0)</f>
-        <v>249350</v>
+        <v>249100</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>253</v>
@@ -6845,11 +6845,11 @@
         <v>85000000</v>
       </c>
       <c r="E43" s="24" t="n">
-        <v>0</v>
+        <v>17000000</v>
       </c>
       <c r="F43" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D43),MAX(0,D43-E43),0)</f>
-        <v>85000000</v>
+        <v>68000000</v>
       </c>
       <c r="G43" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D43),ROUNDUP(D43/C43,0),"No limit")</f>
@@ -6857,11 +6857,11 @@
       </c>
       <c r="H43" s="25" t="n">
         <f aca="false">IFERROR(INT(E43/C43),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="25" t="n">
         <f aca="false">IFERROR(ROUNDUP(F43/C43,0),0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J43" s="11" t="s">
         <v>249</v>
@@ -6950,10 +6950,10 @@
         <v>4500000</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>31500000</v>
+        <v>27000000</v>
       </c>
       <c r="E46" s="24" t="n">
-        <v>4500000</v>
+        <v>0</v>
       </c>
       <c r="F46" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D46),MAX(0,D46-E46),0)</f>
@@ -6961,11 +6961,11 @@
       </c>
       <c r="G46" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D46),ROUNDUP(D46/C46,0),"No limit")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H46" s="25" t="n">
         <f aca="false">IFERROR(INT(E46/C46),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="25" t="n">
         <f aca="false">IFERROR(ROUNDUP(F46/C46,0),0)</f>
@@ -6989,7 +6989,7 @@
         <v>300</v>
       </c>
       <c r="E47" s="24" t="n">
-        <v>0</v>
+        <v>40250000</v>
       </c>
       <c r="F47" s="25" t="n">
         <f aca="false">IF(ISNUMBER(D47),MAX(0,D47-E47),0)</f>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="H47" s="25" t="n">
         <f aca="false">IFERROR(INT(E47/C47),0)</f>
-        <v>0</v>
+        <v>40250000</v>
       </c>
       <c r="I47" s="25" t="n">
         <f aca="false">IFERROR(ROUNDUP(F47/C47,0),0)</f>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="E49" s="20" t="n">
         <f aca="false">SUM(E5:E47)</f>
-        <v>485123500</v>
+        <v>558501630</v>
       </c>
       <c r="F49" s="20"/>
     </row>
@@ -7028,7 +7028,7 @@
       <c r="E50" s="20"/>
       <c r="F50" s="20" t="n">
         <f aca="false">SUM(F5:F47)</f>
-        <v>7416376500</v>
+        <v>7378748370</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7038,7 +7038,7 @@
       <c r="E51" s="20"/>
       <c r="F51" s="20" t="n">
         <f aca="false">SUMIF(J5:J47,"Yes",F5:F47)</f>
-        <v>5455000000</v>
+        <v>5430000000</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>16960544.1746998</v>
+        <v>16965752.2572045</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -4207,7 +4207,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>518688875.910035</v>
+        <v>524609676.304537</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7127,7 +7127,7 @@
         <v>315</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>8434225</v>
+        <v>11980000</v>
       </c>
       <c r="C5" s="26" t="n">
         <v>336000</v>
@@ -7142,7 +7142,7 @@
         <v>226</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>735</v>
+        <v>759</v>
       </c>
       <c r="H5" s="26" t="n">
         <v>306</v>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="B6" s="27" t="n">
         <f aca="false">SUMIFS(B13:B69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
-        <v>32500000</v>
+        <v>29200000</v>
       </c>
       <c r="C6" s="27" t="n">
         <f aca="false">SUMIFS(C13:C69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
-        <v>40934225</v>
+        <v>41180000</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5+C6</f>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="G7" s="27" t="n">
         <f aca="false">G5+G6</f>
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="H7" s="27" t="n">
         <f aca="false">H5+H6</f>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B7-B8</f>
-        <v>40934225</v>
+        <v>41180000</v>
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">C7-C8</f>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="G9" s="28" t="n">
         <f aca="false">G7-G8</f>
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="H9" s="28" t="n">
         <f aca="false">H7-H8</f>
@@ -8380,7 +8380,7 @@
         <v>249</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K43" s="15" t="s">
         <v>364</v>
@@ -8846,7 +8846,7 @@
         <v>385</v>
       </c>
       <c r="B57" s="30" t="n">
-        <v>44475</v>
+        <v>82475</v>
       </c>
       <c r="C57" s="30" t="n">
         <v>0</v>
@@ -8861,7 +8861,7 @@
         <v>10</v>
       </c>
       <c r="G57" s="30" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="H57" s="30" t="n">
         <v>0</v>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>16965752.2572045</v>
+        <v>17159415.2601599</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="562">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -1107,6 +1107,18 @@
     <t xml:space="preserve">Iso Fest milestone 17</t>
   </si>
   <si>
+    <t xml:space="preserve">VisionQuest level 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected about Oct 14. At level 15 now, +5 a day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VisionQuest levels 35 and 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected about Oct 15 and 16. Ion types read from icons</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gold Rush run</t>
   </si>
   <si>
@@ -1489,6 +1501,12 @@
   </si>
   <si>
     <t xml:space="preserve">100 campaign and 50 Iso-8 energy; enough fragments for one training orb and one energy orb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VisionQuest: spend 10 surge energy in A.I. Avengers campaign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 levels. Resets about 6:40 PM</t>
   </si>
   <si>
     <t xml:space="preserve">Iron Vengeance: free web store milestone points</t>
@@ -4207,7 +4225,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>524609676.304537</v>
+        <v>524759892.696805</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7075,7 +7093,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -7153,31 +7171,31 @@
         <v>316</v>
       </c>
       <c r="B6" s="27" t="n">
-        <f aca="false">SUMIFS(B13:B69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
+        <f aca="false">SUMIFS(B13:B71,$I$13:$I$71,"Yes",$J$13:$J$71,"No")</f>
         <v>29200000</v>
       </c>
       <c r="C6" s="27" t="n">
-        <f aca="false">SUMIFS(C13:C69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
-        <v>4450000</v>
+        <f aca="false">SUMIFS(C13:C71,$I$13:$I$71,"Yes",$J$13:$J$71,"No")</f>
+        <v>4650000</v>
       </c>
       <c r="D6" s="27" t="n">
-        <f aca="false">SUMIFS(D13:D69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
-        <v>3136000</v>
+        <f aca="false">SUMIFS(D13:D71,$I$13:$I$71,"Yes",$J$13:$J$71,"No")</f>
+        <v>3886000</v>
       </c>
       <c r="E6" s="27" t="n">
-        <f aca="false">SUMIFS(E13:E69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
-        <v>4636000</v>
+        <f aca="false">SUMIFS(E13:E71,$I$13:$I$71,"Yes",$J$13:$J$71,"No")</f>
+        <v>5386000</v>
       </c>
       <c r="F6" s="27" t="n">
-        <f aca="false">SUMIFS(F13:F69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
+        <f aca="false">SUMIFS(F13:F71,$I$13:$I$71,"Yes",$J$13:$J$71,"No")</f>
         <v>0</v>
       </c>
       <c r="G6" s="27" t="n">
-        <f aca="false">SUMIFS(G13:G69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
+        <f aca="false">SUMIFS(G13:G71,$I$13:$I$71,"Yes",$J$13:$J$71,"No")</f>
         <v>100</v>
       </c>
       <c r="H6" s="27" t="n">
-        <f aca="false">SUMIFS(H13:H69,$I$13:$I$69,"Yes",$J$13:$J$69,"No")</f>
+        <f aca="false">SUMIFS(H13:H71,$I$13:$I$71,"Yes",$J$13:$J$71,"No")</f>
         <v>940</v>
       </c>
     </row>
@@ -7191,15 +7209,15 @@
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5+C6</f>
-        <v>4786000</v>
+        <v>4986000</v>
       </c>
       <c r="D7" s="27" t="n">
         <f aca="false">D5+D6</f>
-        <v>7096000</v>
+        <v>7846000</v>
       </c>
       <c r="E7" s="27" t="n">
         <f aca="false">E5+E6</f>
-        <v>18286000</v>
+        <v>19036000</v>
       </c>
       <c r="F7" s="27" t="n">
         <f aca="false">F5+F6</f>
@@ -7219,31 +7237,31 @@
         <v>318</v>
       </c>
       <c r="B8" s="27" t="n">
-        <f aca="false">SUMIF($J$73:$J$93,"Planned",B73:B93)</f>
+        <f aca="false">SUMIF($J$75:$J$95,"Planned",B75:B95)</f>
         <v>0</v>
       </c>
       <c r="C8" s="27" t="n">
-        <f aca="false">SUMIF($J$73:$J$93,"Planned",C73:C93)</f>
+        <f aca="false">SUMIF($J$75:$J$95,"Planned",C75:C95)</f>
         <v>1710000</v>
       </c>
       <c r="D8" s="27" t="n">
-        <f aca="false">SUMIF($J$73:$J$93,"Planned",D73:D93)</f>
+        <f aca="false">SUMIF($J$75:$J$95,"Planned",D75:D95)</f>
         <v>1710000</v>
       </c>
       <c r="E8" s="27" t="n">
-        <f aca="false">SUMIF($J$73:$J$93,"Planned",E73:E93)</f>
+        <f aca="false">SUMIF($J$75:$J$95,"Planned",E75:E95)</f>
         <v>2640000</v>
       </c>
       <c r="F8" s="27" t="n">
-        <f aca="false">SUMIF($J$73:$J$93,"Planned",F73:F93)</f>
+        <f aca="false">SUMIF($J$75:$J$95,"Planned",F75:F95)</f>
         <v>0</v>
       </c>
       <c r="G8" s="27" t="n">
-        <f aca="false">SUMIF($J$73:$J$93,"Planned",G73:G93)</f>
+        <f aca="false">SUMIF($J$75:$J$95,"Planned",G75:G95)</f>
         <v>0</v>
       </c>
       <c r="H8" s="27" t="n">
-        <f aca="false">SUMIF($J$73:$J$93,"Planned",H73:H93)</f>
+        <f aca="false">SUMIF($J$75:$J$95,"Planned",H75:H95)</f>
         <v>0</v>
       </c>
     </row>
@@ -7257,15 +7275,15 @@
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">C7-C8</f>
-        <v>3076000</v>
+        <v>3276000</v>
       </c>
       <c r="D9" s="28" t="n">
         <f aca="false">D7-D8</f>
-        <v>5386000</v>
+        <v>6136000</v>
       </c>
       <c r="E9" s="28" t="n">
         <f aca="false">E7-E8</f>
-        <v>15646000</v>
+        <v>16396000</v>
       </c>
       <c r="F9" s="28" t="n">
         <f aca="false">F7-F8</f>
@@ -8251,10 +8269,10 @@
         <v>358</v>
       </c>
       <c r="B40" s="30" t="n">
-        <v>900000</v>
+        <v>0</v>
       </c>
       <c r="C40" s="30" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="D40" s="30" t="n">
         <v>0</v>
@@ -8272,7 +8290,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J40" s="11" t="s">
         <v>253</v>
@@ -8292,36 +8310,36 @@
         <v>0</v>
       </c>
       <c r="D41" s="30" t="n">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="E41" s="30" t="n">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="F41" s="30" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="30" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H41" s="30" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J41" s="11" t="s">
         <v>253</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B42" s="30" t="n">
-        <v>3300000</v>
+        <v>900000</v>
       </c>
       <c r="C42" s="30" t="n">
         <v>0</v>
@@ -8342,48 +8360,48 @@
         <v>0</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="B43" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="H43" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K43" s="15" t="s">
         <v>363</v>
-      </c>
-      <c r="B43" s="30" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="C43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="K43" s="15" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8391,10 +8409,10 @@
         <v>365</v>
       </c>
       <c r="B44" s="30" t="n">
-        <v>0</v>
+        <v>3300000</v>
       </c>
       <c r="C44" s="30" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="D44" s="30" t="n">
         <v>0</v>
@@ -8415,7 +8433,7 @@
         <v>249</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K44" s="15" t="s">
         <v>366</v>
@@ -8426,7 +8444,7 @@
         <v>367</v>
       </c>
       <c r="B45" s="30" t="n">
-        <v>0</v>
+        <v>3300000</v>
       </c>
       <c r="C45" s="30" t="n">
         <v>0</v>
@@ -8450,7 +8468,7 @@
         <v>249</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K45" s="15" t="s">
         <v>368</v>
@@ -8464,13 +8482,13 @@
         <v>0</v>
       </c>
       <c r="C46" s="30" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="D46" s="30" t="n">
-        <v>136000</v>
+        <v>0</v>
       </c>
       <c r="E46" s="30" t="n">
-        <v>136000</v>
+        <v>0</v>
       </c>
       <c r="F46" s="30" t="n">
         <v>0</v>
@@ -8496,7 +8514,7 @@
         <v>371</v>
       </c>
       <c r="B47" s="30" t="n">
-        <v>750000</v>
+        <v>0</v>
       </c>
       <c r="C47" s="30" t="n">
         <v>0</v>
@@ -8531,16 +8549,16 @@
         <v>373</v>
       </c>
       <c r="B48" s="30" t="n">
-        <v>750000</v>
+        <v>0</v>
       </c>
       <c r="C48" s="30" t="n">
         <v>0</v>
       </c>
       <c r="D48" s="30" t="n">
-        <v>0</v>
+        <v>136000</v>
       </c>
       <c r="E48" s="30" t="n">
-        <v>0</v>
+        <v>136000</v>
       </c>
       <c r="F48" s="30" t="n">
         <v>0</v>
@@ -8593,12 +8611,12 @@
         <v>253</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B50" s="30" t="n">
         <v>750000</v>
@@ -8628,12 +8646,12 @@
         <v>253</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B51" s="30" t="n">
         <v>750000</v>
@@ -8663,12 +8681,12 @@
         <v>253</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B52" s="30" t="n">
         <v>750000</v>
@@ -8698,12 +8716,12 @@
         <v>253</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B53" s="30" t="n">
         <v>750000</v>
@@ -8733,12 +8751,12 @@
         <v>253</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B54" s="30" t="n">
         <v>750000</v>
@@ -8768,18 +8786,18 @@
         <v>253</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B55" s="30" t="n">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="C55" s="30" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="D55" s="30" t="n">
         <v>0</v>
@@ -8803,15 +8821,15 @@
         <v>253</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B56" s="30" t="n">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="C56" s="30" t="n">
         <v>0</v>
@@ -8838,7 +8856,7 @@
         <v>253</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8846,10 +8864,10 @@
         <v>385</v>
       </c>
       <c r="B57" s="30" t="n">
-        <v>82475</v>
+        <v>0</v>
       </c>
       <c r="C57" s="30" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="D57" s="30" t="n">
         <v>0</v>
@@ -8858,10 +8876,10 @@
         <v>0</v>
       </c>
       <c r="F57" s="30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G57" s="30" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H57" s="30" t="n">
         <v>0</v>
@@ -8870,7 +8888,7 @@
         <v>249</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K57" s="15" t="s">
         <v>386</v>
@@ -8881,7 +8899,7 @@
         <v>387</v>
       </c>
       <c r="B58" s="30" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="C58" s="30" t="n">
         <v>0</v>
@@ -8905,7 +8923,7 @@
         <v>249</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K58" s="15" t="s">
         <v>388</v>
@@ -8916,7 +8934,7 @@
         <v>389</v>
       </c>
       <c r="B59" s="30" t="n">
-        <v>0</v>
+        <v>82475</v>
       </c>
       <c r="C59" s="30" t="n">
         <v>0</v>
@@ -8928,49 +8946,93 @@
         <v>0</v>
       </c>
       <c r="F59" s="30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G59" s="30" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H59" s="30" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K59" s="15" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="12"/>
-      <c r="B60" s="30"/>
-      <c r="C60" s="30"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
-      <c r="F60" s="30"/>
-      <c r="G60" s="30"/>
-      <c r="H60" s="30"/>
-      <c r="I60" s="11"/>
-      <c r="J60" s="11"/>
-      <c r="K60" s="12"/>
+      <c r="A60" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="B60" s="30" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C60" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="K60" s="15" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="12"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="11"/>
-      <c r="J61" s="11"/>
-      <c r="K61" s="12"/>
+      <c r="A61" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="B61" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="K61" s="15" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12"/>
@@ -9076,120 +9138,78 @@
       <c r="J69" s="11"/>
       <c r="K69" s="12"/>
     </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="12"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="11"/>
+      <c r="K70" s="12"/>
+    </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="29" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="B72" s="3" t="s">
+      <c r="A71" s="12"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="30"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="12"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="29" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D74" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E74" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="F74" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="G74" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="H72" s="3" t="s">
+      <c r="H74" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="I72" s="3" t="s">
+      <c r="I74" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J72" s="3" t="s">
+      <c r="J74" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K72" s="3" t="s">
+      <c r="K74" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="B73" s="30" t="n">
-        <v>1837500</v>
-      </c>
-      <c r="C73" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G73" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H73" s="30" t="n">
-        <v>183</v>
-      </c>
-      <c r="I73" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="11" t="s">
-        <v>394</v>
-      </c>
-      <c r="K73" s="15" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="B74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C74" s="30" t="n">
-        <v>359800</v>
-      </c>
-      <c r="D74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="11" t="s">
-        <v>394</v>
-      </c>
-      <c r="K74" s="15"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="s">
         <v>397</v>
       </c>
       <c r="B75" s="30" t="n">
-        <v>9791250</v>
+        <v>1837500</v>
       </c>
       <c r="C75" s="30" t="n">
         <v>0</v>
@@ -9201,27 +9221,27 @@
         <v>0</v>
       </c>
       <c r="F75" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="G75" s="30" t="n">
-        <v>0</v>
-      </c>
       <c r="H75" s="30" t="n">
-        <v>979</v>
+        <v>183</v>
       </c>
       <c r="I75" s="30" t="n">
-        <v>55000000</v>
+        <v>0</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="K75" s="15" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B76" s="30" t="n">
         <v>0</v>
@@ -9248,17 +9268,17 @@
         <v>0</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>394</v>
-      </c>
-      <c r="K76" s="15" t="s">
         <v>398</v>
       </c>
+      <c r="K76" s="15"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="B77" s="26"/>
+        <v>401</v>
+      </c>
+      <c r="B77" s="30" t="n">
+        <v>9791250</v>
+      </c>
       <c r="C77" s="30" t="n">
         <v>0</v>
       </c>
@@ -9268,14 +9288,20 @@
       <c r="E77" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F77" s="26"/>
-      <c r="G77" s="26"/>
-      <c r="H77" s="26"/>
+      <c r="F77" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="30" t="n">
+        <v>979</v>
+      </c>
       <c r="I77" s="30" t="n">
-        <v>3000000</v>
+        <v>55000000</v>
       </c>
       <c r="J77" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="K77" s="15" t="s">
         <v>402</v>
@@ -9285,9 +9311,11 @@
       <c r="A78" s="12" t="s">
         <v>403</v>
       </c>
-      <c r="B78" s="26"/>
+      <c r="B78" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="C78" s="30" t="n">
-        <v>0</v>
+        <v>359800</v>
       </c>
       <c r="D78" s="30" t="n">
         <v>0</v>
@@ -9295,14 +9323,20 @@
       <c r="E78" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F78" s="26"/>
-      <c r="G78" s="26"/>
-      <c r="H78" s="26"/>
+      <c r="F78" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="I78" s="30" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="J78" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="K78" s="15" t="s">
         <v>402</v>
@@ -9329,15 +9363,15 @@
         <v>3000000</v>
       </c>
       <c r="J79" s="11" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B80" s="26"/>
       <c r="C80" s="30" t="n">
@@ -9356,15 +9390,15 @@
         <v>3000000</v>
       </c>
       <c r="J80" s="11" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="K80" s="15" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B81" s="26"/>
       <c r="C81" s="30" t="n">
@@ -9376,75 +9410,59 @@
       <c r="E81" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F81" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="30" t="n">
-        <v>0</v>
-      </c>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26"/>
+      <c r="H81" s="26"/>
       <c r="I81" s="30" t="n">
-        <v>17000000</v>
+        <v>3000000</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>407</v>
-      </c>
-      <c r="B82" s="30" t="n">
-        <v>0</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="B82" s="26"/>
       <c r="C82" s="30" t="n">
-        <v>1710500</v>
+        <v>0</v>
       </c>
       <c r="D82" s="30" t="n">
-        <v>1710000</v>
+        <v>0</v>
       </c>
       <c r="E82" s="30" t="n">
-        <v>2640000</v>
-      </c>
-      <c r="F82" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="30" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F82" s="26"/>
+      <c r="G82" s="26"/>
+      <c r="H82" s="26"/>
       <c r="I82" s="30" t="n">
-        <v>17000000</v>
+        <v>3000000</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="K82" s="15" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="B83" s="30" t="n">
-        <v>0</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="B83" s="26"/>
       <c r="C83" s="30" t="n">
-        <v>1710000</v>
+        <v>0</v>
       </c>
       <c r="D83" s="30" t="n">
-        <v>1710000</v>
+        <v>0</v>
       </c>
       <c r="E83" s="30" t="n">
-        <v>2640000</v>
+        <v>0</v>
       </c>
       <c r="F83" s="30" t="n">
         <v>0</v>
@@ -9459,10 +9477,10 @@
         <v>17000000</v>
       </c>
       <c r="J83" s="11" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="K83" s="15" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9472,9 +9490,15 @@
       <c r="B84" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C84" s="26"/>
-      <c r="D84" s="26"/>
-      <c r="E84" s="26"/>
+      <c r="C84" s="30" t="n">
+        <v>1710500</v>
+      </c>
+      <c r="D84" s="30" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="E84" s="30" t="n">
+        <v>2640000</v>
+      </c>
       <c r="F84" s="30" t="n">
         <v>0</v>
       </c>
@@ -9488,10 +9512,10 @@
         <v>17000000</v>
       </c>
       <c r="J84" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="K84" s="15" t="s">
         <v>412</v>
-      </c>
-      <c r="K84" s="15" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9501,9 +9525,15 @@
       <c r="B85" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C85" s="26"/>
-      <c r="D85" s="26"/>
-      <c r="E85" s="26"/>
+      <c r="C85" s="30" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="D85" s="30" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="E85" s="30" t="n">
+        <v>2640000</v>
+      </c>
       <c r="F85" s="30" t="n">
         <v>0</v>
       </c>
@@ -9517,15 +9547,15 @@
         <v>17000000</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="K85" s="15" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B86" s="30" t="n">
         <v>0</v>
@@ -9546,66 +9576,98 @@
         <v>17000000</v>
       </c>
       <c r="J86" s="11" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="K86" s="15" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B87" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="26"/>
+      <c r="D87" s="26"/>
+      <c r="E87" s="26"/>
+      <c r="F87" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J87" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="K87" s="15" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="B88" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="26"/>
+      <c r="D88" s="26"/>
+      <c r="E88" s="26"/>
+      <c r="F88" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J88" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="K88" s="15" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="B89" s="30" t="n">
         <v>13000000</v>
       </c>
-      <c r="C87" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="26"/>
-      <c r="G87" s="26"/>
-      <c r="H87" s="26"/>
-      <c r="I87" s="30" t="n">
+      <c r="C89" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="26"/>
+      <c r="G89" s="26"/>
+      <c r="H89" s="26"/>
+      <c r="I89" s="30" t="n">
         <v>8000000</v>
       </c>
-      <c r="J87" s="11" t="s">
-        <v>412</v>
-      </c>
-      <c r="K87" s="15" t="s">
+      <c r="J89" s="11" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="12"/>
-      <c r="B88" s="30"/>
-      <c r="C88" s="30"/>
-      <c r="D88" s="30"/>
-      <c r="E88" s="30"/>
-      <c r="F88" s="30"/>
-      <c r="G88" s="30"/>
-      <c r="H88" s="30"/>
-      <c r="I88" s="30"/>
-      <c r="J88" s="11"/>
-      <c r="K88" s="12"/>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="12"/>
-      <c r="B89" s="30"/>
-      <c r="C89" s="30"/>
-      <c r="D89" s="30"/>
-      <c r="E89" s="30"/>
-      <c r="F89" s="30"/>
-      <c r="G89" s="30"/>
-      <c r="H89" s="30"/>
-      <c r="I89" s="30"/>
-      <c r="J89" s="11"/>
-      <c r="K89" s="12"/>
+      <c r="K89" s="15" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="12"/>
@@ -9659,12 +9721,38 @@
       <c r="J93" s="11"/>
       <c r="K93" s="12"/>
     </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="12"/>
+      <c r="B94" s="30"/>
+      <c r="C94" s="30"/>
+      <c r="D94" s="30"/>
+      <c r="E94" s="30"/>
+      <c r="F94" s="30"/>
+      <c r="G94" s="30"/>
+      <c r="H94" s="30"/>
+      <c r="I94" s="30"/>
+      <c r="J94" s="11"/>
+      <c r="K94" s="12"/>
+    </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="16" t="s">
-        <v>417</v>
-      </c>
-      <c r="I95" s="20" t="n">
-        <f aca="false">SUMIF(J73:J93,"Planned",I73:I93)</f>
+      <c r="A95" s="12"/>
+      <c r="B95" s="30"/>
+      <c r="C95" s="30"/>
+      <c r="D95" s="30"/>
+      <c r="E95" s="30"/>
+      <c r="F95" s="30"/>
+      <c r="G95" s="30"/>
+      <c r="H95" s="30"/>
+      <c r="I95" s="30"/>
+      <c r="J95" s="11"/>
+      <c r="K95" s="12"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="I97" s="20" t="n">
+        <f aca="false">SUMIF(J75:J95,"Planned",I75:I95)</f>
         <v>46000000</v>
       </c>
     </row>
@@ -9674,22 +9762,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J73:J93">
+  <conditionalFormatting sqref="J75:J95">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J13:J69">
+  <conditionalFormatting sqref="J13:J71">
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13:J69" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13:J71" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J73:J93" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J75:J95" type="list">
       <formula1>"Planned,Done,Skipped"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9709,7 +9797,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
@@ -9720,12 +9808,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9739,53 +9827,53 @@
         <v>308</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -9797,19 +9885,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C7" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -9821,19 +9909,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>435</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>431</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -9845,19 +9933,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -9869,19 +9957,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -9893,19 +9981,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -9917,19 +10005,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -9941,19 +10029,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -9965,19 +10053,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -9989,19 +10077,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -10013,19 +10101,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -10037,16 +10125,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -10059,19 +10147,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -10083,19 +10171,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>454</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>450</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -10107,19 +10195,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -10131,24 +10219,24 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -10160,16 +10248,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C23" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -10182,16 +10270,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -10204,19 +10292,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -10228,19 +10316,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C26" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -10252,16 +10340,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -10274,16 +10362,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C28" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -10296,21 +10384,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -10323,16 +10411,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C31" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -10345,16 +10433,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="B32" s="13" t="s">
         <v>481</v>
       </c>
-      <c r="B32" s="13" t="s">
-        <v>477</v>
-      </c>
       <c r="C32" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -10367,19 +10455,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C33" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
@@ -10391,16 +10479,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C34" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -10413,16 +10501,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
+        <v>492</v>
+      </c>
+      <c r="B35" s="13" t="s">
         <v>488</v>
       </c>
-      <c r="B35" s="13" t="s">
-        <v>484</v>
-      </c>
       <c r="C35" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -10435,16 +10523,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="C36" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -10457,16 +10545,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -10477,93 +10565,115 @@
       <c r="K37" s="32"/>
       <c r="L37" s="32"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="16" t="s">
-        <v>493</v>
-      </c>
-      <c r="E39" s="20" t="n">
-        <f aca="false">SUMPRODUCT(($C$5:$C$37)*(E5:E37="Done"))</f>
-        <v>2400000</v>
-      </c>
-      <c r="F39" s="20" t="n">
-        <f aca="false">SUMPRODUCT(($C$5:$C$37)*(F5:F37="Done"))</f>
-        <v>0</v>
-      </c>
-      <c r="G39" s="20" t="n">
-        <f aca="false">SUMPRODUCT(($C$5:$C$37)*(G5:G37="Done"))</f>
-        <v>0</v>
-      </c>
-      <c r="H39" s="20" t="n">
-        <f aca="false">SUMPRODUCT(($C$5:$C$37)*(H5:H37="Done"))</f>
-        <v>0</v>
-      </c>
-      <c r="I39" s="20" t="n">
-        <f aca="false">SUMPRODUCT(($C$5:$C$37)*(I5:I37="Done"))</f>
-        <v>0</v>
-      </c>
-      <c r="J39" s="20" t="n">
-        <f aca="false">SUMPRODUCT(($C$5:$C$37)*(J5:J37="Done"))</f>
-        <v>0</v>
-      </c>
-      <c r="K39" s="20" t="n">
-        <f aca="false">SUMPRODUCT(($C$5:$C$37)*(K5:K37="Done"))</f>
-        <v>0</v>
-      </c>
-      <c r="L39" s="20" t="n">
-        <f aca="false">SUMPRODUCT(($C$5:$C$37)*(L5:L37="Done"))</f>
-        <v>0</v>
-      </c>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="13" t="s">
+        <v>497</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="C38" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
+      <c r="L38" s="32"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>494</v>
-      </c>
-      <c r="E40" s="33" t="str">
-        <f aca="false">COUNTIFS($B$5:$B$37,"Required",E5:E37,"Done")&amp;" of 11"</f>
+        <v>499</v>
+      </c>
+      <c r="E40" s="20" t="n">
+        <f aca="false">SUMPRODUCT(($C$5:$C$38)*(E5:E38="Done"))</f>
+        <v>2400000</v>
+      </c>
+      <c r="F40" s="20" t="n">
+        <f aca="false">SUMPRODUCT(($C$5:$C$38)*(F5:F38="Done"))</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="20" t="n">
+        <f aca="false">SUMPRODUCT(($C$5:$C$38)*(G5:G38="Done"))</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="20" t="n">
+        <f aca="false">SUMPRODUCT(($C$5:$C$38)*(H5:H38="Done"))</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="20" t="n">
+        <f aca="false">SUMPRODUCT(($C$5:$C$38)*(I5:I38="Done"))</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="20" t="n">
+        <f aca="false">SUMPRODUCT(($C$5:$C$38)*(J5:J38="Done"))</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="20" t="n">
+        <f aca="false">SUMPRODUCT(($C$5:$C$38)*(K5:K38="Done"))</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="20" t="n">
+        <f aca="false">SUMPRODUCT(($C$5:$C$38)*(L5:L38="Done"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="E41" s="33" t="str">
+        <f aca="false">COUNTIFS($B$5:$B$38,"Required",E5:E38,"Done")&amp;" of 11"</f>
         <v>11 of 11</v>
       </c>
-      <c r="F40" s="33" t="str">
-        <f aca="false">COUNTIFS($B$5:$B$37,"Required",F5:F37,"Done")&amp;" of 11"</f>
+      <c r="F41" s="33" t="str">
+        <f aca="false">COUNTIFS($B$5:$B$38,"Required",F5:F38,"Done")&amp;" of 11"</f>
         <v>0 of 11</v>
       </c>
-      <c r="G40" s="33" t="str">
-        <f aca="false">COUNTIFS($B$5:$B$37,"Required",G5:G37,"Done")&amp;" of 11"</f>
+      <c r="G41" s="33" t="str">
+        <f aca="false">COUNTIFS($B$5:$B$38,"Required",G5:G38,"Done")&amp;" of 11"</f>
         <v>0 of 11</v>
       </c>
-      <c r="H40" s="33" t="str">
-        <f aca="false">COUNTIFS($B$5:$B$37,"Required",H5:H37,"Done")&amp;" of 11"</f>
+      <c r="H41" s="33" t="str">
+        <f aca="false">COUNTIFS($B$5:$B$38,"Required",H5:H38,"Done")&amp;" of 11"</f>
         <v>0 of 11</v>
       </c>
-      <c r="I40" s="33" t="str">
-        <f aca="false">COUNTIFS($B$5:$B$37,"Required",I5:I37,"Done")&amp;" of 11"</f>
+      <c r="I41" s="33" t="str">
+        <f aca="false">COUNTIFS($B$5:$B$38,"Required",I5:I38,"Done")&amp;" of 11"</f>
         <v>0 of 11</v>
       </c>
-      <c r="J40" s="33" t="str">
-        <f aca="false">COUNTIFS($B$5:$B$37,"Required",J5:J37,"Done")&amp;" of 11"</f>
+      <c r="J41" s="33" t="str">
+        <f aca="false">COUNTIFS($B$5:$B$38,"Required",J5:J38,"Done")&amp;" of 11"</f>
         <v>0 of 11</v>
       </c>
-      <c r="K40" s="33" t="str">
-        <f aca="false">COUNTIFS($B$5:$B$37,"Required",K5:K37,"Done")&amp;" of 11"</f>
+      <c r="K41" s="33" t="str">
+        <f aca="false">COUNTIFS($B$5:$B$38,"Required",K5:K38,"Done")&amp;" of 11"</f>
         <v>0 of 11</v>
       </c>
-      <c r="L40" s="33" t="str">
-        <f aca="false">COUNTIFS($B$5:$B$37,"Required",L5:L37,"Done")&amp;" of 11"</f>
+      <c r="L41" s="33" t="str">
+        <f aca="false">COUNTIFS($B$5:$B$38,"Required",L5:L38,"Done")&amp;" of 11"</f>
         <v>0 of 11</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
-        <v>495</v>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>501</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:L37">
+  <conditionalFormatting sqref="E5:L38">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5:L37" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5:L38" type="list">
       <formula1>"Done"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10597,12 +10707,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10610,10 +10720,10 @@
         <v>155</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10624,13 +10734,13 @@
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10641,7 +10751,7 @@
         <v>308343695</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -10691,7 +10801,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -10699,7 +10809,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -10708,11 +10818,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>17159415.2601599</v>
+        <v>17164328.6617692</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10723,19 +10833,19 @@
         <v>168</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>501</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
@@ -10751,7 +10861,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -10777,7 +10887,7 @@
       <c r="B14" s="26"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -10803,7 +10913,7 @@
       <c r="B15" s="26"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -10829,7 +10939,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -10854,10 +10964,10 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="12" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -10882,10 +10992,10 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="12" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -10910,10 +11020,10 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="12" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -10938,10 +11048,10 @@
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="12" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -10966,10 +11076,10 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="12" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -10994,10 +11104,10 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="12" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -11023,7 +11133,7 @@
       <c r="B23" s="26"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -11048,10 +11158,10 @@
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="12" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -11076,10 +11186,10 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="12" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -11104,10 +11214,10 @@
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="12" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -11135,7 +11245,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -11162,10 +11272,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -11192,10 +11302,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -11222,10 +11332,10 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
@@ -11246,10 +11356,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -11276,7 +11386,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -11304,10 +11414,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -11334,7 +11444,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -11362,10 +11472,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -11392,7 +11502,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -11420,10 +11530,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -11450,7 +11560,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -11478,10 +11588,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -11508,7 +11618,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -11536,10 +11646,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -11566,7 +11676,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -11594,10 +11704,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -11624,7 +11734,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -11652,7 +11762,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -11680,7 +11790,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -11708,7 +11818,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -11736,7 +11846,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -11764,7 +11874,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -11792,7 +11902,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -11820,7 +11930,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -11848,7 +11958,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -11876,7 +11986,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -11904,7 +12014,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -11926,7 +12036,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -4225,7 +4225,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>524759892.696805</v>
+        <v>525413739.367938</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7157,13 +7157,13 @@
         <v>13650000</v>
       </c>
       <c r="F5" s="26" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G5" s="26" t="n">
         <v>759</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>306</v>
+        <v>492</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="F7" s="27" t="n">
         <f aca="false">F5+F6</f>
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G7" s="27" t="n">
         <f aca="false">G5+G6</f>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="H7" s="27" t="n">
         <f aca="false">H5+H6</f>
-        <v>1246</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="F9" s="28" t="n">
         <f aca="false">F7-F8</f>
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G9" s="28" t="n">
         <f aca="false">G7-G8</f>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="H9" s="28" t="n">
         <f aca="false">H7-H8</f>
-        <v>1246</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>17164328.6617692</v>
+        <v>17185715.2757584</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="631">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -686,6 +686,15 @@
   </si>
   <si>
     <t xml:space="preserve">Score earned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cell 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immortal Weapons</t>
   </si>
   <si>
     <t xml:space="preserve">Type character names exactly as on the Tower Roster tab so team power fills in.</t>
@@ -4818,22 +4827,42 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11"/>
+      <c r="A33" s="11" t="s">
+        <v>218</v>
+      </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
+      <c r="D33" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>119</v>
+      </c>
       <c r="I33" s="24" t="n">
         <f aca="false">SUMIF('Tower Roster'!$A$5:$A$44,D33,'Tower Roster'!$C$5:$C$44)+SUMIF('Tower Roster'!$A$5:$A$44,E33,'Tower Roster'!$C$5:$C$44)+SUMIF('Tower Roster'!$A$5:$A$44,F33,'Tower Roster'!$C$5:$C$44)+SUMIF('Tower Roster'!$A$5:$A$44,G33,'Tower Roster'!$C$5:$C$44)+SUMIF('Tower Roster'!$A$5:$A$44,H33,'Tower Roster'!$C$5:$C$44)</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="11"/>
+        <v>4789170</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="K33" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="25" t="n">
+        <v>400</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11"/>
@@ -5539,7 +5568,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -5601,20 +5630,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5627,13 +5656,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B6" s="19" t="n">
         <v>558501630</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">B6+Scoring!F51</f>
@@ -5642,14 +5671,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6))+SUMPRODUCT((B13:B76="")*(F13:F76="Claimed"))</f>
         <v>42</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E7" s="16" t="n">
         <f aca="false">IFERROR(INDEX(A13:A76,MATCH(E6,B13:B76,1)),37)</f>
@@ -5665,7 +5694,7 @@
         <v>43</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E8" s="16" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6)*(F13:F76&lt;&gt;"Claimed"))</f>
@@ -5683,7 +5712,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,B76-B6)</f>
@@ -5692,11 +5721,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>525563829.978157</v>
+        <v>525654635.46022</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5704,7 +5733,7 @@
         <v>159</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C12" s="21" t="s">
         <v>162</v>
@@ -5713,7 +5742,7 @@
         <v>13</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>12</v>
@@ -5725,7 +5754,7 @@
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="12" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="24" t="str">
@@ -5742,7 +5771,7 @@
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="12" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="24" t="str">
@@ -5759,7 +5788,7 @@
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="12" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="24" t="str">
@@ -5776,7 +5805,7 @@
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="12" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="24" t="str">
@@ -5793,7 +5822,7 @@
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="12" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="24" t="str">
@@ -5810,7 +5839,7 @@
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="12" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="24" t="str">
@@ -5827,7 +5856,7 @@
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="12" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="24" t="str">
@@ -5844,7 +5873,7 @@
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="12" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="24" t="str">
@@ -5861,7 +5890,7 @@
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="12" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D21" s="12"/>
       <c r="E21" s="24" t="str">
@@ -5878,7 +5907,7 @@
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="12" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="24" t="str">
@@ -5895,7 +5924,7 @@
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="24" t="str">
@@ -5912,7 +5941,7 @@
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="12" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="24" t="str">
@@ -5929,7 +5958,7 @@
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="12" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="24" t="str">
@@ -5946,7 +5975,7 @@
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="12" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="24" t="str">
@@ -5963,7 +5992,7 @@
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="12" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="24" t="str">
@@ -5980,7 +6009,7 @@
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="12" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="24" t="str">
@@ -5997,7 +6026,7 @@
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="24" t="str">
@@ -6014,7 +6043,7 @@
       </c>
       <c r="B30" s="14"/>
       <c r="C30" s="12" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="24" t="str">
@@ -6031,7 +6060,7 @@
       </c>
       <c r="B31" s="14"/>
       <c r="C31" s="12" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="24" t="str">
@@ -6048,7 +6077,7 @@
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="12" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="24" t="str">
@@ -6065,7 +6094,7 @@
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="12" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="24" t="str">
@@ -6082,7 +6111,7 @@
       </c>
       <c r="B34" s="14"/>
       <c r="C34" s="12" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="24" t="str">
@@ -6099,7 +6128,7 @@
       </c>
       <c r="B35" s="14"/>
       <c r="C35" s="12" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="24" t="str">
@@ -6116,7 +6145,7 @@
       </c>
       <c r="B36" s="14"/>
       <c r="C36" s="12" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="24" t="str">
@@ -6133,7 +6162,7 @@
       </c>
       <c r="B37" s="14"/>
       <c r="C37" s="12" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="24" t="str">
@@ -6150,7 +6179,7 @@
       </c>
       <c r="B38" s="14"/>
       <c r="C38" s="12" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="24" t="str">
@@ -6167,7 +6196,7 @@
       </c>
       <c r="B39" s="14"/>
       <c r="C39" s="12" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="24" t="str">
@@ -6184,7 +6213,7 @@
       </c>
       <c r="B40" s="14"/>
       <c r="C40" s="12" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="24" t="str">
@@ -6201,7 +6230,7 @@
       </c>
       <c r="B41" s="14"/>
       <c r="C41" s="12" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="24" t="str">
@@ -6219,7 +6248,7 @@
       <c r="B42" s="14"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E42" s="24" t="str">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
@@ -6236,7 +6265,7 @@
       <c r="B43" s="14"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E43" s="24" t="str">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
@@ -6253,7 +6282,7 @@
       <c r="B44" s="14"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E44" s="24" t="str">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
@@ -6270,7 +6299,7 @@
       <c r="B45" s="14"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E45" s="24" t="str">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
@@ -6286,7 +6315,7 @@
       </c>
       <c r="B46" s="14"/>
       <c r="C46" s="12" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="24" t="str">
@@ -6303,7 +6332,7 @@
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="12" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="24" t="str">
@@ -6320,7 +6349,7 @@
       </c>
       <c r="B48" s="14"/>
       <c r="C48" s="12" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="24" t="str">
@@ -6337,7 +6366,7 @@
       </c>
       <c r="B49" s="14"/>
       <c r="C49" s="12" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="24" t="str">
@@ -6356,7 +6385,7 @@
         <v>435000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="24" t="n">
@@ -6375,7 +6404,7 @@
         <v>450000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="24" t="n">
@@ -6394,7 +6423,7 @@
         <v>480000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="24" t="n">
@@ -6413,10 +6442,10 @@
         <v>510000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E53" s="24" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
@@ -6434,7 +6463,7 @@
         <v>540000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="24" t="n">
@@ -6453,7 +6482,7 @@
         <v>570000000</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D55" s="12"/>
       <c r="E55" s="24" t="n">
@@ -6472,7 +6501,7 @@
         <v>600000000</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D56" s="12"/>
       <c r="E56" s="24" t="n">
@@ -6491,7 +6520,7 @@
         <v>630000000</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D57" s="12"/>
       <c r="E57" s="24" t="n">
@@ -6510,7 +6539,7 @@
         <v>660000000</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D58" s="12"/>
       <c r="E58" s="24" t="n">
@@ -6529,7 +6558,7 @@
         <v>690000000</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D59" s="12"/>
       <c r="E59" s="24" t="n">
@@ -6548,7 +6577,7 @@
         <v>750000000</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D60" s="12"/>
       <c r="E60" s="24" t="n">
@@ -6567,7 +6596,7 @@
         <v>825000000</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D61" s="12"/>
       <c r="E61" s="24" t="n">
@@ -6586,7 +6615,7 @@
         <v>900000000</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D62" s="12"/>
       <c r="E62" s="24" t="n">
@@ -6605,7 +6634,7 @@
         <v>975000000</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D63" s="12"/>
       <c r="E63" s="24" t="n">
@@ -6624,7 +6653,7 @@
         <v>1050000000</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D64" s="12"/>
       <c r="E64" s="24" t="n">
@@ -6643,7 +6672,7 @@
         <v>1125000000</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D65" s="12"/>
       <c r="E65" s="24" t="n">
@@ -6662,7 +6691,7 @@
         <v>1200000000</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D66" s="12"/>
       <c r="E66" s="24" t="n">
@@ -6681,7 +6710,7 @@
         <v>1350000000</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D67" s="12"/>
       <c r="E67" s="24" t="n">
@@ -6700,7 +6729,7 @@
         <v>1500000000</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D68" s="12"/>
       <c r="E68" s="24" t="n">
@@ -6719,7 +6748,7 @@
         <v>1650000000</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D69" s="12"/>
       <c r="E69" s="24" t="n">
@@ -6738,7 +6767,7 @@
         <v>1875000000</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D70" s="12"/>
       <c r="E70" s="24" t="n">
@@ -6757,7 +6786,7 @@
         <v>2250000000</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D71" s="12"/>
       <c r="E71" s="24" t="n">
@@ -6776,7 +6805,7 @@
         <v>2625000000</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D72" s="12"/>
       <c r="E72" s="24" t="n">
@@ -6795,7 +6824,7 @@
         <v>3000000000</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D73" s="12"/>
       <c r="E73" s="24" t="n">
@@ -6814,7 +6843,7 @@
         <v>3375000000</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D74" s="12"/>
       <c r="E74" s="24" t="n">
@@ -6833,7 +6862,7 @@
         <v>3750000000</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D75" s="12"/>
       <c r="E75" s="24" t="n">
@@ -6852,7 +6881,7 @@
         <v>4125000000</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D76" s="12"/>
       <c r="E76" s="24" t="n">
@@ -6912,52 +6941,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>4000000</v>
@@ -6985,15 +7014,15 @@
         <v>6</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C6" s="14" t="n">
         <v>4000000</v>
@@ -7021,15 +7050,15 @@
         <v>7</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C7" s="14" t="n">
         <v>1</v>
@@ -7057,15 +7086,15 @@
         <v>952348370</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C8" s="14" t="n">
         <v>4000</v>
@@ -7093,7 +7122,7 @@
         <v>249100</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7101,7 +7130,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C9" s="14" t="n">
         <v>3000000</v>
@@ -7129,7 +7158,7 @@
         <v>4</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7137,7 +7166,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C10" s="14" t="n">
         <v>8000000</v>
@@ -7165,15 +7194,15 @@
         <v>5</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C11" s="14" t="n">
         <v>7000000</v>
@@ -7201,15 +7230,15 @@
         <v>0</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C12" s="14" t="n">
         <v>17000000</v>
@@ -7237,15 +7266,15 @@
         <v>0</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C13" s="14" t="n">
         <v>7000000</v>
@@ -7273,15 +7302,15 @@
         <v>0</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>17000000</v>
@@ -7309,15 +7338,15 @@
         <v>5</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C15" s="14" t="n">
         <v>7000000</v>
@@ -7345,15 +7374,15 @@
         <v>0</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C16" s="14" t="n">
         <v>17000000</v>
@@ -7381,15 +7410,15 @@
         <v>5</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C17" s="14" t="n">
         <v>3000000</v>
@@ -7417,15 +7446,15 @@
         <v>0</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C18" s="14" t="n">
         <v>8000000</v>
@@ -7453,15 +7482,15 @@
         <v>0</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C19" s="14" t="n">
         <v>3000000</v>
@@ -7489,15 +7518,15 @@
         <v>0</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C20" s="14" t="n">
         <v>8000000</v>
@@ -7525,15 +7554,15 @@
         <v>0</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C21" s="14" t="n">
         <v>3000000</v>
@@ -7561,15 +7590,15 @@
         <v>2</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C22" s="14" t="n">
         <v>8000000</v>
@@ -7597,15 +7626,15 @@
         <v>2</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C23" s="14" t="n">
         <v>3000000</v>
@@ -7633,15 +7662,15 @@
         <v>3</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C24" s="14" t="n">
         <v>8000000</v>
@@ -7669,15 +7698,15 @@
         <v>3</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C25" s="14" t="n">
         <v>8000000</v>
@@ -7705,15 +7734,15 @@
         <v>2</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C26" s="14" t="n">
         <v>17000000</v>
@@ -7741,15 +7770,15 @@
         <v>5</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C27" s="14" t="n">
         <v>8000000</v>
@@ -7777,15 +7806,15 @@
         <v>2</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C28" s="14" t="n">
         <v>17000000</v>
@@ -7813,15 +7842,15 @@
         <v>5</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C29" s="14" t="n">
         <v>8000000</v>
@@ -7849,15 +7878,15 @@
         <v>3</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C30" s="14" t="n">
         <v>17000000</v>
@@ -7885,15 +7914,15 @@
         <v>5</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C31" s="14" t="n">
         <v>40000000</v>
@@ -7921,15 +7950,15 @@
         <v>2</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C32" s="14" t="n">
         <v>80000000</v>
@@ -7957,15 +7986,15 @@
         <v>2</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C33" s="14" t="n">
         <v>150000000</v>
@@ -7993,15 +8022,15 @@
         <v>2</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C34" s="14" t="n">
         <v>200000000</v>
@@ -8029,15 +8058,15 @@
         <v>1</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C35" s="14" t="n">
         <v>200000000</v>
@@ -8065,15 +8094,15 @@
         <v>1</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C36" s="14" t="n">
         <v>17000000</v>
@@ -8101,15 +8130,15 @@
         <v>5</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C37" s="14" t="n">
         <v>150000000</v>
@@ -8137,15 +8166,15 @@
         <v>5</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C38" s="14" t="n">
         <v>17000000</v>
@@ -8173,15 +8202,15 @@
         <v>5</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C39" s="14" t="n">
         <v>50000000</v>
@@ -8209,15 +8238,15 @@
         <v>5</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C40" s="14" t="n">
         <v>150000000</v>
@@ -8245,15 +8274,15 @@
         <v>5</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C41" s="14" t="n">
         <v>17000000</v>
@@ -8281,15 +8310,15 @@
         <v>5</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C42" s="14" t="n">
         <v>150000000</v>
@@ -8317,15 +8346,15 @@
         <v>5</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C43" s="14" t="n">
         <v>17000000</v>
@@ -8353,15 +8382,15 @@
         <v>4</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C44" s="14" t="n">
         <v>50000000</v>
@@ -8389,15 +8418,15 @@
         <v>5</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C45" s="14" t="n">
         <v>150000000</v>
@@ -8425,15 +8454,15 @@
         <v>5</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C46" s="14" t="n">
         <v>4500000</v>
@@ -8461,21 +8490,21 @@
         <v>6</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C47" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E47" s="25" t="n">
         <v>40250000</v>
@@ -8497,12 +8526,12 @@
         <v>0</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="16" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E49" s="20" t="n">
         <f aca="false">SUM(E5:E47)</f>
@@ -8512,7 +8541,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="16" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E50" s="20"/>
       <c r="F50" s="20" t="n">
@@ -8522,7 +8551,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="16" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E51" s="20"/>
       <c r="F51" s="20" t="n">
@@ -8532,7 +8561,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -8577,43 +8606,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B5" s="27" t="n">
         <v>11980000</v>
@@ -8639,7 +8668,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B6" s="28" t="n">
         <f aca="false">SUMIFS(B13:B75,$I$13:$I$75,"Yes",$J$13:$J$75,"No")</f>
@@ -8672,7 +8701,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B7" s="28" t="n">
         <f aca="false">B5+B6</f>
@@ -8705,7 +8734,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B8" s="28" t="n">
         <f aca="false">SUMIF($J$79:$J$99,"Planned",B79:B99)</f>
@@ -8738,7 +8767,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">B7-B8</f>
@@ -8771,44 +8800,44 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>13</v>
@@ -8816,7 +8845,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B13" s="30" t="n">
         <v>100000</v>
@@ -8840,18 +8869,18 @@
         <v>0</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B14" s="30" t="n">
         <v>1600000</v>
@@ -8875,18 +8904,18 @@
         <v>0</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B15" s="30" t="n">
         <v>1600000</v>
@@ -8910,18 +8939,18 @@
         <v>0</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B16" s="30" t="n">
         <v>1600000</v>
@@ -8945,18 +8974,18 @@
         <v>0</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B17" s="30" t="n">
         <v>1600000</v>
@@ -8980,18 +9009,18 @@
         <v>0</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B18" s="30" t="n">
         <v>1600000</v>
@@ -9015,18 +9044,18 @@
         <v>0</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B19" s="30" t="n">
         <v>1600000</v>
@@ -9050,18 +9079,18 @@
         <v>0</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B20" s="30" t="n">
         <v>1600000</v>
@@ -9085,18 +9114,18 @@
         <v>0</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B21" s="30" t="n">
         <v>100000</v>
@@ -9120,16 +9149,16 @@
         <v>0</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B22" s="30" t="n">
         <v>200000</v>
@@ -9153,16 +9182,16 @@
         <v>0</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K22" s="15"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B23" s="30" t="n">
         <v>0</v>
@@ -9186,18 +9215,18 @@
         <v>0</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B24" s="30" t="n">
         <v>150000</v>
@@ -9221,16 +9250,16 @@
         <v>15</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B25" s="30" t="n">
         <v>150000</v>
@@ -9254,16 +9283,16 @@
         <v>20</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B26" s="30" t="n">
         <v>200000</v>
@@ -9287,16 +9316,16 @@
         <v>25</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K26" s="15"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B27" s="30" t="n">
         <v>250000</v>
@@ -9320,16 +9349,16 @@
         <v>30</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K27" s="15"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B28" s="30" t="n">
         <v>300000</v>
@@ -9353,16 +9382,16 @@
         <v>40</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K28" s="15"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B29" s="30" t="n">
         <v>350000</v>
@@ -9386,16 +9415,16 @@
         <v>45</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K29" s="15"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B30" s="30" t="n">
         <v>0</v>
@@ -9419,18 +9448,18 @@
         <v>0</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B31" s="30" t="n">
         <v>0</v>
@@ -9454,18 +9483,18 @@
         <v>0</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B32" s="30" t="n">
         <v>0</v>
@@ -9489,18 +9518,18 @@
         <v>0</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B33" s="30" t="n">
         <v>0</v>
@@ -9524,16 +9553,16 @@
         <v>800</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K33" s="15"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B34" s="30" t="n">
         <v>10000000</v>
@@ -9557,16 +9586,16 @@
         <v>0</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K34" s="15"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B35" s="30" t="n">
         <v>500000</v>
@@ -9590,16 +9619,16 @@
         <v>0</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K35" s="15"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B36" s="30" t="n">
         <v>0</v>
@@ -9623,18 +9652,18 @@
         <v>0</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B37" s="30" t="n">
         <v>0</v>
@@ -9658,18 +9687,18 @@
         <v>0</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B38" s="30" t="n">
         <v>0</v>
@@ -9693,18 +9722,18 @@
         <v>0</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B39" s="30" t="n">
         <v>0</v>
@@ -9728,16 +9757,16 @@
         <v>0</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K39" s="15"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B40" s="30" t="n">
         <v>0</v>
@@ -9761,18 +9790,18 @@
         <v>0</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B41" s="30" t="n">
         <v>0</v>
@@ -9796,18 +9825,18 @@
         <v>0</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B42" s="30" t="n">
         <v>0</v>
@@ -9831,18 +9860,18 @@
         <v>500</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B43" s="30" t="n">
         <v>0</v>
@@ -9866,18 +9895,18 @@
         <v>500</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B44" s="30" t="n">
         <v>0</v>
@@ -9901,18 +9930,18 @@
         <v>1000</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B45" s="30" t="n">
         <v>0</v>
@@ -9936,18 +9965,18 @@
         <v>0</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B46" s="30" t="n">
         <v>900000</v>
@@ -9971,18 +10000,18 @@
         <v>0</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B47" s="30" t="n">
         <v>0</v>
@@ -10006,18 +10035,18 @@
         <v>90</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B48" s="30" t="n">
         <v>3300000</v>
@@ -10041,18 +10070,18 @@
         <v>0</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B49" s="30" t="n">
         <v>3300000</v>
@@ -10076,18 +10105,18 @@
         <v>0</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B50" s="30" t="n">
         <v>0</v>
@@ -10111,18 +10140,18 @@
         <v>0</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B51" s="30" t="n">
         <v>0</v>
@@ -10146,18 +10175,18 @@
         <v>0</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B52" s="30" t="n">
         <v>0</v>
@@ -10181,18 +10210,18 @@
         <v>0</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B53" s="30" t="n">
         <v>750000</v>
@@ -10216,18 +10245,18 @@
         <v>0</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B54" s="30" t="n">
         <v>750000</v>
@@ -10251,18 +10280,18 @@
         <v>0</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B55" s="30" t="n">
         <v>750000</v>
@@ -10286,18 +10315,18 @@
         <v>0</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B56" s="30" t="n">
         <v>750000</v>
@@ -10321,18 +10350,18 @@
         <v>0</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B57" s="30" t="n">
         <v>750000</v>
@@ -10356,18 +10385,18 @@
         <v>0</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B58" s="30" t="n">
         <v>750000</v>
@@ -10391,18 +10420,18 @@
         <v>0</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B59" s="30" t="n">
         <v>750000</v>
@@ -10426,18 +10455,18 @@
         <v>0</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B60" s="30" t="n">
         <v>750000</v>
@@ -10461,18 +10490,18 @@
         <v>0</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B61" s="30" t="n">
         <v>0</v>
@@ -10496,18 +10525,18 @@
         <v>0</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B62" s="30" t="n">
         <v>0</v>
@@ -10531,18 +10560,18 @@
         <v>0</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B63" s="30" t="n">
         <v>82475</v>
@@ -10566,18 +10595,18 @@
         <v>0</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B64" s="30" t="n">
         <v>11000</v>
@@ -10601,18 +10630,18 @@
         <v>0</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B65" s="30" t="n">
         <v>0</v>
@@ -10636,13 +10665,13 @@
         <v>0</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10777,33 +10806,33 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="23" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>10</v>
@@ -10817,7 +10846,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B79" s="30" t="n">
         <v>1837500</v>
@@ -10844,15 +10873,15 @@
         <v>0</v>
       </c>
       <c r="J79" s="11" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B80" s="30" t="n">
         <v>0</v>
@@ -10879,13 +10908,13 @@
         <v>0</v>
       </c>
       <c r="J80" s="11" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K80" s="15"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B81" s="30" t="n">
         <v>9791250</v>
@@ -10912,15 +10941,15 @@
         <v>55000000</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B82" s="30" t="n">
         <v>0</v>
@@ -10947,15 +10976,15 @@
         <v>0</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K82" s="15" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B83" s="27"/>
       <c r="C83" s="30" t="n">
@@ -10974,15 +11003,15 @@
         <v>3000000</v>
       </c>
       <c r="J83" s="11" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K83" s="15" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B84" s="27"/>
       <c r="C84" s="30" t="n">
@@ -11001,15 +11030,15 @@
         <v>3000000</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K84" s="15" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B85" s="27"/>
       <c r="C85" s="30" t="n">
@@ -11028,15 +11057,15 @@
         <v>3000000</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K85" s="15" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B86" s="27"/>
       <c r="C86" s="30" t="n">
@@ -11055,15 +11084,15 @@
         <v>3000000</v>
       </c>
       <c r="J86" s="11" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K86" s="15" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B87" s="27"/>
       <c r="C87" s="30" t="n">
@@ -11088,15 +11117,15 @@
         <v>17000000</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K87" s="15" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="12" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B88" s="30" t="n">
         <v>0</v>
@@ -11123,15 +11152,15 @@
         <v>17000000</v>
       </c>
       <c r="J88" s="11" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K88" s="15" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="12" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B89" s="30" t="n">
         <v>0</v>
@@ -11158,15 +11187,15 @@
         <v>17000000</v>
       </c>
       <c r="J89" s="11" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K89" s="15" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="12" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B90" s="30" t="n">
         <v>0</v>
@@ -11187,15 +11216,15 @@
         <v>17000000</v>
       </c>
       <c r="J90" s="11" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="K90" s="15" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="12" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B91" s="30" t="n">
         <v>0</v>
@@ -11216,15 +11245,15 @@
         <v>17000000</v>
       </c>
       <c r="J91" s="11" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="K91" s="15" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="12" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B92" s="30" t="n">
         <v>0</v>
@@ -11245,15 +11274,15 @@
         <v>17000000</v>
       </c>
       <c r="J92" s="11" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="K92" s="15" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="12" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B93" s="30" t="n">
         <v>13000000</v>
@@ -11274,10 +11303,10 @@
         <v>8000000</v>
       </c>
       <c r="J93" s="11" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="K93" s="15" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11360,7 +11389,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="16" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="I101" s="20" t="n">
         <f aca="false">SUMIF(J79:J99,"Planned",I79:I99)</f>
@@ -11419,72 +11448,72 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C6" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -11496,19 +11525,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C7" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -11520,19 +11549,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -11544,19 +11573,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C9" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -11568,19 +11597,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C10" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -11592,19 +11621,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C11" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -11616,19 +11645,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C12" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -11640,19 +11669,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C13" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -11664,19 +11693,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C14" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -11688,19 +11717,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C15" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -11712,19 +11741,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C16" s="24" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -11736,16 +11765,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C17" s="24" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -11758,19 +11787,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C18" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -11782,19 +11811,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C19" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -11806,19 +11835,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C20" s="24" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -11830,24 +11859,24 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C22" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -11859,16 +11888,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C23" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -11881,16 +11910,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
+        <v>536</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>533</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>530</v>
-      </c>
       <c r="C24" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -11903,19 +11932,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -11927,19 +11956,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -11951,16 +11980,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -11973,16 +12002,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C28" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -11995,21 +12024,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C30" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -12022,16 +12051,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C31" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -12044,16 +12073,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -12066,19 +12095,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
@@ -12090,16 +12119,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -12112,16 +12141,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C35" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -12134,16 +12163,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C36" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -12156,16 +12185,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C37" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -12178,16 +12207,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C38" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="E38" s="32"/>
       <c r="F38" s="32"/>
@@ -12200,7 +12229,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E40" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$38)*(E5:E38="Done"))</f>
@@ -12237,7 +12266,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E41" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$38,"Required",E5:E38,"Done")&amp;" of 11"</f>
@@ -12274,7 +12303,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
   </sheetData>
@@ -12318,23 +12347,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12345,24 +12374,24 @@
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B6" s="19" t="n">
         <v>308343695</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -12386,7 +12415,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E7" s="20" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -12412,7 +12441,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -12420,7 +12449,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -12429,11 +12458,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>17190624.5774776</v>
+        <v>17193594.7255043</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12441,28 +12470,28 @@
         <v>159</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12472,7 +12501,7 @@
       <c r="B13" s="27"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -12498,7 +12527,7 @@
       <c r="B14" s="27"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -12524,7 +12553,7 @@
       <c r="B15" s="27"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -12550,7 +12579,7 @@
       <c r="B16" s="27"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -12575,10 +12604,10 @@
       </c>
       <c r="B17" s="27"/>
       <c r="C17" s="12" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -12603,10 +12632,10 @@
       </c>
       <c r="B18" s="27"/>
       <c r="C18" s="12" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -12631,10 +12660,10 @@
       </c>
       <c r="B19" s="27"/>
       <c r="C19" s="12" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -12659,10 +12688,10 @@
       </c>
       <c r="B20" s="27"/>
       <c r="C20" s="12" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -12687,10 +12716,10 @@
       </c>
       <c r="B21" s="27"/>
       <c r="C21" s="12" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -12715,10 +12744,10 @@
       </c>
       <c r="B22" s="27"/>
       <c r="C22" s="12" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -12744,7 +12773,7 @@
       <c r="B23" s="27"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -12769,10 +12798,10 @@
       </c>
       <c r="B24" s="27"/>
       <c r="C24" s="12" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -12797,10 +12826,10 @@
       </c>
       <c r="B25" s="27"/>
       <c r="C25" s="12" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -12825,10 +12854,10 @@
       </c>
       <c r="B26" s="27"/>
       <c r="C26" s="12" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -12856,7 +12885,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -12883,10 +12912,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
+        <v>603</v>
+      </c>
+      <c r="D28" s="12" t="s">
         <v>600</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>597</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -12913,10 +12942,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -12943,10 +12972,10 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E30" s="27"/>
       <c r="F30" s="27"/>
@@ -12967,10 +12996,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -12997,7 +13026,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -13025,10 +13054,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -13055,7 +13084,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -13083,10 +13112,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -13113,7 +13142,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -13141,10 +13170,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -13171,7 +13200,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -13199,10 +13228,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -13229,7 +13258,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -13257,10 +13286,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -13287,7 +13316,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -13315,10 +13344,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -13345,7 +13374,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -13373,7 +13402,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -13401,7 +13430,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -13429,7 +13458,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -13457,7 +13486,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -13485,7 +13514,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -13513,7 +13542,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -13541,7 +13570,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -13569,7 +13598,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -13597,7 +13626,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -13625,7 +13654,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -13647,7 +13676,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -5725,7 +5725,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>525654635.46022</v>
+        <v>552080687.146026</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8645,7 +8645,7 @@
         <v>377</v>
       </c>
       <c r="B5" s="27" t="n">
-        <v>11980000</v>
+        <v>12170000</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>336000</v>
@@ -8660,7 +8660,7 @@
         <v>227</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>759</v>
+        <v>807</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>492</v>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="B7" s="28" t="n">
         <f aca="false">B5+B6</f>
-        <v>41180000</v>
+        <v>41370000</v>
       </c>
       <c r="C7" s="28" t="n">
         <f aca="false">C5+C6</f>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="G7" s="28" t="n">
         <f aca="false">G5+G6</f>
-        <v>859</v>
+        <v>907</v>
       </c>
       <c r="H7" s="28" t="n">
         <f aca="false">H5+H6</f>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">B7-B8</f>
-        <v>41180000</v>
+        <v>41370000</v>
       </c>
       <c r="C9" s="29" t="n">
         <f aca="false">C7-C8</f>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="G9" s="29" t="n">
         <f aca="false">G7-G8</f>
-        <v>859</v>
+        <v>907</v>
       </c>
       <c r="H9" s="29" t="n">
         <f aca="false">H7-H8</f>
@@ -10574,7 +10574,7 @@
         <v>458</v>
       </c>
       <c r="B63" s="30" t="n">
-        <v>82475</v>
+        <v>168250</v>
       </c>
       <c r="C63" s="30" t="n">
         <v>0</v>
@@ -10589,7 +10589,7 @@
         <v>10</v>
       </c>
       <c r="G63" s="30" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="H63" s="30" t="n">
         <v>0</v>
@@ -10609,7 +10609,7 @@
         <v>460</v>
       </c>
       <c r="B64" s="30" t="n">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="C64" s="30" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>17193594.7255043</v>
+        <v>18057962.3055084</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="634">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -1327,13 +1327,22 @@
     <t xml:space="preserve">Kyln tower. Ion type read from icons, confirm</t>
   </si>
   <si>
+    <t xml:space="preserve">Gold Rush, Oct 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claimed, 900K in current stock</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gold Rush run</t>
   </si>
   <si>
+    <t xml:space="preserve">Runs Sundays, Mondays and other days. Set to Yes on days it runs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training Day run</t>
+  </si>
+  <si>
     <t xml:space="preserve">Set to Yes on days it runs. Copy the row for more runs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Training Day run</t>
   </si>
   <si>
     <t xml:space="preserve">Level 110 gold orb, promo code Oct 11</t>
@@ -5725,7 +5734,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>552080687.146026</v>
+        <v>552133663.562459</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8593,7 +8602,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -8645,7 +8654,7 @@
         <v>377</v>
       </c>
       <c r="B5" s="27" t="n">
-        <v>12170000</v>
+        <v>13070000</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>336000</v>
@@ -8671,31 +8680,31 @@
         <v>378</v>
       </c>
       <c r="B6" s="28" t="n">
-        <f aca="false">SUMIFS(B13:B75,$I$13:$I$75,"Yes",$J$13:$J$75,"No")</f>
+        <f aca="false">SUMIFS(B13:B76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
         <v>29200000</v>
       </c>
       <c r="C6" s="28" t="n">
-        <f aca="false">SUMIFS(C13:C75,$I$13:$I$75,"Yes",$J$13:$J$75,"No")</f>
+        <f aca="false">SUMIFS(C13:C76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
         <v>4650000</v>
       </c>
       <c r="D6" s="28" t="n">
-        <f aca="false">SUMIFS(D13:D75,$I$13:$I$75,"Yes",$J$13:$J$75,"No")</f>
+        <f aca="false">SUMIFS(D13:D76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
         <v>3886000</v>
       </c>
       <c r="E6" s="28" t="n">
-        <f aca="false">SUMIFS(E13:E75,$I$13:$I$75,"Yes",$J$13:$J$75,"No")</f>
+        <f aca="false">SUMIFS(E13:E76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
         <v>5386000</v>
       </c>
       <c r="F6" s="28" t="n">
-        <f aca="false">SUMIFS(F13:F75,$I$13:$I$75,"Yes",$J$13:$J$75,"No")</f>
+        <f aca="false">SUMIFS(F13:F76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
         <v>0</v>
       </c>
       <c r="G6" s="28" t="n">
-        <f aca="false">SUMIFS(G13:G75,$I$13:$I$75,"Yes",$J$13:$J$75,"No")</f>
+        <f aca="false">SUMIFS(G13:G76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
         <v>100</v>
       </c>
       <c r="H6" s="28" t="n">
-        <f aca="false">SUMIFS(H13:H75,$I$13:$I$75,"Yes",$J$13:$J$75,"No")</f>
+        <f aca="false">SUMIFS(H13:H76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
         <v>940</v>
       </c>
     </row>
@@ -8705,7 +8714,7 @@
       </c>
       <c r="B7" s="28" t="n">
         <f aca="false">B5+B6</f>
-        <v>41370000</v>
+        <v>42270000</v>
       </c>
       <c r="C7" s="28" t="n">
         <f aca="false">C5+C6</f>
@@ -8737,31 +8746,31 @@
         <v>380</v>
       </c>
       <c r="B8" s="28" t="n">
-        <f aca="false">SUMIF($J$79:$J$99,"Planned",B79:B99)</f>
+        <f aca="false">SUMIF($J$80:$J$100,"Planned",B80:B100)</f>
         <v>0</v>
       </c>
       <c r="C8" s="28" t="n">
-        <f aca="false">SUMIF($J$79:$J$99,"Planned",C79:C99)</f>
+        <f aca="false">SUMIF($J$80:$J$100,"Planned",C80:C100)</f>
         <v>1710000</v>
       </c>
       <c r="D8" s="28" t="n">
-        <f aca="false">SUMIF($J$79:$J$99,"Planned",D79:D99)</f>
+        <f aca="false">SUMIF($J$80:$J$100,"Planned",D80:D100)</f>
         <v>1710000</v>
       </c>
       <c r="E8" s="28" t="n">
-        <f aca="false">SUMIF($J$79:$J$99,"Planned",E79:E99)</f>
+        <f aca="false">SUMIF($J$80:$J$100,"Planned",E80:E100)</f>
         <v>2640000</v>
       </c>
       <c r="F8" s="28" t="n">
-        <f aca="false">SUMIF($J$79:$J$99,"Planned",F79:F99)</f>
+        <f aca="false">SUMIF($J$80:$J$100,"Planned",F80:F100)</f>
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <f aca="false">SUMIF($J$79:$J$99,"Planned",G79:G99)</f>
+        <f aca="false">SUMIF($J$80:$J$100,"Planned",G80:G100)</f>
         <v>0</v>
       </c>
       <c r="H8" s="28" t="n">
-        <f aca="false">SUMIF($J$79:$J$99,"Planned",H79:H99)</f>
+        <f aca="false">SUMIF($J$80:$J$100,"Planned",H80:H100)</f>
         <v>0</v>
       </c>
     </row>
@@ -8771,7 +8780,7 @@
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">B7-B8</f>
-        <v>41370000</v>
+        <v>42270000</v>
       </c>
       <c r="C9" s="29" t="n">
         <f aca="false">C7-C8</f>
@@ -9979,7 +9988,7 @@
         <v>431</v>
       </c>
       <c r="B46" s="30" t="n">
-        <v>900000</v>
+        <v>0</v>
       </c>
       <c r="C46" s="30" t="n">
         <v>0</v>
@@ -10000,7 +10009,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="J46" s="11" t="s">
         <v>315</v>
@@ -10014,7 +10023,7 @@
         <v>433</v>
       </c>
       <c r="B47" s="30" t="n">
-        <v>0</v>
+        <v>900000</v>
       </c>
       <c r="C47" s="30" t="n">
         <v>0</v>
@@ -10029,10 +10038,10 @@
         <v>0</v>
       </c>
       <c r="G47" s="30" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H47" s="30" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I47" s="11" t="s">
         <v>315</v>
@@ -10041,15 +10050,15 @@
         <v>315</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B48" s="30" t="n">
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="C48" s="30" t="n">
         <v>0</v>
@@ -10064,24 +10073,24 @@
         <v>0</v>
       </c>
       <c r="G48" s="30" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H48" s="30" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B49" s="30" t="n">
         <v>3300000</v>
@@ -10111,18 +10120,18 @@
         <v>311</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B50" s="30" t="n">
-        <v>0</v>
+        <v>3300000</v>
       </c>
       <c r="C50" s="30" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="D50" s="30" t="n">
         <v>0</v>
@@ -10143,21 +10152,21 @@
         <v>311</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B51" s="30" t="n">
         <v>0</v>
       </c>
       <c r="C51" s="30" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="D51" s="30" t="n">
         <v>0</v>
@@ -10181,12 +10190,12 @@
         <v>315</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B52" s="30" t="n">
         <v>0</v>
@@ -10195,10 +10204,10 @@
         <v>0</v>
       </c>
       <c r="D52" s="30" t="n">
-        <v>136000</v>
+        <v>0</v>
       </c>
       <c r="E52" s="30" t="n">
-        <v>136000</v>
+        <v>0</v>
       </c>
       <c r="F52" s="30" t="n">
         <v>0</v>
@@ -10216,24 +10225,24 @@
         <v>315</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B53" s="30" t="n">
-        <v>750000</v>
+        <v>0</v>
       </c>
       <c r="C53" s="30" t="n">
         <v>0</v>
       </c>
       <c r="D53" s="30" t="n">
-        <v>0</v>
+        <v>136000</v>
       </c>
       <c r="E53" s="30" t="n">
-        <v>0</v>
+        <v>136000</v>
       </c>
       <c r="F53" s="30" t="n">
         <v>0</v>
@@ -10251,12 +10260,12 @@
         <v>315</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B54" s="30" t="n">
         <v>750000</v>
@@ -10286,12 +10295,12 @@
         <v>315</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B55" s="30" t="n">
         <v>750000</v>
@@ -10321,12 +10330,12 @@
         <v>315</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B56" s="30" t="n">
         <v>750000</v>
@@ -10356,12 +10365,12 @@
         <v>315</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B57" s="30" t="n">
         <v>750000</v>
@@ -10391,12 +10400,12 @@
         <v>315</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B58" s="30" t="n">
         <v>750000</v>
@@ -10426,12 +10435,12 @@
         <v>315</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B59" s="30" t="n">
         <v>750000</v>
@@ -10461,12 +10470,12 @@
         <v>315</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B60" s="30" t="n">
         <v>750000</v>
@@ -10496,18 +10505,18 @@
         <v>315</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B61" s="30" t="n">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="C61" s="30" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="D61" s="30" t="n">
         <v>0</v>
@@ -10531,18 +10540,18 @@
         <v>315</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B62" s="30" t="n">
         <v>0</v>
       </c>
       <c r="C62" s="30" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="D62" s="30" t="n">
         <v>0</v>
@@ -10566,15 +10575,15 @@
         <v>315</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B63" s="30" t="n">
-        <v>168250</v>
+        <v>0</v>
       </c>
       <c r="C63" s="30" t="n">
         <v>0</v>
@@ -10586,10 +10595,10 @@
         <v>0</v>
       </c>
       <c r="F63" s="30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G63" s="30" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H63" s="30" t="n">
         <v>0</v>
@@ -10598,18 +10607,18 @@
         <v>311</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B64" s="30" t="n">
-        <v>12000</v>
+        <v>168250</v>
       </c>
       <c r="C64" s="30" t="n">
         <v>0</v>
@@ -10621,10 +10630,10 @@
         <v>0</v>
       </c>
       <c r="F64" s="30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G64" s="30" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H64" s="30" t="n">
         <v>0</v>
@@ -10636,15 +10645,15 @@
         <v>311</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B65" s="30" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="C65" s="30" t="n">
         <v>0</v>
@@ -10665,27 +10674,49 @@
         <v>0</v>
       </c>
       <c r="I65" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="K65" s="15" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="B66" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="J65" s="11" t="s">
+      <c r="J66" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="K65" s="15" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="12"/>
-      <c r="B66" s="30"/>
-      <c r="C66" s="30"/>
-      <c r="D66" s="30"/>
-      <c r="E66" s="30"/>
-      <c r="F66" s="30"/>
-      <c r="G66" s="30"/>
-      <c r="H66" s="30"/>
-      <c r="I66" s="11"/>
-      <c r="J66" s="11"/>
-      <c r="K66" s="12"/>
+      <c r="K66" s="15" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="12"/>
@@ -10804,79 +10835,57 @@
       <c r="J75" s="11"/>
       <c r="K75" s="12"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="23" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="B78" s="3" t="s">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="12"/>
+      <c r="B76" s="30"/>
+      <c r="C76" s="30"/>
+      <c r="D76" s="30"/>
+      <c r="E76" s="30"/>
+      <c r="F76" s="30"/>
+      <c r="G76" s="30"/>
+      <c r="H76" s="30"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="11"/>
+      <c r="K76" s="12"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="23" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D79" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="E78" s="3" t="s">
+      <c r="E79" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="F79" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="G79" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="H78" s="3" t="s">
+      <c r="H79" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="I78" s="3" t="s">
+      <c r="I79" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J78" s="3" t="s">
+      <c r="J79" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K78" s="3" t="s">
+      <c r="K79" s="3" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="12" t="s">
-        <v>466</v>
-      </c>
-      <c r="B79" s="30" t="n">
-        <v>1837500</v>
-      </c>
-      <c r="C79" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G79" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79" s="30" t="n">
-        <v>183</v>
-      </c>
-      <c r="I79" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="K79" s="15" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10884,10 +10893,10 @@
         <v>469</v>
       </c>
       <c r="B80" s="30" t="n">
-        <v>0</v>
+        <v>1837500</v>
       </c>
       <c r="C80" s="30" t="n">
-        <v>359800</v>
+        <v>0</v>
       </c>
       <c r="D80" s="30" t="n">
         <v>0</v>
@@ -10896,66 +10905,66 @@
         <v>0</v>
       </c>
       <c r="F80" s="30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G80" s="30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" s="30" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="I80" s="30" t="n">
         <v>0</v>
       </c>
       <c r="J80" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="K80" s="15"/>
+        <v>470</v>
+      </c>
+      <c r="K80" s="15" t="s">
+        <v>471</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="B81" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="30" t="n">
+        <v>359800</v>
+      </c>
+      <c r="D81" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="B81" s="30" t="n">
-        <v>9791250</v>
-      </c>
-      <c r="C81" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="30" t="n">
-        <v>979</v>
-      </c>
-      <c r="I81" s="30" t="n">
-        <v>55000000</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="K81" s="15" t="s">
-        <v>471</v>
-      </c>
+      <c r="K81" s="15"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B82" s="30" t="n">
-        <v>0</v>
+        <v>9791250</v>
       </c>
       <c r="C82" s="30" t="n">
-        <v>359800</v>
+        <v>0</v>
       </c>
       <c r="D82" s="30" t="n">
         <v>0</v>
@@ -10964,31 +10973,33 @@
         <v>0</v>
       </c>
       <c r="F82" s="30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" s="30" t="n">
         <v>0</v>
       </c>
       <c r="H82" s="30" t="n">
-        <v>0</v>
+        <v>979</v>
       </c>
       <c r="I82" s="30" t="n">
-        <v>0</v>
+        <v>55000000</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K82" s="15" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="s">
-        <v>473</v>
-      </c>
-      <c r="B83" s="27"/>
+        <v>475</v>
+      </c>
+      <c r="B83" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="C83" s="30" t="n">
-        <v>0</v>
+        <v>359800</v>
       </c>
       <c r="D83" s="30" t="n">
         <v>0</v>
@@ -10996,17 +11007,23 @@
       <c r="E83" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F83" s="27"/>
-      <c r="G83" s="27"/>
-      <c r="H83" s="27"/>
+      <c r="F83" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="I83" s="30" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="J83" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="K83" s="15" t="s">
         <v>474</v>
-      </c>
-      <c r="K83" s="15" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11030,15 +11047,15 @@
         <v>3000000</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="K84" s="15" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B85" s="27"/>
       <c r="C85" s="30" t="n">
@@ -11057,15 +11074,15 @@
         <v>3000000</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="K85" s="15" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B86" s="27"/>
       <c r="C86" s="30" t="n">
@@ -11084,15 +11101,15 @@
         <v>3000000</v>
       </c>
       <c r="J86" s="11" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="K86" s="15" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B87" s="27"/>
       <c r="C87" s="30" t="n">
@@ -11104,40 +11121,32 @@
       <c r="E87" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F87" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="30" t="n">
-        <v>0</v>
-      </c>
+      <c r="F87" s="27"/>
+      <c r="G87" s="27"/>
+      <c r="H87" s="27"/>
       <c r="I87" s="30" t="n">
-        <v>17000000</v>
+        <v>3000000</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="K87" s="15" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="12" t="s">
-        <v>480</v>
-      </c>
-      <c r="B88" s="30" t="n">
-        <v>0</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="B88" s="27"/>
       <c r="C88" s="30" t="n">
-        <v>1710500</v>
+        <v>0</v>
       </c>
       <c r="D88" s="30" t="n">
-        <v>1710000</v>
+        <v>0</v>
       </c>
       <c r="E88" s="30" t="n">
-        <v>2640000</v>
+        <v>0</v>
       </c>
       <c r="F88" s="30" t="n">
         <v>0</v>
@@ -11152,21 +11161,21 @@
         <v>17000000</v>
       </c>
       <c r="J88" s="11" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="K88" s="15" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="12" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B89" s="30" t="n">
         <v>0</v>
       </c>
       <c r="C89" s="30" t="n">
-        <v>1710000</v>
+        <v>1710500</v>
       </c>
       <c r="D89" s="30" t="n">
         <v>1710000</v>
@@ -11187,22 +11196,28 @@
         <v>17000000</v>
       </c>
       <c r="J89" s="11" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="K89" s="15" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="12" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B90" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C90" s="27"/>
-      <c r="D90" s="27"/>
-      <c r="E90" s="27"/>
+      <c r="C90" s="30" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="D90" s="30" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="E90" s="30" t="n">
+        <v>2640000</v>
+      </c>
       <c r="F90" s="30" t="n">
         <v>0</v>
       </c>
@@ -11216,15 +11231,15 @@
         <v>17000000</v>
       </c>
       <c r="J90" s="11" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="K90" s="15" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="12" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B91" s="30" t="n">
         <v>0</v>
@@ -11245,15 +11260,15 @@
         <v>17000000</v>
       </c>
       <c r="J91" s="11" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K91" s="15" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="12" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B92" s="30" t="n">
         <v>0</v>
@@ -11274,53 +11289,69 @@
         <v>17000000</v>
       </c>
       <c r="J92" s="11" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K92" s="15" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="B93" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="27"/>
+      <c r="D93" s="27"/>
+      <c r="E93" s="27"/>
+      <c r="F93" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J93" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="B93" s="30" t="n">
+      <c r="K93" s="15" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="B94" s="30" t="n">
         <v>13000000</v>
       </c>
-      <c r="C93" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" s="27"/>
-      <c r="G93" s="27"/>
-      <c r="H93" s="27"/>
-      <c r="I93" s="30" t="n">
+      <c r="C94" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="27"/>
+      <c r="G94" s="27"/>
+      <c r="H94" s="27"/>
+      <c r="I94" s="30" t="n">
         <v>8000000</v>
       </c>
-      <c r="J93" s="11" t="s">
-        <v>485</v>
-      </c>
-      <c r="K93" s="15" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="12"/>
-      <c r="B94" s="30"/>
-      <c r="C94" s="30"/>
-      <c r="D94" s="30"/>
-      <c r="E94" s="30"/>
-      <c r="F94" s="30"/>
-      <c r="G94" s="30"/>
-      <c r="H94" s="30"/>
-      <c r="I94" s="30"/>
-      <c r="J94" s="11"/>
-      <c r="K94" s="12"/>
+      <c r="J94" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="K94" s="15" t="s">
+        <v>492</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="12"/>
@@ -11387,12 +11418,25 @@
       <c r="J99" s="11"/>
       <c r="K99" s="12"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="16" t="s">
-        <v>490</v>
-      </c>
-      <c r="I101" s="20" t="n">
-        <f aca="false">SUMIF(J79:J99,"Planned",I79:I99)</f>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="12"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
+      <c r="J100" s="11"/>
+      <c r="K100" s="12"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="I102" s="20" t="n">
+        <f aca="false">SUMIF(J80:J100,"Planned",I80:I100)</f>
         <v>46000000</v>
       </c>
     </row>
@@ -11402,22 +11446,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J79:J99">
+  <conditionalFormatting sqref="J80:J100">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J13:J75">
+  <conditionalFormatting sqref="J13:J76">
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13:J75" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13:J76" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J79:J99" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J80:J100" type="list">
       <formula1>"Planned,Done,Skipped"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -11448,12 +11492,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11467,53 +11511,53 @@
         <v>370</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C6" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -11525,19 +11569,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C7" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -11549,19 +11593,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -11573,19 +11617,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C9" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -11597,19 +11641,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C10" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -11621,19 +11665,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C11" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -11645,19 +11689,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C12" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -11669,19 +11713,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C13" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -11693,19 +11737,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C14" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -11717,19 +11761,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C15" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -11741,19 +11785,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C16" s="24" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -11765,16 +11809,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C17" s="24" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -11787,19 +11831,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C18" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -11811,19 +11855,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C19" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -11835,19 +11879,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C20" s="24" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -11859,24 +11903,24 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C22" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -11888,16 +11932,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C23" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -11910,16 +11954,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>536</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>533</v>
-      </c>
       <c r="C24" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -11932,19 +11976,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -11956,19 +12000,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -11980,16 +12024,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -12002,16 +12046,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C28" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -12024,21 +12068,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C30" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -12051,16 +12095,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C31" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -12073,16 +12117,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -12095,19 +12139,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
@@ -12119,16 +12163,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -12141,16 +12185,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C35" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -12163,16 +12207,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C36" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -12185,16 +12229,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C37" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -12207,16 +12251,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C38" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E38" s="32"/>
       <c r="F38" s="32"/>
@@ -12229,7 +12273,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E40" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$38)*(E5:E38="Done"))</f>
@@ -12266,7 +12310,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="E41" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$38,"Required",E5:E38,"Done")&amp;" of 11"</f>
@@ -12303,7 +12347,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -12347,12 +12391,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12360,10 +12404,10 @@
         <v>224</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12374,13 +12418,13 @@
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12391,7 +12435,7 @@
         <v>308343695</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -12441,7 +12485,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -12449,7 +12493,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -12458,11 +12502,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>18057962.3055084</v>
+        <v>18059695.1080089</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12473,19 +12517,19 @@
         <v>233</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
@@ -12501,7 +12545,7 @@
       <c r="B13" s="27"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -12527,7 +12571,7 @@
       <c r="B14" s="27"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -12553,7 +12597,7 @@
       <c r="B15" s="27"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -12579,7 +12623,7 @@
       <c r="B16" s="27"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -12604,10 +12648,10 @@
       </c>
       <c r="B17" s="27"/>
       <c r="C17" s="12" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -12632,10 +12676,10 @@
       </c>
       <c r="B18" s="27"/>
       <c r="C18" s="12" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -12660,10 +12704,10 @@
       </c>
       <c r="B19" s="27"/>
       <c r="C19" s="12" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -12688,10 +12732,10 @@
       </c>
       <c r="B20" s="27"/>
       <c r="C20" s="12" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -12716,10 +12760,10 @@
       </c>
       <c r="B21" s="27"/>
       <c r="C21" s="12" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -12744,10 +12788,10 @@
       </c>
       <c r="B22" s="27"/>
       <c r="C22" s="12" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -12773,7 +12817,7 @@
       <c r="B23" s="27"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -12798,10 +12842,10 @@
       </c>
       <c r="B24" s="27"/>
       <c r="C24" s="12" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -12826,10 +12870,10 @@
       </c>
       <c r="B25" s="27"/>
       <c r="C25" s="12" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -12854,10 +12898,10 @@
       </c>
       <c r="B26" s="27"/>
       <c r="C26" s="12" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -12885,7 +12929,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -12912,10 +12956,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="D28" s="12" t="s">
         <v>603</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>600</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -12942,10 +12986,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -12972,10 +13016,10 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E30" s="27"/>
       <c r="F30" s="27"/>
@@ -12996,10 +13040,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -13026,7 +13070,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -13054,10 +13098,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -13084,7 +13128,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -13112,10 +13156,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -13142,7 +13186,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -13170,10 +13214,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -13200,7 +13244,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -13228,10 +13272,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -13258,7 +13302,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -13286,10 +13330,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -13316,7 +13360,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -13344,10 +13388,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -13374,7 +13418,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -13402,7 +13446,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -13430,7 +13474,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -13458,7 +13502,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -13486,7 +13530,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -13514,7 +13558,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -13542,7 +13586,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -13570,7 +13614,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -13598,7 +13642,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -13626,7 +13670,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -13654,7 +13698,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -13676,7 +13720,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -1432,7 +1432,7 @@
     <t xml:space="preserve">Gold orbs</t>
   </si>
   <si>
-    <t xml:space="preserve">Random amount. Enter what you get</t>
+    <t xml:space="preserve">Running total of basic gold orbs opened. Already in current stock</t>
   </si>
   <si>
     <t xml:space="preserve">Planned upgrades</t>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>552133663.562459</v>
+        <v>552176552.000634</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8654,7 +8654,7 @@
         <v>377</v>
       </c>
       <c r="B5" s="27" t="n">
-        <v>13070000</v>
+        <v>13545000</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>336000</v>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="B7" s="28" t="n">
         <f aca="false">B5+B6</f>
-        <v>42270000</v>
+        <v>42745000</v>
       </c>
       <c r="C7" s="28" t="n">
         <f aca="false">C5+C6</f>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">B7-B8</f>
-        <v>42270000</v>
+        <v>42745000</v>
       </c>
       <c r="C9" s="29" t="n">
         <f aca="false">C7-C8</f>
@@ -10688,7 +10688,7 @@
         <v>465</v>
       </c>
       <c r="B66" s="30" t="n">
-        <v>0</v>
+        <v>375000</v>
       </c>
       <c r="C66" s="30" t="n">
         <v>0</v>
@@ -12506,7 +12506,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>18059695.1080089</v>
+        <v>18061097.9395796</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -5734,7 +5734,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>552176552.000634</v>
+        <v>552245628.915153</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8654,7 +8654,7 @@
         <v>377</v>
       </c>
       <c r="B5" s="27" t="n">
-        <v>13545000</v>
+        <v>13554775</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>336000</v>
@@ -8669,7 +8669,7 @@
         <v>227</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>807</v>
+        <v>871</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>492</v>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="B7" s="28" t="n">
         <f aca="false">B5+B6</f>
-        <v>42745000</v>
+        <v>42754775</v>
       </c>
       <c r="C7" s="28" t="n">
         <f aca="false">C5+C6</f>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="G7" s="28" t="n">
         <f aca="false">G5+G6</f>
-        <v>907</v>
+        <v>971</v>
       </c>
       <c r="H7" s="28" t="n">
         <f aca="false">H5+H6</f>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">B7-B8</f>
-        <v>42745000</v>
+        <v>42754775</v>
       </c>
       <c r="C9" s="29" t="n">
         <f aca="false">C7-C8</f>
@@ -8800,7 +8800,7 @@
       </c>
       <c r="G9" s="29" t="n">
         <f aca="false">G7-G8</f>
-        <v>907</v>
+        <v>971</v>
       </c>
       <c r="H9" s="29" t="n">
         <f aca="false">H7-H8</f>
@@ -10618,7 +10618,7 @@
         <v>461</v>
       </c>
       <c r="B64" s="30" t="n">
-        <v>168250</v>
+        <v>178025</v>
       </c>
       <c r="C64" s="30" t="n">
         <v>0</v>
@@ -10668,7 +10668,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="30" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H65" s="30" t="n">
         <v>0</v>
@@ -12506,7 +12506,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>18061097.9395796</v>
+        <v>18063357.3768684</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="640">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -1465,24 +1465,45 @@
     <t xml:space="preserve">Doctor Strange to level 101</t>
   </si>
   <si>
+    <t xml:space="preserve">Skipped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Astral team is low priority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whiplash to level 101</t>
+  </si>
+  <si>
     <t xml:space="preserve">Planned</t>
   </si>
   <si>
+    <t xml:space="preserve">Expect about 1.65M gold and 164 orange, like Storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storm to level 101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uncanny Avengers, from training screen Oct 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Second Uncanny Avenger to level 101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate from Storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Third Uncanny Avenger to level 101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate from Storm. Needs battle pass level 95 orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whiplash to gear tier 20</t>
+  </si>
+  <si>
     <t xml:space="preserve">Check cost in game</t>
   </si>
   <si>
-    <t xml:space="preserve">Whiplash to level 101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yellowjacket to level 101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ancient One to level 101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whiplash to gear tier 20</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hulk Iso-8 to T3 level 5</t>
   </si>
   <si>
@@ -1496,9 +1517,6 @@
   </si>
   <si>
     <t xml:space="preserve">Blade (Mighty) Iso-8 to T3 level 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skipped</t>
   </si>
   <si>
     <t xml:space="preserve">Spider-Woman (Julia) Iso-8 to T3 level 5</t>
@@ -5734,7 +5752,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>552245628.915153</v>
+        <v>552317272.231916</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8602,7 +8620,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -8654,7 +8672,7 @@
         <v>377</v>
       </c>
       <c r="B5" s="27" t="n">
-        <v>13554775</v>
+        <v>15270000</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>336000</v>
@@ -8672,7 +8690,7 @@
         <v>871</v>
       </c>
       <c r="H5" s="27" t="n">
-        <v>492</v>
+        <v>522</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8681,7 +8699,7 @@
       </c>
       <c r="B6" s="28" t="n">
         <f aca="false">SUMIFS(B13:B76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
-        <v>29200000</v>
+        <v>28750000</v>
       </c>
       <c r="C6" s="28" t="n">
         <f aca="false">SUMIFS(C13:C76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
@@ -8705,7 +8723,7 @@
       </c>
       <c r="H6" s="28" t="n">
         <f aca="false">SUMIFS(H13:H76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
-        <v>940</v>
+        <v>885</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8714,7 +8732,7 @@
       </c>
       <c r="B7" s="28" t="n">
         <f aca="false">B5+B6</f>
-        <v>42754775</v>
+        <v>44020000</v>
       </c>
       <c r="C7" s="28" t="n">
         <f aca="false">C5+C6</f>
@@ -8738,7 +8756,7 @@
       </c>
       <c r="H7" s="28" t="n">
         <f aca="false">H5+H6</f>
-        <v>1432</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8746,32 +8764,32 @@
         <v>380</v>
       </c>
       <c r="B8" s="28" t="n">
-        <f aca="false">SUMIF($J$80:$J$100,"Planned",B80:B100)</f>
-        <v>0</v>
+        <f aca="false">SUMIF($J$80:$J$101,"Planned",B80:B101)</f>
+        <v>4950010</v>
       </c>
       <c r="C8" s="28" t="n">
-        <f aca="false">SUMIF($J$80:$J$100,"Planned",C80:C100)</f>
+        <f aca="false">SUMIF($J$80:$J$101,"Planned",C80:C101)</f>
         <v>1710000</v>
       </c>
       <c r="D8" s="28" t="n">
-        <f aca="false">SUMIF($J$80:$J$100,"Planned",D80:D100)</f>
+        <f aca="false">SUMIF($J$80:$J$101,"Planned",D80:D101)</f>
         <v>1710000</v>
       </c>
       <c r="E8" s="28" t="n">
-        <f aca="false">SUMIF($J$80:$J$100,"Planned",E80:E100)</f>
+        <f aca="false">SUMIF($J$80:$J$101,"Planned",E80:E101)</f>
         <v>2640000</v>
       </c>
       <c r="F8" s="28" t="n">
-        <f aca="false">SUMIF($J$80:$J$100,"Planned",F80:F100)</f>
-        <v>0</v>
+        <f aca="false">SUMIF($J$80:$J$101,"Planned",F80:F101)</f>
+        <v>9</v>
       </c>
       <c r="G8" s="28" t="n">
-        <f aca="false">SUMIF($J$80:$J$100,"Planned",G80:G100)</f>
-        <v>0</v>
+        <f aca="false">SUMIF($J$80:$J$101,"Planned",G80:G101)</f>
+        <v>3</v>
       </c>
       <c r="H8" s="28" t="n">
-        <f aca="false">SUMIF($J$80:$J$100,"Planned",H80:H100)</f>
-        <v>0</v>
+        <f aca="false">SUMIF($J$80:$J$101,"Planned",H80:H101)</f>
+        <v>492</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8780,7 +8798,7 @@
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">B7-B8</f>
-        <v>42754775</v>
+        <v>39069990</v>
       </c>
       <c r="C9" s="29" t="n">
         <f aca="false">C7-C8</f>
@@ -8796,15 +8814,15 @@
       </c>
       <c r="F9" s="29" t="n">
         <f aca="false">F7-F8</f>
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="G9" s="29" t="n">
         <f aca="false">G7-G8</f>
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="H9" s="29" t="n">
         <f aca="false">H7-H8</f>
-        <v>1432</v>
+        <v>915</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9328,7 +9346,7 @@
         <v>311</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="K26" s="15"/>
     </row>
@@ -9361,7 +9379,7 @@
         <v>311</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="K27" s="15"/>
     </row>
@@ -11074,17 +11092,19 @@
         <v>3000000</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K85" s="15" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
-        <v>480</v>
-      </c>
-      <c r="B86" s="27"/>
+        <v>482</v>
+      </c>
+      <c r="B86" s="30" t="n">
+        <v>1650010</v>
+      </c>
       <c r="C86" s="30" t="n">
         <v>0</v>
       </c>
@@ -11094,24 +11114,32 @@
       <c r="E86" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="27"/>
-      <c r="G86" s="27"/>
-      <c r="H86" s="27"/>
+      <c r="F86" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G86" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="30" t="n">
+        <v>164</v>
+      </c>
       <c r="I86" s="30" t="n">
         <v>3000000</v>
       </c>
       <c r="J86" s="11" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K86" s="15" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="s">
-        <v>481</v>
-      </c>
-      <c r="B87" s="27"/>
+        <v>484</v>
+      </c>
+      <c r="B87" s="30" t="n">
+        <v>1650000</v>
+      </c>
       <c r="C87" s="30" t="n">
         <v>0</v>
       </c>
@@ -11121,24 +11149,32 @@
       <c r="E87" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F87" s="27"/>
-      <c r="G87" s="27"/>
-      <c r="H87" s="27"/>
+      <c r="F87" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G87" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="30" t="n">
+        <v>164</v>
+      </c>
       <c r="I87" s="30" t="n">
         <v>3000000</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K87" s="15" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="12" t="s">
-        <v>482</v>
-      </c>
-      <c r="B88" s="27"/>
+        <v>486</v>
+      </c>
+      <c r="B88" s="30" t="n">
+        <v>1650000</v>
+      </c>
       <c r="C88" s="30" t="n">
         <v>0</v>
       </c>
@@ -11149,39 +11185,37 @@
         <v>0</v>
       </c>
       <c r="F88" s="30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G88" s="30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" s="30" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="I88" s="30" t="n">
-        <v>17000000</v>
+        <v>3000000</v>
       </c>
       <c r="J88" s="11" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K88" s="15" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="12" t="s">
-        <v>483</v>
-      </c>
-      <c r="B89" s="30" t="n">
-        <v>0</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="B89" s="27"/>
       <c r="C89" s="30" t="n">
-        <v>1710500</v>
+        <v>0</v>
       </c>
       <c r="D89" s="30" t="n">
-        <v>1710000</v>
+        <v>0</v>
       </c>
       <c r="E89" s="30" t="n">
-        <v>2640000</v>
+        <v>0</v>
       </c>
       <c r="F89" s="30" t="n">
         <v>0</v>
@@ -11196,21 +11230,21 @@
         <v>17000000</v>
       </c>
       <c r="J89" s="11" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="K89" s="15" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="12" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B90" s="30" t="n">
         <v>0</v>
       </c>
       <c r="C90" s="30" t="n">
-        <v>1710000</v>
+        <v>1710500</v>
       </c>
       <c r="D90" s="30" t="n">
         <v>1710000</v>
@@ -11231,22 +11265,28 @@
         <v>17000000</v>
       </c>
       <c r="J90" s="11" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="K90" s="15" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="12" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B91" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C91" s="27"/>
-      <c r="D91" s="27"/>
-      <c r="E91" s="27"/>
+      <c r="C91" s="30" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="D91" s="30" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="E91" s="30" t="n">
+        <v>2640000</v>
+      </c>
       <c r="F91" s="30" t="n">
         <v>0</v>
       </c>
@@ -11260,15 +11300,15 @@
         <v>17000000</v>
       </c>
       <c r="J91" s="11" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="K91" s="15" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="12" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B92" s="30" t="n">
         <v>0</v>
@@ -11289,15 +11329,15 @@
         <v>17000000</v>
       </c>
       <c r="J92" s="11" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="K92" s="15" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="12" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B93" s="30" t="n">
         <v>0</v>
@@ -11318,53 +11358,69 @@
         <v>17000000</v>
       </c>
       <c r="J93" s="11" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="K93" s="15" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="12" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B94" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="27"/>
+      <c r="D94" s="27"/>
+      <c r="E94" s="27"/>
+      <c r="F94" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="30" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J94" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="K94" s="15" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="B95" s="30" t="n">
         <v>13000000</v>
       </c>
-      <c r="C94" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" s="27"/>
-      <c r="G94" s="27"/>
-      <c r="H94" s="27"/>
-      <c r="I94" s="30" t="n">
+      <c r="C95" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="27"/>
+      <c r="G95" s="27"/>
+      <c r="H95" s="27"/>
+      <c r="I95" s="30" t="n">
         <v>8000000</v>
       </c>
-      <c r="J94" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="K94" s="15" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="12"/>
-      <c r="B95" s="30"/>
-      <c r="C95" s="30"/>
-      <c r="D95" s="30"/>
-      <c r="E95" s="30"/>
-      <c r="F95" s="30"/>
-      <c r="G95" s="30"/>
-      <c r="H95" s="30"/>
-      <c r="I95" s="30"/>
-      <c r="J95" s="11"/>
-      <c r="K95" s="12"/>
+      <c r="J95" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="K95" s="15" t="s">
+        <v>498</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="12"/>
@@ -11431,12 +11487,25 @@
       <c r="J100" s="11"/>
       <c r="K100" s="12"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="16" t="s">
-        <v>493</v>
-      </c>
-      <c r="I102" s="20" t="n">
-        <f aca="false">SUMIF(J80:J100,"Planned",I80:I100)</f>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="12"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="30"/>
+      <c r="D101" s="30"/>
+      <c r="E101" s="30"/>
+      <c r="F101" s="30"/>
+      <c r="G101" s="30"/>
+      <c r="H101" s="30"/>
+      <c r="I101" s="30"/>
+      <c r="J101" s="11"/>
+      <c r="K101" s="12"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="I103" s="20" t="n">
+        <f aca="false">SUMIF(J80:J101,"Planned",I80:I101)</f>
         <v>46000000</v>
       </c>
     </row>
@@ -11446,7 +11515,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J80:J100">
+  <conditionalFormatting sqref="J80:J101">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Done"</formula>
     </cfRule>
@@ -11461,7 +11530,7 @@
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J80:J100" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J80:J101" type="list">
       <formula1>"Planned,Done,Skipped"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -11492,12 +11561,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11511,50 +11580,50 @@
         <v>370</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C6" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>470</v>
@@ -11569,16 +11638,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C7" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="E7" s="32" t="s">
         <v>470</v>
@@ -11593,16 +11662,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="E8" s="32" t="s">
         <v>470</v>
@@ -11617,16 +11686,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
+        <v>519</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>513</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>507</v>
       </c>
       <c r="C9" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="E9" s="32" t="s">
         <v>470</v>
@@ -11641,16 +11710,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C10" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="E10" s="32" t="s">
         <v>470</v>
@@ -11665,16 +11734,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C11" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="E11" s="32" t="s">
         <v>470</v>
@@ -11689,16 +11758,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C12" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E12" s="32" t="s">
         <v>470</v>
@@ -11713,16 +11782,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C13" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="E13" s="32" t="s">
         <v>470</v>
@@ -11737,16 +11806,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C14" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="E14" s="32" t="s">
         <v>470</v>
@@ -11761,16 +11830,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C15" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="E15" s="32" t="s">
         <v>470</v>
@@ -11785,16 +11854,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C16" s="24" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="E16" s="32" t="s">
         <v>470</v>
@@ -11809,16 +11878,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C17" s="24" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -11831,16 +11900,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C18" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="E18" s="32" t="s">
         <v>470</v>
@@ -11855,16 +11924,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C19" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="E19" s="32" t="s">
         <v>470</v>
@@ -11879,16 +11948,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
+        <v>538</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>532</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>526</v>
       </c>
       <c r="C20" s="24" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="E20" s="32" t="s">
         <v>470</v>
@@ -11903,21 +11972,21 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C22" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="E22" s="32" t="s">
         <v>470</v>
@@ -11932,16 +12001,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C23" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -11954,16 +12023,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C24" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -11976,16 +12045,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="E25" s="32" t="s">
         <v>470</v>
@@ -12000,16 +12069,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="E26" s="32" t="s">
         <v>470</v>
@@ -12024,16 +12093,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -12046,16 +12115,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="C28" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -12068,21 +12137,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="C30" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -12095,16 +12164,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="C31" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -12117,16 +12186,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -12139,16 +12208,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="E33" s="32" t="s">
         <v>470</v>
@@ -12163,16 +12232,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -12185,16 +12254,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="C35" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -12207,16 +12276,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
+        <v>572</v>
+      </c>
+      <c r="B36" s="13" t="s">
         <v>566</v>
       </c>
-      <c r="B36" s="13" t="s">
-        <v>560</v>
-      </c>
       <c r="C36" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -12229,16 +12298,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="C37" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -12251,16 +12320,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="C38" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="E38" s="32"/>
       <c r="F38" s="32"/>
@@ -12273,7 +12342,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E40" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$38)*(E5:E38="Done"))</f>
@@ -12310,7 +12379,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="E41" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$38,"Required",E5:E38,"Done")&amp;" of 11"</f>
@@ -12347,7 +12416,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>
@@ -12391,12 +12460,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12404,10 +12473,10 @@
         <v>224</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12418,13 +12487,13 @@
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12435,7 +12504,7 @@
         <v>308343695</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -12485,7 +12554,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -12493,7 +12562,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -12502,11 +12571,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>18063357.3768684</v>
+        <v>18065700.7440924</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12517,19 +12586,19 @@
         <v>233</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>579</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
@@ -12545,7 +12614,7 @@
       <c r="B13" s="27"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -12571,7 +12640,7 @@
       <c r="B14" s="27"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -12597,7 +12666,7 @@
       <c r="B15" s="27"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -12623,7 +12692,7 @@
       <c r="B16" s="27"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -12648,10 +12717,10 @@
       </c>
       <c r="B17" s="27"/>
       <c r="C17" s="12" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -12676,10 +12745,10 @@
       </c>
       <c r="B18" s="27"/>
       <c r="C18" s="12" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -12704,10 +12773,10 @@
       </c>
       <c r="B19" s="27"/>
       <c r="C19" s="12" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -12732,10 +12801,10 @@
       </c>
       <c r="B20" s="27"/>
       <c r="C20" s="12" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -12760,10 +12829,10 @@
       </c>
       <c r="B21" s="27"/>
       <c r="C21" s="12" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -12788,10 +12857,10 @@
       </c>
       <c r="B22" s="27"/>
       <c r="C22" s="12" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -12817,7 +12886,7 @@
       <c r="B23" s="27"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -12842,10 +12911,10 @@
       </c>
       <c r="B24" s="27"/>
       <c r="C24" s="12" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -12870,10 +12939,10 @@
       </c>
       <c r="B25" s="27"/>
       <c r="C25" s="12" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -12898,10 +12967,10 @@
       </c>
       <c r="B26" s="27"/>
       <c r="C26" s="12" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -12929,7 +12998,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -12956,10 +13025,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -12986,10 +13055,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -13016,10 +13085,10 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="E30" s="27"/>
       <c r="F30" s="27"/>
@@ -13040,10 +13109,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -13070,7 +13139,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -13098,10 +13167,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -13128,7 +13197,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -13156,10 +13225,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -13186,7 +13255,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -13214,10 +13283,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -13244,7 +13313,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -13272,10 +13341,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -13302,7 +13371,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -13330,10 +13399,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -13360,7 +13429,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -13388,10 +13457,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -13418,7 +13487,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -13446,7 +13515,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -13474,7 +13543,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -13502,7 +13571,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -13530,7 +13599,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -13558,7 +13627,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -13586,7 +13655,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -13614,7 +13683,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -13642,7 +13711,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -13670,7 +13739,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -13698,7 +13767,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -13720,7 +13789,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="639">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -1348,9 +1348,6 @@
     <t xml:space="preserve">Level 110 gold orb, promo code Oct 11</t>
   </si>
   <si>
-    <t xml:space="preserve">825K + 825K + 1.65M. Copy the row for each new orb</t>
-  </si>
-  <si>
     <t xml:space="preserve">Level 110 gold orb, Breaker of Nature level 120</t>
   </si>
   <si>
@@ -1771,7 +1768,7 @@
     <t xml:space="preserve">Objectives done, required</t>
   </si>
   <si>
-    <t xml:space="preserve">Oct 11 is filled in from your screenshots. The calendar and battle pass rows are left for you.</t>
+    <t xml:space="preserve">Oct 11 and Oct 12 are filled in from your screenshots. The calendar and battle pass rows are left for you.</t>
   </si>
   <si>
     <t xml:space="preserve">Iso Fest Milestones</t>
@@ -5752,7 +5749,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>552317272.231916</v>
+        <v>552405216.273781</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8672,7 +8669,7 @@
         <v>377</v>
       </c>
       <c r="B5" s="27" t="n">
-        <v>15270000</v>
+        <v>16720000</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>336000</v>
@@ -8699,7 +8696,7 @@
       </c>
       <c r="B6" s="28" t="n">
         <f aca="false">SUMIFS(B13:B76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
-        <v>28750000</v>
+        <v>27050000</v>
       </c>
       <c r="C6" s="28" t="n">
         <f aca="false">SUMIFS(C13:C76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
@@ -8732,7 +8729,7 @@
       </c>
       <c r="B7" s="28" t="n">
         <f aca="false">B5+B6</f>
-        <v>44020000</v>
+        <v>43770000</v>
       </c>
       <c r="C7" s="28" t="n">
         <f aca="false">C5+C6</f>
@@ -8798,7 +8795,7 @@
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">B7-B8</f>
-        <v>39069990</v>
+        <v>38819990</v>
       </c>
       <c r="C9" s="29" t="n">
         <f aca="false">C7-C8</f>
@@ -8899,7 +8896,7 @@
         <v>311</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>388</v>
@@ -8934,7 +8931,7 @@
         <v>311</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="K14" s="15" t="s">
         <v>390</v>
@@ -10110,15 +10107,15 @@
       <c r="A49" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="B49" s="30" t="n">
+      <c r="B49" s="30" t="s">
+        <v>389</v>
+      </c>
+      <c r="C49" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="D49" s="30" t="n">
         <v>3300000</v>
       </c>
-      <c r="C49" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="30" t="n">
-        <v>0</v>
-      </c>
       <c r="E49" s="30" t="n">
         <v>0</v>
       </c>
@@ -10131,19 +10128,19 @@
       <c r="H49" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I49" s="11" t="s">
-        <v>311</v>
+      <c r="I49" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="J49" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="K49" s="15" t="s">
-        <v>438</v>
+      <c r="K49" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B50" s="30" t="n">
         <v>3300000</v>
@@ -10173,12 +10170,12 @@
         <v>311</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B51" s="30" t="n">
         <v>0</v>
@@ -10208,12 +10205,12 @@
         <v>315</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B52" s="30" t="n">
         <v>0</v>
@@ -10243,12 +10240,12 @@
         <v>315</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B53" s="30" t="n">
         <v>0</v>
@@ -10278,12 +10275,12 @@
         <v>315</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B54" s="30" t="n">
         <v>750000</v>
@@ -10313,12 +10310,12 @@
         <v>315</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B55" s="30" t="n">
         <v>750000</v>
@@ -10348,12 +10345,12 @@
         <v>315</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B56" s="30" t="n">
         <v>750000</v>
@@ -10383,12 +10380,12 @@
         <v>315</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B57" s="30" t="n">
         <v>750000</v>
@@ -10418,12 +10415,12 @@
         <v>315</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B58" s="30" t="n">
         <v>750000</v>
@@ -10453,12 +10450,12 @@
         <v>315</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B59" s="30" t="n">
         <v>750000</v>
@@ -10488,12 +10485,12 @@
         <v>315</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B60" s="30" t="n">
         <v>750000</v>
@@ -10523,12 +10520,12 @@
         <v>315</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B61" s="30" t="n">
         <v>750000</v>
@@ -10558,12 +10555,12 @@
         <v>315</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B62" s="30" t="n">
         <v>0</v>
@@ -10593,12 +10590,12 @@
         <v>315</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B63" s="30" t="n">
         <v>0</v>
@@ -10628,12 +10625,12 @@
         <v>315</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B64" s="30" t="n">
         <v>178025</v>
@@ -10663,12 +10660,12 @@
         <v>311</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B65" s="30" t="n">
         <v>12000</v>
@@ -10698,12 +10695,12 @@
         <v>311</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B66" s="30" t="n">
         <v>375000</v>
@@ -10733,7 +10730,7 @@
         <v>315</v>
       </c>
       <c r="K66" s="15" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10868,12 +10865,12 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="23" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>370</v>
@@ -10908,7 +10905,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B80" s="30" t="n">
         <v>1837500</v>
@@ -10935,15 +10932,15 @@
         <v>0</v>
       </c>
       <c r="J80" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="K80" s="15" t="s">
         <v>470</v>
-      </c>
-      <c r="K80" s="15" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B81" s="30" t="n">
         <v>0</v>
@@ -10970,13 +10967,13 @@
         <v>0</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K81" s="15"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B82" s="30" t="n">
         <v>9791250</v>
@@ -11003,15 +11000,15 @@
         <v>55000000</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K82" s="15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B83" s="30" t="n">
         <v>0</v>
@@ -11038,15 +11035,15 @@
         <v>0</v>
       </c>
       <c r="J83" s="11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K83" s="15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B84" s="27"/>
       <c r="C84" s="30" t="n">
@@ -11065,15 +11062,15 @@
         <v>3000000</v>
       </c>
       <c r="J84" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="K84" s="15" t="s">
         <v>477</v>
-      </c>
-      <c r="K84" s="15" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B85" s="27"/>
       <c r="C85" s="30" t="n">
@@ -11092,15 +11089,15 @@
         <v>3000000</v>
       </c>
       <c r="J85" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="K85" s="15" t="s">
         <v>480</v>
-      </c>
-      <c r="K85" s="15" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B86" s="30" t="n">
         <v>1650010</v>
@@ -11127,15 +11124,15 @@
         <v>3000000</v>
       </c>
       <c r="J86" s="11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K86" s="15" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B87" s="30" t="n">
         <v>1650000</v>
@@ -11162,15 +11159,15 @@
         <v>3000000</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K87" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="12" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B88" s="30" t="n">
         <v>1650000</v>
@@ -11197,15 +11194,15 @@
         <v>3000000</v>
       </c>
       <c r="J88" s="11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K88" s="15" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="12" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B89" s="27"/>
       <c r="C89" s="30" t="n">
@@ -11230,15 +11227,15 @@
         <v>17000000</v>
       </c>
       <c r="J89" s="11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K89" s="15" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="12" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B90" s="30" t="n">
         <v>0</v>
@@ -11265,15 +11262,15 @@
         <v>17000000</v>
       </c>
       <c r="J90" s="11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K90" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="12" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B91" s="30" t="n">
         <v>0</v>
@@ -11300,15 +11297,15 @@
         <v>17000000</v>
       </c>
       <c r="J91" s="11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K91" s="15" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="12" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B92" s="30" t="n">
         <v>0</v>
@@ -11329,15 +11326,15 @@
         <v>17000000</v>
       </c>
       <c r="J92" s="11" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K92" s="15" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="12" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B93" s="30" t="n">
         <v>0</v>
@@ -11358,15 +11355,15 @@
         <v>17000000</v>
       </c>
       <c r="J93" s="11" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K93" s="15" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="12" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B94" s="30" t="n">
         <v>0</v>
@@ -11387,15 +11384,15 @@
         <v>17000000</v>
       </c>
       <c r="J94" s="11" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K94" s="15" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B95" s="30" t="n">
         <v>13000000</v>
@@ -11416,10 +11413,10 @@
         <v>8000000</v>
       </c>
       <c r="J95" s="11" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K95" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11502,7 +11499,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="16" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I103" s="20" t="n">
         <f aca="false">SUMIF(J80:J101,"Planned",I80:I101)</f>
@@ -11561,12 +11558,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11580,55 +11577,57 @@
         <v>370</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>509</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
+        <v>511</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>512</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>513</v>
       </c>
       <c r="C6" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>470</v>
-      </c>
-      <c r="F6" s="32"/>
+        <v>469</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>469</v>
+      </c>
       <c r="G6" s="32"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
@@ -11638,21 +11637,23 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C7" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>470</v>
-      </c>
-      <c r="F7" s="32"/>
+        <v>469</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>469</v>
+      </c>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
@@ -11662,21 +11663,23 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>470</v>
-      </c>
-      <c r="F8" s="32"/>
+        <v>469</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>469</v>
+      </c>
       <c r="G8" s="32"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
@@ -11686,21 +11689,23 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C9" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>470</v>
-      </c>
-      <c r="F9" s="32"/>
+        <v>469</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>469</v>
+      </c>
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
@@ -11710,21 +11715,23 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C10" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>470</v>
-      </c>
-      <c r="F10" s="32"/>
+        <v>469</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>469</v>
+      </c>
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
@@ -11734,21 +11741,23 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C11" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>470</v>
-      </c>
-      <c r="F11" s="32"/>
+        <v>469</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>469</v>
+      </c>
       <c r="G11" s="32"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
@@ -11758,21 +11767,23 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C12" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>470</v>
-      </c>
-      <c r="F12" s="32"/>
+        <v>469</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>469</v>
+      </c>
       <c r="G12" s="32"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
@@ -11782,21 +11793,23 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C13" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>470</v>
-      </c>
-      <c r="F13" s="32"/>
+        <v>469</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>469</v>
+      </c>
       <c r="G13" s="32"/>
       <c r="H13" s="32"/>
       <c r="I13" s="32"/>
@@ -11806,21 +11819,23 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C14" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>470</v>
-      </c>
-      <c r="F14" s="32"/>
+        <v>469</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>469</v>
+      </c>
       <c r="G14" s="32"/>
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
@@ -11830,21 +11845,23 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C15" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>470</v>
-      </c>
-      <c r="F15" s="32"/>
+        <v>469</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>469</v>
+      </c>
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
       <c r="I15" s="32"/>
@@ -11854,21 +11871,23 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C16" s="24" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>470</v>
-      </c>
-      <c r="F16" s="32"/>
+        <v>469</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>469</v>
+      </c>
       <c r="G16" s="32"/>
       <c r="H16" s="32"/>
       <c r="I16" s="32"/>
@@ -11878,19 +11897,21 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>531</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>532</v>
       </c>
       <c r="C17" s="24" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
+      <c r="F17" s="32" t="s">
+        <v>469</v>
+      </c>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
       <c r="I17" s="32"/>
@@ -11900,21 +11921,23 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C18" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>470</v>
-      </c>
-      <c r="F18" s="32"/>
+        <v>469</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>469</v>
+      </c>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
       <c r="I18" s="32"/>
@@ -11924,21 +11947,23 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C19" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>470</v>
-      </c>
-      <c r="F19" s="32"/>
+        <v>469</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>469</v>
+      </c>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
       <c r="I19" s="32"/>
@@ -11948,21 +11973,23 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C20" s="24" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>470</v>
-      </c>
-      <c r="F20" s="32"/>
+        <v>469</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>469</v>
+      </c>
       <c r="G20" s="32"/>
       <c r="H20" s="32"/>
       <c r="I20" s="32"/>
@@ -11972,24 +11999,24 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
+        <v>540</v>
+      </c>
+      <c r="B22" s="13" t="s">
         <v>541</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="C22" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="15" t="s">
         <v>542</v>
       </c>
-      <c r="C22" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>543</v>
-      </c>
       <c r="E22" s="32" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -12001,16 +12028,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B23" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="C23" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>542</v>
-      </c>
-      <c r="C23" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>543</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -12023,16 +12050,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B24" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="C24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="15" t="s">
         <v>542</v>
-      </c>
-      <c r="C24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>543</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -12045,21 +12072,23 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
+        <v>545</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>546</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>547</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>470</v>
-      </c>
-      <c r="F25" s="32"/>
+        <v>469</v>
+      </c>
+      <c r="F25" s="32" t="s">
+        <v>469</v>
+      </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
@@ -12069,19 +12098,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>546</v>
+      </c>
+      <c r="C26" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="15" t="s">
         <v>549</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>547</v>
-      </c>
-      <c r="C26" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>550</v>
-      </c>
       <c r="E26" s="32" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -12093,16 +12122,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
+        <v>550</v>
+      </c>
+      <c r="B27" s="13" t="s">
         <v>551</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="C27" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="15" t="s">
         <v>552</v>
-      </c>
-      <c r="C27" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>553</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -12115,16 +12144,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="B28" s="13" t="s">
         <v>554</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="C28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="15" t="s">
         <v>555</v>
-      </c>
-      <c r="C28" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>556</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -12137,21 +12166,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
+        <v>557</v>
+      </c>
+      <c r="B30" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="C30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="15" t="s">
         <v>559</v>
-      </c>
-      <c r="C30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>560</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -12164,16 +12193,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
+        <v>560</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="C31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="15" t="s">
         <v>561</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>559</v>
-      </c>
-      <c r="C31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>562</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -12186,16 +12215,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
+        <v>562</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="15" t="s">
         <v>563</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>559</v>
-      </c>
-      <c r="C32" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>564</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -12208,19 +12237,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
+        <v>564</v>
+      </c>
+      <c r="B33" s="13" t="s">
         <v>565</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="C33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="15" t="s">
         <v>566</v>
       </c>
-      <c r="C33" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>567</v>
-      </c>
       <c r="E33" s="32" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
@@ -12232,16 +12261,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
+        <v>567</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="15" t="s">
         <v>568</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>559</v>
-      </c>
-      <c r="C34" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>569</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -12254,16 +12283,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
+        <v>569</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>565</v>
+      </c>
+      <c r="C35" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="15" t="s">
         <v>570</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>566</v>
-      </c>
-      <c r="C35" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>571</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -12276,16 +12305,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C36" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -12298,16 +12327,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
+        <v>572</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="C37" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="15" t="s">
         <v>573</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>559</v>
-      </c>
-      <c r="C37" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>574</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -12320,16 +12349,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
+        <v>574</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="C38" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="15" t="s">
         <v>575</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>559</v>
-      </c>
-      <c r="C38" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>576</v>
       </c>
       <c r="E38" s="32"/>
       <c r="F38" s="32"/>
@@ -12342,7 +12371,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E40" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$38)*(E5:E38="Done"))</f>
@@ -12350,7 +12379,7 @@
       </c>
       <c r="F40" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$38)*(F5:F38="Done"))</f>
-        <v>0</v>
+        <v>2500000</v>
       </c>
       <c r="G40" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$38)*(G5:G38="Done"))</f>
@@ -12379,7 +12408,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E41" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$38,"Required",E5:E38,"Done")&amp;" of 11"</f>
@@ -12387,7 +12416,7 @@
       </c>
       <c r="F41" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$38,"Required",F5:F38,"Done")&amp;" of 11"</f>
-        <v>0 of 11</v>
+        <v>11 of 11</v>
       </c>
       <c r="G41" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$38,"Required",G5:G38,"Done")&amp;" of 11"</f>
@@ -12416,7 +12445,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>
@@ -12460,12 +12489,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12473,10 +12502,10 @@
         <v>224</v>
       </c>
       <c r="B4" s="17" t="s">
+        <v>581</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>582</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12487,13 +12516,13 @@
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="16" t="s">
+        <v>583</v>
+      </c>
+      <c r="F5" s="16" t="s">
         <v>584</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="G5" s="16" t="s">
         <v>585</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12504,7 +12533,7 @@
         <v>308343695</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -12554,7 +12583,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -12562,7 +12591,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -12571,11 +12600,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>18065700.7440924</v>
+        <v>18068577.2973275</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12586,19 +12615,19 @@
         <v>233</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>585</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>586</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
@@ -12614,7 +12643,7 @@
       <c r="B13" s="27"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -12640,7 +12669,7 @@
       <c r="B14" s="27"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -12666,7 +12695,7 @@
       <c r="B15" s="27"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -12692,7 +12721,7 @@
       <c r="B16" s="27"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -12717,10 +12746,10 @@
       </c>
       <c r="B17" s="27"/>
       <c r="C17" s="12" t="s">
+        <v>594</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>595</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>596</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -12745,10 +12774,10 @@
       </c>
       <c r="B18" s="27"/>
       <c r="C18" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>597</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>598</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -12773,10 +12802,10 @@
       </c>
       <c r="B19" s="27"/>
       <c r="C19" s="12" t="s">
+        <v>598</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>599</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>600</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -12801,10 +12830,10 @@
       </c>
       <c r="B20" s="27"/>
       <c r="C20" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>601</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>602</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -12829,10 +12858,10 @@
       </c>
       <c r="B21" s="27"/>
       <c r="C21" s="12" t="s">
+        <v>602</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>603</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>604</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -12857,10 +12886,10 @@
       </c>
       <c r="B22" s="27"/>
       <c r="C22" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>605</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>606</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -12886,7 +12915,7 @@
       <c r="B23" s="27"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -12911,10 +12940,10 @@
       </c>
       <c r="B24" s="27"/>
       <c r="C24" s="12" t="s">
+        <v>607</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>608</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>609</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -12939,10 +12968,10 @@
       </c>
       <c r="B25" s="27"/>
       <c r="C25" s="12" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -12967,10 +12996,10 @@
       </c>
       <c r="B26" s="27"/>
       <c r="C26" s="12" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -12998,7 +13027,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -13025,10 +13054,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -13055,10 +13084,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -13085,10 +13114,10 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="D30" s="12" t="s">
         <v>614</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>615</v>
       </c>
       <c r="E30" s="27"/>
       <c r="F30" s="27"/>
@@ -13109,10 +13138,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -13139,7 +13168,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -13167,10 +13196,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -13197,7 +13226,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -13225,10 +13254,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -13255,7 +13284,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -13283,10 +13312,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -13313,7 +13342,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -13341,10 +13370,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -13371,7 +13400,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -13399,10 +13428,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -13429,7 +13458,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -13457,10 +13486,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -13487,7 +13516,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -13515,7 +13544,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -13543,7 +13572,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -13571,7 +13600,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -13599,7 +13628,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -13627,7 +13656,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -13655,7 +13684,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -13683,7 +13712,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -13711,7 +13740,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -13739,7 +13768,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -13767,7 +13796,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -13789,7 +13818,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="640">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -1480,19 +1480,22 @@
     <t xml:space="preserve">Storm to level 101</t>
   </si>
   <si>
-    <t xml:space="preserve">Uncanny Avengers, from training screen Oct 12</t>
+    <t xml:space="preserve">First Uncanny Avenger. Then retry Spider-Man tower cell 20</t>
   </si>
   <si>
     <t xml:space="preserve">Second Uncanny Avenger to level 101</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimate from Storm</t>
+    <t xml:space="preserve">If needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only if cell 20 still fails after Storm</t>
   </si>
   <si>
     <t xml:space="preserve">Third Uncanny Avenger to level 101</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimate from Storm. Needs battle pass level 95 orange</t>
+    <t xml:space="preserve">Only if cell 20 still fails. Needs battle pass level 95 orange</t>
   </si>
   <si>
     <t xml:space="preserve">Whiplash to gear tier 20</t>
@@ -5749,7 +5752,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>552405216.273781</v>
+        <v>553369423.586879</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8762,7 +8765,7 @@
       </c>
       <c r="B8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",B80:B101)</f>
-        <v>4950010</v>
+        <v>1650010</v>
       </c>
       <c r="C8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",C80:C101)</f>
@@ -8778,15 +8781,15 @@
       </c>
       <c r="F8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",F80:F101)</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",G80:G101)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",H80:H101)</f>
-        <v>492</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8795,7 +8798,7 @@
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">B7-B8</f>
-        <v>38819990</v>
+        <v>42119990</v>
       </c>
       <c r="C9" s="29" t="n">
         <f aca="false">C7-C8</f>
@@ -8811,15 +8814,15 @@
       </c>
       <c r="F9" s="29" t="n">
         <f aca="false">F7-F8</f>
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="G9" s="29" t="n">
         <f aca="false">G7-G8</f>
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="H9" s="29" t="n">
         <f aca="false">H7-H8</f>
-        <v>915</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11159,15 +11162,15 @@
         <v>3000000</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="K87" s="15" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="12" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B88" s="30" t="n">
         <v>1650000</v>
@@ -11194,15 +11197,15 @@
         <v>3000000</v>
       </c>
       <c r="J88" s="11" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="K88" s="15" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="12" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B89" s="27"/>
       <c r="C89" s="30" t="n">
@@ -11230,12 +11233,12 @@
         <v>479</v>
       </c>
       <c r="K89" s="15" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="12" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B90" s="30" t="n">
         <v>0</v>
@@ -11265,12 +11268,12 @@
         <v>469</v>
       </c>
       <c r="K90" s="15" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="12" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B91" s="30" t="n">
         <v>0</v>
@@ -11300,12 +11303,12 @@
         <v>479</v>
       </c>
       <c r="K91" s="15" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="12" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B92" s="30" t="n">
         <v>0</v>
@@ -11329,12 +11332,12 @@
         <v>476</v>
       </c>
       <c r="K92" s="15" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="12" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B93" s="30" t="n">
         <v>0</v>
@@ -11358,12 +11361,12 @@
         <v>476</v>
       </c>
       <c r="K93" s="15" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="12" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B94" s="30" t="n">
         <v>0</v>
@@ -11387,12 +11390,12 @@
         <v>476</v>
       </c>
       <c r="K94" s="15" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="12" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B95" s="30" t="n">
         <v>13000000</v>
@@ -11416,7 +11419,7 @@
         <v>476</v>
       </c>
       <c r="K95" s="15" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11499,11 +11502,11 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="16" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="I103" s="20" t="n">
         <f aca="false">SUMIF(J80:J101,"Planned",I80:I101)</f>
-        <v>46000000</v>
+        <v>40000000</v>
       </c>
     </row>
   </sheetData>
@@ -11528,7 +11531,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J80:J101" type="list">
-      <formula1>"Planned,Done,Skipped"</formula1>
+      <formula1>"Planned,If needed,Done,Skipped"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -11558,12 +11561,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11577,50 +11580,50 @@
         <v>370</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C6" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>469</v>
@@ -11637,16 +11640,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C7" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E7" s="32" t="s">
         <v>469</v>
@@ -11663,16 +11666,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E8" s="32" t="s">
         <v>469</v>
@@ -11689,16 +11692,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C9" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E9" s="32" t="s">
         <v>469</v>
@@ -11715,16 +11718,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C10" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E10" s="32" t="s">
         <v>469</v>
@@ -11741,16 +11744,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C11" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E11" s="32" t="s">
         <v>469</v>
@@ -11767,16 +11770,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C12" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E12" s="32" t="s">
         <v>469</v>
@@ -11793,16 +11796,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C13" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E13" s="32" t="s">
         <v>469</v>
@@ -11819,16 +11822,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C14" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E14" s="32" t="s">
         <v>469</v>
@@ -11845,16 +11848,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C15" s="24" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E15" s="32" t="s">
         <v>469</v>
@@ -11871,16 +11874,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C16" s="24" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E16" s="32" t="s">
         <v>469</v>
@@ -11897,16 +11900,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C17" s="24" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32" t="s">
@@ -11921,16 +11924,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C18" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E18" s="32" t="s">
         <v>469</v>
@@ -11947,16 +11950,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C19" s="24" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E19" s="32" t="s">
         <v>469</v>
@@ -11973,16 +11976,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C20" s="24" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E20" s="32" t="s">
         <v>469</v>
@@ -11999,21 +12002,21 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C22" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E22" s="32" t="s">
         <v>469</v>
@@ -12028,16 +12031,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
+        <v>544</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>542</v>
+      </c>
+      <c r="C23" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>543</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>541</v>
-      </c>
-      <c r="C23" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>542</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -12050,16 +12053,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C24" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -12072,16 +12075,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E25" s="32" t="s">
         <v>469</v>
@@ -12098,16 +12101,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E26" s="32" t="s">
         <v>469</v>
@@ -12122,16 +12125,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
@@ -12144,16 +12147,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C28" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
@@ -12166,21 +12169,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C30" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
@@ -12193,16 +12196,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C31" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
@@ -12215,16 +12218,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -12237,16 +12240,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E33" s="32" t="s">
         <v>469</v>
@@ -12261,16 +12264,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -12283,16 +12286,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C35" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="32"/>
@@ -12305,16 +12308,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
+        <v>572</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>566</v>
+      </c>
+      <c r="C36" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="15" t="s">
         <v>571</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>565</v>
-      </c>
-      <c r="C36" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>570</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
@@ -12327,16 +12330,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C37" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
@@ -12349,16 +12352,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C38" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E38" s="32"/>
       <c r="F38" s="32"/>
@@ -12371,7 +12374,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E40" s="20" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$38)*(E5:E38="Done"))</f>
@@ -12408,7 +12411,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E41" s="33" t="str">
         <f aca="false">COUNTIFS($B$5:$B$38,"Required",E5:E38,"Done")&amp;" of 11"</f>
@@ -12445,7 +12448,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>
@@ -12489,12 +12492,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12502,10 +12505,10 @@
         <v>224</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12516,13 +12519,13 @@
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12533,7 +12536,7 @@
         <v>308343695</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -12583,7 +12586,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B9" s="34" t="n">
         <v>20</v>
@@ -12591,7 +12594,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -12600,11 +12603,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>18068577.2973275</v>
+        <v>18100115.4758211</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12615,19 +12618,19 @@
         <v>233</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
@@ -12643,7 +12646,7 @@
       <c r="B13" s="27"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -12669,7 +12672,7 @@
       <c r="B14" s="27"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>0</v>
@@ -12695,7 +12698,7 @@
       <c r="B15" s="27"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>0</v>
@@ -12721,7 +12724,7 @@
       <c r="B16" s="27"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -12746,10 +12749,10 @@
       </c>
       <c r="B17" s="27"/>
       <c r="C17" s="12" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E17" s="30" t="n">
         <v>0</v>
@@ -12774,10 +12777,10 @@
       </c>
       <c r="B18" s="27"/>
       <c r="C18" s="12" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0</v>
@@ -12802,10 +12805,10 @@
       </c>
       <c r="B19" s="27"/>
       <c r="C19" s="12" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -12830,10 +12833,10 @@
       </c>
       <c r="B20" s="27"/>
       <c r="C20" s="12" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0</v>
@@ -12858,10 +12861,10 @@
       </c>
       <c r="B21" s="27"/>
       <c r="C21" s="12" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0</v>
@@ -12886,10 +12889,10 @@
       </c>
       <c r="B22" s="27"/>
       <c r="C22" s="12" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -12915,7 +12918,7 @@
       <c r="B23" s="27"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>900000</v>
@@ -12940,10 +12943,10 @@
       </c>
       <c r="B24" s="27"/>
       <c r="C24" s="12" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>900000</v>
@@ -12968,10 +12971,10 @@
       </c>
       <c r="B25" s="27"/>
       <c r="C25" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="D25" s="12" t="s">
         <v>609</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>608</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -12996,10 +12999,10 @@
       </c>
       <c r="B26" s="27"/>
       <c r="C26" s="12" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>900000</v>
@@ -13027,7 +13030,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>900000</v>
@@ -13054,10 +13057,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>950000</v>
@@ -13084,10 +13087,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>0</v>
@@ -13114,10 +13117,10 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E30" s="27"/>
       <c r="F30" s="27"/>
@@ -13138,10 +13141,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -13168,7 +13171,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="30" t="n">
@@ -13196,10 +13199,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E33" s="30" t="n">
         <v>0</v>
@@ -13226,7 +13229,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="30" t="n">
@@ -13254,10 +13257,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E35" s="30" t="n">
         <v>0</v>
@@ -13284,7 +13287,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="30" t="n">
@@ -13312,10 +13315,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -13342,7 +13345,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="30" t="n">
@@ -13370,10 +13373,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E39" s="30" t="n">
         <v>0</v>
@@ -13400,7 +13403,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="30" t="n">
@@ -13428,10 +13431,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E41" s="30" t="n">
         <v>0</v>
@@ -13458,7 +13461,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="30" t="n">
@@ -13486,10 +13489,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -13516,7 +13519,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="30" t="n">
@@ -13544,7 +13547,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="30" t="n">
@@ -13572,7 +13575,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="30" t="n">
@@ -13600,7 +13603,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="30" t="n">
@@ -13628,7 +13631,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="30" t="n">
@@ -13656,7 +13659,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="30" t="n">
@@ -13684,7 +13687,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="30" t="n">
@@ -13712,7 +13715,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="30" t="n">
@@ -13740,7 +13743,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="30" t="n">
@@ -13768,7 +13771,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="30" t="n">
@@ -13796,7 +13799,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="30" t="n">
@@ -13818,7 +13821,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -1288,7 +1288,7 @@
     <t xml:space="preserve">Iso Fest milestone 16</t>
   </si>
   <si>
-    <t xml:space="preserve">About 16.7 million points away</t>
+    <t xml:space="preserve">Reached Oct 12, ready to claim</t>
   </si>
   <si>
     <t xml:space="preserve">Iso Fest milestone 17</t>
@@ -1423,7 +1423,7 @@
     <t xml:space="preserve">Misc</t>
   </si>
   <si>
-    <t xml:space="preserve">Running total of random drops and other small sources. Already in current stock</t>
+    <t xml:space="preserve">Running total of random drops and other small sources, including Jocasta orbs. Already in current stock</t>
   </si>
   <si>
     <t xml:space="preserve">Gold orbs</t>
@@ -5686,14 +5686,14 @@
         <v>226</v>
       </c>
       <c r="B6" s="19" t="n">
-        <v>558501630</v>
+        <v>577001630</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>227</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">B6+Scoring!F51</f>
-        <v>5988501630</v>
+        <v>6007001630</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6))+SUMPRODUCT((B13:B76="")*(F13:F76="Claimed"))</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>229</v>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B8" s="16" t="n">
         <f aca="false">IFERROR(INDEX(A13:A76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),"All done")</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>230</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="B9" s="20" t="n">
         <f aca="false">IFERROR(INDEX(E13:E76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),0)</f>
-        <v>11498370</v>
+        <v>22998370</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,B76-B6)</f>
-        <v>3566498370</v>
+        <v>3547998370</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>553369423.586879</v>
+        <v>555276317.656699</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6514,10 +6514,10 @@
       <c r="D55" s="12"/>
       <c r="E55" s="24" t="n">
         <f aca="false">IF(B55="","",MAX(0,B55-$B$6))</f>
-        <v>11498370</v>
+        <v>0</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6533,7 +6533,7 @@
       <c r="D56" s="12"/>
       <c r="E56" s="24" t="n">
         <f aca="false">IF(B56="","",MAX(0,B56-$B$6))</f>
-        <v>41498370</v>
+        <v>22998370</v>
       </c>
       <c r="F56" s="11" t="s">
         <v>169</v>
@@ -6552,7 +6552,7 @@
       <c r="D57" s="12"/>
       <c r="E57" s="24" t="n">
         <f aca="false">IF(B57="","",MAX(0,B57-$B$6))</f>
-        <v>71498370</v>
+        <v>52998370</v>
       </c>
       <c r="F57" s="11" t="s">
         <v>169</v>
@@ -6571,7 +6571,7 @@
       <c r="D58" s="12"/>
       <c r="E58" s="24" t="n">
         <f aca="false">IF(B58="","",MAX(0,B58-$B$6))</f>
-        <v>101498370</v>
+        <v>82998370</v>
       </c>
       <c r="F58" s="11" t="s">
         <v>169</v>
@@ -6590,7 +6590,7 @@
       <c r="D59" s="12"/>
       <c r="E59" s="24" t="n">
         <f aca="false">IF(B59="","",MAX(0,B59-$B$6))</f>
-        <v>131498370</v>
+        <v>112998370</v>
       </c>
       <c r="F59" s="11" t="s">
         <v>169</v>
@@ -6609,7 +6609,7 @@
       <c r="D60" s="12"/>
       <c r="E60" s="24" t="n">
         <f aca="false">IF(B60="","",MAX(0,B60-$B$6))</f>
-        <v>191498370</v>
+        <v>172998370</v>
       </c>
       <c r="F60" s="11" t="s">
         <v>169</v>
@@ -6628,7 +6628,7 @@
       <c r="D61" s="12"/>
       <c r="E61" s="24" t="n">
         <f aca="false">IF(B61="","",MAX(0,B61-$B$6))</f>
-        <v>266498370</v>
+        <v>247998370</v>
       </c>
       <c r="F61" s="11" t="s">
         <v>169</v>
@@ -6647,7 +6647,7 @@
       <c r="D62" s="12"/>
       <c r="E62" s="24" t="n">
         <f aca="false">IF(B62="","",MAX(0,B62-$B$6))</f>
-        <v>341498370</v>
+        <v>322998370</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>169</v>
@@ -6666,7 +6666,7 @@
       <c r="D63" s="12"/>
       <c r="E63" s="24" t="n">
         <f aca="false">IF(B63="","",MAX(0,B63-$B$6))</f>
-        <v>416498370</v>
+        <v>397998370</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>169</v>
@@ -6685,7 +6685,7 @@
       <c r="D64" s="12"/>
       <c r="E64" s="24" t="n">
         <f aca="false">IF(B64="","",MAX(0,B64-$B$6))</f>
-        <v>491498370</v>
+        <v>472998370</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>169</v>
@@ -6704,7 +6704,7 @@
       <c r="D65" s="12"/>
       <c r="E65" s="24" t="n">
         <f aca="false">IF(B65="","",MAX(0,B65-$B$6))</f>
-        <v>566498370</v>
+        <v>547998370</v>
       </c>
       <c r="F65" s="11" t="s">
         <v>169</v>
@@ -6723,7 +6723,7 @@
       <c r="D66" s="12"/>
       <c r="E66" s="24" t="n">
         <f aca="false">IF(B66="","",MAX(0,B66-$B$6))</f>
-        <v>641498370</v>
+        <v>622998370</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>169</v>
@@ -6742,7 +6742,7 @@
       <c r="D67" s="12"/>
       <c r="E67" s="24" t="n">
         <f aca="false">IF(B67="","",MAX(0,B67-$B$6))</f>
-        <v>791498370</v>
+        <v>772998370</v>
       </c>
       <c r="F67" s="11" t="s">
         <v>169</v>
@@ -6761,7 +6761,7 @@
       <c r="D68" s="12"/>
       <c r="E68" s="24" t="n">
         <f aca="false">IF(B68="","",MAX(0,B68-$B$6))</f>
-        <v>941498370</v>
+        <v>922998370</v>
       </c>
       <c r="F68" s="11" t="s">
         <v>169</v>
@@ -6780,7 +6780,7 @@
       <c r="D69" s="12"/>
       <c r="E69" s="24" t="n">
         <f aca="false">IF(B69="","",MAX(0,B69-$B$6))</f>
-        <v>1091498370</v>
+        <v>1072998370</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>169</v>
@@ -6799,7 +6799,7 @@
       <c r="D70" s="12"/>
       <c r="E70" s="24" t="n">
         <f aca="false">IF(B70="","",MAX(0,B70-$B$6))</f>
-        <v>1316498370</v>
+        <v>1297998370</v>
       </c>
       <c r="F70" s="11" t="s">
         <v>169</v>
@@ -6818,7 +6818,7 @@
       <c r="D71" s="12"/>
       <c r="E71" s="24" t="n">
         <f aca="false">IF(B71="","",MAX(0,B71-$B$6))</f>
-        <v>1691498370</v>
+        <v>1672998370</v>
       </c>
       <c r="F71" s="11" t="s">
         <v>169</v>
@@ -6837,7 +6837,7 @@
       <c r="D72" s="12"/>
       <c r="E72" s="24" t="n">
         <f aca="false">IF(B72="","",MAX(0,B72-$B$6))</f>
-        <v>2066498370</v>
+        <v>2047998370</v>
       </c>
       <c r="F72" s="11" t="s">
         <v>169</v>
@@ -6856,7 +6856,7 @@
       <c r="D73" s="12"/>
       <c r="E73" s="24" t="n">
         <f aca="false">IF(B73="","",MAX(0,B73-$B$6))</f>
-        <v>2441498370</v>
+        <v>2422998370</v>
       </c>
       <c r="F73" s="11" t="s">
         <v>169</v>
@@ -6875,7 +6875,7 @@
       <c r="D74" s="12"/>
       <c r="E74" s="24" t="n">
         <f aca="false">IF(B74="","",MAX(0,B74-$B$6))</f>
-        <v>2816498370</v>
+        <v>2797998370</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>169</v>
@@ -6894,7 +6894,7 @@
       <c r="D75" s="12"/>
       <c r="E75" s="24" t="n">
         <f aca="false">IF(B75="","",MAX(0,B75-$B$6))</f>
-        <v>3191498370</v>
+        <v>3172998370</v>
       </c>
       <c r="F75" s="11" t="s">
         <v>169</v>
@@ -6913,7 +6913,7 @@
       <c r="D76" s="12"/>
       <c r="E76" s="24" t="n">
         <f aca="false">IF(B76="","",MAX(0,B76-$B$6))</f>
-        <v>3566498370</v>
+        <v>3547998370</v>
       </c>
       <c r="F76" s="11" t="s">
         <v>169</v>
@@ -7094,11 +7094,11 @@
         <v>1000000000</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>47651630</v>
+        <v>52651630</v>
       </c>
       <c r="F7" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D7),MAX(0,D7-E7),0)</f>
-        <v>952348370</v>
+        <v>947348370</v>
       </c>
       <c r="G7" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D7),ROUNDUP(D7/C7,0),"No limit")</f>
@@ -7106,11 +7106,11 @@
       </c>
       <c r="H7" s="22" t="n">
         <f aca="false">IFERROR(INT(E7/C7),0)</f>
-        <v>47651630</v>
+        <v>52651630</v>
       </c>
       <c r="I7" s="22" t="n">
         <f aca="false">IFERROR(ROUNDUP(F7/C7,0),0)</f>
-        <v>952348370</v>
+        <v>947348370</v>
       </c>
       <c r="J7" s="11" t="s">
         <v>315</v>
@@ -7130,11 +7130,11 @@
         <v>1000000000</v>
       </c>
       <c r="E8" s="25" t="n">
-        <v>3600000</v>
+        <v>17100000</v>
       </c>
       <c r="F8" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D8),MAX(0,D8-E8),0)</f>
-        <v>996400000</v>
+        <v>982900000</v>
       </c>
       <c r="G8" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D8),ROUNDUP(D8/C8,0),"No limit")</f>
@@ -7142,11 +7142,11 @@
       </c>
       <c r="H8" s="22" t="n">
         <f aca="false">IFERROR(INT(E8/C8),0)</f>
-        <v>900</v>
+        <v>4275</v>
       </c>
       <c r="I8" s="22" t="n">
         <f aca="false">IFERROR(ROUNDUP(F8/C8,0),0)</f>
-        <v>249100</v>
+        <v>245725</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>315</v>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="E49" s="20" t="n">
         <f aca="false">SUM(E5:E47)</f>
-        <v>558501630</v>
+        <v>577001630</v>
       </c>
       <c r="F49" s="20"/>
     </row>
@@ -8573,7 +8573,7 @@
       <c r="E50" s="20"/>
       <c r="F50" s="20" t="n">
         <f aca="false">SUM(F5:F47)</f>
-        <v>7378748370</v>
+        <v>7360248370</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8672,7 +8672,7 @@
         <v>377</v>
       </c>
       <c r="B5" s="27" t="n">
-        <v>16720000</v>
+        <v>16828000</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>336000</v>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="B7" s="28" t="n">
         <f aca="false">B5+B6</f>
-        <v>43770000</v>
+        <v>43878000</v>
       </c>
       <c r="C7" s="28" t="n">
         <f aca="false">C5+C6</f>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">B7-B8</f>
-        <v>42119990</v>
+        <v>42227990</v>
       </c>
       <c r="C9" s="29" t="n">
         <f aca="false">C7-C8</f>
@@ -10671,7 +10671,7 @@
         <v>462</v>
       </c>
       <c r="B65" s="30" t="n">
-        <v>12000</v>
+        <v>120000</v>
       </c>
       <c r="C65" s="30" t="n">
         <v>0</v>
@@ -12533,7 +12533,7 @@
         <v>226</v>
       </c>
       <c r="B6" s="19" t="n">
-        <v>308343695</v>
+        <v>325778995</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>587</v>
@@ -12557,14 +12557,14 @@
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">IFERROR(INDEX(A13:A54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),"All done")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>230</v>
       </c>
       <c r="E7" s="20" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
-        <v>0</v>
+        <v>950000</v>
       </c>
       <c r="F7" s="20" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*F13:F54)</f>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="G7" s="20" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*G13:G54)</f>
-        <v>0</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="B8" s="20" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>16656305</v>
+        <v>24221005</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>116656305</v>
+        <v>99221005</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>18100115.4758211</v>
+        <v>15528494.8366765</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="I28" s="24" t="n">
         <f aca="false">IF(B28="","",MAX(0,B28-$B$6))</f>
-        <v>16656305</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="I29" s="24" t="n">
         <f aca="false">IF(B29="","",MAX(0,B29-$B$6))</f>
-        <v>41656305</v>
+        <v>24221005</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="I30" s="24" t="n">
         <f aca="false">IF(B30="","",MAX(0,B30-$B$6))</f>
-        <v>66656305</v>
+        <v>49221005</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="I31" s="24" t="n">
         <f aca="false">IF(B31="","",MAX(0,B31-$B$6))</f>
-        <v>91656305</v>
+        <v>74221005</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="I32" s="24" t="n">
         <f aca="false">IF(B32="","",MAX(0,B32-$B$6))</f>
-        <v>116656305</v>
+        <v>99221005</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="I33" s="24" t="n">
         <f aca="false">IF(B33="","",MAX(0,B33-$B$6))</f>
-        <v>141656305</v>
+        <v>124221005</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="I34" s="24" t="n">
         <f aca="false">IF(B34="","",MAX(0,B34-$B$6))</f>
-        <v>166656305</v>
+        <v>149221005</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13276,7 +13276,7 @@
       </c>
       <c r="I35" s="24" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
-        <v>191656305</v>
+        <v>174221005</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="I36" s="24" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>216656305</v>
+        <v>199221005</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13334,7 +13334,7 @@
       </c>
       <c r="I37" s="24" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>241656305</v>
+        <v>224221005</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="I38" s="24" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>291656305</v>
+        <v>274221005</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="I39" s="24" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>341656305</v>
+        <v>324221005</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="I40" s="24" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>441656305</v>
+        <v>424221005</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13450,7 +13450,7 @@
       </c>
       <c r="I41" s="24" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>591656305</v>
+        <v>574221005</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="I42" s="24" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>791656305</v>
+        <v>774221005</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="I43" s="24" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>991656305</v>
+        <v>974221005</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="I44" s="24" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>1191656305</v>
+        <v>1174221005</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="I45" s="24" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1391656305</v>
+        <v>1374221005</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="I46" s="24" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1591656305</v>
+        <v>1574221005</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="I47" s="24" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1791656305</v>
+        <v>1774221005</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="I48" s="24" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1991656305</v>
+        <v>1974221005</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="I49" s="24" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>2191656305</v>
+        <v>2174221005</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="I50" s="24" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2391656305</v>
+        <v>2374221005</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="I51" s="24" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2591656305</v>
+        <v>2574221005</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="I52" s="24" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2791656305</v>
+        <v>2774221005</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="I53" s="24" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2991656305</v>
+        <v>2974221005</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="I54" s="24" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>3191656305</v>
+        <v>3174221005</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -1480,7 +1480,7 @@
     <t xml:space="preserve">Storm to level 101</t>
   </si>
   <si>
-    <t xml:space="preserve">First Uncanny Avenger. Then retry Spider-Man tower cell 20</t>
+    <t xml:space="preserve">Leveled Oct 12. Retry Spider-Man tower cell 20</t>
   </si>
   <si>
     <t xml:space="preserve">Second Uncanny Avenger to level 101</t>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">B6+Scoring!F51</f>
-        <v>6007001630</v>
+        <v>6004001630</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>555276317.656699</v>
+        <v>556352310.953285</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7094,11 +7094,11 @@
         <v>1000000000</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>52651630</v>
+        <v>49651630</v>
       </c>
       <c r="F7" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D7),MAX(0,D7-E7),0)</f>
-        <v>947348370</v>
+        <v>950348370</v>
       </c>
       <c r="G7" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D7),ROUNDUP(D7/C7,0),"No limit")</f>
@@ -7106,11 +7106,11 @@
       </c>
       <c r="H7" s="22" t="n">
         <f aca="false">IFERROR(INT(E7/C7),0)</f>
-        <v>52651630</v>
+        <v>49651630</v>
       </c>
       <c r="I7" s="22" t="n">
         <f aca="false">IFERROR(ROUNDUP(F7/C7,0),0)</f>
-        <v>947348370</v>
+        <v>950348370</v>
       </c>
       <c r="J7" s="11" t="s">
         <v>315</v>
@@ -7166,11 +7166,11 @@
         <v>15000000</v>
       </c>
       <c r="E9" s="25" t="n">
-        <v>3000000</v>
+        <v>6000000</v>
       </c>
       <c r="F9" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D9),MAX(0,D9-E9),0)</f>
-        <v>12000000</v>
+        <v>9000000</v>
       </c>
       <c r="G9" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D9),ROUNDUP(D9/C9,0),"No limit")</f>
@@ -7178,11 +7178,11 @@
       </c>
       <c r="H9" s="22" t="n">
         <f aca="false">IFERROR(INT(E9/C9),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="22" t="n">
         <f aca="false">IFERROR(ROUNDUP(F9/C9,0),0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J9" s="11" t="s">
         <v>311</v>
@@ -8583,7 +8583,7 @@
       <c r="E51" s="20"/>
       <c r="F51" s="20" t="n">
         <f aca="false">SUMIF(J5:J47,"Yes",F5:F47)</f>
-        <v>5430000000</v>
+        <v>5427000000</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8672,7 +8672,7 @@
         <v>377</v>
       </c>
       <c r="B5" s="27" t="n">
-        <v>16828000</v>
+        <v>13730000</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>336000</v>
@@ -8684,13 +8684,13 @@
         <v>13650000</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H5" s="27" t="n">
-        <v>522</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="B7" s="28" t="n">
         <f aca="false">B5+B6</f>
-        <v>43878000</v>
+        <v>40780000</v>
       </c>
       <c r="C7" s="28" t="n">
         <f aca="false">C5+C6</f>
@@ -8748,15 +8748,15 @@
       </c>
       <c r="F7" s="28" t="n">
         <f aca="false">F5+F6</f>
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G7" s="28" t="n">
         <f aca="false">G5+G6</f>
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H7" s="28" t="n">
         <f aca="false">H5+H6</f>
-        <v>1407</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="B8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",B80:B101)</f>
-        <v>1650010</v>
+        <v>0</v>
       </c>
       <c r="C8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",C80:C101)</f>
@@ -8781,15 +8781,15 @@
       </c>
       <c r="F8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",F80:F101)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",G80:G101)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",H80:H101)</f>
-        <v>164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">B7-B8</f>
-        <v>42227990</v>
+        <v>40780000</v>
       </c>
       <c r="C9" s="29" t="n">
         <f aca="false">C7-C8</f>
@@ -11127,7 +11127,7 @@
         <v>3000000</v>
       </c>
       <c r="J86" s="11" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="K86" s="15" t="s">
         <v>482</v>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="I103" s="20" t="n">
         <f aca="false">SUMIF(J80:J101,"Planned",I80:I101)</f>
-        <v>40000000</v>
+        <v>37000000</v>
       </c>
     </row>
   </sheetData>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>15528494.8366765</v>
+        <v>15558585.3607401</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -1486,13 +1486,13 @@
     <t xml:space="preserve">Second Uncanny Avenger to level 101</t>
   </si>
   <si>
+    <t xml:space="preserve">Cell 20 failed with Storm. Level the weakest member next</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Third Uncanny Avenger to level 101</t>
+  </si>
+  <si>
     <t xml:space="preserve">If needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only if cell 20 still fails after Storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Third Uncanny Avenger to level 101</t>
   </si>
   <si>
     <t xml:space="preserve">Only if cell 20 still fails. Needs battle pass level 95 orange</t>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>556352310.953285</v>
+        <v>556874246.856147</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="B8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",B80:B101)</f>
-        <v>0</v>
+        <v>1650000</v>
       </c>
       <c r="C8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",C80:C101)</f>
@@ -8781,15 +8781,15 @@
       </c>
       <c r="F8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",F80:F101)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",G80:G101)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",H80:H101)</f>
-        <v>0</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">B7-B8</f>
-        <v>40780000</v>
+        <v>39130000</v>
       </c>
       <c r="C9" s="29" t="n">
         <f aca="false">C7-C8</f>
@@ -8814,15 +8814,15 @@
       </c>
       <c r="F9" s="29" t="n">
         <f aca="false">F7-F8</f>
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G9" s="29" t="n">
         <f aca="false">G7-G8</f>
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H9" s="29" t="n">
         <f aca="false">H7-H8</f>
-        <v>1243</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11162,15 +11162,15 @@
         <v>3000000</v>
       </c>
       <c r="J87" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="K87" s="15" t="s">
         <v>484</v>
-      </c>
-      <c r="K87" s="15" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="12" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B88" s="30" t="n">
         <v>1650000</v>
@@ -11197,7 +11197,7 @@
         <v>3000000</v>
       </c>
       <c r="J88" s="11" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K88" s="15" t="s">
         <v>487</v>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="I103" s="20" t="n">
         <f aca="false">SUMIF(J80:J101,"Planned",I80:I101)</f>
-        <v>37000000</v>
+        <v>40000000</v>
       </c>
     </row>
   </sheetData>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>15558585.3607401</v>
+        <v>15573181.4977898</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="640">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -1483,10 +1483,10 @@
     <t xml:space="preserve">Leveled Oct 12. Retry Spider-Man tower cell 20</t>
   </si>
   <si>
-    <t xml:space="preserve">Second Uncanny Avenger to level 101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cell 20 failed with Storm. Level the weakest member next</t>
+    <t xml:space="preserve">Beast to level 101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leveled Oct 12. Retry cell 20</t>
   </si>
   <si>
     <t xml:space="preserve">Third Uncanny Avenger to level 101</t>
@@ -1513,7 +1513,7 @@
     <t xml:space="preserve">Spider-Man Iso-8 to T3 level 5</t>
   </si>
   <si>
-    <t xml:space="preserve">Assumed same as Hulk. Confirm with Quick Upgrade</t>
+    <t xml:space="preserve">Quick Upgrade cost Oct 12. Affordable now</t>
   </si>
   <si>
     <t xml:space="preserve">Blade (Mighty) Iso-8 to T3 level 5</t>
@@ -5686,14 +5686,14 @@
         <v>226</v>
       </c>
       <c r="B6" s="19" t="n">
-        <v>577001630</v>
+        <v>581651630</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>227</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">B6+Scoring!F51</f>
-        <v>6004001630</v>
+        <v>6002651630</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="B9" s="20" t="n">
         <f aca="false">IFERROR(INDEX(E13:E76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),0)</f>
-        <v>22998370</v>
+        <v>18348370</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,B76-B6)</f>
-        <v>3547998370</v>
+        <v>3543348370</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>556874246.856147</v>
+        <v>557112913.759841</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6533,7 +6533,7 @@
       <c r="D56" s="12"/>
       <c r="E56" s="24" t="n">
         <f aca="false">IF(B56="","",MAX(0,B56-$B$6))</f>
-        <v>22998370</v>
+        <v>18348370</v>
       </c>
       <c r="F56" s="11" t="s">
         <v>169</v>
@@ -6552,7 +6552,7 @@
       <c r="D57" s="12"/>
       <c r="E57" s="24" t="n">
         <f aca="false">IF(B57="","",MAX(0,B57-$B$6))</f>
-        <v>52998370</v>
+        <v>48348370</v>
       </c>
       <c r="F57" s="11" t="s">
         <v>169</v>
@@ -6571,7 +6571,7 @@
       <c r="D58" s="12"/>
       <c r="E58" s="24" t="n">
         <f aca="false">IF(B58="","",MAX(0,B58-$B$6))</f>
-        <v>82998370</v>
+        <v>78348370</v>
       </c>
       <c r="F58" s="11" t="s">
         <v>169</v>
@@ -6590,7 +6590,7 @@
       <c r="D59" s="12"/>
       <c r="E59" s="24" t="n">
         <f aca="false">IF(B59="","",MAX(0,B59-$B$6))</f>
-        <v>112998370</v>
+        <v>108348370</v>
       </c>
       <c r="F59" s="11" t="s">
         <v>169</v>
@@ -6609,7 +6609,7 @@
       <c r="D60" s="12"/>
       <c r="E60" s="24" t="n">
         <f aca="false">IF(B60="","",MAX(0,B60-$B$6))</f>
-        <v>172998370</v>
+        <v>168348370</v>
       </c>
       <c r="F60" s="11" t="s">
         <v>169</v>
@@ -6628,7 +6628,7 @@
       <c r="D61" s="12"/>
       <c r="E61" s="24" t="n">
         <f aca="false">IF(B61="","",MAX(0,B61-$B$6))</f>
-        <v>247998370</v>
+        <v>243348370</v>
       </c>
       <c r="F61" s="11" t="s">
         <v>169</v>
@@ -6647,7 +6647,7 @@
       <c r="D62" s="12"/>
       <c r="E62" s="24" t="n">
         <f aca="false">IF(B62="","",MAX(0,B62-$B$6))</f>
-        <v>322998370</v>
+        <v>318348370</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>169</v>
@@ -6666,7 +6666,7 @@
       <c r="D63" s="12"/>
       <c r="E63" s="24" t="n">
         <f aca="false">IF(B63="","",MAX(0,B63-$B$6))</f>
-        <v>397998370</v>
+        <v>393348370</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>169</v>
@@ -6685,7 +6685,7 @@
       <c r="D64" s="12"/>
       <c r="E64" s="24" t="n">
         <f aca="false">IF(B64="","",MAX(0,B64-$B$6))</f>
-        <v>472998370</v>
+        <v>468348370</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>169</v>
@@ -6704,7 +6704,7 @@
       <c r="D65" s="12"/>
       <c r="E65" s="24" t="n">
         <f aca="false">IF(B65="","",MAX(0,B65-$B$6))</f>
-        <v>547998370</v>
+        <v>543348370</v>
       </c>
       <c r="F65" s="11" t="s">
         <v>169</v>
@@ -6723,7 +6723,7 @@
       <c r="D66" s="12"/>
       <c r="E66" s="24" t="n">
         <f aca="false">IF(B66="","",MAX(0,B66-$B$6))</f>
-        <v>622998370</v>
+        <v>618348370</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>169</v>
@@ -6742,7 +6742,7 @@
       <c r="D67" s="12"/>
       <c r="E67" s="24" t="n">
         <f aca="false">IF(B67="","",MAX(0,B67-$B$6))</f>
-        <v>772998370</v>
+        <v>768348370</v>
       </c>
       <c r="F67" s="11" t="s">
         <v>169</v>
@@ -6761,7 +6761,7 @@
       <c r="D68" s="12"/>
       <c r="E68" s="24" t="n">
         <f aca="false">IF(B68="","",MAX(0,B68-$B$6))</f>
-        <v>922998370</v>
+        <v>918348370</v>
       </c>
       <c r="F68" s="11" t="s">
         <v>169</v>
@@ -6780,7 +6780,7 @@
       <c r="D69" s="12"/>
       <c r="E69" s="24" t="n">
         <f aca="false">IF(B69="","",MAX(0,B69-$B$6))</f>
-        <v>1072998370</v>
+        <v>1068348370</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>169</v>
@@ -6799,7 +6799,7 @@
       <c r="D70" s="12"/>
       <c r="E70" s="24" t="n">
         <f aca="false">IF(B70="","",MAX(0,B70-$B$6))</f>
-        <v>1297998370</v>
+        <v>1293348370</v>
       </c>
       <c r="F70" s="11" t="s">
         <v>169</v>
@@ -6818,7 +6818,7 @@
       <c r="D71" s="12"/>
       <c r="E71" s="24" t="n">
         <f aca="false">IF(B71="","",MAX(0,B71-$B$6))</f>
-        <v>1672998370</v>
+        <v>1668348370</v>
       </c>
       <c r="F71" s="11" t="s">
         <v>169</v>
@@ -6837,7 +6837,7 @@
       <c r="D72" s="12"/>
       <c r="E72" s="24" t="n">
         <f aca="false">IF(B72="","",MAX(0,B72-$B$6))</f>
-        <v>2047998370</v>
+        <v>2043348370</v>
       </c>
       <c r="F72" s="11" t="s">
         <v>169</v>
@@ -6856,7 +6856,7 @@
       <c r="D73" s="12"/>
       <c r="E73" s="24" t="n">
         <f aca="false">IF(B73="","",MAX(0,B73-$B$6))</f>
-        <v>2422998370</v>
+        <v>2418348370</v>
       </c>
       <c r="F73" s="11" t="s">
         <v>169</v>
@@ -6875,7 +6875,7 @@
       <c r="D74" s="12"/>
       <c r="E74" s="24" t="n">
         <f aca="false">IF(B74="","",MAX(0,B74-$B$6))</f>
-        <v>2797998370</v>
+        <v>2793348370</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>169</v>
@@ -6894,7 +6894,7 @@
       <c r="D75" s="12"/>
       <c r="E75" s="24" t="n">
         <f aca="false">IF(B75="","",MAX(0,B75-$B$6))</f>
-        <v>3172998370</v>
+        <v>3168348370</v>
       </c>
       <c r="F75" s="11" t="s">
         <v>169</v>
@@ -6913,7 +6913,7 @@
       <c r="D76" s="12"/>
       <c r="E76" s="24" t="n">
         <f aca="false">IF(B76="","",MAX(0,B76-$B$6))</f>
-        <v>3547998370</v>
+        <v>3543348370</v>
       </c>
       <c r="F76" s="11" t="s">
         <v>169</v>
@@ -7094,11 +7094,11 @@
         <v>1000000000</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>49651630</v>
+        <v>51301630</v>
       </c>
       <c r="F7" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D7),MAX(0,D7-E7),0)</f>
-        <v>950348370</v>
+        <v>948698370</v>
       </c>
       <c r="G7" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D7),ROUNDUP(D7/C7,0),"No limit")</f>
@@ -7106,11 +7106,11 @@
       </c>
       <c r="H7" s="22" t="n">
         <f aca="false">IFERROR(INT(E7/C7),0)</f>
-        <v>49651630</v>
+        <v>51301630</v>
       </c>
       <c r="I7" s="22" t="n">
         <f aca="false">IFERROR(ROUNDUP(F7/C7,0),0)</f>
-        <v>950348370</v>
+        <v>948698370</v>
       </c>
       <c r="J7" s="11" t="s">
         <v>315</v>
@@ -7166,11 +7166,11 @@
         <v>15000000</v>
       </c>
       <c r="E9" s="25" t="n">
-        <v>6000000</v>
+        <v>9000000</v>
       </c>
       <c r="F9" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D9),MAX(0,D9-E9),0)</f>
-        <v>9000000</v>
+        <v>6000000</v>
       </c>
       <c r="G9" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D9),ROUNDUP(D9/C9,0),"No limit")</f>
@@ -7178,11 +7178,11 @@
       </c>
       <c r="H9" s="22" t="n">
         <f aca="false">IFERROR(INT(E9/C9),0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" s="22" t="n">
         <f aca="false">IFERROR(ROUNDUP(F9/C9,0),0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" s="11" t="s">
         <v>311</v>
@@ -7670,11 +7670,11 @@
         <v>15000000</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>6000000</v>
+        <v>9000000</v>
       </c>
       <c r="F23" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D23),MAX(0,D23-E23),0)</f>
-        <v>9000000</v>
+        <v>6000000</v>
       </c>
       <c r="G23" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D23),ROUNDUP(D23/C23,0),"No limit")</f>
@@ -7682,11 +7682,11 @@
       </c>
       <c r="H23" s="22" t="n">
         <f aca="false">IFERROR(INT(E23/C23),0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23" s="22" t="n">
         <f aca="false">IFERROR(ROUNDUP(F23/C23,0),0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>311</v>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="E49" s="20" t="n">
         <f aca="false">SUM(E5:E47)</f>
-        <v>577001630</v>
+        <v>584651630</v>
       </c>
       <c r="F49" s="20"/>
     </row>
@@ -8573,7 +8573,7 @@
       <c r="E50" s="20"/>
       <c r="F50" s="20" t="n">
         <f aca="false">SUM(F5:F47)</f>
-        <v>7360248370</v>
+        <v>7352598370</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8583,7 +8583,7 @@
       <c r="E51" s="20"/>
       <c r="F51" s="20" t="n">
         <f aca="false">SUMIF(J5:J47,"Yes",F5:F47)</f>
-        <v>5427000000</v>
+        <v>5421000000</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8672,25 +8672,25 @@
         <v>377</v>
       </c>
       <c r="B5" s="27" t="n">
-        <v>13730000</v>
+        <v>12080000</v>
       </c>
       <c r="C5" s="27" t="n">
-        <v>336000</v>
+        <v>1530000</v>
       </c>
       <c r="D5" s="27" t="n">
         <v>3960000</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>13650000</v>
+        <v>15550000</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H5" s="27" t="n">
-        <v>358</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="C6" s="28" t="n">
         <f aca="false">SUMIFS(C13:C76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
-        <v>4650000</v>
+        <v>3700000</v>
       </c>
       <c r="D6" s="28" t="n">
         <f aca="false">SUMIFS(D13:D76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="E6" s="28" t="n">
         <f aca="false">SUMIFS(E13:E76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
-        <v>5386000</v>
+        <v>3486000</v>
       </c>
       <c r="F6" s="28" t="n">
         <f aca="false">SUMIFS(F13:F76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
@@ -8732,11 +8732,11 @@
       </c>
       <c r="B7" s="28" t="n">
         <f aca="false">B5+B6</f>
-        <v>40780000</v>
+        <v>39130000</v>
       </c>
       <c r="C7" s="28" t="n">
         <f aca="false">C5+C6</f>
-        <v>4986000</v>
+        <v>5230000</v>
       </c>
       <c r="D7" s="28" t="n">
         <f aca="false">D5+D6</f>
@@ -8748,15 +8748,15 @@
       </c>
       <c r="F7" s="28" t="n">
         <f aca="false">F5+F6</f>
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G7" s="28" t="n">
         <f aca="false">G5+G6</f>
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H7" s="28" t="n">
         <f aca="false">H5+H6</f>
-        <v>1243</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8765,31 +8765,31 @@
       </c>
       <c r="B8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",B80:B101)</f>
-        <v>1650000</v>
+        <v>0</v>
       </c>
       <c r="C8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",C80:C101)</f>
-        <v>1710000</v>
+        <v>1370000</v>
       </c>
       <c r="D8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",D80:D101)</f>
-        <v>1710000</v>
+        <v>1370000</v>
       </c>
       <c r="E8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",E80:E101)</f>
-        <v>2640000</v>
+        <v>2130000</v>
       </c>
       <c r="F8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",F80:F101)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",G80:G101)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",H80:H101)</f>
-        <v>164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8802,15 +8802,15 @@
       </c>
       <c r="C9" s="29" t="n">
         <f aca="false">C7-C8</f>
-        <v>3276000</v>
+        <v>3860000</v>
       </c>
       <c r="D9" s="29" t="n">
         <f aca="false">D7-D8</f>
-        <v>6136000</v>
+        <v>6476000</v>
       </c>
       <c r="E9" s="29" t="n">
         <f aca="false">E7-E8</f>
-        <v>16396000</v>
+        <v>16906000</v>
       </c>
       <c r="F9" s="29" t="n">
         <f aca="false">F7-F8</f>
@@ -9752,7 +9752,7 @@
         <v>311</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="K38" s="15" t="s">
         <v>418</v>
@@ -10114,13 +10114,13 @@
         <v>389</v>
       </c>
       <c r="C49" s="30" t="s">
+        <v>417</v>
+      </c>
+      <c r="D49" s="30" t="s">
         <v>387</v>
       </c>
-      <c r="D49" s="30" t="n">
+      <c r="E49" s="30" t="n">
         <v>3300000</v>
-      </c>
-      <c r="E49" s="30" t="n">
-        <v>0</v>
       </c>
       <c r="F49" s="30" t="n">
         <v>0</v>
@@ -11162,7 +11162,7 @@
         <v>3000000</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="K87" s="15" t="s">
         <v>484</v>
@@ -11279,13 +11279,13 @@
         <v>0</v>
       </c>
       <c r="C91" s="30" t="n">
-        <v>1710000</v>
+        <v>1370000</v>
       </c>
       <c r="D91" s="30" t="n">
-        <v>1710000</v>
+        <v>1370000</v>
       </c>
       <c r="E91" s="30" t="n">
-        <v>2640000</v>
+        <v>2130000</v>
       </c>
       <c r="F91" s="30" t="n">
         <v>0</v>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="I103" s="20" t="n">
         <f aca="false">SUMIF(J80:J101,"Planned",I80:I101)</f>
-        <v>40000000</v>
+        <v>37000000</v>
       </c>
     </row>
   </sheetData>
@@ -12540,7 +12540,7 @@
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
-        <v>2250000</v>
+        <v>1300000</v>
       </c>
       <c r="F6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*F13:F54)</f>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="G6" s="20" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*G13:G54)</f>
-        <v>7600000</v>
+        <v>5700000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="E7" s="20" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
-        <v>950000</v>
+        <v>0</v>
       </c>
       <c r="F7" s="20" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*F13:F54)</f>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="G7" s="20" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*G13:G54)</f>
-        <v>1900000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>15573181.4977898</v>
+        <v>15600301.6147948</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13072,7 +13072,7 @@
         <v>1900000</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I28" s="24" t="n">
         <f aca="false">IF(B28="","",MAX(0,B28-$B$6))</f>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -1513,7 +1513,7 @@
     <t xml:space="preserve">Spider-Man Iso-8 to T3 level 5</t>
   </si>
   <si>
-    <t xml:space="preserve">Quick Upgrade cost Oct 12. Affordable now</t>
+    <t xml:space="preserve">Done Oct 12, plus 500 ion 1 to unlock the T4 matrix</t>
   </si>
   <si>
     <t xml:space="preserve">Blade (Mighty) Iso-8 to T3 level 5</t>
@@ -5686,14 +5686,14 @@
         <v>226</v>
       </c>
       <c r="B6" s="19" t="n">
-        <v>581651630</v>
+        <v>649301650</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>227</v>
       </c>
       <c r="E6" s="20" t="n">
         <f aca="false">B6+Scoring!F51</f>
-        <v>6002651630</v>
+        <v>6007301650</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6))+SUMPRODUCT((B13:B76="")*(F13:F76="Claimed"))</f>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>229</v>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B8" s="16" t="n">
         <f aca="false">IFERROR(INDEX(A13:A76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),"All done")</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>230</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="B9" s="20" t="n">
         <f aca="false">IFERROR(INDEX(E13:E76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),0)</f>
-        <v>18348370</v>
+        <v>10698350</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">MAX(0,B76-B6)</f>
-        <v>3543348370</v>
+        <v>3475698350</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>557112913.759841</v>
+        <v>548207240.6819</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6533,10 +6533,10 @@
       <c r="D56" s="12"/>
       <c r="E56" s="24" t="n">
         <f aca="false">IF(B56="","",MAX(0,B56-$B$6))</f>
-        <v>18348370</v>
+        <v>0</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6552,10 +6552,10 @@
       <c r="D57" s="12"/>
       <c r="E57" s="24" t="n">
         <f aca="false">IF(B57="","",MAX(0,B57-$B$6))</f>
-        <v>48348370</v>
+        <v>0</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6571,7 +6571,7 @@
       <c r="D58" s="12"/>
       <c r="E58" s="24" t="n">
         <f aca="false">IF(B58="","",MAX(0,B58-$B$6))</f>
-        <v>78348370</v>
+        <v>10698350</v>
       </c>
       <c r="F58" s="11" t="s">
         <v>169</v>
@@ -6590,7 +6590,7 @@
       <c r="D59" s="12"/>
       <c r="E59" s="24" t="n">
         <f aca="false">IF(B59="","",MAX(0,B59-$B$6))</f>
-        <v>108348370</v>
+        <v>40698350</v>
       </c>
       <c r="F59" s="11" t="s">
         <v>169</v>
@@ -6609,7 +6609,7 @@
       <c r="D60" s="12"/>
       <c r="E60" s="24" t="n">
         <f aca="false">IF(B60="","",MAX(0,B60-$B$6))</f>
-        <v>168348370</v>
+        <v>100698350</v>
       </c>
       <c r="F60" s="11" t="s">
         <v>169</v>
@@ -6628,7 +6628,7 @@
       <c r="D61" s="12"/>
       <c r="E61" s="24" t="n">
         <f aca="false">IF(B61="","",MAX(0,B61-$B$6))</f>
-        <v>243348370</v>
+        <v>175698350</v>
       </c>
       <c r="F61" s="11" t="s">
         <v>169</v>
@@ -6647,7 +6647,7 @@
       <c r="D62" s="12"/>
       <c r="E62" s="24" t="n">
         <f aca="false">IF(B62="","",MAX(0,B62-$B$6))</f>
-        <v>318348370</v>
+        <v>250698350</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>169</v>
@@ -6666,7 +6666,7 @@
       <c r="D63" s="12"/>
       <c r="E63" s="24" t="n">
         <f aca="false">IF(B63="","",MAX(0,B63-$B$6))</f>
-        <v>393348370</v>
+        <v>325698350</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>169</v>
@@ -6685,7 +6685,7 @@
       <c r="D64" s="12"/>
       <c r="E64" s="24" t="n">
         <f aca="false">IF(B64="","",MAX(0,B64-$B$6))</f>
-        <v>468348370</v>
+        <v>400698350</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>169</v>
@@ -6704,7 +6704,7 @@
       <c r="D65" s="12"/>
       <c r="E65" s="24" t="n">
         <f aca="false">IF(B65="","",MAX(0,B65-$B$6))</f>
-        <v>543348370</v>
+        <v>475698350</v>
       </c>
       <c r="F65" s="11" t="s">
         <v>169</v>
@@ -6723,7 +6723,7 @@
       <c r="D66" s="12"/>
       <c r="E66" s="24" t="n">
         <f aca="false">IF(B66="","",MAX(0,B66-$B$6))</f>
-        <v>618348370</v>
+        <v>550698350</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>169</v>
@@ -6742,7 +6742,7 @@
       <c r="D67" s="12"/>
       <c r="E67" s="24" t="n">
         <f aca="false">IF(B67="","",MAX(0,B67-$B$6))</f>
-        <v>768348370</v>
+        <v>700698350</v>
       </c>
       <c r="F67" s="11" t="s">
         <v>169</v>
@@ -6761,7 +6761,7 @@
       <c r="D68" s="12"/>
       <c r="E68" s="24" t="n">
         <f aca="false">IF(B68="","",MAX(0,B68-$B$6))</f>
-        <v>918348370</v>
+        <v>850698350</v>
       </c>
       <c r="F68" s="11" t="s">
         <v>169</v>
@@ -6780,7 +6780,7 @@
       <c r="D69" s="12"/>
       <c r="E69" s="24" t="n">
         <f aca="false">IF(B69="","",MAX(0,B69-$B$6))</f>
-        <v>1068348370</v>
+        <v>1000698350</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>169</v>
@@ -6799,7 +6799,7 @@
       <c r="D70" s="12"/>
       <c r="E70" s="24" t="n">
         <f aca="false">IF(B70="","",MAX(0,B70-$B$6))</f>
-        <v>1293348370</v>
+        <v>1225698350</v>
       </c>
       <c r="F70" s="11" t="s">
         <v>169</v>
@@ -6818,7 +6818,7 @@
       <c r="D71" s="12"/>
       <c r="E71" s="24" t="n">
         <f aca="false">IF(B71="","",MAX(0,B71-$B$6))</f>
-        <v>1668348370</v>
+        <v>1600698350</v>
       </c>
       <c r="F71" s="11" t="s">
         <v>169</v>
@@ -6837,7 +6837,7 @@
       <c r="D72" s="12"/>
       <c r="E72" s="24" t="n">
         <f aca="false">IF(B72="","",MAX(0,B72-$B$6))</f>
-        <v>2043348370</v>
+        <v>1975698350</v>
       </c>
       <c r="F72" s="11" t="s">
         <v>169</v>
@@ -6856,7 +6856,7 @@
       <c r="D73" s="12"/>
       <c r="E73" s="24" t="n">
         <f aca="false">IF(B73="","",MAX(0,B73-$B$6))</f>
-        <v>2418348370</v>
+        <v>2350698350</v>
       </c>
       <c r="F73" s="11" t="s">
         <v>169</v>
@@ -6875,7 +6875,7 @@
       <c r="D74" s="12"/>
       <c r="E74" s="24" t="n">
         <f aca="false">IF(B74="","",MAX(0,B74-$B$6))</f>
-        <v>2793348370</v>
+        <v>2725698350</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>169</v>
@@ -6894,7 +6894,7 @@
       <c r="D75" s="12"/>
       <c r="E75" s="24" t="n">
         <f aca="false">IF(B75="","",MAX(0,B75-$B$6))</f>
-        <v>3168348370</v>
+        <v>3100698350</v>
       </c>
       <c r="F75" s="11" t="s">
         <v>169</v>
@@ -6913,7 +6913,7 @@
       <c r="D76" s="12"/>
       <c r="E76" s="24" t="n">
         <f aca="false">IF(B76="","",MAX(0,B76-$B$6))</f>
-        <v>3543348370</v>
+        <v>3475698350</v>
       </c>
       <c r="F76" s="11" t="s">
         <v>169</v>
@@ -7094,11 +7094,11 @@
         <v>1000000000</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>51301630</v>
+        <v>55951650</v>
       </c>
       <c r="F7" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D7),MAX(0,D7-E7),0)</f>
-        <v>948698370</v>
+        <v>944048350</v>
       </c>
       <c r="G7" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D7),ROUNDUP(D7/C7,0),"No limit")</f>
@@ -7106,11 +7106,11 @@
       </c>
       <c r="H7" s="22" t="n">
         <f aca="false">IFERROR(INT(E7/C7),0)</f>
-        <v>51301630</v>
+        <v>55951650</v>
       </c>
       <c r="I7" s="22" t="n">
         <f aca="false">IFERROR(ROUNDUP(F7/C7,0),0)</f>
-        <v>948698370</v>
+        <v>944048350</v>
       </c>
       <c r="J7" s="11" t="s">
         <v>315</v>
@@ -7598,11 +7598,11 @@
         <v>15000000</v>
       </c>
       <c r="E21" s="25" t="n">
-        <v>9000000</v>
+        <v>12000000</v>
       </c>
       <c r="F21" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D21),MAX(0,D21-E21),0)</f>
-        <v>6000000</v>
+        <v>3000000</v>
       </c>
       <c r="G21" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D21),ROUNDUP(D21/C21,0),"No limit")</f>
@@ -7610,11 +7610,11 @@
       </c>
       <c r="H21" s="22" t="n">
         <f aca="false">IFERROR(INT(E21/C21),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21" s="22" t="n">
         <f aca="false">IFERROR(ROUNDUP(F21/C21,0),0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>311</v>
@@ -7634,11 +7634,11 @@
         <v>40000000</v>
       </c>
       <c r="E22" s="25" t="n">
-        <v>24000000</v>
+        <v>32000000</v>
       </c>
       <c r="F22" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D22),MAX(0,D22-E22),0)</f>
-        <v>16000000</v>
+        <v>8000000</v>
       </c>
       <c r="G22" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D22),ROUNDUP(D22/C22,0),"No limit")</f>
@@ -7646,11 +7646,11 @@
       </c>
       <c r="H22" s="22" t="n">
         <f aca="false">IFERROR(INT(E22/C22),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" s="22" t="n">
         <f aca="false">IFERROR(ROUNDUP(F22/C22,0),0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>311</v>
@@ -7670,11 +7670,11 @@
         <v>15000000</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>9000000</v>
+        <v>12000000</v>
       </c>
       <c r="F23" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D23),MAX(0,D23-E23),0)</f>
-        <v>6000000</v>
+        <v>3000000</v>
       </c>
       <c r="G23" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D23),ROUNDUP(D23/C23,0),"No limit")</f>
@@ -7682,11 +7682,11 @@
       </c>
       <c r="H23" s="22" t="n">
         <f aca="false">IFERROR(INT(E23/C23),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23" s="22" t="n">
         <f aca="false">IFERROR(ROUNDUP(F23/C23,0),0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>311</v>
@@ -7706,11 +7706,11 @@
         <v>40000000</v>
       </c>
       <c r="E24" s="25" t="n">
-        <v>16000000</v>
+        <v>24000000</v>
       </c>
       <c r="F24" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D24),MAX(0,D24-E24),0)</f>
-        <v>24000000</v>
+        <v>16000000</v>
       </c>
       <c r="G24" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D24),ROUNDUP(D24/C24,0),"No limit")</f>
@@ -7718,11 +7718,11 @@
       </c>
       <c r="H24" s="22" t="n">
         <f aca="false">IFERROR(INT(E24/C24),0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24" s="22" t="n">
         <f aca="false">IFERROR(ROUNDUP(F24/C24,0),0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J24" s="11" t="s">
         <v>311</v>
@@ -7742,11 +7742,11 @@
         <v>40000000</v>
       </c>
       <c r="E25" s="25" t="n">
-        <v>24000000</v>
+        <v>32000000</v>
       </c>
       <c r="F25" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D25),MAX(0,D25-E25),0)</f>
-        <v>16000000</v>
+        <v>8000000</v>
       </c>
       <c r="G25" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D25),ROUNDUP(D25/C25,0),"No limit")</f>
@@ -7754,11 +7754,11 @@
       </c>
       <c r="H25" s="22" t="n">
         <f aca="false">IFERROR(INT(E25/C25),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I25" s="22" t="n">
         <f aca="false">IFERROR(ROUNDUP(F25/C25,0),0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>311</v>
@@ -7814,11 +7814,11 @@
         <v>40000000</v>
       </c>
       <c r="E27" s="25" t="n">
-        <v>24000000</v>
+        <v>32000000</v>
       </c>
       <c r="F27" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D27),MAX(0,D27-E27),0)</f>
-        <v>16000000</v>
+        <v>8000000</v>
       </c>
       <c r="G27" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D27),ROUNDUP(D27/C27,0),"No limit")</f>
@@ -7826,11 +7826,11 @@
       </c>
       <c r="H27" s="22" t="n">
         <f aca="false">IFERROR(INT(E27/C27),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27" s="22" t="n">
         <f aca="false">IFERROR(ROUNDUP(F27/C27,0),0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>311</v>
@@ -7886,11 +7886,11 @@
         <v>40000000</v>
       </c>
       <c r="E29" s="25" t="n">
-        <v>16000000</v>
+        <v>24000000</v>
       </c>
       <c r="F29" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D29),MAX(0,D29-E29),0)</f>
-        <v>24000000</v>
+        <v>16000000</v>
       </c>
       <c r="G29" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D29),ROUNDUP(D29/C29,0),"No limit")</f>
@@ -7898,11 +7898,11 @@
       </c>
       <c r="H29" s="22" t="n">
         <f aca="false">IFERROR(INT(E29/C29),0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29" s="22" t="n">
         <f aca="false">IFERROR(ROUNDUP(F29/C29,0),0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>311</v>
@@ -8390,11 +8390,11 @@
         <v>85000000</v>
       </c>
       <c r="E43" s="25" t="n">
-        <v>17000000</v>
+        <v>34000000</v>
       </c>
       <c r="F43" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D43),MAX(0,D43-E43),0)</f>
-        <v>68000000</v>
+        <v>51000000</v>
       </c>
       <c r="G43" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D43),ROUNDUP(D43/C43,0),"No limit")</f>
@@ -8402,11 +8402,11 @@
       </c>
       <c r="H43" s="22" t="n">
         <f aca="false">IFERROR(INT(E43/C43),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" s="22" t="n">
         <f aca="false">IFERROR(ROUNDUP(F43/C43,0),0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J43" s="11" t="s">
         <v>311</v>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="E49" s="20" t="n">
         <f aca="false">SUM(E5:E47)</f>
-        <v>584651630</v>
+        <v>652301650</v>
       </c>
       <c r="F49" s="20"/>
     </row>
@@ -8573,7 +8573,7 @@
       <c r="E50" s="20"/>
       <c r="F50" s="20" t="n">
         <f aca="false">SUM(F5:F47)</f>
-        <v>7352598370</v>
+        <v>7284948350</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8583,7 +8583,7 @@
       <c r="E51" s="20"/>
       <c r="F51" s="20" t="n">
         <f aca="false">SUMIF(J5:J47,"Yes",F5:F47)</f>
-        <v>5421000000</v>
+        <v>5358000000</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8675,13 +8675,13 @@
         <v>12080000</v>
       </c>
       <c r="C5" s="27" t="n">
-        <v>1530000</v>
+        <v>159500</v>
       </c>
       <c r="D5" s="27" t="n">
-        <v>3960000</v>
+        <v>2590000</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>15550000</v>
+        <v>13420000</v>
       </c>
       <c r="F5" s="27" t="n">
         <v>221</v>
@@ -8736,15 +8736,15 @@
       </c>
       <c r="C7" s="28" t="n">
         <f aca="false">C5+C6</f>
-        <v>5230000</v>
+        <v>3859500</v>
       </c>
       <c r="D7" s="28" t="n">
         <f aca="false">D5+D6</f>
-        <v>7846000</v>
+        <v>6476000</v>
       </c>
       <c r="E7" s="28" t="n">
         <f aca="false">E5+E6</f>
-        <v>19036000</v>
+        <v>16906000</v>
       </c>
       <c r="F7" s="28" t="n">
         <f aca="false">F5+F6</f>
@@ -8769,15 +8769,15 @@
       </c>
       <c r="C8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",C80:C101)</f>
-        <v>1370000</v>
+        <v>0</v>
       </c>
       <c r="D8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",D80:D101)</f>
-        <v>1370000</v>
+        <v>0</v>
       </c>
       <c r="E8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",E80:E101)</f>
-        <v>2130000</v>
+        <v>0</v>
       </c>
       <c r="F8" s="28" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",F80:F101)</f>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="C9" s="29" t="n">
         <f aca="false">C7-C8</f>
-        <v>3860000</v>
+        <v>3859500</v>
       </c>
       <c r="D9" s="29" t="n">
         <f aca="false">D7-D8</f>
@@ -11300,7 +11300,7 @@
         <v>17000000</v>
       </c>
       <c r="J91" s="11" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="K91" s="15" t="s">
         <v>493</v>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="I103" s="20" t="n">
         <f aca="false">SUMIF(J80:J101,"Planned",I80:I101)</f>
-        <v>37000000</v>
+        <v>20000000</v>
       </c>
     </row>
   </sheetData>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>15600301.6147948</v>
+        <v>15649710.6454122</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -5752,7 +5752,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>548207240.6819</v>
+        <v>548219128.227808</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7094,11 +7094,11 @@
         <v>1000000000</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>55951650</v>
+        <v>52951650</v>
       </c>
       <c r="F7" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D7),MAX(0,D7-E7),0)</f>
-        <v>944048350</v>
+        <v>947048350</v>
       </c>
       <c r="G7" s="22" t="n">
         <f aca="false">IF(ISNUMBER(D7),ROUNDUP(D7/C7,0),"No limit")</f>
@@ -7106,11 +7106,11 @@
       </c>
       <c r="H7" s="22" t="n">
         <f aca="false">IFERROR(INT(E7/C7),0)</f>
-        <v>55951650</v>
+        <v>52951650</v>
       </c>
       <c r="I7" s="22" t="n">
         <f aca="false">IFERROR(ROUNDUP(F7/C7,0),0)</f>
-        <v>944048350</v>
+        <v>947048350</v>
       </c>
       <c r="J7" s="11" t="s">
         <v>315</v>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="E49" s="20" t="n">
         <f aca="false">SUM(E5:E47)</f>
-        <v>652301650</v>
+        <v>649301650</v>
       </c>
       <c r="F49" s="20"/>
     </row>
@@ -8573,7 +8573,7 @@
       <c r="E50" s="20"/>
       <c r="F50" s="20" t="n">
         <f aca="false">SUM(F5:F47)</f>
-        <v>7284948350</v>
+        <v>7287948350</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="B11" s="20" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>15649710.6454122</v>
+        <v>15650049.9927477</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -18,7 +18,7 @@
     <sheet name="Iso Fest" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Build Priority'!$A$4:$L$26</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Build Priority'!$A$4:$L$27</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Scoring!$A$4:$J$47</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Tower Roster'!$A$4:$I$44</definedName>
   </definedNames>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1241" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="647">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -232,6 +232,24 @@
     <t xml:space="preserve">5 red stars, 80 of 200 shards. Keep some resources in reserve</t>
   </si>
   <si>
+    <t xml:space="preserve">Jocasta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.I. Avengers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blitz tasks in Iron Vengeance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blitz twice with her for 80M points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power cores for more shards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unlocked Oct 12, 1 of 55 shards to next star. Milestone 48 gives her 7 red stars</t>
+  </si>
+  <si>
     <t xml:space="preserve">Doctor Strange</t>
   </si>
   <si>
@@ -1070,9 +1088,6 @@
   </si>
   <si>
     <t xml:space="preserve">Blitz with Jocasta, 7 yellow stars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jocasta</t>
   </si>
   <si>
     <t xml:space="preserve">Upgrade Jocasta to Gear Tier 21</t>
@@ -2661,7 +2676,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -3135,9 +3150,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>66</v>
@@ -3146,9 +3161,11 @@
         <v>67</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="E16" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="F16" s="4"/>
       <c r="G16" s="7" t="s">
         <v>68</v>
@@ -3157,68 +3174,72 @@
         <v>69</v>
       </c>
       <c r="I16" s="8" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I17" s="8" t="n">
         <v>3000000</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J17" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="K16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="7"/>
       <c r="K17" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="n">
         <v>13</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="F18" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I18" s="8" t="n">
         <v>0</v>
@@ -3227,28 +3248,28 @@
       <c r="K18" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L18" s="9"/>
+      <c r="L18" s="9" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="n">
         <v>13</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="E19" s="4"/>
-      <c r="F19" s="6" t="s">
-        <v>51</v>
-      </c>
+      <c r="F19" s="4"/>
       <c r="G19" s="7"/>
       <c r="H19" s="7" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I19" s="8" t="n">
         <v>0</v>
@@ -3264,10 +3285,10 @@
         <v>13</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>105</v>
@@ -3278,7 +3299,7 @@
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>0</v>
@@ -3287,23 +3308,39 @@
       <c r="K20" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L20" s="9" t="s">
-        <v>77</v>
-      </c>
+      <c r="L20" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="11"/>
+      <c r="A21" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="7"/>
+      <c r="K21" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10"/>
@@ -3375,14 +3412,28 @@
       <c r="K26" s="10"/>
       <c r="L26" s="11"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
-        <v>78</v>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="11"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L26"/>
-  <conditionalFormatting sqref="K5:K26">
+  <autoFilter ref="A4:L27"/>
+  <conditionalFormatting sqref="K5:K27">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Done"</formula>
     </cfRule>
@@ -3391,7 +3442,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K5:K26" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K5:K27" type="list">
       <formula1>"Not started,In progress,Done,Skipped"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3428,12 +3479,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3444,22 +3495,22 @@
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>13</v>
@@ -3476,10 +3527,10 @@
         <v>1739574</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>41</v>
@@ -3490,7 +3541,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>105</v>
@@ -3499,10 +3550,10 @@
         <v>1702227</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="10"/>
@@ -3511,7 +3562,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>105</v>
@@ -3520,10 +3571,10 @@
         <v>1663516</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="10"/>
@@ -3532,7 +3583,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>105</v>
@@ -3541,23 +3592,23 @@
         <v>1649971</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
       <c r="I8" s="14" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>105</v>
@@ -3566,10 +3617,10 @@
         <v>1461088</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="10"/>
@@ -3578,7 +3629,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>100</v>
@@ -3587,10 +3638,10 @@
         <v>1401716</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="10"/>
@@ -3599,7 +3650,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B11" s="11" t="n">
         <v>100</v>
@@ -3608,10 +3659,10 @@
         <v>1341960</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="10"/>
@@ -3620,7 +3671,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B12" s="11" t="n">
         <v>105</v>
@@ -3629,10 +3680,10 @@
         <v>1322529</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="10"/>
@@ -3641,7 +3692,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B13" s="11" t="n">
         <v>105</v>
@@ -3650,10 +3701,10 @@
         <v>1238262</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="10"/>
@@ -3662,7 +3713,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B14" s="11" t="n">
         <v>105</v>
@@ -3671,10 +3722,10 @@
         <v>1095153</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="10"/>
@@ -3683,7 +3734,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B15" s="11" t="n">
         <v>103</v>
@@ -3692,10 +3743,10 @@
         <v>1062491</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="10"/>
@@ -3704,7 +3755,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>105</v>
@@ -3713,10 +3764,10 @@
         <v>1039168</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="10"/>
@@ -3725,7 +3776,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B17" s="11" t="n">
         <v>104</v>
@@ -3734,10 +3785,10 @@
         <v>993737</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="10"/>
@@ -3746,7 +3797,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B18" s="11" t="n">
         <v>100</v>
@@ -3755,10 +3806,10 @@
         <v>946060</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="10"/>
@@ -3767,7 +3818,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B19" s="11" t="n">
         <v>105</v>
@@ -3776,10 +3827,10 @@
         <v>900021</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="10"/>
@@ -3788,7 +3839,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B20" s="11" t="n">
         <v>100</v>
@@ -3797,10 +3848,10 @@
         <v>889970</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="10"/>
@@ -3809,7 +3860,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B21" s="11" t="n">
         <v>100</v>
@@ -3818,10 +3869,10 @@
         <v>867448</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="10"/>
@@ -3830,7 +3881,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B22" s="11" t="n">
         <v>100</v>
@@ -3839,10 +3890,10 @@
         <v>847430</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="10"/>
@@ -3860,10 +3911,10 @@
         <v>827833</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>15</v>
@@ -3871,12 +3922,12 @@
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
       <c r="I23" s="14" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B24" s="11" t="n">
         <v>101</v>
@@ -3885,10 +3936,10 @@
         <v>818549</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="10"/>
@@ -3897,7 +3948,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B25" s="11" t="n">
         <v>103</v>
@@ -3906,10 +3957,10 @@
         <v>787184</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="10"/>
@@ -3918,7 +3969,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B26" s="11" t="n">
         <v>96</v>
@@ -3927,10 +3978,10 @@
         <v>736328</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="10"/>
@@ -3948,10 +3999,10 @@
         <v>731016</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>15</v>
@@ -3959,12 +4010,12 @@
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
       <c r="I27" s="14" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B28" s="11" t="n">
         <v>95</v>
@@ -3973,10 +4024,10 @@
         <v>573611</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F28" s="12"/>
       <c r="G28" s="10"/>
@@ -3985,7 +4036,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B29" s="11" t="n">
         <v>100</v>
@@ -3994,10 +4045,10 @@
         <v>556594</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="10"/>
@@ -4006,7 +4057,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B30" s="11" t="n">
         <v>95</v>
@@ -4015,10 +4066,10 @@
         <v>427837</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="10"/>
@@ -4027,7 +4078,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B31" s="11" t="n">
         <v>90</v>
@@ -4036,10 +4087,10 @@
         <v>334475</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F31" s="12"/>
       <c r="G31" s="10"/>
@@ -4048,7 +4099,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B32" s="11" t="n">
         <v>95</v>
@@ -4057,10 +4108,10 @@
         <v>309062</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="10"/>
@@ -4069,7 +4120,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B33" s="11" t="n">
         <v>90</v>
@@ -4078,10 +4129,10 @@
         <v>305523</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F33" s="12"/>
       <c r="G33" s="10"/>
@@ -4090,7 +4141,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B34" s="11" t="n">
         <v>95</v>
@@ -4099,10 +4150,10 @@
         <v>302615</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F34" s="12"/>
       <c r="G34" s="10"/>
@@ -4111,7 +4162,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B35" s="11" t="n">
         <v>90</v>
@@ -4120,10 +4171,10 @@
         <v>269160</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F35" s="12"/>
       <c r="G35" s="10"/>
@@ -4132,7 +4183,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B36" s="11" t="n">
         <v>80</v>
@@ -4141,10 +4192,10 @@
         <v>250273</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F36" s="12"/>
       <c r="G36" s="10"/>
@@ -4153,7 +4204,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B37" s="11" t="n">
         <v>90</v>
@@ -4162,10 +4213,10 @@
         <v>245993</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="F37" s="12"/>
       <c r="G37" s="10"/>
@@ -4174,7 +4225,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B38" s="11" t="n">
         <v>75</v>
@@ -4183,10 +4234,10 @@
         <v>228686</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F38" s="12"/>
       <c r="G38" s="10"/>
@@ -4195,7 +4246,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B39" s="11" t="n">
         <v>75</v>
@@ -4204,10 +4255,10 @@
         <v>144778</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F39" s="12"/>
       <c r="G39" s="10"/>
@@ -4225,10 +4276,10 @@
         <v>33212</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F40" s="12" t="s">
         <v>15</v>
@@ -4236,7 +4287,7 @@
       <c r="G40" s="10"/>
       <c r="H40" s="10"/>
       <c r="I40" s="14" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4250,10 +4301,10 @@
         <v>32994</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>15</v>
@@ -4273,10 +4324,10 @@
         <v>26827</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F42" s="12" t="s">
         <v>15</v>
@@ -4284,36 +4335,36 @@
       <c r="G42" s="10"/>
       <c r="H42" s="10"/>
       <c r="I42" s="14" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B43" s="11"/>
       <c r="C43" s="13"/>
       <c r="D43" s="11" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E43" s="11"/>
       <c r="F43" s="12" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G43" s="10"/>
       <c r="H43" s="10"/>
       <c r="I43" s="14" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B44" s="11"/>
       <c r="C44" s="13"/>
       <c r="D44" s="11" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E44" s="11"/>
       <c r="F44" s="12"/>
@@ -4323,7 +4374,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B46" s="16" t="n">
         <f aca="false">COUNT(C5:C44)</f>
@@ -4332,7 +4383,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B47" s="16" t="n">
         <f aca="false">COUNTIF(C5:C44,"&gt;=1000000")</f>
@@ -4341,7 +4392,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B48" s="16" t="n">
         <f aca="false">COUNTIF(H5:H44,"Yes")</f>
@@ -4393,17 +4444,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B4" s="17" t="n">
         <v>46332.7083333333</v>
@@ -4411,7 +4462,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>400</v>
@@ -4419,7 +4470,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B6" s="15" t="n">
         <f aca="false">IFERROR(INDEX(A10:A29,MATCH(TRUE(),INDEX(B10:B29&gt;B5,0),0)),"All done")</f>
@@ -4428,7 +4479,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B7" s="19" t="n">
         <f aca="false">IFERROR(INDEX(B10:B29,MATCH(TRUE(),INDEX(B10:B29&gt;B5,0),0))-B5,0)</f>
@@ -4437,19 +4488,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F9" s="20" t="s">
         <v>12</v>
@@ -4463,14 +4514,14 @@
         <v>400</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4481,14 +4532,14 @@
         <v>800</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4499,14 +4550,14 @@
         <v>1200</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E12" s="14"/>
       <c r="F12" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4517,14 +4568,14 @@
         <v>1600</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4535,14 +4586,14 @@
         <v>2000</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E14" s="14"/>
       <c r="F14" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4553,16 +4604,16 @@
         <v>2400</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4573,14 +4624,14 @@
         <v>2800</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E16" s="14"/>
       <c r="F16" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4591,14 +4642,14 @@
         <v>3200</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E17" s="14"/>
       <c r="F17" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4609,14 +4660,14 @@
         <v>3600</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E18" s="14"/>
       <c r="F18" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4627,14 +4678,14 @@
         <v>4000</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E19" s="14"/>
       <c r="F19" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4645,16 +4696,16 @@
         <v>4400</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4665,16 +4716,16 @@
         <v>4800</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4685,16 +4736,16 @@
         <v>5200</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4705,16 +4756,16 @@
         <v>5600</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4725,14 +4776,14 @@
         <v>6000</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E24" s="14"/>
       <c r="F24" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4743,16 +4794,16 @@
         <v>6400</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4763,16 +4814,16 @@
         <v>6800</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4784,11 +4835,11 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E27" s="14"/>
       <c r="F27" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4800,13 +4851,13 @@
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4818,54 +4869,54 @@
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E29" s="14"/>
       <c r="F29" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="22" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>13</v>
@@ -4873,31 +4924,31 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
       <c r="D33" s="10" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="I33" s="23" t="n">
         <f aca="false">SUMIF('Tower Roster'!$A$5:$A$44,D33,'Tower Roster'!$C$5:$C$44)+SUMIF('Tower Roster'!$A$5:$A$44,E33,'Tower Roster'!$C$5:$C$44)+SUMIF('Tower Roster'!$A$5:$A$44,F33,'Tower Roster'!$C$5:$C$44)+SUMIF('Tower Roster'!$A$5:$A$44,G33,'Tower Roster'!$C$5:$C$44)+SUMIF('Tower Roster'!$A$5:$A$44,H33,'Tower Roster'!$C$5:$C$44)</f>
         <v>4789170</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="K33" s="10" t="n">
         <v>1</v>
@@ -4906,7 +4957,7 @@
         <v>400</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5613,7 +5664,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -5675,25 +5726,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>46313.7083333333</v>
@@ -5701,29 +5752,29 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B6" s="18" t="n">
-        <v>649301650</v>
+        <v>666802650</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E6" s="19" t="n">
         <f aca="false">B6+Scoring!F51</f>
-        <v>6007301650</v>
+        <v>6024802650</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B7" s="15" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6))+SUMPRODUCT((B13:B76="")*(F13:F76="Claimed"))</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E7" s="15" t="n">
         <f aca="false">IFERROR(INDEX(A13:A76,MATCH(E6,B13:B76,1)),37)</f>
@@ -5732,14 +5783,14 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B8" s="15" t="n">
         <f aca="false">IFERROR(INDEX(A13:A76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),"All done")</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E8" s="15" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6)*(F13:F76&lt;&gt;"Claimed"))</f>
@@ -5748,46 +5799,46 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(INDEX(E13:E76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),0)</f>
-        <v>10698350</v>
+        <v>23197350</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B10" s="19" t="n">
         <f aca="false">MAX(0,B76-B6)</f>
-        <v>3475698350</v>
+        <v>3458197350</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B11" s="19" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>552748939.953026</v>
+        <v>550168601.469724</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>12</v>
@@ -5799,7 +5850,7 @@
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="11" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="23" t="str">
@@ -5807,7 +5858,7 @@
         <v/>
       </c>
       <c r="F13" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5816,7 +5867,7 @@
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="11" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="23" t="str">
@@ -5824,7 +5875,7 @@
         <v/>
       </c>
       <c r="F14" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5833,7 +5884,7 @@
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="11" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="23" t="str">
@@ -5841,7 +5892,7 @@
         <v/>
       </c>
       <c r="F15" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5850,7 +5901,7 @@
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="11" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="23" t="str">
@@ -5858,7 +5909,7 @@
         <v/>
       </c>
       <c r="F16" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5867,7 +5918,7 @@
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="11" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="23" t="str">
@@ -5875,7 +5926,7 @@
         <v/>
       </c>
       <c r="F17" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5884,7 +5935,7 @@
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="11" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="23" t="str">
@@ -5892,7 +5943,7 @@
         <v/>
       </c>
       <c r="F18" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5901,7 +5952,7 @@
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="11" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="23" t="str">
@@ -5909,7 +5960,7 @@
         <v/>
       </c>
       <c r="F19" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5918,7 +5969,7 @@
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="11" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="23" t="str">
@@ -5926,7 +5977,7 @@
         <v/>
       </c>
       <c r="F20" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5935,7 +5986,7 @@
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="11" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="23" t="str">
@@ -5943,7 +5994,7 @@
         <v/>
       </c>
       <c r="F21" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5952,7 +6003,7 @@
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="11" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="23" t="str">
@@ -5960,7 +6011,7 @@
         <v/>
       </c>
       <c r="F22" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5969,7 +6020,7 @@
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="11" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D23" s="11"/>
       <c r="E23" s="23" t="str">
@@ -5977,7 +6028,7 @@
         <v/>
       </c>
       <c r="F23" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5986,7 +6037,7 @@
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="11" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D24" s="11"/>
       <c r="E24" s="23" t="str">
@@ -5994,7 +6045,7 @@
         <v/>
       </c>
       <c r="F24" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6003,7 +6054,7 @@
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="11" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D25" s="11"/>
       <c r="E25" s="23" t="str">
@@ -6011,7 +6062,7 @@
         <v/>
       </c>
       <c r="F25" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6020,7 +6071,7 @@
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="11" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="D26" s="11"/>
       <c r="E26" s="23" t="str">
@@ -6028,7 +6079,7 @@
         <v/>
       </c>
       <c r="F26" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6037,7 +6088,7 @@
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="11" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="D27" s="11"/>
       <c r="E27" s="23" t="str">
@@ -6045,7 +6096,7 @@
         <v/>
       </c>
       <c r="F27" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6054,7 +6105,7 @@
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="11" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D28" s="11"/>
       <c r="E28" s="23" t="str">
@@ -6062,7 +6113,7 @@
         <v/>
       </c>
       <c r="F28" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6071,7 +6122,7 @@
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="11" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="23" t="str">
@@ -6079,7 +6130,7 @@
         <v/>
       </c>
       <c r="F29" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6088,7 +6139,7 @@
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="11" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D30" s="11"/>
       <c r="E30" s="23" t="str">
@@ -6096,7 +6147,7 @@
         <v/>
       </c>
       <c r="F30" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6105,7 +6156,7 @@
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="11" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D31" s="11"/>
       <c r="E31" s="23" t="str">
@@ -6113,7 +6164,7 @@
         <v/>
       </c>
       <c r="F31" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6122,7 +6173,7 @@
       </c>
       <c r="B32" s="13"/>
       <c r="C32" s="11" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D32" s="11"/>
       <c r="E32" s="23" t="str">
@@ -6130,7 +6181,7 @@
         <v/>
       </c>
       <c r="F32" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6139,7 +6190,7 @@
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="11" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="D33" s="11"/>
       <c r="E33" s="23" t="str">
@@ -6147,7 +6198,7 @@
         <v/>
       </c>
       <c r="F33" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6156,7 +6207,7 @@
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="11" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="D34" s="11"/>
       <c r="E34" s="23" t="str">
@@ -6164,7 +6215,7 @@
         <v/>
       </c>
       <c r="F34" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6173,7 +6224,7 @@
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="11" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D35" s="11"/>
       <c r="E35" s="23" t="str">
@@ -6181,7 +6232,7 @@
         <v/>
       </c>
       <c r="F35" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6190,7 +6241,7 @@
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="11" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D36" s="11"/>
       <c r="E36" s="23" t="str">
@@ -6198,7 +6249,7 @@
         <v/>
       </c>
       <c r="F36" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6207,7 +6258,7 @@
       </c>
       <c r="B37" s="13"/>
       <c r="C37" s="11" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D37" s="11"/>
       <c r="E37" s="23" t="str">
@@ -6215,7 +6266,7 @@
         <v/>
       </c>
       <c r="F37" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6224,7 +6275,7 @@
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="11" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D38" s="11"/>
       <c r="E38" s="23" t="str">
@@ -6232,7 +6283,7 @@
         <v/>
       </c>
       <c r="F38" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6241,7 +6292,7 @@
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="11" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D39" s="11"/>
       <c r="E39" s="23" t="str">
@@ -6249,7 +6300,7 @@
         <v/>
       </c>
       <c r="F39" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6258,7 +6309,7 @@
       </c>
       <c r="B40" s="13"/>
       <c r="C40" s="11" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D40" s="11"/>
       <c r="E40" s="23" t="str">
@@ -6266,7 +6317,7 @@
         <v/>
       </c>
       <c r="F40" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6275,7 +6326,7 @@
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="11" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D41" s="11"/>
       <c r="E41" s="23" t="str">
@@ -6283,7 +6334,7 @@
         <v/>
       </c>
       <c r="F41" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6293,14 +6344,14 @@
       <c r="B42" s="13"/>
       <c r="C42" s="11"/>
       <c r="D42" s="11" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E42" s="23" t="str">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
         <v/>
       </c>
       <c r="F42" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6310,14 +6361,14 @@
       <c r="B43" s="13"/>
       <c r="C43" s="11"/>
       <c r="D43" s="11" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E43" s="23" t="str">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
         <v/>
       </c>
       <c r="F43" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6327,14 +6378,14 @@
       <c r="B44" s="13"/>
       <c r="C44" s="11"/>
       <c r="D44" s="11" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E44" s="23" t="str">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
         <v/>
       </c>
       <c r="F44" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6344,14 +6395,14 @@
       <c r="B45" s="13"/>
       <c r="C45" s="11"/>
       <c r="D45" s="11" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E45" s="23" t="str">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
         <v/>
       </c>
       <c r="F45" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6360,7 +6411,7 @@
       </c>
       <c r="B46" s="13"/>
       <c r="C46" s="11" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D46" s="11"/>
       <c r="E46" s="23" t="str">
@@ -6368,7 +6419,7 @@
         <v/>
       </c>
       <c r="F46" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6377,7 +6428,7 @@
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="11" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D47" s="11"/>
       <c r="E47" s="23" t="str">
@@ -6385,7 +6436,7 @@
         <v/>
       </c>
       <c r="F47" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6394,7 +6445,7 @@
       </c>
       <c r="B48" s="13"/>
       <c r="C48" s="11" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D48" s="11"/>
       <c r="E48" s="23" t="str">
@@ -6402,7 +6453,7 @@
         <v/>
       </c>
       <c r="F48" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6411,7 +6462,7 @@
       </c>
       <c r="B49" s="13"/>
       <c r="C49" s="11" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D49" s="11"/>
       <c r="E49" s="23" t="str">
@@ -6419,7 +6470,7 @@
         <v/>
       </c>
       <c r="F49" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6430,7 +6481,7 @@
         <v>435000000</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D50" s="11"/>
       <c r="E50" s="23" t="n">
@@ -6438,7 +6489,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6449,7 +6500,7 @@
         <v>450000000</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D51" s="11"/>
       <c r="E51" s="23" t="n">
@@ -6457,7 +6508,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6468,7 +6519,7 @@
         <v>480000000</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D52" s="11"/>
       <c r="E52" s="23" t="n">
@@ -6476,7 +6527,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6487,17 +6538,17 @@
         <v>510000000</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="E53" s="23" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
         <v>0</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6508,7 +6559,7 @@
         <v>540000000</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D54" s="11"/>
       <c r="E54" s="23" t="n">
@@ -6516,7 +6567,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6527,7 +6578,7 @@
         <v>570000000</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="D55" s="11"/>
       <c r="E55" s="23" t="n">
@@ -6535,7 +6586,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6546,7 +6597,7 @@
         <v>600000000</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D56" s="11"/>
       <c r="E56" s="23" t="n">
@@ -6554,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6565,7 +6616,7 @@
         <v>630000000</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D57" s="11"/>
       <c r="E57" s="23" t="n">
@@ -6573,7 +6624,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6584,15 +6635,15 @@
         <v>660000000</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D58" s="11"/>
       <c r="E58" s="23" t="n">
         <f aca="false">IF(B58="","",MAX(0,B58-$B$6))</f>
-        <v>10698350</v>
+        <v>0</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6603,15 +6654,15 @@
         <v>690000000</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="23" t="n">
         <f aca="false">IF(B59="","",MAX(0,B59-$B$6))</f>
-        <v>40698350</v>
+        <v>23197350</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6622,15 +6673,15 @@
         <v>750000000</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D60" s="11"/>
       <c r="E60" s="23" t="n">
         <f aca="false">IF(B60="","",MAX(0,B60-$B$6))</f>
-        <v>100698350</v>
+        <v>83197350</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6641,15 +6692,15 @@
         <v>825000000</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D61" s="11"/>
       <c r="E61" s="23" t="n">
         <f aca="false">IF(B61="","",MAX(0,B61-$B$6))</f>
-        <v>175698350</v>
+        <v>158197350</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6660,15 +6711,15 @@
         <v>900000000</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="D62" s="11"/>
       <c r="E62" s="23" t="n">
         <f aca="false">IF(B62="","",MAX(0,B62-$B$6))</f>
-        <v>250698350</v>
+        <v>233197350</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6679,15 +6730,15 @@
         <v>975000000</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D63" s="11"/>
       <c r="E63" s="23" t="n">
         <f aca="false">IF(B63="","",MAX(0,B63-$B$6))</f>
-        <v>325698350</v>
+        <v>308197350</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6698,15 +6749,15 @@
         <v>1050000000</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D64" s="11"/>
       <c r="E64" s="23" t="n">
         <f aca="false">IF(B64="","",MAX(0,B64-$B$6))</f>
-        <v>400698350</v>
+        <v>383197350</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6717,15 +6768,15 @@
         <v>1125000000</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="D65" s="11"/>
       <c r="E65" s="23" t="n">
         <f aca="false">IF(B65="","",MAX(0,B65-$B$6))</f>
-        <v>475698350</v>
+        <v>458197350</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6736,15 +6787,15 @@
         <v>1200000000</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D66" s="11"/>
       <c r="E66" s="23" t="n">
         <f aca="false">IF(B66="","",MAX(0,B66-$B$6))</f>
-        <v>550698350</v>
+        <v>533197350</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6755,15 +6806,15 @@
         <v>1350000000</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="23" t="n">
         <f aca="false">IF(B67="","",MAX(0,B67-$B$6))</f>
-        <v>700698350</v>
+        <v>683197350</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6774,15 +6825,15 @@
         <v>1500000000</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D68" s="11"/>
       <c r="E68" s="23" t="n">
         <f aca="false">IF(B68="","",MAX(0,B68-$B$6))</f>
-        <v>850698350</v>
+        <v>833197350</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6793,15 +6844,15 @@
         <v>1650000000</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="23" t="n">
         <f aca="false">IF(B69="","",MAX(0,B69-$B$6))</f>
-        <v>1000698350</v>
+        <v>983197350</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6812,15 +6863,15 @@
         <v>1875000000</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="D70" s="11"/>
       <c r="E70" s="23" t="n">
         <f aca="false">IF(B70="","",MAX(0,B70-$B$6))</f>
-        <v>1225698350</v>
+        <v>1208197350</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6831,15 +6882,15 @@
         <v>2250000000</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D71" s="11"/>
       <c r="E71" s="23" t="n">
         <f aca="false">IF(B71="","",MAX(0,B71-$B$6))</f>
-        <v>1600698350</v>
+        <v>1583197350</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6850,15 +6901,15 @@
         <v>2625000000</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="D72" s="11"/>
       <c r="E72" s="23" t="n">
         <f aca="false">IF(B72="","",MAX(0,B72-$B$6))</f>
-        <v>1975698350</v>
+        <v>1958197350</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6869,15 +6920,15 @@
         <v>3000000000</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D73" s="11"/>
       <c r="E73" s="23" t="n">
         <f aca="false">IF(B73="","",MAX(0,B73-$B$6))</f>
-        <v>2350698350</v>
+        <v>2333197350</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6888,15 +6939,15 @@
         <v>3375000000</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D74" s="11"/>
       <c r="E74" s="23" t="n">
         <f aca="false">IF(B74="","",MAX(0,B74-$B$6))</f>
-        <v>2725698350</v>
+        <v>2708197350</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6907,15 +6958,15 @@
         <v>3750000000</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="D75" s="11"/>
       <c r="E75" s="23" t="n">
         <f aca="false">IF(B75="","",MAX(0,B75-$B$6))</f>
-        <v>3100698350</v>
+        <v>3083197350</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6926,15 +6977,15 @@
         <v>4125000000</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D76" s="11"/>
       <c r="E76" s="23" t="n">
         <f aca="false">IF(B76="","",MAX(0,B76-$B$6))</f>
-        <v>3475698350</v>
+        <v>3458197350</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6986,52 +7037,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>4000000</v>
@@ -7059,15 +7110,15 @@
         <v>6</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>4000000</v>
@@ -7095,15 +7146,15 @@
         <v>7</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>1</v>
@@ -7112,11 +7163,11 @@
         <v>1000000000</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>52951650</v>
+        <v>52952650</v>
       </c>
       <c r="F7" s="21" t="n">
         <f aca="false">IF(ISNUMBER(D7),MAX(0,D7-E7),0)</f>
-        <v>947048350</v>
+        <v>947047350</v>
       </c>
       <c r="G7" s="21" t="n">
         <f aca="false">IF(ISNUMBER(D7),ROUNDUP(D7/C7,0),"No limit")</f>
@@ -7124,22 +7175,22 @@
       </c>
       <c r="H7" s="21" t="n">
         <f aca="false">IFERROR(INT(E7/C7),0)</f>
-        <v>52951650</v>
+        <v>52952650</v>
       </c>
       <c r="I7" s="21" t="n">
         <f aca="false">IFERROR(ROUNDUP(F7/C7,0),0)</f>
-        <v>947048350</v>
+        <v>947047350</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>4000</v>
@@ -7148,11 +7199,11 @@
         <v>1000000000</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>17100000</v>
+        <v>34600000</v>
       </c>
       <c r="F8" s="21" t="n">
         <f aca="false">IF(ISNUMBER(D8),MAX(0,D8-E8),0)</f>
-        <v>982900000</v>
+        <v>965400000</v>
       </c>
       <c r="G8" s="21" t="n">
         <f aca="false">IF(ISNUMBER(D8),ROUNDUP(D8/C8,0),"No limit")</f>
@@ -7160,14 +7211,14 @@
       </c>
       <c r="H8" s="21" t="n">
         <f aca="false">IFERROR(INT(E8/C8),0)</f>
-        <v>4275</v>
+        <v>8650</v>
       </c>
       <c r="I8" s="21" t="n">
         <f aca="false">IFERROR(ROUNDUP(F8/C8,0),0)</f>
-        <v>245725</v>
+        <v>241350</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7175,7 +7226,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>3000000</v>
@@ -7203,7 +7254,7 @@
         <v>2</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7211,7 +7262,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>8000000</v>
@@ -7239,15 +7290,15 @@
         <v>5</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>7000000</v>
@@ -7275,15 +7326,15 @@
         <v>0</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>17000000</v>
@@ -7311,15 +7362,15 @@
         <v>0</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>7000000</v>
@@ -7347,15 +7398,15 @@
         <v>0</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>17000000</v>
@@ -7383,15 +7434,15 @@
         <v>5</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C15" s="13" t="n">
         <v>7000000</v>
@@ -7419,15 +7470,15 @@
         <v>0</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>17000000</v>
@@ -7455,15 +7506,15 @@
         <v>5</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>3000000</v>
@@ -7491,15 +7542,15 @@
         <v>0</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>8000000</v>
@@ -7527,15 +7578,15 @@
         <v>0</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>3000000</v>
@@ -7563,15 +7614,15 @@
         <v>0</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>8000000</v>
@@ -7599,15 +7650,15 @@
         <v>0</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>3000000</v>
@@ -7635,15 +7686,15 @@
         <v>1</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>8000000</v>
@@ -7671,15 +7722,15 @@
         <v>1</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>3000000</v>
@@ -7707,15 +7758,15 @@
         <v>1</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>8000000</v>
@@ -7743,15 +7794,15 @@
         <v>2</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>8000000</v>
@@ -7779,15 +7830,15 @@
         <v>1</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>17000000</v>
@@ -7815,15 +7866,15 @@
         <v>5</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>8000000</v>
@@ -7851,15 +7902,15 @@
         <v>1</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>17000000</v>
@@ -7887,15 +7938,15 @@
         <v>5</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>8000000</v>
@@ -7923,15 +7974,15 @@
         <v>2</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>17000000</v>
@@ -7959,15 +8010,15 @@
         <v>5</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>40000000</v>
@@ -7995,15 +8046,15 @@
         <v>2</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>80000000</v>
@@ -8031,15 +8082,15 @@
         <v>2</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>150000000</v>
@@ -8067,15 +8118,15 @@
         <v>2</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>346</v>
+        <v>66</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>200000000</v>
@@ -8103,15 +8154,15 @@
         <v>1</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>346</v>
+        <v>66</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>200000000</v>
@@ -8139,15 +8190,15 @@
         <v>1</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>17000000</v>
@@ -8175,15 +8226,15 @@
         <v>5</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>150000000</v>
@@ -8211,15 +8262,15 @@
         <v>5</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C38" s="13" t="n">
         <v>17000000</v>
@@ -8247,15 +8298,15 @@
         <v>5</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C39" s="13" t="n">
         <v>50000000</v>
@@ -8283,15 +8334,15 @@
         <v>5</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C40" s="13" t="n">
         <v>150000000</v>
@@ -8319,15 +8370,15 @@
         <v>5</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C41" s="13" t="n">
         <v>17000000</v>
@@ -8355,15 +8406,15 @@
         <v>5</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C42" s="13" t="n">
         <v>150000000</v>
@@ -8391,15 +8442,15 @@
         <v>5</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C43" s="13" t="n">
         <v>17000000</v>
@@ -8427,15 +8478,15 @@
         <v>3</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C44" s="13" t="n">
         <v>50000000</v>
@@ -8463,15 +8514,15 @@
         <v>5</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C45" s="13" t="n">
         <v>150000000</v>
@@ -8499,15 +8550,15 @@
         <v>5</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C46" s="13" t="n">
         <v>4500000</v>
@@ -8535,21 +8586,21 @@
         <v>6</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C47" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="E47" s="24" t="n">
         <v>40250000</v>
@@ -8571,32 +8622,32 @@
         <v>0</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="15" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="E49" s="19" t="n">
         <f aca="false">SUM(E5:E47)</f>
-        <v>649301650</v>
+        <v>666802650</v>
       </c>
       <c r="F49" s="19"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="15" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="E50" s="19"/>
       <c r="F50" s="19" t="n">
         <f aca="false">SUM(F5:F47)</f>
-        <v>7287948350</v>
+        <v>7270447350</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="15" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E51" s="19"/>
       <c r="F51" s="19" t="n">
@@ -8606,7 +8657,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="2" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -8651,46 +8702,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>12080000</v>
+        <v>12130000</v>
       </c>
       <c r="C5" s="26" t="n">
         <v>159500</v>
@@ -8713,7 +8764,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B6" s="27" t="n">
         <f aca="false">SUMIFS(B13:B76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
@@ -8746,11 +8797,11 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
-        <v>39130000</v>
+        <v>39180000</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">C5+C6</f>
@@ -8779,7 +8830,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B8" s="27" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",B80:B101)</f>
@@ -8812,11 +8863,11 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B7-B8</f>
-        <v>39130000</v>
+        <v>39180000</v>
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">C7-C8</f>
@@ -8845,44 +8896,44 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>13</v>
@@ -8890,7 +8941,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B13" s="29" t="n">
         <v>100000</v>
@@ -8914,18 +8965,18 @@
         <v>0</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="B14" s="29" t="n">
         <v>1600000</v>
@@ -8949,18 +9000,18 @@
         <v>0</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B15" s="29" t="n">
         <v>1600000</v>
@@ -8984,18 +9035,18 @@
         <v>0</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B16" s="29" t="n">
         <v>1600000</v>
@@ -9019,18 +9070,18 @@
         <v>0</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B17" s="29" t="n">
         <v>1600000</v>
@@ -9054,18 +9105,18 @@
         <v>0</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B18" s="29" t="n">
         <v>1600000</v>
@@ -9089,18 +9140,18 @@
         <v>0</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B19" s="29" t="n">
         <v>1600000</v>
@@ -9124,18 +9175,18 @@
         <v>0</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B20" s="29" t="n">
         <v>1600000</v>
@@ -9159,18 +9210,18 @@
         <v>0</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B21" s="29" t="n">
         <v>100000</v>
@@ -9194,16 +9245,16 @@
         <v>0</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B22" s="29" t="n">
         <v>200000</v>
@@ -9227,16 +9278,16 @@
         <v>0</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B23" s="29" t="n">
         <v>0</v>
@@ -9260,18 +9311,18 @@
         <v>0</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B24" s="29" t="n">
         <v>150000</v>
@@ -9295,16 +9346,16 @@
         <v>15</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="K24" s="14"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B25" s="29" t="n">
         <v>150000</v>
@@ -9328,16 +9379,16 @@
         <v>20</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="K25" s="14"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B26" s="29" t="n">
         <v>200000</v>
@@ -9361,16 +9412,16 @@
         <v>25</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="K26" s="14"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B27" s="29" t="n">
         <v>250000</v>
@@ -9394,16 +9445,16 @@
         <v>30</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="K27" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B28" s="29" t="n">
         <v>300000</v>
@@ -9427,16 +9478,16 @@
         <v>40</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K28" s="14"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B29" s="29" t="n">
         <v>350000</v>
@@ -9460,16 +9511,16 @@
         <v>45</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K29" s="14"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B30" s="29" t="n">
         <v>0</v>
@@ -9493,18 +9544,18 @@
         <v>0</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B31" s="29" t="n">
         <v>0</v>
@@ -9528,18 +9579,18 @@
         <v>0</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B32" s="29" t="n">
         <v>0</v>
@@ -9563,18 +9614,18 @@
         <v>0</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B33" s="29" t="n">
         <v>0</v>
@@ -9598,16 +9649,16 @@
         <v>800</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K33" s="14"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B34" s="29" t="n">
         <v>10000000</v>
@@ -9631,16 +9682,16 @@
         <v>0</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K34" s="14"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B35" s="29" t="n">
         <v>500000</v>
@@ -9664,16 +9715,16 @@
         <v>0</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K35" s="14"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B36" s="29" t="n">
         <v>0</v>
@@ -9697,18 +9748,18 @@
         <v>0</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K36" s="14" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B37" s="29" t="n">
         <v>0</v>
@@ -9732,18 +9783,18 @@
         <v>0</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K37" s="14" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B38" s="29" t="n">
         <v>0</v>
@@ -9767,18 +9818,18 @@
         <v>0</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B39" s="29" t="n">
         <v>0</v>
@@ -9802,16 +9853,16 @@
         <v>0</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K39" s="14"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B40" s="29" t="n">
         <v>0</v>
@@ -9835,18 +9886,18 @@
         <v>0</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K40" s="14" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B41" s="29" t="n">
         <v>0</v>
@@ -9870,18 +9921,18 @@
         <v>0</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K41" s="14" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B42" s="29" t="n">
         <v>0</v>
@@ -9905,18 +9956,18 @@
         <v>500</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K42" s="14" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="B43" s="29" t="n">
         <v>0</v>
@@ -9940,18 +9991,18 @@
         <v>500</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K43" s="14" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="B44" s="29" t="n">
         <v>0</v>
@@ -9975,18 +10026,18 @@
         <v>1000</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K44" s="14" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B45" s="29" t="n">
         <v>0</v>
@@ -10010,18 +10061,18 @@
         <v>0</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K45" s="14" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B46" s="29" t="n">
         <v>0</v>
@@ -10045,18 +10096,18 @@
         <v>0</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K46" s="14" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B47" s="29" t="n">
         <v>900000</v>
@@ -10080,18 +10131,18 @@
         <v>0</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K47" s="14" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B48" s="29" t="n">
         <v>0</v>
@@ -10115,27 +10166,27 @@
         <v>90</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K48" s="14" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B49" s="29" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="E49" s="29" t="n">
         <v>3300000</v>
@@ -10153,7 +10204,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="K49" s="14" t="n">
         <v>0</v>
@@ -10161,7 +10212,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="B50" s="29" t="n">
         <v>3300000</v>
@@ -10185,18 +10236,18 @@
         <v>0</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="K50" s="14" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B51" s="29" t="n">
         <v>0</v>
@@ -10220,18 +10271,18 @@
         <v>0</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K51" s="14" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B52" s="29" t="n">
         <v>0</v>
@@ -10255,18 +10306,18 @@
         <v>0</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K52" s="14" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="11" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B53" s="29" t="n">
         <v>0</v>
@@ -10290,18 +10341,18 @@
         <v>0</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K53" s="14" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B54" s="29" t="n">
         <v>750000</v>
@@ -10325,18 +10376,18 @@
         <v>0</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K54" s="14" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B55" s="29" t="n">
         <v>750000</v>
@@ -10360,18 +10411,18 @@
         <v>0</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K55" s="14" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="11" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B56" s="29" t="n">
         <v>750000</v>
@@ -10395,18 +10446,18 @@
         <v>0</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K56" s="14" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="11" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B57" s="29" t="n">
         <v>750000</v>
@@ -10430,18 +10481,18 @@
         <v>0</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K57" s="14" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B58" s="29" t="n">
         <v>750000</v>
@@ -10465,18 +10516,18 @@
         <v>0</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J58" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K58" s="14" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B59" s="29" t="n">
         <v>750000</v>
@@ -10500,18 +10551,18 @@
         <v>0</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K59" s="14" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B60" s="29" t="n">
         <v>750000</v>
@@ -10535,18 +10586,18 @@
         <v>0</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K60" s="14" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="11" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B61" s="29" t="n">
         <v>750000</v>
@@ -10570,18 +10621,18 @@
         <v>0</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K61" s="14" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B62" s="29" t="n">
         <v>0</v>
@@ -10605,18 +10656,18 @@
         <v>0</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K62" s="14" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B63" s="29" t="n">
         <v>0</v>
@@ -10640,18 +10691,18 @@
         <v>0</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K63" s="14" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="11" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B64" s="29" t="n">
         <v>178025</v>
@@ -10675,18 +10726,18 @@
         <v>0</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="K64" s="14" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="11" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B65" s="29" t="n">
         <v>120000</v>
@@ -10710,18 +10761,18 @@
         <v>0</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="K65" s="14" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B66" s="29" t="n">
         <v>375000</v>
@@ -10745,13 +10796,13 @@
         <v>0</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="K66" s="14" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10886,33 +10937,33 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="22" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>10</v>
@@ -10926,7 +10977,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="11" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B80" s="29" t="n">
         <v>1837500</v>
@@ -10953,15 +11004,15 @@
         <v>0</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K80" s="14" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="11" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B81" s="29" t="n">
         <v>0</v>
@@ -10988,13 +11039,13 @@
         <v>0</v>
       </c>
       <c r="J81" s="10" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K81" s="14"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="11" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B82" s="29" t="n">
         <v>9791250</v>
@@ -11021,15 +11072,15 @@
         <v>55000000</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K82" s="14" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="11" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B83" s="29" t="n">
         <v>0</v>
@@ -11056,15 +11107,15 @@
         <v>0</v>
       </c>
       <c r="J83" s="10" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K83" s="14" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="11" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B84" s="26"/>
       <c r="C84" s="29" t="n">
@@ -11083,15 +11134,15 @@
         <v>3000000</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="K84" s="14" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="11" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B85" s="26"/>
       <c r="C85" s="29" t="n">
@@ -11110,15 +11161,15 @@
         <v>3000000</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="K85" s="14" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="11" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B86" s="29" t="n">
         <v>1650010</v>
@@ -11145,15 +11196,15 @@
         <v>3000000</v>
       </c>
       <c r="J86" s="10" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K86" s="14" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="11" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B87" s="29" t="n">
         <v>1650000</v>
@@ -11180,15 +11231,15 @@
         <v>3000000</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K87" s="14" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="11" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B88" s="29" t="n">
         <v>1650000</v>
@@ -11215,15 +11266,15 @@
         <v>3000000</v>
       </c>
       <c r="J88" s="10" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="K88" s="14" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="11" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B89" s="26"/>
       <c r="C89" s="29" t="n">
@@ -11248,15 +11299,15 @@
         <v>17000000</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="K89" s="14" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="11" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B90" s="29" t="n">
         <v>0</v>
@@ -11283,15 +11334,15 @@
         <v>17000000</v>
       </c>
       <c r="J90" s="10" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K90" s="14" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="11" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B91" s="29" t="n">
         <v>0</v>
@@ -11318,15 +11369,15 @@
         <v>17000000</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K91" s="14" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="11" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B92" s="29" t="n">
         <v>0</v>
@@ -11347,15 +11398,15 @@
         <v>17000000</v>
       </c>
       <c r="J92" s="10" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="K92" s="14" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="11" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B93" s="29" t="n">
         <v>0</v>
@@ -11376,15 +11427,15 @@
         <v>17000000</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="K93" s="14" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="11" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B94" s="29" t="n">
         <v>0</v>
@@ -11405,15 +11456,15 @@
         <v>17000000</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="K94" s="14" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="11" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B95" s="29" t="n">
         <v>13000000</v>
@@ -11434,10 +11485,10 @@
         <v>8000000</v>
       </c>
       <c r="J95" s="10" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="K95" s="14" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11520,7 +11571,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="15" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="I103" s="19" t="n">
         <f aca="false">SUMIF(J80:J101,"Planned",I80:I101)</f>
@@ -11579,75 +11630,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G6" s="31"/>
       <c r="H6" s="31"/>
@@ -11658,22 +11709,22 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C7" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G7" s="31"/>
       <c r="H7" s="31"/>
@@ -11684,22 +11735,22 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G8" s="31"/>
       <c r="H8" s="31"/>
@@ -11710,22 +11761,22 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G9" s="31"/>
       <c r="H9" s="31"/>
@@ -11736,22 +11787,22 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G10" s="31"/>
       <c r="H10" s="31"/>
@@ -11762,22 +11813,22 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G11" s="31"/>
       <c r="H11" s="31"/>
@@ -11788,22 +11839,22 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G12" s="31"/>
       <c r="H12" s="31"/>
@@ -11814,22 +11865,22 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G13" s="31"/>
       <c r="H13" s="31"/>
@@ -11840,22 +11891,22 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G14" s="31"/>
       <c r="H14" s="31"/>
@@ -11866,22 +11917,22 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G15" s="31"/>
       <c r="H15" s="31"/>
@@ -11892,22 +11943,22 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G16" s="31"/>
       <c r="H16" s="31"/>
@@ -11918,20 +11969,20 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G17" s="31"/>
       <c r="H17" s="31"/>
@@ -11942,22 +11993,22 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G18" s="31"/>
       <c r="H18" s="31"/>
@@ -11968,22 +12019,22 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G19" s="31"/>
       <c r="H19" s="31"/>
@@ -11994,22 +12045,22 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G20" s="31"/>
       <c r="H20" s="31"/>
@@ -12020,24 +12071,24 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="30" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F22" s="31"/>
       <c r="G22" s="31"/>
@@ -12049,16 +12100,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C23" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="E23" s="31"/>
       <c r="F23" s="31"/>
@@ -12071,16 +12122,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
@@ -12093,22 +12144,22 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
@@ -12119,19 +12170,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C26" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F26" s="31"/>
       <c r="G26" s="31"/>
@@ -12143,16 +12194,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="E27" s="31"/>
       <c r="F27" s="31"/>
@@ -12165,16 +12216,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C28" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="E28" s="31"/>
       <c r="F28" s="31"/>
@@ -12187,21 +12238,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="30" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="E30" s="31"/>
       <c r="F30" s="31"/>
@@ -12214,16 +12265,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C31" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="E31" s="31"/>
       <c r="F31" s="31"/>
@@ -12236,16 +12287,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C32" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="E32" s="31"/>
       <c r="F32" s="31"/>
@@ -12258,19 +12309,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C33" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F33" s="31"/>
       <c r="G33" s="31"/>
@@ -12282,16 +12333,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C34" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="E34" s="31"/>
       <c r="F34" s="31"/>
@@ -12304,16 +12355,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C35" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E35" s="31"/>
       <c r="F35" s="31"/>
@@ -12326,16 +12377,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C36" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E36" s="31"/>
       <c r="F36" s="31"/>
@@ -12348,16 +12399,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="E37" s="31"/>
       <c r="F37" s="31"/>
@@ -12370,16 +12421,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C38" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="E38" s="31"/>
       <c r="F38" s="31"/>
@@ -12392,7 +12443,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="E40" s="19" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$38)*(E5:E38="Done"))</f>
@@ -12429,7 +12480,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="E41" s="32" t="str">
         <f aca="false">COUNTIFS($B$5:$B$38,"Required",E5:E38,"Done")&amp;" of 11"</f>
@@ -12466,7 +12517,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
   </sheetData>
@@ -12510,51 +12561,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B6" s="18" t="n">
-        <v>325778995</v>
+        <v>330153995</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="E6" s="19" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -12571,14 +12622,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B7" s="15" t="n">
         <f aca="false">IFERROR(INDEX(A13:A54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),"All done")</f>
         <v>17</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E7" s="19" t="n">
         <f aca="false">SUMPRODUCT((B13:B54&lt;&gt;"")*(B13:B54&lt;=$B$6)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -12595,16 +12646,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B8" s="19" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>24221005</v>
+        <v>19846005</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B9" s="33" t="n">
         <v>20</v>
@@ -12612,49 +12663,49 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="B10" s="19" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>99221005</v>
+        <v>94846005</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="B11" s="19" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>15779362.855067</v>
+        <v>15089160.2513664</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>593</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>588</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12664,7 +12715,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="E13" s="29" t="n">
         <v>0</v>
@@ -12676,7 +12727,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I13" s="23" t="str">
         <f aca="false">IF(B13="","",MAX(0,B13-$B$6))</f>
@@ -12690,7 +12741,7 @@
       <c r="B14" s="26"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="E14" s="29" t="n">
         <v>0</v>
@@ -12702,7 +12753,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I14" s="23" t="str">
         <f aca="false">IF(B14="","",MAX(0,B14-$B$6))</f>
@@ -12716,7 +12767,7 @@
       <c r="B15" s="26"/>
       <c r="C15" s="11"/>
       <c r="D15" s="11" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="E15" s="29" t="n">
         <v>0</v>
@@ -12728,7 +12779,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I15" s="23" t="str">
         <f aca="false">IF(B15="","",MAX(0,B15-$B$6))</f>
@@ -12742,7 +12793,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="E16" s="29" t="n">
         <v>0</v>
@@ -12754,7 +12805,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I16" s="23" t="str">
         <f aca="false">IF(B16="","",MAX(0,B16-$B$6))</f>
@@ -12767,10 +12818,10 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="11" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="E17" s="29" t="n">
         <v>0</v>
@@ -12782,7 +12833,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I17" s="23" t="str">
         <f aca="false">IF(B17="","",MAX(0,B17-$B$6))</f>
@@ -12795,10 +12846,10 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="11" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="E18" s="29" t="n">
         <v>0</v>
@@ -12810,7 +12861,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I18" s="23" t="str">
         <f aca="false">IF(B18="","",MAX(0,B18-$B$6))</f>
@@ -12823,10 +12874,10 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="11" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="E19" s="29" t="n">
         <v>0</v>
@@ -12838,7 +12889,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I19" s="23" t="str">
         <f aca="false">IF(B19="","",MAX(0,B19-$B$6))</f>
@@ -12851,10 +12902,10 @@
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="11" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="E20" s="29" t="n">
         <v>0</v>
@@ -12866,7 +12917,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I20" s="23" t="str">
         <f aca="false">IF(B20="","",MAX(0,B20-$B$6))</f>
@@ -12879,10 +12930,10 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="11" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="E21" s="29" t="n">
         <v>0</v>
@@ -12894,7 +12945,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I21" s="23" t="str">
         <f aca="false">IF(B21="","",MAX(0,B21-$B$6))</f>
@@ -12907,10 +12958,10 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="11" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="E22" s="29" t="n">
         <v>0</v>
@@ -12922,7 +12973,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I22" s="23" t="str">
         <f aca="false">IF(B22="","",MAX(0,B22-$B$6))</f>
@@ -12936,7 +12987,7 @@
       <c r="B23" s="26"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="E23" s="29" t="n">
         <v>900000</v>
@@ -12948,7 +12999,7 @@
         <v>1900000</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I23" s="23" t="str">
         <f aca="false">IF(B23="","",MAX(0,B23-$B$6))</f>
@@ -12961,10 +13012,10 @@
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="11" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E24" s="29" t="n">
         <v>900000</v>
@@ -12976,7 +13027,7 @@
         <v>1900000</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I24" s="23" t="str">
         <f aca="false">IF(B24="","",MAX(0,B24-$B$6))</f>
@@ -12989,10 +13040,10 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="11" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E25" s="29" t="n">
         <v>0</v>
@@ -13004,7 +13055,7 @@
         <v>1900000</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I25" s="23" t="str">
         <f aca="false">IF(B25="","",MAX(0,B25-$B$6))</f>
@@ -13017,10 +13068,10 @@
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="11" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E26" s="29" t="n">
         <v>900000</v>
@@ -13032,7 +13083,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I26" s="23" t="str">
         <f aca="false">IF(B26="","",MAX(0,B26-$B$6))</f>
@@ -13048,7 +13099,7 @@
       </c>
       <c r="C27" s="11"/>
       <c r="D27" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E27" s="29" t="n">
         <v>900000</v>
@@ -13060,7 +13111,7 @@
         <v>1900000</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I27" s="23" t="n">
         <f aca="false">IF(B27="","",MAX(0,B27-$B$6))</f>
@@ -13075,10 +13126,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E28" s="29" t="n">
         <v>950000</v>
@@ -13090,7 +13141,7 @@
         <v>1900000</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I28" s="23" t="n">
         <f aca="false">IF(B28="","",MAX(0,B28-$B$6))</f>
@@ -13105,10 +13156,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E29" s="29" t="n">
         <v>0</v>
@@ -13120,11 +13171,11 @@
         <v>1900000</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I29" s="23" t="n">
         <f aca="false">IF(B29="","",MAX(0,B29-$B$6))</f>
-        <v>24221005</v>
+        <v>19846005</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13135,20 +13186,20 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
       <c r="G30" s="26"/>
       <c r="H30" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I30" s="23" t="n">
         <f aca="false">IF(B30="","",MAX(0,B30-$B$6))</f>
-        <v>49221005</v>
+        <v>44846005</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13159,10 +13210,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E31" s="29" t="n">
         <v>0</v>
@@ -13174,11 +13225,11 @@
         <v>1900000</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I31" s="23" t="n">
         <f aca="false">IF(B31="","",MAX(0,B31-$B$6))</f>
-        <v>74221005</v>
+        <v>69846005</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13189,7 +13240,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="D32" s="11"/>
       <c r="E32" s="29" t="n">
@@ -13202,11 +13253,11 @@
         <v>1900000</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I32" s="23" t="n">
         <f aca="false">IF(B32="","",MAX(0,B32-$B$6))</f>
-        <v>99221005</v>
+        <v>94846005</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13217,10 +13268,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E33" s="29" t="n">
         <v>0</v>
@@ -13232,11 +13283,11 @@
         <v>1900000</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I33" s="23" t="n">
         <f aca="false">IF(B33="","",MAX(0,B33-$B$6))</f>
-        <v>124221005</v>
+        <v>119846005</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13247,7 +13298,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D34" s="11"/>
       <c r="E34" s="29" t="n">
@@ -13260,11 +13311,11 @@
         <v>1900000</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I34" s="23" t="n">
         <f aca="false">IF(B34="","",MAX(0,B34-$B$6))</f>
-        <v>149221005</v>
+        <v>144846005</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13275,10 +13326,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E35" s="29" t="n">
         <v>0</v>
@@ -13290,11 +13341,11 @@
         <v>1900000</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I35" s="23" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
-        <v>174221005</v>
+        <v>169846005</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13305,7 +13356,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="D36" s="11"/>
       <c r="E36" s="29" t="n">
@@ -13318,11 +13369,11 @@
         <v>1900000</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I36" s="23" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>199221005</v>
+        <v>194846005</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13333,10 +13384,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E37" s="29" t="n">
         <v>0</v>
@@ -13348,11 +13399,11 @@
         <v>1900000</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I37" s="23" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>224221005</v>
+        <v>219846005</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13363,7 +13414,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="D38" s="11"/>
       <c r="E38" s="29" t="n">
@@ -13376,11 +13427,11 @@
         <v>2000000</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I38" s="23" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>274221005</v>
+        <v>269846005</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13391,10 +13442,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E39" s="29" t="n">
         <v>0</v>
@@ -13406,11 +13457,11 @@
         <v>2000000</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I39" s="23" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>324221005</v>
+        <v>319846005</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13421,7 +13472,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="D40" s="11"/>
       <c r="E40" s="29" t="n">
@@ -13434,11 +13485,11 @@
         <v>2000000</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I40" s="23" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>424221005</v>
+        <v>419846005</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13449,10 +13500,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E41" s="29" t="n">
         <v>0</v>
@@ -13464,11 +13515,11 @@
         <v>2000000</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I41" s="23" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>574221005</v>
+        <v>569846005</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13479,7 +13530,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="D42" s="11"/>
       <c r="E42" s="29" t="n">
@@ -13492,11 +13543,11 @@
         <v>2000000</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I42" s="23" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>774221005</v>
+        <v>769846005</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13507,10 +13558,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E43" s="29" t="n">
         <v>0</v>
@@ -13522,11 +13573,11 @@
         <v>2000000</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I43" s="23" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>974221005</v>
+        <v>969846005</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13537,7 +13588,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="29" t="n">
@@ -13550,11 +13601,11 @@
         <v>2700000</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I44" s="23" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>1174221005</v>
+        <v>1169846005</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13565,7 +13616,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="D45" s="11"/>
       <c r="E45" s="29" t="n">
@@ -13578,11 +13629,11 @@
         <v>2700000</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I45" s="23" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1374221005</v>
+        <v>1369846005</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13593,7 +13644,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="D46" s="11"/>
       <c r="E46" s="29" t="n">
@@ -13606,11 +13657,11 @@
         <v>2700000</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I46" s="23" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1574221005</v>
+        <v>1569846005</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13621,7 +13672,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="D47" s="11"/>
       <c r="E47" s="29" t="n">
@@ -13634,11 +13685,11 @@
         <v>2700000</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I47" s="23" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1774221005</v>
+        <v>1769846005</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13649,7 +13700,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="D48" s="11"/>
       <c r="E48" s="29" t="n">
@@ -13662,11 +13713,11 @@
         <v>2700000</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I48" s="23" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1974221005</v>
+        <v>1969846005</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13677,7 +13728,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="D49" s="11"/>
       <c r="E49" s="29" t="n">
@@ -13690,11 +13741,11 @@
         <v>2700000</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I49" s="23" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>2174221005</v>
+        <v>2169846005</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13705,7 +13756,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="D50" s="11"/>
       <c r="E50" s="29" t="n">
@@ -13718,11 +13769,11 @@
         <v>2700000</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I50" s="23" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2374221005</v>
+        <v>2369846005</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13733,7 +13784,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="D51" s="11"/>
       <c r="E51" s="29" t="n">
@@ -13746,11 +13797,11 @@
         <v>2700000</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I51" s="23" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2574221005</v>
+        <v>2569846005</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13761,7 +13812,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="D52" s="11"/>
       <c r="E52" s="29" t="n">
@@ -13774,11 +13825,11 @@
         <v>2700000</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I52" s="23" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2774221005</v>
+        <v>2769846005</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13789,7 +13840,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="D53" s="11"/>
       <c r="E53" s="29" t="n">
@@ -13802,11 +13853,11 @@
         <v>2700000</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I53" s="23" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2974221005</v>
+        <v>2969846005</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13817,7 +13868,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="D54" s="11"/>
       <c r="E54" s="29" t="n">
@@ -13830,16 +13881,16 @@
         <v>2700000</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I54" s="23" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>3174221005</v>
+        <v>3169846005</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -181,7 +181,7 @@
     <t xml:space="preserve">Main team; Diamond 4 at milestone 47</t>
   </si>
   <si>
-    <t xml:space="preserve">T3 L5 done Oct 12, T4 matrix unlocked. 3 diamonds</t>
+    <t xml:space="preserve">T3 L5 done Oct 12, T4 matrix unlocked. 4 diamonds</t>
   </si>
   <si>
     <t xml:space="preserve">Blade (Mighty)</t>
@@ -241,13 +241,13 @@
     <t xml:space="preserve">Blitz tasks in Iron Vengeance</t>
   </si>
   <si>
-    <t xml:space="preserve">Blitz twice with her for 80M points</t>
+    <t xml:space="preserve">Done. Hold until next blitz tier is reachable</t>
   </si>
   <si>
     <t xml:space="preserve">Power cores for more shards</t>
   </si>
   <si>
-    <t xml:space="preserve">Unlocked Oct 12, 1 of 55 shards to next star. Milestone 48 gives her 7 red stars</t>
+    <t xml:space="preserve">Blitzed twice Oct 12. 1 of 55 shards to next star. Milestone 48 gives her 7 red stars</t>
   </si>
   <si>
     <t xml:space="preserve">Doctor Strange</t>
@@ -3174,7 +3174,7 @@
         <v>69</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>80000000</v>
+        <v>0</v>
       </c>
       <c r="J16" s="7" t="s">
         <v>70</v>
@@ -5755,7 +5755,7 @@
         <v>234</v>
       </c>
       <c r="B6" s="18" t="n">
-        <v>666802650</v>
+        <v>746802650</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>235</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="B7" s="15" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6))+SUMPRODUCT((B13:B76="")*(F13:F76="Claimed"))</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>237</v>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="B8" s="15" t="n">
         <f aca="false">IFERROR(INDEX(A13:A76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),"All done")</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>238</v>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(INDEX(E13:E76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),0)</f>
-        <v>23197350</v>
+        <v>3197350</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="B10" s="19" t="n">
         <f aca="false">MAX(0,B76-B6)</f>
-        <v>3458197350</v>
+        <v>3378197350</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="B11" s="19" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>550168601.469724</v>
+        <v>537656223.555091</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6659,10 +6659,10 @@
       <c r="D59" s="11"/>
       <c r="E59" s="23" t="n">
         <f aca="false">IF(B59="","",MAX(0,B59-$B$6))</f>
-        <v>23197350</v>
+        <v>0</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6678,7 +6678,7 @@
       <c r="D60" s="11"/>
       <c r="E60" s="23" t="n">
         <f aca="false">IF(B60="","",MAX(0,B60-$B$6))</f>
-        <v>83197350</v>
+        <v>3197350</v>
       </c>
       <c r="F60" s="10" t="s">
         <v>177</v>
@@ -6697,7 +6697,7 @@
       <c r="D61" s="11"/>
       <c r="E61" s="23" t="n">
         <f aca="false">IF(B61="","",MAX(0,B61-$B$6))</f>
-        <v>158197350</v>
+        <v>78197350</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>177</v>
@@ -6716,7 +6716,7 @@
       <c r="D62" s="11"/>
       <c r="E62" s="23" t="n">
         <f aca="false">IF(B62="","",MAX(0,B62-$B$6))</f>
-        <v>233197350</v>
+        <v>153197350</v>
       </c>
       <c r="F62" s="10" t="s">
         <v>177</v>
@@ -6735,7 +6735,7 @@
       <c r="D63" s="11"/>
       <c r="E63" s="23" t="n">
         <f aca="false">IF(B63="","",MAX(0,B63-$B$6))</f>
-        <v>308197350</v>
+        <v>228197350</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>177</v>
@@ -6754,7 +6754,7 @@
       <c r="D64" s="11"/>
       <c r="E64" s="23" t="n">
         <f aca="false">IF(B64="","",MAX(0,B64-$B$6))</f>
-        <v>383197350</v>
+        <v>303197350</v>
       </c>
       <c r="F64" s="10" t="s">
         <v>177</v>
@@ -6773,7 +6773,7 @@
       <c r="D65" s="11"/>
       <c r="E65" s="23" t="n">
         <f aca="false">IF(B65="","",MAX(0,B65-$B$6))</f>
-        <v>458197350</v>
+        <v>378197350</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>177</v>
@@ -6792,7 +6792,7 @@
       <c r="D66" s="11"/>
       <c r="E66" s="23" t="n">
         <f aca="false">IF(B66="","",MAX(0,B66-$B$6))</f>
-        <v>533197350</v>
+        <v>453197350</v>
       </c>
       <c r="F66" s="10" t="s">
         <v>177</v>
@@ -6811,7 +6811,7 @@
       <c r="D67" s="11"/>
       <c r="E67" s="23" t="n">
         <f aca="false">IF(B67="","",MAX(0,B67-$B$6))</f>
-        <v>683197350</v>
+        <v>603197350</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>177</v>
@@ -6830,7 +6830,7 @@
       <c r="D68" s="11"/>
       <c r="E68" s="23" t="n">
         <f aca="false">IF(B68="","",MAX(0,B68-$B$6))</f>
-        <v>833197350</v>
+        <v>753197350</v>
       </c>
       <c r="F68" s="10" t="s">
         <v>177</v>
@@ -6849,7 +6849,7 @@
       <c r="D69" s="11"/>
       <c r="E69" s="23" t="n">
         <f aca="false">IF(B69="","",MAX(0,B69-$B$6))</f>
-        <v>983197350</v>
+        <v>903197350</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>177</v>
@@ -6868,7 +6868,7 @@
       <c r="D70" s="11"/>
       <c r="E70" s="23" t="n">
         <f aca="false">IF(B70="","",MAX(0,B70-$B$6))</f>
-        <v>1208197350</v>
+        <v>1128197350</v>
       </c>
       <c r="F70" s="10" t="s">
         <v>177</v>
@@ -6887,7 +6887,7 @@
       <c r="D71" s="11"/>
       <c r="E71" s="23" t="n">
         <f aca="false">IF(B71="","",MAX(0,B71-$B$6))</f>
-        <v>1583197350</v>
+        <v>1503197350</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>177</v>
@@ -6906,7 +6906,7 @@
       <c r="D72" s="11"/>
       <c r="E72" s="23" t="n">
         <f aca="false">IF(B72="","",MAX(0,B72-$B$6))</f>
-        <v>1958197350</v>
+        <v>1878197350</v>
       </c>
       <c r="F72" s="10" t="s">
         <v>177</v>
@@ -6925,7 +6925,7 @@
       <c r="D73" s="11"/>
       <c r="E73" s="23" t="n">
         <f aca="false">IF(B73="","",MAX(0,B73-$B$6))</f>
-        <v>2333197350</v>
+        <v>2253197350</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>177</v>
@@ -6944,7 +6944,7 @@
       <c r="D74" s="11"/>
       <c r="E74" s="23" t="n">
         <f aca="false">IF(B74="","",MAX(0,B74-$B$6))</f>
-        <v>2708197350</v>
+        <v>2628197350</v>
       </c>
       <c r="F74" s="10" t="s">
         <v>177</v>
@@ -6963,7 +6963,7 @@
       <c r="D75" s="11"/>
       <c r="E75" s="23" t="n">
         <f aca="false">IF(B75="","",MAX(0,B75-$B$6))</f>
-        <v>3083197350</v>
+        <v>3003197350</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>177</v>
@@ -6982,7 +6982,7 @@
       <c r="D76" s="11"/>
       <c r="E76" s="23" t="n">
         <f aca="false">IF(B76="","",MAX(0,B76-$B$6))</f>
-        <v>3458197350</v>
+        <v>3378197350</v>
       </c>
       <c r="F76" s="10" t="s">
         <v>177</v>
@@ -8027,11 +8027,11 @@
         <v>80000000</v>
       </c>
       <c r="E31" s="24" t="n">
-        <v>0</v>
+        <v>80000000</v>
       </c>
       <c r="F31" s="21" t="n">
         <f aca="false">IF(ISNUMBER(D31),MAX(0,D31-E31),0)</f>
-        <v>80000000</v>
+        <v>0</v>
       </c>
       <c r="G31" s="21" t="n">
         <f aca="false">IF(ISNUMBER(D31),ROUNDUP(D31/C31,0),"No limit")</f>
@@ -8039,11 +8039,11 @@
       </c>
       <c r="H31" s="21" t="n">
         <f aca="false">IFERROR(INT(E31/C31),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" s="21" t="n">
         <f aca="false">IFERROR(ROUNDUP(F31/C31,0),0)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J31" s="10" t="s">
         <v>319</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="E49" s="19" t="n">
         <f aca="false">SUM(E5:E47)</f>
-        <v>666802650</v>
+        <v>746802650</v>
       </c>
       <c r="F49" s="19"/>
     </row>
@@ -8642,7 +8642,7 @@
       <c r="E50" s="19"/>
       <c r="F50" s="19" t="n">
         <f aca="false">SUM(F5:F47)</f>
-        <v>7270447350</v>
+        <v>7190447350</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8652,7 +8652,7 @@
       <c r="E51" s="19"/>
       <c r="F51" s="19" t="n">
         <f aca="false">SUMIF(J5:J47,"Yes",F5:F47)</f>
-        <v>5358000000</v>
+        <v>5278000000</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12602,7 +12602,7 @@
         <v>234</v>
       </c>
       <c r="B6" s="18" t="n">
-        <v>330153995</v>
+        <v>347958315</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>594</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="B8" s="19" t="n">
         <f aca="false">IFERROR(INDEX(I13:I54,MATCH(TRUE(),INDEX(B13:B54&gt;B6,0),0)),0)</f>
-        <v>19846005</v>
+        <v>2041685</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="B10" s="19" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
-        <v>94846005</v>
+        <v>77041685</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="B11" s="19" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>15089160.2513664</v>
+        <v>12261551.7161515</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="I29" s="23" t="n">
         <f aca="false">IF(B29="","",MAX(0,B29-$B$6))</f>
-        <v>19846005</v>
+        <v>2041685</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="I30" s="23" t="n">
         <f aca="false">IF(B30="","",MAX(0,B30-$B$6))</f>
-        <v>44846005</v>
+        <v>27041685</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13229,7 +13229,7 @@
       </c>
       <c r="I31" s="23" t="n">
         <f aca="false">IF(B31="","",MAX(0,B31-$B$6))</f>
-        <v>69846005</v>
+        <v>52041685</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="I32" s="23" t="n">
         <f aca="false">IF(B32="","",MAX(0,B32-$B$6))</f>
-        <v>94846005</v>
+        <v>77041685</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="I33" s="23" t="n">
         <f aca="false">IF(B33="","",MAX(0,B33-$B$6))</f>
-        <v>119846005</v>
+        <v>102041685</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13315,7 +13315,7 @@
       </c>
       <c r="I34" s="23" t="n">
         <f aca="false">IF(B34="","",MAX(0,B34-$B$6))</f>
-        <v>144846005</v>
+        <v>127041685</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="I35" s="23" t="n">
         <f aca="false">IF(B35="","",MAX(0,B35-$B$6))</f>
-        <v>169846005</v>
+        <v>152041685</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="I36" s="23" t="n">
         <f aca="false">IF(B36="","",MAX(0,B36-$B$6))</f>
-        <v>194846005</v>
+        <v>177041685</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="I37" s="23" t="n">
         <f aca="false">IF(B37="","",MAX(0,B37-$B$6))</f>
-        <v>219846005</v>
+        <v>202041685</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="I38" s="23" t="n">
         <f aca="false">IF(B38="","",MAX(0,B38-$B$6))</f>
-        <v>269846005</v>
+        <v>252041685</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="I39" s="23" t="n">
         <f aca="false">IF(B39="","",MAX(0,B39-$B$6))</f>
-        <v>319846005</v>
+        <v>302041685</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="I40" s="23" t="n">
         <f aca="false">IF(B40="","",MAX(0,B40-$B$6))</f>
-        <v>419846005</v>
+        <v>402041685</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13519,7 +13519,7 @@
       </c>
       <c r="I41" s="23" t="n">
         <f aca="false">IF(B41="","",MAX(0,B41-$B$6))</f>
-        <v>569846005</v>
+        <v>552041685</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13547,7 +13547,7 @@
       </c>
       <c r="I42" s="23" t="n">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
-        <v>769846005</v>
+        <v>752041685</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="I43" s="23" t="n">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
-        <v>969846005</v>
+        <v>952041685</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="I44" s="23" t="n">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
-        <v>1169846005</v>
+        <v>1152041685</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="I45" s="23" t="n">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
-        <v>1369846005</v>
+        <v>1352041685</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13661,7 +13661,7 @@
       </c>
       <c r="I46" s="23" t="n">
         <f aca="false">IF(B46="","",MAX(0,B46-$B$6))</f>
-        <v>1569846005</v>
+        <v>1552041685</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13689,7 +13689,7 @@
       </c>
       <c r="I47" s="23" t="n">
         <f aca="false">IF(B47="","",MAX(0,B47-$B$6))</f>
-        <v>1769846005</v>
+        <v>1752041685</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13717,7 +13717,7 @@
       </c>
       <c r="I48" s="23" t="n">
         <f aca="false">IF(B48="","",MAX(0,B48-$B$6))</f>
-        <v>1969846005</v>
+        <v>1952041685</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="I49" s="23" t="n">
         <f aca="false">IF(B49="","",MAX(0,B49-$B$6))</f>
-        <v>2169846005</v>
+        <v>2152041685</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="I50" s="23" t="n">
         <f aca="false">IF(B50="","",MAX(0,B50-$B$6))</f>
-        <v>2369846005</v>
+        <v>2352041685</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13801,7 +13801,7 @@
       </c>
       <c r="I51" s="23" t="n">
         <f aca="false">IF(B51="","",MAX(0,B51-$B$6))</f>
-        <v>2569846005</v>
+        <v>2552041685</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="I52" s="23" t="n">
         <f aca="false">IF(B52="","",MAX(0,B52-$B$6))</f>
-        <v>2769846005</v>
+        <v>2752041685</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13857,7 +13857,7 @@
       </c>
       <c r="I53" s="23" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
-        <v>2969846005</v>
+        <v>2952041685</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13885,7 +13885,7 @@
       </c>
       <c r="I54" s="23" t="n">
         <f aca="false">IF(B54="","",MAX(0,B54-$B$6))</f>
-        <v>3169846005</v>
+        <v>3152041685</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -32,12 +32,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="646">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
   <si>
-    <t xml:space="preserve">Iron Raider goal: all five at gear tier 20 for Omega tower floors. Lower number means build first. Change Priority or Status anytime and sort by Priority. Blank yellow cells are details to fill in from the game.</t>
+    <t xml:space="preserve">Focus now: Amazing Avengers for Spider-Man tower cell 20. Iron Raider goal: all five at gear tier 20 for Omega tower floors. Lower number means build first. Change Priority or Status anytime and sort by Priority. Blank yellow cells are details to fill in from the game.</t>
   </si>
   <si>
     <t xml:space="preserve">Priority</t>
@@ -1513,10 +1513,7 @@
     <t xml:space="preserve">Third Uncanny Avenger to level 101</t>
   </si>
   <si>
-    <t xml:space="preserve">If needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only if cell 20 still fails. Needs battle pass level 95 orange</t>
+    <t xml:space="preserve">Amazing Avengers carry cell 20 now</t>
   </si>
   <si>
     <t xml:space="preserve">Whiplash to gear tier 20</t>
@@ -2742,7 +2739,7 @@
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>14</v>
@@ -2780,7 +2777,7 @@
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>22</v>
@@ -2818,7 +2815,7 @@
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>27</v>
@@ -2856,7 +2853,7 @@
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>32</v>
@@ -2894,7 +2891,7 @@
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>36</v>
@@ -2932,7 +2929,7 @@
     </row>
     <row r="10" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>40</v>
@@ -2970,7 +2967,7 @@
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>47</v>
@@ -3008,7 +3005,7 @@
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>50</v>
@@ -3044,7 +3041,7 @@
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>56</v>
@@ -3082,7 +3079,7 @@
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>59</v>
@@ -5821,7 +5818,7 @@
       </c>
       <c r="B11" s="19" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>537656223.555091</v>
+        <v>538195003.702131</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11266,15 +11263,15 @@
         <v>3000000</v>
       </c>
       <c r="J88" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="K88" s="14" t="s">
         <v>493</v>
-      </c>
-      <c r="K88" s="14" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="11" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B89" s="26"/>
       <c r="C89" s="29" t="n">
@@ -11302,12 +11299,12 @@
         <v>486</v>
       </c>
       <c r="K89" s="14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="11" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B90" s="29" t="n">
         <v>0</v>
@@ -11337,12 +11334,12 @@
         <v>476</v>
       </c>
       <c r="K90" s="14" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="11" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B91" s="29" t="n">
         <v>0</v>
@@ -11372,12 +11369,12 @@
         <v>476</v>
       </c>
       <c r="K91" s="14" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="11" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B92" s="29" t="n">
         <v>0</v>
@@ -11401,12 +11398,12 @@
         <v>483</v>
       </c>
       <c r="K92" s="14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="11" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B93" s="29" t="n">
         <v>0</v>
@@ -11430,12 +11427,12 @@
         <v>483</v>
       </c>
       <c r="K93" s="14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="11" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B94" s="29" t="n">
         <v>0</v>
@@ -11459,12 +11456,12 @@
         <v>483</v>
       </c>
       <c r="K94" s="14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="11" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B95" s="29" t="n">
         <v>13000000</v>
@@ -11488,7 +11485,7 @@
         <v>483</v>
       </c>
       <c r="K95" s="14" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11571,7 +11568,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="15" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="I103" s="19" t="n">
         <f aca="false">SUMIF(J80:J101,"Planned",I80:I101)</f>
@@ -11630,12 +11627,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11649,50 +11646,50 @@
         <v>377</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>516</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
+        <v>518</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>519</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>520</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E6" s="31" t="s">
         <v>476</v>
@@ -11709,16 +11706,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C7" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E7" s="31" t="s">
         <v>476</v>
@@ -11735,16 +11732,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E8" s="31" t="s">
         <v>476</v>
@@ -11761,16 +11758,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E9" s="31" t="s">
         <v>476</v>
@@ -11787,16 +11784,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E10" s="31" t="s">
         <v>476</v>
@@ -11813,16 +11810,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E11" s="31" t="s">
         <v>476</v>
@@ -11839,16 +11836,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E12" s="31" t="s">
         <v>476</v>
@@ -11865,16 +11862,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E13" s="31" t="s">
         <v>476</v>
@@ -11891,16 +11888,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E14" s="31" t="s">
         <v>476</v>
@@ -11917,16 +11914,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E15" s="31" t="s">
         <v>476</v>
@@ -11943,16 +11940,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>1000000</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E16" s="31" t="s">
         <v>476</v>
@@ -11969,16 +11966,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>538</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>539</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>100000</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="31" t="s">
@@ -11993,16 +11990,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E18" s="31" t="s">
         <v>476</v>
@@ -12019,16 +12016,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>25000</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E19" s="31" t="s">
         <v>476</v>
@@ -12045,16 +12042,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>75000</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E20" s="31" t="s">
         <v>476</v>
@@ -12071,21 +12068,21 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="30" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>548</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="C22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14" t="s">
         <v>549</v>
-      </c>
-      <c r="C22" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>550</v>
       </c>
       <c r="E22" s="31" t="s">
         <v>476</v>
@@ -12100,16 +12097,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B23" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="C23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="14" t="s">
         <v>549</v>
-      </c>
-      <c r="C23" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>550</v>
       </c>
       <c r="E23" s="31"/>
       <c r="F23" s="31"/>
@@ -12122,16 +12119,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B24" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="C24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14" t="s">
         <v>549</v>
-      </c>
-      <c r="C24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>550</v>
       </c>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
@@ -12144,16 +12141,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
+        <v>552</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>553</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>554</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>900000</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E25" s="31" t="s">
         <v>476</v>
@@ -12170,16 +12167,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="C26" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14" t="s">
         <v>556</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>554</v>
-      </c>
-      <c r="C26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>557</v>
       </c>
       <c r="E26" s="31" t="s">
         <v>476</v>
@@ -12194,16 +12191,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>558</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="C27" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14" t="s">
         <v>559</v>
-      </c>
-      <c r="C27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>560</v>
       </c>
       <c r="E27" s="31"/>
       <c r="F27" s="31"/>
@@ -12216,16 +12213,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="B28" s="12" t="s">
         <v>561</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="C28" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14" t="s">
         <v>562</v>
-      </c>
-      <c r="C28" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>563</v>
       </c>
       <c r="E28" s="31"/>
       <c r="F28" s="31"/>
@@ -12238,21 +12235,21 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="30" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="B30" s="12" t="s">
         <v>565</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="C30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14" t="s">
         <v>566</v>
-      </c>
-      <c r="C30" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>567</v>
       </c>
       <c r="E30" s="31"/>
       <c r="F30" s="31"/>
@@ -12265,16 +12262,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="C31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14" t="s">
         <v>568</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>566</v>
-      </c>
-      <c r="C31" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>569</v>
       </c>
       <c r="E31" s="31"/>
       <c r="F31" s="31"/>
@@ -12287,16 +12284,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="C32" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14" t="s">
         <v>570</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>566</v>
-      </c>
-      <c r="C32" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>571</v>
       </c>
       <c r="E32" s="31"/>
       <c r="F32" s="31"/>
@@ -12309,16 +12306,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
+        <v>571</v>
+      </c>
+      <c r="B33" s="12" t="s">
         <v>572</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="C33" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="14" t="s">
         <v>573</v>
-      </c>
-      <c r="C33" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>574</v>
       </c>
       <c r="E33" s="31" t="s">
         <v>476</v>
@@ -12333,16 +12330,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
+        <v>574</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="C34" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="14" t="s">
         <v>575</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>566</v>
-      </c>
-      <c r="C34" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>576</v>
       </c>
       <c r="E34" s="31"/>
       <c r="F34" s="31"/>
@@ -12355,16 +12352,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>572</v>
+      </c>
+      <c r="C35" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="14" t="s">
         <v>577</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>573</v>
-      </c>
-      <c r="C35" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>578</v>
       </c>
       <c r="E35" s="31"/>
       <c r="F35" s="31"/>
@@ -12377,16 +12374,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C36" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E36" s="31"/>
       <c r="F36" s="31"/>
@@ -12399,16 +12396,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="C37" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="14" t="s">
         <v>580</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>566</v>
-      </c>
-      <c r="C37" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>581</v>
       </c>
       <c r="E37" s="31"/>
       <c r="F37" s="31"/>
@@ -12421,16 +12418,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="C38" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="14" t="s">
         <v>582</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>566</v>
-      </c>
-      <c r="C38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>583</v>
       </c>
       <c r="E38" s="31"/>
       <c r="F38" s="31"/>
@@ -12443,7 +12440,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E40" s="19" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$38)*(E5:E38="Done"))</f>
@@ -12480,7 +12477,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E41" s="32" t="str">
         <f aca="false">COUNTIFS($B$5:$B$38,"Required",E5:E38,"Done")&amp;" of 11"</f>
@@ -12517,7 +12514,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>
@@ -12561,12 +12558,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12574,10 +12571,10 @@
         <v>232</v>
       </c>
       <c r="B4" s="16" t="s">
+        <v>588</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>589</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12588,13 +12585,13 @@
         <v>46313.7083333333</v>
       </c>
       <c r="E5" s="15" t="s">
+        <v>590</v>
+      </c>
+      <c r="F5" s="15" t="s">
         <v>591</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="G5" s="15" t="s">
         <v>592</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12605,7 +12602,7 @@
         <v>347958315</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E6" s="19" t="n">
         <f aca="false">SUMPRODUCT((A13:A54&lt;=$B$9)*(H13:H54&lt;&gt;"Claimed")*E13:E54)</f>
@@ -12655,7 +12652,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B9" s="33" t="n">
         <v>20</v>
@@ -12663,7 +12660,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B10" s="19" t="n">
         <f aca="false">MAX(0,INDEX(B13:B54,B9)-B6)</f>
@@ -12672,11 +12669,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B11" s="19" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>12261551.7161515</v>
+        <v>12273838.8889894</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12687,19 +12684,19 @@
         <v>241</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>592</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>593</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
@@ -12715,7 +12712,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E13" s="29" t="n">
         <v>0</v>
@@ -12741,7 +12738,7 @@
       <c r="B14" s="26"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E14" s="29" t="n">
         <v>0</v>
@@ -12767,7 +12764,7 @@
       <c r="B15" s="26"/>
       <c r="C15" s="11"/>
       <c r="D15" s="11" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E15" s="29" t="n">
         <v>0</v>
@@ -12793,7 +12790,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E16" s="29" t="n">
         <v>0</v>
@@ -12818,10 +12815,10 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>602</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>603</v>
       </c>
       <c r="E17" s="29" t="n">
         <v>0</v>
@@ -12846,10 +12843,10 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="11" t="s">
+        <v>603</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>604</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>605</v>
       </c>
       <c r="E18" s="29" t="n">
         <v>0</v>
@@ -12874,10 +12871,10 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="11" t="s">
+        <v>605</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>606</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>607</v>
       </c>
       <c r="E19" s="29" t="n">
         <v>0</v>
@@ -12902,10 +12899,10 @@
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="11" t="s">
+        <v>607</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>608</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>609</v>
       </c>
       <c r="E20" s="29" t="n">
         <v>0</v>
@@ -12930,10 +12927,10 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>610</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>611</v>
       </c>
       <c r="E21" s="29" t="n">
         <v>0</v>
@@ -12958,10 +12955,10 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="11" t="s">
+        <v>611</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>612</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>613</v>
       </c>
       <c r="E22" s="29" t="n">
         <v>0</v>
@@ -12987,7 +12984,7 @@
       <c r="B23" s="26"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E23" s="29" t="n">
         <v>900000</v>
@@ -13012,10 +13009,10 @@
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="11" t="s">
+        <v>614</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>615</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>616</v>
       </c>
       <c r="E24" s="29" t="n">
         <v>900000</v>
@@ -13040,10 +13037,10 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="11" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E25" s="29" t="n">
         <v>0</v>
@@ -13068,10 +13065,10 @@
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="11" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E26" s="29" t="n">
         <v>900000</v>
@@ -13099,7 +13096,7 @@
       </c>
       <c r="C27" s="11"/>
       <c r="D27" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E27" s="29" t="n">
         <v>900000</v>
@@ -13126,10 +13123,10 @@
         <v>325000000</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E28" s="29" t="n">
         <v>950000</v>
@@ -13156,10 +13153,10 @@
         <v>350000000</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E29" s="29" t="n">
         <v>0</v>
@@ -13186,10 +13183,10 @@
         <v>375000000</v>
       </c>
       <c r="C30" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>621</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>622</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
@@ -13210,10 +13207,10 @@
         <v>400000000</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E31" s="29" t="n">
         <v>0</v>
@@ -13240,7 +13237,7 @@
         <v>425000000</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D32" s="11"/>
       <c r="E32" s="29" t="n">
@@ -13268,10 +13265,10 @@
         <v>450000000</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E33" s="29" t="n">
         <v>0</v>
@@ -13298,7 +13295,7 @@
         <v>475000000</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D34" s="11"/>
       <c r="E34" s="29" t="n">
@@ -13326,10 +13323,10 @@
         <v>500000000</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E35" s="29" t="n">
         <v>0</v>
@@ -13356,7 +13353,7 @@
         <v>525000000</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D36" s="11"/>
       <c r="E36" s="29" t="n">
@@ -13384,10 +13381,10 @@
         <v>550000000</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E37" s="29" t="n">
         <v>0</v>
@@ -13414,7 +13411,7 @@
         <v>600000000</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D38" s="11"/>
       <c r="E38" s="29" t="n">
@@ -13442,10 +13439,10 @@
         <v>650000000</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E39" s="29" t="n">
         <v>0</v>
@@ -13472,7 +13469,7 @@
         <v>750000000</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D40" s="11"/>
       <c r="E40" s="29" t="n">
@@ -13500,10 +13497,10 @@
         <v>900000000</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E41" s="29" t="n">
         <v>0</v>
@@ -13530,7 +13527,7 @@
         <v>1100000000</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D42" s="11"/>
       <c r="E42" s="29" t="n">
@@ -13558,10 +13555,10 @@
         <v>1300000000</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E43" s="29" t="n">
         <v>0</v>
@@ -13588,7 +13585,7 @@
         <v>1500000000</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="29" t="n">
@@ -13616,7 +13613,7 @@
         <v>1700000000</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D45" s="11"/>
       <c r="E45" s="29" t="n">
@@ -13644,7 +13641,7 @@
         <v>1900000000</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D46" s="11"/>
       <c r="E46" s="29" t="n">
@@ -13672,7 +13669,7 @@
         <v>2100000000</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D47" s="11"/>
       <c r="E47" s="29" t="n">
@@ -13700,7 +13697,7 @@
         <v>2300000000</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D48" s="11"/>
       <c r="E48" s="29" t="n">
@@ -13728,7 +13725,7 @@
         <v>2500000000</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D49" s="11"/>
       <c r="E49" s="29" t="n">
@@ -13756,7 +13753,7 @@
         <v>2700000000</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D50" s="11"/>
       <c r="E50" s="29" t="n">
@@ -13784,7 +13781,7 @@
         <v>2900000000</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D51" s="11"/>
       <c r="E51" s="29" t="n">
@@ -13812,7 +13809,7 @@
         <v>3100000000</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D52" s="11"/>
       <c r="E52" s="29" t="n">
@@ -13840,7 +13837,7 @@
         <v>3300000000</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D53" s="11"/>
       <c r="E53" s="29" t="n">
@@ -13868,7 +13865,7 @@
         <v>3500000000</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D54" s="11"/>
       <c r="E54" s="29" t="n">
@@ -13890,7 +13887,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
   </sheetData>

--- a/Event_Tracker.xlsx
+++ b/Event_Tracker.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="648">
   <si>
     <t xml:space="preserve">Build Priority</t>
   </si>
@@ -379,10 +379,16 @@
     <t xml:space="preserve">Kingo</t>
   </si>
   <si>
-    <t xml:space="preserve">Red stars, 13 of 300 shards</t>
+    <t xml:space="preserve">6 yellow, 4 red stars, 13 of 300 shards</t>
   </si>
   <si>
     <t xml:space="preserve">6 6 6 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider-Man tower rewards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gear tier 19, all six pieces ready for 20. Tower milestones give his shards, red stars and diamonds</t>
   </si>
   <si>
     <t xml:space="preserve">Super Skrull</t>
@@ -3724,14 +3730,18 @@
       <c r="E14" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F14" s="12"/>
+      <c r="F14" s="12" t="s">
+        <v>117</v>
+      </c>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
-      <c r="I14" s="14"/>
+      <c r="I14" s="14" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B15" s="11" t="n">
         <v>103</v>
@@ -3752,7 +3762,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>105</v>
@@ -3761,10 +3771,10 @@
         <v>1039168</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="10"/>
@@ -3773,7 +3783,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B17" s="11" t="n">
         <v>104</v>
@@ -3794,7 +3804,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B18" s="11" t="n">
         <v>100</v>
@@ -3815,7 +3825,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B19" s="11" t="n">
         <v>105</v>
@@ -3824,7 +3834,7 @@
         <v>900021</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>116</v>
@@ -3836,7 +3846,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B20" s="11" t="n">
         <v>100</v>
@@ -3857,7 +3867,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B21" s="11" t="n">
         <v>100</v>
@@ -3878,7 +3888,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B22" s="11" t="n">
         <v>100</v>
@@ -3919,12 +3929,12 @@
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
       <c r="I23" s="14" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B24" s="11" t="n">
         <v>101</v>
@@ -3945,7 +3955,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B25" s="11" t="n">
         <v>103</v>
@@ -3966,7 +3976,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B26" s="11" t="n">
         <v>96</v>
@@ -4007,12 +4017,12 @@
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
       <c r="I27" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B28" s="11" t="n">
         <v>95</v>
@@ -4021,7 +4031,7 @@
         <v>573611</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>116</v>
@@ -4033,7 +4043,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B29" s="11" t="n">
         <v>100</v>
@@ -4042,7 +4052,7 @@
         <v>556594</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>100</v>
@@ -4054,7 +4064,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B30" s="11" t="n">
         <v>95</v>
@@ -4075,7 +4085,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B31" s="11" t="n">
         <v>90</v>
@@ -4096,7 +4106,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B32" s="11" t="n">
         <v>95</v>
@@ -4105,7 +4115,7 @@
         <v>309062</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>116</v>
@@ -4117,7 +4127,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B33" s="11" t="n">
         <v>90</v>
@@ -4138,7 +4148,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B34" s="11" t="n">
         <v>95</v>
@@ -4147,7 +4157,7 @@
         <v>302615</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>116</v>
@@ -4159,7 +4169,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B35" s="11" t="n">
         <v>90</v>
@@ -4180,7 +4190,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B36" s="11" t="n">
         <v>80</v>
@@ -4189,7 +4199,7 @@
         <v>250273</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>100</v>
@@ -4201,7 +4211,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B37" s="11" t="n">
         <v>90</v>
@@ -4210,10 +4220,10 @@
         <v>245993</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F37" s="12"/>
       <c r="G37" s="10"/>
@@ -4222,7 +4232,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B38" s="11" t="n">
         <v>75</v>
@@ -4231,7 +4241,7 @@
         <v>228686</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>116</v>
@@ -4243,7 +4253,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B39" s="11" t="n">
         <v>75</v>
@@ -4252,7 +4262,7 @@
         <v>144778</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>116</v>
@@ -4273,10 +4283,10 @@
         <v>33212</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F40" s="12" t="s">
         <v>15</v>
@@ -4284,7 +4294,7 @@
       <c r="G40" s="10"/>
       <c r="H40" s="10"/>
       <c r="I40" s="14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4301,7 +4311,7 @@
         <v>102</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>15</v>
@@ -4321,10 +4331,10 @@
         <v>26827</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F42" s="12" t="s">
         <v>15</v>
@@ -4332,17 +4342,17 @@
       <c r="G42" s="10"/>
       <c r="H42" s="10"/>
       <c r="I42" s="14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B43" s="11"/>
       <c r="C43" s="13"/>
       <c r="D43" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E43" s="11"/>
       <c r="F43" s="12" t="s">
@@ -4351,17 +4361,17 @@
       <c r="G43" s="10"/>
       <c r="H43" s="10"/>
       <c r="I43" s="14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B44" s="11"/>
       <c r="C44" s="13"/>
       <c r="D44" s="11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E44" s="11"/>
       <c r="F44" s="12"/>
@@ -4371,7 +4381,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B46" s="16" t="n">
         <f aca="false">COUNT(C5:C44)</f>
@@ -4380,7 +4390,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B47" s="16" t="n">
         <f aca="false">COUNTIF(C5:C44,"&gt;=1000000")</f>
@@ -4389,7 +4399,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B48" s="16" t="n">
         <f aca="false">COUNTIF(H5:H44,"Yes")</f>
@@ -4441,17 +4451,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B4" s="17" t="n">
         <v>46332.7083333333</v>
@@ -4459,7 +4469,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>400</v>
@@ -4467,7 +4477,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B6" s="15" t="n">
         <f aca="false">IFERROR(INDEX(A10:A29,MATCH(TRUE(),INDEX(B10:B29&gt;B5,0),0)),"All done")</f>
@@ -4476,7 +4486,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B7" s="19" t="n">
         <f aca="false">IFERROR(INDEX(B10:B29,MATCH(TRUE(),INDEX(B10:B29&gt;B5,0),0))-B5,0)</f>
@@ -4485,19 +4495,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F9" s="20" t="s">
         <v>12</v>
@@ -4511,14 +4521,14 @@
         <v>400</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4529,14 +4539,14 @@
         <v>800</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4547,14 +4557,14 @@
         <v>1200</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E12" s="14"/>
       <c r="F12" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4565,14 +4575,14 @@
         <v>1600</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4583,14 +4593,14 @@
         <v>2000</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E14" s="14"/>
       <c r="F14" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4601,16 +4611,16 @@
         <v>2400</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4621,14 +4631,14 @@
         <v>2800</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E16" s="14"/>
       <c r="F16" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4639,14 +4649,14 @@
         <v>3200</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E17" s="14"/>
       <c r="F17" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4657,14 +4667,14 @@
         <v>3600</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E18" s="14"/>
       <c r="F18" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4675,14 +4685,14 @@
         <v>4000</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E19" s="14"/>
       <c r="F19" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4693,16 +4703,16 @@
         <v>4400</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4713,16 +4723,16 @@
         <v>4800</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4733,16 +4743,16 @@
         <v>5200</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4753,16 +4763,16 @@
         <v>5600</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4773,14 +4783,14 @@
         <v>6000</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E24" s="14"/>
       <c r="F24" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4791,16 +4801,16 @@
         <v>6400</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4811,16 +4821,16 @@
         <v>6800</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D26" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E26" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="E26" s="14" t="s">
-        <v>206</v>
-      </c>
       <c r="F26" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4832,11 +4842,11 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E27" s="14"/>
       <c r="F27" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4848,13 +4858,13 @@
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4866,54 +4876,54 @@
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E29" s="14"/>
       <c r="F29" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="22" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>13</v>
@@ -4921,7 +4931,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
@@ -4929,23 +4939,23 @@
         <v>113</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I33" s="23" t="n">
         <f aca="false">SUMIF('Tower Roster'!$A$5:$A$44,D33,'Tower Roster'!$C$5:$C$44)+SUMIF('Tower Roster'!$A$5:$A$44,E33,'Tower Roster'!$C$5:$C$44)+SUMIF('Tower Roster'!$A$5:$A$44,F33,'Tower Roster'!$C$5:$C$44)+SUMIF('Tower Roster'!$A$5:$A$44,G33,'Tower Roster'!$C$5:$C$44)+SUMIF('Tower Roster'!$A$5:$A$44,H33,'Tower Roster'!$C$5:$C$44)</f>
         <v>4789170</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K33" s="10" t="n">
         <v>1</v>
@@ -4954,7 +4964,7 @@
         <v>400</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5661,7 +5671,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -5723,25 +5733,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>46313.7083333333</v>
@@ -5749,13 +5759,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>746802650</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E6" s="19" t="n">
         <f aca="false">B6+Scoring!F51</f>
@@ -5764,14 +5774,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B7" s="15" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6))+SUMPRODUCT((B13:B76="")*(F13:F76="Claimed"))</f>
         <v>47</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E7" s="15" t="n">
         <f aca="false">IFERROR(INDEX(A13:A76,MATCH(E6,B13:B76,1)),37)</f>
@@ -5780,14 +5790,14 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B8" s="15" t="n">
         <f aca="false">IFERROR(INDEX(A13:A76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),"All done")</f>
         <v>48</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E8" s="15" t="n">
         <f aca="false">SUMPRODUCT((B13:B76&lt;&gt;"")*(B13:B76&lt;=B6)*(F13:F76&lt;&gt;"Claimed"))</f>
@@ -5796,7 +5806,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(INDEX(E13:E76,MATCH(TRUE(),INDEX(B13:B76&gt;B6,0),0)),0)</f>
@@ -5805,7 +5815,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B10" s="19" t="n">
         <f aca="false">MAX(0,B76-B6)</f>
@@ -5814,28 +5824,28 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B11" s="19" t="n">
         <f aca="true">IFERROR(B10/MAX(B5-NOW(),0.01),0)</f>
-        <v>538195003.702131</v>
+        <v>538287967.167291</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>12</v>
@@ -5847,7 +5857,7 @@
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="23" t="str">
@@ -5855,7 +5865,7 @@
         <v/>
       </c>
       <c r="F13" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5864,7 +5874,7 @@
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="11" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="23" t="str">
@@ -5872,7 +5882,7 @@
         <v/>
       </c>
       <c r="F14" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5881,7 +5891,7 @@
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="23" t="str">
@@ -5889,7 +5899,7 @@
         <v/>
       </c>
       <c r="F15" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5898,7 +5908,7 @@
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="23" t="str">
@@ -5906,7 +5916,7 @@
         <v/>
       </c>
       <c r="F16" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5915,7 +5925,7 @@
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="23" t="str">
@@ -5923,7 +5933,7 @@
         <v/>
       </c>
       <c r="F17" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5932,7 +5942,7 @@
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="23" t="str">
@@ -5940,7 +5950,7 @@
         <v/>
       </c>
       <c r="F18" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5949,7 +5959,7 @@
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="23" t="str">
@@ -5957,7 +5967,7 @@
         <v/>
       </c>
       <c r="F19" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5966,7 +5976,7 @@
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="23" t="str">
@@ -5974,7 +5984,7 @@
         <v/>
       </c>
       <c r="F20" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5983,7 +5993,7 @@
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="23" t="str">
@@ -5991,7 +6001,7 @@
         <v/>
       </c>
       <c r="F21" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6000,7 +6010,7 @@
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="23" t="str">
@@ -6008,7 +6018,7 @@
         <v/>
       </c>
       <c r="F22" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6017,7 +6027,7 @@
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D23" s="11"/>
       <c r="E23" s="23" t="str">
@@ -6025,7 +6035,7 @@
         <v/>
       </c>
       <c r="F23" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6034,7 +6044,7 @@
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="11" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D24" s="11"/>
       <c r="E24" s="23" t="str">
@@ -6042,7 +6052,7 @@
         <v/>
       </c>
       <c r="F24" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6051,7 +6061,7 @@
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="11" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D25" s="11"/>
       <c r="E25" s="23" t="str">
@@ -6059,7 +6069,7 @@
         <v/>
       </c>
       <c r="F25" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6068,7 +6078,7 @@
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="11" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D26" s="11"/>
       <c r="E26" s="23" t="str">
@@ -6076,7 +6086,7 @@
         <v/>
       </c>
       <c r="F26" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6085,7 +6095,7 @@
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="11" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D27" s="11"/>
       <c r="E27" s="23" t="str">
@@ -6093,7 +6103,7 @@
         <v/>
       </c>
       <c r="F27" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6102,7 +6112,7 @@
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D28" s="11"/>
       <c r="E28" s="23" t="str">
@@ -6110,7 +6120,7 @@
         <v/>
       </c>
       <c r="F28" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6119,7 +6129,7 @@
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="11" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="23" t="str">
@@ -6127,7 +6137,7 @@
         <v/>
       </c>
       <c r="F29" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6136,7 +6146,7 @@
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="11" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D30" s="11"/>
       <c r="E30" s="23" t="str">
@@ -6144,7 +6154,7 @@
         <v/>
       </c>
       <c r="F30" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6153,7 +6163,7 @@
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="11" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D31" s="11"/>
       <c r="E31" s="23" t="str">
@@ -6161,7 +6171,7 @@
         <v/>
       </c>
       <c r="F31" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6170,7 +6180,7 @@
       </c>
       <c r="B32" s="13"/>
       <c r="C32" s="11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D32" s="11"/>
       <c r="E32" s="23" t="str">
@@ -6178,7 +6188,7 @@
         <v/>
       </c>
       <c r="F32" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6187,7 +6197,7 @@
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D33" s="11"/>
       <c r="E33" s="23" t="str">
@@ -6195,7 +6205,7 @@
         <v/>
       </c>
       <c r="F33" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6204,7 +6214,7 @@
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="11" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D34" s="11"/>
       <c r="E34" s="23" t="str">
@@ -6212,7 +6222,7 @@
         <v/>
       </c>
       <c r="F34" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6221,7 +6231,7 @@
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D35" s="11"/>
       <c r="E35" s="23" t="str">
@@ -6229,7 +6239,7 @@
         <v/>
       </c>
       <c r="F35" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6238,7 +6248,7 @@
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D36" s="11"/>
       <c r="E36" s="23" t="str">
@@ -6246,7 +6256,7 @@
         <v/>
       </c>
       <c r="F36" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6255,7 +6265,7 @@
       </c>
       <c r="B37" s="13"/>
       <c r="C37" s="11" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D37" s="11"/>
       <c r="E37" s="23" t="str">
@@ -6263,7 +6273,7 @@
         <v/>
       </c>
       <c r="F37" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6272,7 +6282,7 @@
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D38" s="11"/>
       <c r="E38" s="23" t="str">
@@ -6280,7 +6290,7 @@
         <v/>
       </c>
       <c r="F38" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6289,7 +6299,7 @@
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="11" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D39" s="11"/>
       <c r="E39" s="23" t="str">
@@ -6297,7 +6307,7 @@
         <v/>
       </c>
       <c r="F39" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6306,7 +6316,7 @@
       </c>
       <c r="B40" s="13"/>
       <c r="C40" s="11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D40" s="11"/>
       <c r="E40" s="23" t="str">
@@ -6314,7 +6324,7 @@
         <v/>
       </c>
       <c r="F40" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6323,7 +6333,7 @@
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="11" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D41" s="11"/>
       <c r="E41" s="23" t="str">
@@ -6331,7 +6341,7 @@
         <v/>
       </c>
       <c r="F41" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6341,14 +6351,14 @@
       <c r="B42" s="13"/>
       <c r="C42" s="11"/>
       <c r="D42" s="11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E42" s="23" t="str">
         <f aca="false">IF(B42="","",MAX(0,B42-$B$6))</f>
         <v/>
       </c>
       <c r="F42" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6358,14 +6368,14 @@
       <c r="B43" s="13"/>
       <c r="C43" s="11"/>
       <c r="D43" s="11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E43" s="23" t="str">
         <f aca="false">IF(B43="","",MAX(0,B43-$B$6))</f>
         <v/>
       </c>
       <c r="F43" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6375,14 +6385,14 @@
       <c r="B44" s="13"/>
       <c r="C44" s="11"/>
       <c r="D44" s="11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E44" s="23" t="str">
         <f aca="false">IF(B44="","",MAX(0,B44-$B$6))</f>
         <v/>
       </c>
       <c r="F44" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6392,14 +6402,14 @@
       <c r="B45" s="13"/>
       <c r="C45" s="11"/>
       <c r="D45" s="11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E45" s="23" t="str">
         <f aca="false">IF(B45="","",MAX(0,B45-$B$6))</f>
         <v/>
       </c>
       <c r="F45" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6408,7 +6418,7 @@
       </c>
       <c r="B46" s="13"/>
       <c r="C46" s="11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D46" s="11"/>
       <c r="E46" s="23" t="str">
@@ -6416,7 +6426,7 @@
         <v/>
       </c>
       <c r="F46" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6425,7 +6435,7 @@
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D47" s="11"/>
       <c r="E47" s="23" t="str">
@@ -6433,7 +6443,7 @@
         <v/>
       </c>
       <c r="F47" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6442,7 +6452,7 @@
       </c>
       <c r="B48" s="13"/>
       <c r="C48" s="11" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D48" s="11"/>
       <c r="E48" s="23" t="str">
@@ -6450,7 +6460,7 @@
         <v/>
       </c>
       <c r="F48" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6459,7 +6469,7 @@
       </c>
       <c r="B49" s="13"/>
       <c r="C49" s="11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D49" s="11"/>
       <c r="E49" s="23" t="str">
@@ -6467,7 +6477,7 @@
         <v/>
       </c>
       <c r="F49" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6478,7 +6488,7 @@
         <v>435000000</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D50" s="11"/>
       <c r="E50" s="23" t="n">
@@ -6486,7 +6496,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6497,7 +6507,7 @@
         <v>450000000</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D51" s="11"/>
       <c r="E51" s="23" t="n">
@@ -6505,7 +6515,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6516,7 +6526,7 @@
         <v>480000000</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D52" s="11"/>
       <c r="E52" s="23" t="n">
@@ -6524,7 +6534,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6535,17 +6545,17 @@
         <v>510000000</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E53" s="23" t="n">
         <f aca="false">IF(B53="","",MAX(0,B53-$B$6))</f>
         <v>0</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6556,7 +6566,7 @@
         <v>540000000</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D54" s="11"/>
       <c r="E54" s="23" t="n">
@@ -6564,7 +6574,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6575,7 +6585,7 @@
         <v>570000000</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D55" s="11"/>
       <c r="E55" s="23" t="n">
@@ -6583,7 +6593,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6594,7 +6604,7 @@
         <v>600000000</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D56" s="11"/>
       <c r="E56" s="23" t="n">
@@ -6602,7 +6612,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6613,7 +6623,7 @@
         <v>630000000</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D57" s="11"/>
       <c r="E57" s="23" t="n">
@@ -6621,7 +6631,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6632,7 +6642,7 @@
         <v>660000000</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D58" s="11"/>
       <c r="E58" s="23" t="n">
@@ -6640,7 +6650,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6651,7 +6661,7 @@
         <v>690000000</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="23" t="n">
@@ -6659,7 +6669,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6670,7 +6680,7 @@
         <v>750000000</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D60" s="11"/>
       <c r="E60" s="23" t="n">
@@ -6678,7 +6688,7 @@
         <v>3197350</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6689,7 +6699,7 @@
         <v>825000000</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D61" s="11"/>
       <c r="E61" s="23" t="n">
@@ -6697,7 +6707,7 @@
         <v>78197350</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6708,7 +6718,7 @@
         <v>900000000</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D62" s="11"/>
       <c r="E62" s="23" t="n">
@@ -6716,7 +6726,7 @@
         <v>153197350</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6727,7 +6737,7 @@
         <v>975000000</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D63" s="11"/>
       <c r="E63" s="23" t="n">
@@ -6735,7 +6745,7 @@
         <v>228197350</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6746,7 +6756,7 @@
         <v>1050000000</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D64" s="11"/>
       <c r="E64" s="23" t="n">
@@ -6754,7 +6764,7 @@
         <v>303197350</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6765,7 +6775,7 @@
         <v>1125000000</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D65" s="11"/>
       <c r="E65" s="23" t="n">
@@ -6773,7 +6783,7 @@
         <v>378197350</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6784,7 +6794,7 @@
         <v>1200000000</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D66" s="11"/>
       <c r="E66" s="23" t="n">
@@ -6792,7 +6802,7 @@
         <v>453197350</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6803,7 +6813,7 @@
         <v>1350000000</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="23" t="n">
@@ -6811,7 +6821,7 @@
         <v>603197350</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6822,7 +6832,7 @@
         <v>1500000000</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D68" s="11"/>
       <c r="E68" s="23" t="n">
@@ -6830,7 +6840,7 @@
         <v>753197350</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6841,7 +6851,7 @@
         <v>1650000000</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="23" t="n">
@@ -6849,7 +6859,7 @@
         <v>903197350</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6860,7 +6870,7 @@
         <v>1875000000</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D70" s="11"/>
       <c r="E70" s="23" t="n">
@@ -6868,7 +6878,7 @@
         <v>1128197350</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6879,7 +6889,7 @@
         <v>2250000000</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D71" s="11"/>
       <c r="E71" s="23" t="n">
@@ -6887,7 +6897,7 @@
         <v>1503197350</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6898,7 +6908,7 @@
         <v>2625000000</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D72" s="11"/>
       <c r="E72" s="23" t="n">
@@ -6906,7 +6916,7 @@
         <v>1878197350</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6917,7 +6927,7 @@
         <v>3000000000</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D73" s="11"/>
       <c r="E73" s="23" t="n">
@@ -6925,7 +6935,7 @@
         <v>2253197350</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6936,7 +6946,7 @@
         <v>3375000000</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D74" s="11"/>
       <c r="E74" s="23" t="n">
@@ -6944,7 +6954,7 @@
         <v>2628197350</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6955,7 +6965,7 @@
         <v>3750000000</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D75" s="11"/>
       <c r="E75" s="23" t="n">
@@ -6963,7 +6973,7 @@
         <v>3003197350</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6974,7 +6984,7 @@
         <v>4125000000</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D76" s="11"/>
       <c r="E76" s="23" t="n">
@@ -6982,7 +6992,7 @@
         <v>3378197350</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7034,52 +7044,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>4000000</v>
@@ -7107,15 +7117,15 @@
         <v>6</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>4000000</v>
@@ -7143,15 +7153,15 @@
         <v>7</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>1</v>
@@ -7179,15 +7189,15 @@
         <v>947047350</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>4000</v>
@@ -7215,7 +7225,7 @@
         <v>241350</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7223,7 +7233,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>3000000</v>
@@ -7251,7 +7261,7 @@
         <v>2</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7259,7 +7269,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>8000000</v>
@@ -7287,15 +7297,15 @@
         <v>5</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>7000000</v>
@@ -7323,15 +7333,15 @@
         <v>0</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>17000000</v>
@@ -7359,15 +7369,15 @@
         <v>0</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>7000000</v>
@@ -7395,15 +7405,15 @@
         <v>0</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>17000000</v>
@@ -7431,15 +7441,15 @@
         <v>5</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C15" s="13" t="n">
         <v>7000000</v>
@@ -7467,15 +7477,15 @@
         <v>0</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>17000000</v>
@@ -7503,15 +7513,15 @@
         <v>5</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>3000000</v>
@@ -7539,15 +7549,15 @@
         <v>0</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>8000000</v>
@@ -7575,15 +7585,15 @@
         <v>0</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>3000000</v>
@@ -7611,15 +7621,15 @@
         <v>0</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>8000000</v>
@@ -7647,15 +7657,15 @@
         <v>0</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>3000000</v>
@@ -7683,15 +7693,15 @@
         <v>1</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>8000000</v>
@@ -7719,15 +7729,15 @@
         <v>1</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>3000000</v>
@@ -7755,15 +7765,15 @@
         <v>1</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>8000000</v>
@@ -7791,15 +7801,15 @@
         <v>2</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>8000000</v>
@@ -7827,15 +7837,15 @@
         <v>1</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>17000000</v>
@@ -7863,15 +7873,15 @@
         <v>5</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>8000000</v>
@@ -7899,15 +7909,15 @@
         <v>1</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>17000000</v>
@@ -7935,15 +7945,15 @@
         <v>5</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>8000000</v>
@@ -7971,15 +7981,15 @@
         <v>2</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>17000000</v>
@@ -8007,15 +8017,15 @@
         <v>5</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>40000000</v>
@@ -8043,15 +8053,15 @@
         <v>0</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>80000000</v>
@@ -8079,15 +8089,15 @@
         <v>2</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>150000000</v>
@@ -8115,7 +8125,7 @@
         <v>2</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8123,7 +8133,7 @@
         <v>66</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>200000000</v>
@@ -8151,7 +8161,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8159,7 +8169,7 @@
         <v>66</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>200000000</v>
@@ -8187,15 +8197,15 @@
         <v>1</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>17000000</v>
@@ -8223,15 +8233,15 @@
         <v>5</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>150000000</v>
@@ -8259,15 +8269,15 @@
         <v>5</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C38" s="13" t="n">
         <v>17000000</v>
@@ -8295,15 +8305,15 @@
         <v>5</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C39" s="13" t="n">
         <v>50000000</v>
@@ -8331,15 +8341,15 @@
         <v>5</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C40" s="13" t="n">
         <v>150000000</v>
@@ -8367,15 +8377,15 @@
         <v>5</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C41" s="13" t="n">
         <v>17000000</v>
@@ -8403,15 +8413,15 @@
         <v>5</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C42" s="13" t="n">
         <v>150000000</v>
@@ -8439,15 +8449,15 @@
         <v>5</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C43" s="13" t="n">
         <v>17000000</v>
@@ -8475,15 +8485,15 @@
         <v>3</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C44" s="13" t="n">
         <v>50000000</v>
@@ -8511,15 +8521,15 @@
         <v>5</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C45" s="13" t="n">
         <v>150000000</v>
@@ -8547,15 +8557,15 @@
         <v>5</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C46" s="13" t="n">
         <v>4500000</v>
@@ -8583,21 +8593,21 @@
         <v>6</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C47" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E47" s="24" t="n">
         <v>40250000</v>
@@ -8619,12 +8629,12 @@
         <v>0</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="15" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E49" s="19" t="n">
         <f aca="false">SUM(E5:E47)</f>
@@ -8634,7 +8644,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E50" s="19"/>
       <c r="F50" s="19" t="n">
@@ -8644,7 +8654,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E51" s="19"/>
       <c r="F51" s="19" t="n">
@@ -8654,7 +8664,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -8699,43 +8709,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B5" s="26" t="n">
         <v>12130000</v>
@@ -8761,7 +8771,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B6" s="27" t="n">
         <f aca="false">SUMIFS(B13:B76,$I$13:$I$76,"Yes",$J$13:$J$76,"No")</f>
@@ -8794,7 +8804,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">B5+B6</f>
@@ -8827,7 +8837,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B8" s="27" t="n">
         <f aca="false">SUMIF($J$80:$J$101,"Planned",B80:B101)</f>
@@ -8860,7 +8870,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B7-B8</f>
@@ -8893,44 +8903,44 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>13</v>
@@ -8938,7 +8948,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B13" s="29" t="n">
         <v>100000</v>
@@ -8962,18 +8972,18 @@
         <v>0</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B14" s="29" t="n">
         <v>1600000</v>
@@ -8997,18 +9007,18 @@
         <v>0</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B15" s="29" t="n">
         <v>1600000</v>
@@ -9032,18 +9042,18 @@
         <v>0</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B16" s="29" t="n">
         <v>1600000</v>
@@ -9067,18 +9077,18 @@
         <v>0</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B17" s="29" t="n">
         <v>1600000</v>
@@ -9102,18 +9112,18 @@
         <v>0</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B18" s="29" t="n">
         <v>1600000</v>
@@ -9137,18 +9147,18 @@
         <v>0</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B19" s="29" t="n">
         <v>1600000</v>
@@ -9172,18 +9182,18 @@
         <v>0</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B20" s="29" t="n">
         <v>1600000</v>
@@ -9207,18 +9217,18 @@
         <v>0</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B21" s="29" t="n">
         <v>100000</v>
@@ -9242,16 +9252,16 @@
         <v>0</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B22" s="29" t="n">
         <v>200000</v>
@@ -9275,16 +9285,16 @@
         <v>0</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B23" s="29" t="n">
         <v>0</v>
@@ -9308,18 +9318,18 @@
         <v>0</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B24" s="29" t="n">
         <v>150000</v>
@@ -9343,16 +9353,16 @@
         <v>15</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K24" s="14"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B25" s="29" t="n">
         <v>150000</v>
@@ -9376,16 +9386,16 @@
         <v>20</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K25" s="14"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B26" s="29" t="n">
         <v>200000</v>
@@ -9409,16 +9419,16 @@
         <v>25</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K26" s="14"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B27" s="29" t="n">
         <v>250000</v>
@@ -9442,16 +9452,16 @@
         <v>30</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K27" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B28" s="29" t="n">
         <v>300000</v>
@@ -9475,16 +9485,16 @@
         <v>40</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K28" s="14"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B29" s="29" t="n">
         <v>350000</v>
@@ -9508,16 +9518,16 @@
         <v>45</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K29" s="14"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B30" s="29" t="n">
         <v>0</v>
@@ -9541,18 +9551,18 @@
         <v>0</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B31" s="29" t="n">
         <v>0</v>
@@ -9576,53 +9586,53 @@
         <v>0</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="B32" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="K32" s="14" t="s">
         <v>417</v>
-      </c>
-      <c r="B32" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="K32" s="14" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B33" s="29" t="n">
         <v>0</v>
@@ -9646,16 +9656,16 @@
         <v>800</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K33" s="14"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B34" s="29" t="n">
         <v>10000000</v>
@@ -9679,16 +9689,16 @@
         <v>0</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K34" s="14"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>420</v>
+        <v>422</v>